--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -762,8 +762,431 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pramusim: Arsenal tunduk 2-3 dari Borussia Dortmund di Emirates Cup</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:08:30 +0700</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Arsenal ditundukkan Borussia Dortmund 2-3 dalam laga pramusim bertajuk Emirates Cup di Stadion Emirates, ...</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686948/pramusim-arsenal-tunduk-2-3-dari-borussia-dortmund-di-emirates-cup</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000043587.jpg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sambut HUT RI, PB Jatma Aswaja gelar zikir kebangsaan di Istiqlal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:06:37 +0700</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ANTARA - Pengurus Besar Jam'iyah Ahlith Thariqah Al Mutabaroh Ahlussunnah wal Jama'ah (PB Jatma Aswaja) menggelar Zikir ...</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5686945/sambut-hut-ri-pb-jatma-aswaja-gelar-zikir-kebangsaan-di-istiqlal</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_SAMBUT-HUT-RI-PB-JATMA-ASWAJA-GELAR-ZIKIR-KEBANGSAAN-DI-ISTIQLAL.jpg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pramusim: Liverpool takluk 2-3 dari AS Monaco di Anfield</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 00:44:41 +0700</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Liverpool menelan kekalahan 2-3 dari AS Monaco dalam laga pramusim 2026 di Stadion Anfield, Inggris pada Minggu malam ...</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686944/pramusim-liverpool-takluk-2-3-dari-as-monaco-di-anfield</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/1000043577.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PSSI minta publik tak hujat pemain terkait Piala AFF</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 00:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sekretaris Jendral Persatuan Sepak Bola Seluruh Indonesia (PSSI), Yunus Nusi meminta publik tidak menempatkan pemain ...</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686941/pssi-minta-publik-tak-hujat-pemain-terkait-piala-aff</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/10/IMG_8030.jpeg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yayasan Sekolah di Jaksel Ungkap Eks Pemilik Utang ke Bank Buat Lapangan Padel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 00:59:01 +0700</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mantan pemilik yayasan IWD, diduga menggunakan yayasan untuk kepentingan pribadi dan menyimpan senjata. Salah satunya membuat lapangan padel.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611448/yayasan-sekolah-di-jaksel-ungkap-eks-pemilik-utang-ke-bank-buat-lapangan-padel</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/08/kuasa-hukum-yayasan-sekolah-swasta-di-jaksel-hermawanto-menjelaskan-soal-temuan-ratusan-senjata-1786150520216_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pasutri di Mojokerto Syok Tiba-tiba di Rumahnya Ada Kuburan Bayi</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 00:28:22 +0700</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enggran Eko Budianto</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pasangan di Mojokerto temukan kuburan bayi di pekarangan rumah. Penemuan ini terjadi setelah pulang dari Gresik.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611416/pasutri-di-mojokerto-syok-tiba-tiba-di-rumahnya-ada-kuburan-bayi</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/bayi-dikubur-di-sebelah-sumur-rumah-warga-mojokerto-1786280765341_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Buntut Putusan MA soal Kasus Timah, Pakar Minta Pengadilan Konsisten Gunakan Audit BPK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 00:55:21 +0700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Huda menjelaskan kewenangan BPK menghitung kerugian keuangan negara sesuai dengan amanat Peraturan Mahkamah Agung , putusan MK hingga UU</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866111/buntut-putusan-ma-soal-kasus-timah-pakar-minta-pengadilan-konsisten-gunakan-audit-bpk</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8HGoys_ssFVqS7iCYXN7nF8pZQU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sidang-korupsi-PT-Timah-dengan-terdakwa-Harvey-Moeis-dkk-di-Pengadilan-Tipikor-Jakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tingkatkan Mutu Dokter Indonesia, Kampus Swasta Gandeng UI, Dosen Pakar Bisa Ikut Mengajar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 00:47:33 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kerja sama ini juga mencakup pendampingan dalam pengembangan kurikulum, sistem pembelajaran hingga peningkatan mutu pendidikan</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866110/tingkatkan-mutu-dokter-indonesia-kampus-swasta-gandeng-ui-dosen-pakar-bisa-ikut-mengajar</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/KOteNA0RNnet3qmGm8GTnWBegtY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kampus-Universitas-Indonesia-di-Depok-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Detik-detik Mencekam Pegawai Tutup Lapak di Tengah Kebakaran Mal Nipah Makassar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 00:29:40 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Beredar di media sosial dan menjadi perbincangan warga setelah video memperihatkan kondisi mencekam saat kebakaran di Mal Nipah, Makassar</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866109/detik-detik-mencekam-pegawai-tutup-lapak-di-tengah-kebakaran-mal-nipah-makassar</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/agcpkJPhibG2HYwEc7hsXBKRlyg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Seorang-pria-menjadi-sorotan-di-tengah-kebakaran-di-Mal-Nipah-Makassar.jpg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1185,8 +1185,243 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Menko Pangan minta doa agar semua program pemerintah berjalan optimal</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:42:58 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Pangan Zulkifli Hasan meminta doa dan dukungan masyarakat, utamanya dari warga Jatma Aswaja, ...</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686952/menko-pangan-minta-doa-agar-semua-program-pemerintah-berjalan-optimal</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000177340.jpg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20 Bulan Pemerintahan, Zulhas Akui Tak Semua Program Pemerintah Berhasil: Ada yang Belum</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 02:01:49 +0700</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Zulkifli Hasan atau Zulhas menyebut hampir 2 tahun ada program yang berhasil dan belum, salah satunya MBG</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866114/20-bulan-pemerintahan-zulhas-akui-tak-semua-program-pemerintah-berhasil-ada-yang-belum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/BNe0CId_2a99tvpmY4ZZwt1N04U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/rgizi-gratis-MBG-di-Gedung-Gra.jpg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Prabowo Minta Pertamina Pangkas Layer dan Anak Cucu Perusahaan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:47:06 +0700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Prabowo dalam pertemuan di Kediaman Hambalang meminta Simon untuk memangkas anak perusahaan Pertamina</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866113/prabowo-minta-pertamina-pangkas-layer-dan-anak-cucu-perusahaan</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MackvCUZGbNLLnq3IkwyNkR7jhE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Presiden-Prabowo-Subianto-menerima-Direktur-Utama-Pertamina-Simon-Mantiri.jpg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Zulhas Ungkap Penyebab Prabowo Tak Hadiri Zikir Kebangsaan, Titip Salam dan Permintaan Maaf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:33:31 +0700</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Zulkifli Hasan menyampaikan salam dari Presiden Prabowo kepada para peserta Zikir Kebangsaan di Masjid Istiqlal</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866112/zulhas-ungkap-penyebab-prabowo-tak-hadiri-zikir-kebangsaan-titip-salam-dan-permintaan-maaf</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c0QGsg2O8JT9_f3rBKREvX_aY4k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ZULKIFLI-HASAN-89097.jpg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Hype</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Denny Sumargo Sebut Anak dan Istrinya Ikut Dirundung karena Podcast Bareng Sarwendah dan Ruben Onsu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 02:27:25 +0700</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Denny Sumargo akui dampak podcast Sarwendah-Ruben Onsu menyerang keluarga, bahkan istri &amp; anaknya dibully netizen. Densu berharap semua pihak bisa tenang.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/hype/read/2026/08/09/235845166/denny-sumargo-sebut-anak-dan-istrinya-ikut-dirundung-karena-podcast-bareng</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/D6w0YmIxiwP9_2Y51yV5iJn24mM=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c8191ee571.png,0,-0,1)/data/photo/2026/08/09/6a7873c4d8031.jpg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:I21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1420,8 +1420,102 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Menhut: Pemadaman kebakaran Bromo andalkan "water bombing"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 02:39:38 +0700</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ANTARA - ‎Menteri Kehutanan Raja Juli Antoni meninjau langsung penanganan kebakaran hutan dan lahan di kawasan ...</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5686937/menhut-pemadaman-kebakaran-bromo-andalkan-water-bombing</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENHUT-PEMADAMAN-KEBAKARAN-BROMO-ANDALKAN-22WATER-BOMBING-22.jpg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Prabowo Panggil Dirut Pertamina ke Hambalang, Ini yang Dibahas</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 02:27:47 +0700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kadek Melda Luxiana</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo memanggil Dirut Pertamina ke Hambalang. Apa saja yang dibahas?</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611458/prabowo-panggil-dirut-pertamina-ke-hambalang-ini-yang-dibahas</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/prabowo-panggil-dirut-pertamina-ke-hambalang-dok-instagram-1786303642467_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:I23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1514,8 +1514,102 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Menhut Tinjau Penanganan Kebakaran Bromo, Maksimalkan Penggunaan Water Bombing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 03:39:38 +0700</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>M rofiq</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan Raja Juli Antoni meninjau penanganan kebakaran hutan di Gunung Bromo. Helikopter water bombing digunakan maksimal untuk padamkan api.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611464/menhut-tinjau-penanganan-kebakaran-bromo-maksimalkan-penggunaan-water-bombing</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/menteri-kehutanan-ri-raja-juli-antoni-1786272285884_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MTQ XXXIV Kalbar di Kayong Utara Resmi Berakhir, Kubu Raya Raih Juara Umum</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 03:11:09 +0700</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MTQ XXXIV Tingkat Provinsi Kalbar Tahun 2026 di Sukadana, Kabupaten Kayong Utara resmi ditutup, Kubu Raya juara umum</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866115/mtq-xxxiv-kalbar-di-kayong-utara-resmi-berakhir-kubu-raya-raih-juara-umum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-7mLvM1yZQMwrBzZ6WIrr0Lwydw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penyelenggaraan-MTQ-XXXIV-Kalbar-resmi-ditutup.jpg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I23"/>
+  <autoFilter ref="A1:I25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1608,8 +1608,666 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aldila Sutjiadi terhenti di 16 besar WTA 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:55:30 +0700</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Petenis Indonesia Aldila Sutjiadi bersama pasangannya, Erin Routliffe dari Selandia Baru, terhenti pada babak 16 besar ...</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686960/aldila-sutjiadi-terhenti-di-16-besar-wta-1000-toronto</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/XxjpbeE000052_20260808_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tim sepatu roda Indonesia raih 19 medali di ajang China-ASEAN 2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:50:25 +0700</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Tim sepatu roda Indonesia tampil gemilang pada ajang Belt and Road China-ASEAN Speed Roller Skating Championships 2026 ...</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686956/tim-sepatu-roda-indonesia-raih-19-medali-di-ajang-china-asean-2026</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000043598.jpg</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Badai, Habagat sebabkan 8 tewas dan 486 ribu terdampak di Filipina</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:47:00 +0700</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sebanyak delapan orang meninggal dunia dan satu orang dilaporkan hilang akibat fenomena angin muson barat daya ...</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686953/badai-habagat-sebabkan-8-tewas-dan-486-ribu-terdampak-di-filipina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/20/badai-fengshen-filipina-1.jpg</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2 Pekerja Proyek Tertimpa Beton Turap di Jaktim, Alami Luka di Kepala</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:45:27 +0700</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dua pekerja proyek di Jakarta Timur tertimpa beton turap saat normalisasi saluran. Proses evakuasi berlangsung lebih dari tiga jam.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611467/2-pekerja-proyek-tertimpa-beton-turap-di-jaktim-alami-luka-di-kepala</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/petugas-suku-dinas-penanggulangan-kebakaran-dan-penyelamatan-gulkarmat-jakarta-timur-jaktim-mengevakuasi-dua-pekerja-proyek-no-1786311861874_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dea Annisa Menikah dengan Mazaki Ahmad, Kisah Cinta Berawal dari Syuting</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:12:21 +0700</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Dea Annisa resmi menikah dengan Mazaki Ahmad pada 9 Agustus 2026. Pernikahan intim ini berawal dari syuting film dan dihadiri keluarga terdekat.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611455/dea-annisa-menikah-dengan-mazaki-ahmad-kisah-cinta-berawal-dari-syuting</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/dea-annisa-1786273550004_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kebakaran KMP Mutiara Sentosa, Publik Diminta Tunggu Investigasi KNKT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>KMP Mutiara Sentosa II terbakar di Sumenep membuat 5 orang meninggal. Publik diminta bersabar menunggul hasil investigasi resmi KNKT.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260809203610-12-1390381/kebakaran-kmp-mutiara-sentosa-publik-diminta-tunggu-investigasi-knkt</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/korban-selamat-dari-kebakaran-km-mutiara-sentosa-2-dievakuasi-ke-tanjung-perak-1785713335919_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sejarah Hari Veteran Nasional Diperingati 10 Agustus 2026, Berawal dari Perjuangan di Solo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:04:57 +0700</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sejarah Hari Veteran Nasional yang diperingati 10 Agustus berawal dari perjuangan dalam Serangan Umum Empat Hari di Surakarta (Solo).</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866118/sejarah-hari-veteran-nasional-diperingati-10-agustus-2026-berawal-dari-perjuangan-di-solo</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Ar4COumqszlnzYn6LRmYMlCL-rk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/memperingati-hari-veteran-nasional_20200811_124544.jpg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kebakaran Bromo Meluas Dekati Pemukiman, Menhut Raja Juli Minta Doa agar Api Segera Padam</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:58:31 +0700</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Menhut Raja Juli Antoni turun langsung menangani karhutla Bromo. Prabowo meminta pemerintah all out menghadapi kebakaran.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866117/kebakaran-bromo-meluas-dekati-pemukiman-menhut-raja-juli-minta-doa-agar-api-segera-padam</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fPZCcVEq2iOhp99SRXNEP4WlMl8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Update-kebakaran-kawasan-Gunung-Bromo.jpg</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kejagung Pantau Keamanan Ferry Boboho Selama Permohonan Perlindungan Masih Ditelaah LPSK</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kejagung memantau keamanan Ferry Yanto Hongkiriwang alias Ferry Boboho karena merupakan saksi atas dugaan TPPU Febrie</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866116/kejagung-pantau-keamanan-ferry-boboho-selama-permohonan-perlindungan-masih-ditelaah-lpsk</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/xcinjzDHEoqPz1Dewaap52VsbiM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kantor-lpsk-2608.jpg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1.308 Hektare Sawah Rusak Akibat Banjir, Aceh Barat Percepat Pemulihan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:10:07 +0700</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Erdy Nasrul</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, MEULABOH — Dinas Pertanian Tanaman Pangan dan Hortikultura Kabupaten Aceh Barat menyalurkan dana swakelola kepada kelompok tani untuk mempercepat pemulihan sekitar 1.308 hektare lahan sawah yang rusak akibat banjir...</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjiw8v451/1308-hektare-sawah-rusak-akibat-banjir-aceh-barat-percepat-pemulihan</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/009638800-1786279601-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pramono Anung Ingin Persija Juara, Jadi Kado HUT ke-500 Jakarta</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:15:34 +0700</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Pramono Anung berharap Persija Jakarta meraih gelar juara di bawah kepemimpinan Shin Tae-yong sebagai kado HUT ke-500 Jakarta.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265883/pramono-anung-ingin-persija-juara-jadi-kado-hut-ke-500-jakarta</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/hmsAha9DQnQ4OYdsaA6kcueTlBc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5296510/original/066264600_1753591888-WhatsApp_Image_2025-07-27_at_11.22.56_c63dbb11.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kapolri Ungkap Ancaman Serius yang Mengintai Anak Muda di Dunia Maya</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:00:11 +0700</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>_Kapolri Dorong Duta Kamtibmas Edukasi Generasi Muda Mengenai Potensi Kejahatan di Dunia Maya</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265881/kapolri-ungkap-ancaman-serius-yang-mengintai-anak-muda-di-dunia-maya</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/ng33hO93ECstQkASUrWQ8s_GzJQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9319884/original/099229500_1786311397-71432.jpg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nasaruddin Umar Ungkap Kondisi Ekonomi Indonesia, Minta Umat Bersyukur</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:43:24 +0700</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Menteri Agama Nasaruddin Umar mengajak umat menjaga persatuan dan mensyukuri kondisi Indonesia di tengah tekanan ekonomi global.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265880/nasaruddin-umar-ungkap-kondisi-ekonomi-indonesia-minta-umat-bersyukur</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/nf49WEtqsaX3zAfv54x42mPj_FU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9319881/original/019356100_1786310889-1000177334.jpg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Zulhas Akui Ada Program Pemerintah Belum Optimal, Minta Doa Ulama</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:23:49 +0700</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Zulhas meminta doa ulama dan masyarakat agar pemerintah dapat memperbaiki program yang belum berjalan optimal.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265879/zulhas-akui-ada-program-pemerintah-belum-optimal-minta-doa-ulama</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/GactbfiBqDBZ0stdSzMUYSPEeOI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9319880/original/065743000_1786310624-1000177340.jpg</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I25"/>
+  <autoFilter ref="A1:I39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -2266,8 +2266,1136 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Humaniora kemarin, kirab Merah Putih hingga zikir akbar di Istiqlal</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:04:16 +0700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Terdapat sejumlah berita humaniora menarik yang terjadi pada Minggu (9/8) dan bisa dibaca kembali pada pagi ini untuk ...</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686983/humaniora-kemarin-kirab-merah-putih-hingga-zikir-akbar-di-istiqlal</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/26/foto-terbaik-2025-2696548.jpg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Satgas PRR Kemendagri tinjau proyek PSN di Nagan Raya Aceh</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ANTARA - Tim Satgas Percepatan Rehabilitasi dan Rekonstruksi (PRR) Kementerian Dalam Negeri meninjau perkembangan ...</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5686929/satgas-prr-kemendagri-tinjau-proyek-psn-di-nagan-raya-aceh</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_SATGAS-PRR-KEMENDAGRI-TINJAU-PROYEK-PSN-DI-NAGAN-RAYA-ACEH.jpg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 untuk kembangkan pertanian</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 diluncurkan ke orbit menggunakan roket pengangkut Smart Dragon-3 dari Shandong, China, Rabu (5/8). ...</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5686864/satelit-lampung-1-untuk-kembangkan-pertanian</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/20260809-Satelit-Lampung-1-untuk-kembangkan-pertanian.jpg</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain datangkan Lucas Digne dari Aston Villa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:57:17 +0700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain (PSG) resmi mendatangkan bek kiri timnas Prancis, Lucas Digne dari Aston Villa pada bursa transfer ...</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686981/paris-saint-germain-datangkan-lucas-digne-dari-aston-villa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/01/22/2022-01-22T131523Z_577296983_UP1EI1M10TKFY_RTRMADP_3_SOCCER-ENGLAND-EVE-AVA-REPORT.jpg</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Senin, BMKG: Mayoritas wilayah RI berawan hingga hujan ringan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:56:55 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan cuaca di mayoritas wilayah Indonesia didominasi ...</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686977/senin-bmkg-mayoritas-wilayah-ri-berawan-hingga-hujan-ringan</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/04/23/IMG_20241219_140043.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DKI kemarin, JIS jadi kandang Persija hingga Tj rute Senayan-Ancol</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:52:47 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sejumlah berita di DKI Jakarta pada Minggu (9/8) masih menarik untuk disimak hari ini mulai dari Transjakarta buka rute ...</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686975/dki-kemarin-jis-jadi-kandang-persija-hingga-tj-rute-senayan-ancol</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/22/RESIZED-WhatsApp-Image-2026-06-22-at-18.42.28.jpg</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kriminal kemarin, temuan senjata hingga perusak kabel optik ditangkap</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:50:27 +0700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sejumlah berita kriminal di wilayah Jakarta pada Minggu (9/8) yang masih layak dibaca hari ini antara lain polisi ...</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686971/kriminal-kemarin-temuan-senjata-hingga-perusak-kabel-optik-ditangkap</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/1001016025.jpg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Como 1907 boyong Trevoh Chalobah dari Chelsea</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:49:12 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Klub Liga Italia, Como 1907 resmi memboyong bek timnas Inggris, Trevoh Chalobah dari Chelsea pada bursa transfer musim ...</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686969/como-1907-boyong-trevoh-chalobah-dari-chelsea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000043632.jpg</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cuaca Jakarta diprakirakan akan cerah berawan pada Senin</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:45:30 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan cuaca di seluruh wilayah DKI jakarta akan cerah ...</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686967/cuaca-jakarta-diprakirakan-akan-cerah-berawan-pada-senin</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/19/IMG_20260719_000858.jpg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PD soal Isu Reshuffle: Siapa dan Dari Mana Menterinya, Sepenuhnya Presiden</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:19:12 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Partai Demokrat menegaskan reshuffle kabinet adalah hak prerogatif Presiden. Mereka mendukung pemilihan menteri berdasarkan kemampuan, bukan asal partai.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611470/pd-soal-isu-reshuffle-siapa-dan-dari-mana-menterinya-sepenuhnya-presiden</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/16/sekjen-dpp-partai-demokrat-herman-khaeron-usai-menghadiri-rakerda-dpd-demokrat-bali-di-denpasar-selasa-1692025-1758033321170_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sengketa Ahli Waris Lina Jubaedah Masuk Kasasi, Teddy Pardiyana Pilih Tenang</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:03:38 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sengketa ahli waris Lina Jubaedah berlanjut ke tahap kasasi di Mahkamah Agung. Teddy Pardiyana tetap tenang dan terbuka untuk mediasi dengan Rizky Febian.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611447/sengketa-ahli-waris-lina-jubaedah-masuk-kasasi-teddy-pardiyana-pilih-tenang</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/rizky-febian-1785413128625_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Netanyahu Tolak 15 Poin Rencana Damai Gaza Usulan Board of Peace Trump</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:05:37 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Tolak usulan Board of Peace, Netanyahu ogah tarik militernya dari Jalur Gaza sebelum Hamas serahkan senjata secara penuh.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810055257-120-1390397/netanyahu-tolak-15-poin-rencana-damai-gaza-usulan-board-of-peace-trump</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/10/12/pm-israel-benjamin-netanyahu-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kanada Usir 3 Ribu Warga India hingga Israel Mau Serang Iran Tanpa AS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:45:50 +0700</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Lebih dari tiga ribu WN India dipulangkan dari Kanada sampai Israel mau serang Iran sepihak jika perang AS-Teheran berakhir.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810053224-134-1390395/kanada-usir-3-ribu-warga-india-hingga-israel-mau-serang-iran-tanpa-as</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/04/19/ilustrasi-konflik-israel-iran_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tragedi Maut Ajang Balap Drag Race Kotamobagu: Mobil Pembalap Tabrak Penonton, 7 Tewas, 9 Luka-luka</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:04:31 +0700</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Mobil peserta balap di Kotamobagu Sulut tabrak penonton akibatkan 7 korban tewas dan 9 luka-luka pada Minggu (9/8/2026).</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866125/tragedi-maut-ajang-balap-drag-race-kotamobagu-mobil-pembalap-tabrak-penonton-7-tewas-9-luka-luka</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/sdtdONAMpybx_mtcJWcZYFFaWCI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/drage-race-kotamogaku-kecelakaan-tabrak-penonton.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Daftar Penghargaan Individu SEA V Cup 2026 Putri Leg 2: Indah Guretno Best Libero, Thailand Dominan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:47:05 +0700</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Indah Guretno menjadi satu-satunya wakil Indonesia yang menyabet penghargaan SEA V Cup 2026 putri leg 2 sebagai best libero.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866124/daftar-penghargaan-individu-sea-v-cup-2026-putri-leg-2-indah-guretno-best-libero-thailand-dominan</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ji5jh_awPmeoo7bKdWFIChFnymU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemain-Timnas-Voli-Putri-Indonesia-melakukan-perayaan-setelah-mencetak-poin-saat.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ramai Warga Minta Refund Tiket Kunjungan Bromo di Komentar Unggahan Menhut Raja Juli</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:37:38 +0700</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Penutupan Bromo akibat karhutla membuat calon wisatawan ramai menanyakan mekanisme refund tiket di unggahan Menhut Raja Juli.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866123/ramai-warga-minta-refund-tiket-kunjungan-bromo-di-komentar-unggahan-menhut-raja-juli</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/L5V5p-yUMV9CORbJGZWh8Kcyvtc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Raja-Juli-Antoni-mengunjungi-Kawasan-Hutan-Dengan-Tujuan-Khusus-KHDTK-Tabo-Tabo.jpg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hasil MotoGP Inggris 2026 Tak Memuaskan, Marc Marquez Pilih Kritik Diri Sendiri</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:33:59 +0700</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Marc Marquez gagal menunjukkan performa terbaiknya di MotoGP Inggris 2026 dan menyebut motor bukan menjadi faktor masalah</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866122/hasil-motogp-inggris-2026-tak-memuaskan-marc-marquez-pilih-kritik-diri-sendiri</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/_zd0Xjtfz40QQD41FEpzeehTLvQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Marc-Marquez-dan-Alex-Marquez-MotoGP-Inggris-2025.jpg</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Denny Sumargo Sebut Keluarga Kena Hujat Netizen usai Podcast Bareng Sarwendah</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:24:39 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Denny Sumargo menyebut keluarganya, terutama sang istri, Olivia Allan dan anaknya menjadi sasaran hujatan netizen buntut podcast bersama Sarwendah.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866121/denny-sumargo-sebut-keluarga-kena-hujat-netizen-usai-podcast-bareng-sarwendah</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ik23waLzTdDpWPovuqWu3mZdce4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Denny-Sumargo-1-03082026.jpg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sejak Kapan Bayi Boleh Pakai Skincare? Ini Penjelasan Dokter</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:12:23 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>dr. HANS menjelaskan bahwa bayi boleh memakai skincare sejak bayi baru lahir jika formula produknya memang untuk kulit sensitif.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866120/sejak-kapan-bayi-boleh-pakai-skincare-ini-penjelasan-dokter</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/umKVBJF65IbfXBVjy48cT4Yds4Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/teknik-pijat-lembut-pada-bayi-untuk-meredakan-gejala-batuk-dan-pilek.jpg</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Alasan Maarten Paes Cadangan dalam Kemenangan Ajax atas PEC Zwolle, Bukan Gegara Michel Tak Suka</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:07:47 +0700</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Pelatih Ajax, Michel, mengungkapkan alasan di balik keputusannya mainkan Ter Stegen dan mencadangkan Maarten Paes dalam kemenangan atas PEC Zwolle.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866119/alasan-maarten-paes-cadangan-dalam-kemenangan-ajax-atas-pec-zwolle-bukan-gegara-michel-tak-suka</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2OWvW2i5iEbzDBtJC2ErtaNIvaY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Eskpresi-Maarten-Paes-setelah-menepis-penendang-penalti-FC-Utrecht.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BMKG Ungkap Prakiraan Cuaca Jakarta Senin, Ada Wilayah Berawan Tebal</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:15:51 +0700</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BMKG memprakirakan cuaca Jakarta didominasi cerah berawan pada Senin, dengan sejumlah wilayah berawan tebal.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265899/bmkg-ungkap-prakiraan-cuaca-jakarta-senin-ada-wilayah-berawan-tebal</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/3-F2plV7Pg7xWbP2yDN5g6R05rM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/3453943/original/049969200_1620650232-Jakarta_Cerah.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Yayasan Bongkar Dugaan Kredit Eks Pemilik Sekolah untuk Lapangan Padel</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:15:14 +0700</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Yayasan Harapan Ibu Pondok Pinang membantah sejumlah pernyataan pihak mantan ketua yayasan dan mengungkap dugaan penyalahgunaan kewenangan.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265891/yayasan-bongkar-dugaan-kredit-eks-pemilik-sekolah-untuk-lapangan-padel</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/YAVOExu6fnI0Yew1ROoX836YmpQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9319668/original/013460500_1786264819-71184.jpg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sehari Bersama Caregiver: Nyaris Tak Pernah Pulang dari Rumah Sakit</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Pengalaman merawat sang ibu yang menderita gagal ginjal selama sembilan tahun membentuk Angie menjadi sosok yang terbiasa mendampingi orang sakit.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265029/sehari-bersama-caregiver-nyaris-tak-pernah-pulang-dari-rumah-sakit</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/gG-_zkFKY72s5JWNdtPSRArZzog=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318946/original/065932000_1786172831-DSC00542.jpg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Beton Drainase Roboh, Dua Pekerja Sempat Terjebak</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Proses evakuasi berlangsung lebih dari tiga jam, menyebabkan kepadatan lalu lintas.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265890/beton-drainase-roboh-dua-pekerja-sempat-terjebak</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Tvv251YSKPKSeACTE9mQdjtNuwQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9319886/original/063438000_1786314490-2819b90b-dc27-4278-a00e-307bca883b52.jpg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I39"/>
+  <autoFilter ref="A1:I63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3394,8 +3394,2311 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Simak lagi warta soal wisata kapal pesiar, kenaikan harga ponsel</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:34:39 +0700</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Kanal gaya hidup, hiburan, teknologi, dan otomotif ANTARA pada Minggu (9/8) di antaranya menyiarkan warta tentang ...</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687016/simak-lagi-warta-soal-wisata-kapal-pesiar-kenaikan-harga-ponsel</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/08/kapal-pesiar-seven-seas-navigator-singgah-di-surabaya-080126-Ds-4.jpg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ekonomi kemarin, rencana PTA RI-Mercosur hingga akses aman Bromo</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:26:08 +0700</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Terdapat berbagai peristiwa bidang ekonomi yang terjadi pada Minggu (9/8/2026) yang masih hangat dan relevan untuk ...</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687015/ekonomi-kemarin-rencana-pta-ri-mercosur-hingga-akses-aman-bromo</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/IMG_1009.jpeg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di kawasan TNBTS capai 520 hektare</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:17:53 +0700</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Petugas gabungan memantau kebakaran hutan di kawasan Taman Nasional Bromo Tengger Semeru (TNBTS), Kabupaten Pasuruan, ...</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687011/kebakaran-hutan-di-kawasan-tnbts-capai-520-hektare</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Kebakaran-Hutan-Di-Kawasan-TNBTS-090826-IS-3.jpg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ubud Village Jazz Festival akan digelar lagi tahun depan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:16:05 +0700</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Panitia penyelenggara mengumumkan rencana pelaksanaan Ubud Village Jazz Festival mendatang pada 6–7 Agustus ...</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687009/ubud-village-jazz-festival-akan-digelar-lagi-tahun-depan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/WhatsApp-Image-2026-08-09-at-20.12.20.jpeg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Program "Mat Peci" ubah buruh tani jadi peternak sapi sukses</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Peternakan dan Perikanan (Disnak) Kabupaten Bondowoso, Jawa Timur, menggagas program Mat Peci untuk ...</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5686919/program-mat-peci-ubah-buruh-tani-jadi-peternak-sapi-sukses</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PROGRAM-22MAT-PECI-22-UBAH-BURUH-TANI-JADI-PETERNAK-SAPI-SUKSES.jpg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hukum, dari seleksi anggota Polri hingga penyelundupan 1,3 ton ketamin</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:59:02 +0700</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Kepolisian Negara Republik Indonesia (Polri) menegaskan pemilik sertifikat Pramuka Garuda tetap harus mengikuti tes ...</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687008/hukum-dari-seleksi-anggota-polri-hingga-penyelundupan-13-ton-ketamin</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/1-3-ton-ketamin-narkotika-09082026-tpp-1a.jpg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tanjung Lesung dorong pengembangan sport fishing di Pandeglang</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:56:00 +0700</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Pengelola Kawasan Ekonomi Khusus (KEK) Tanjung Lesung mendorong pengembangan sport fishing sebagai daya tarik wisata ...</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687004/tanjung-lesung-dorong-pengembangan-sport-fishing-di-pandeglang</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000402845.jpg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Politik, dari Pakta Pertahanan Makkah hingga Golkar gaet Gen Z</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:54:46 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Dewan Pakar Badan Pembinaan Ideologi Pancasila (BPIP) Bidang Strategi Hubungan Luar Negeri Darmansjah Djumala menilai ...</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687001/politik-dari-pakta-pertahanan-makkah-hingga-golkar-gaet-gen-z</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/1000582806.jpg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Prabowo perintahkan PLN dan Pertamina segera pangkas anak-cucu perusahaan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:51:17 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memerintahkan jajarannya dan para petinggi BUMN, khususnya Pertamina dan PLN, untuk segera ...</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687000/prabowo-perintahkan-pln-dan-pertamina-segera-pangkas-anak-cucu-perusahaan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_5534.jpeg</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Indonesia dorong penguatan kerja sama BRICS dalam bidang kebudayaan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:40:18 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Indonesia mendorong penguatan kerja sama dalam bidang kebudayaan di antara anggota BRICS, kumpulan negara berkembang ...</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686997/indonesia-dorong-penguatan-kerja-sama-brics-dalam-bidang-kebudayaan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/WhatsApp-Image-2026-08-09-at-19.52.25.jpeg</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Benarkah stevia lebih sehat dari gula biasa? Ini faktanya</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:34:45 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Stevia semakin dikenal sebagai alternatif pengganti gula, terutama bagi orang yang ingin mengurangi konsumsi gula atau ...</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686993/benarkah-stevia-lebih-sehat-dari-gula-biasa-ini-faktanya</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/07/05/stevia-74187_960_720.jpg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kulit gatal setelah pakai jam tangan? Ini penyebab dan solusinya</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:28:52 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sebagian orang mengalami kulit gatal, kemerahan, atau muncul ruam setelah memakai jam tangan. Kondisi tersebut bisa ...</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686992/kulit-gatal-setelah-pakai-jam-tangan-ini-penyebab-dan-solusinya</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/03/03/XiaomiWatchS4-LiquidSilver-Breathingexercises_copy_1280x853.jpg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Jangan biarkan pungli mengakar</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:28:29 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ruang publik selalu lahir dari sebuah gagasan sederhana. Jalan ditutup beberapa jam agar warga bisa berjalan kaki ...</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686989/jangan-biarkan-pungli-mengakar</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/PKL-atau-pedagang-di-CFD-kawasan-Taman-Bungkul-Surabaya-1.jpg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Hidung gatal terus? Ini perbedaan alergi dan pilek yang perlu diketahui</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:22:26 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Hidung gatal sering dianggap sebagai tanda pilek biasa, padahal keluhan tersebut juga dapat muncul akibat rhinitis ...</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5686985/hidung-gatal-terus-ini-perbedaan-alergi-dan-pilek-yang-perlu-diketahui</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/InShot_20251104_154642446.jpg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Teka-teki Febrio Adiono di Kasus Kematian Sutrimo</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:26:59 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Febrio Adiono diduga terlibat dalam kematian Sutrimo di depan klinik Mordent. Polisi menyelidiki identitasnya dan penyebab kematian yang mencurigakan.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611507/teka-teki-febrio-adiono-di-kasus-kematian-sutrimo</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/26/kondisi-klinik-kecantikan-di-kebayoran-baru-jaksel-temoat-pria-bernama-sutrimo-ditemukan-tewas-adhfardetikcom-1785073645811_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>808 Hektare Sawah di 17 Kecamatan Pandeglang Kekeringan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:25:09 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Aris Rivaldo</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DPKP Pandeglang mencatat sebanyak 808 hektare sawah terdampak kekeringan. Jumlah tersebut tersebar di 17 Kecamatan di Pandeglang.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611505/808-hektare-sawah-di-17-kecamatan-pandeglang-kekeringan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/ilustrasi-sawah-kekeringan-aris-rivaldodetikcom-1786321425482_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PKS Sebut Rekrut Kabinet Tak Harus dari Partai, PAN Bicara Aspirasi</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:21:48 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PKS dan PAN sepakat bahwa rekrutmen kabinet harus berdasarkan kapasitas, bukan hanya dari partai. Aspirasi masyarakat dan akademisi juga penting.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611501/pks-sebut-rekrut-kabinet-tak-harus-dari-partai-pan-bicara-aspirasi</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/09/14/ketua-fraksi-pan-saleh-daulay_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kebakaran Mal Nipah Makassar, Pengunjung Pingsan hingga Karyawan Sesak Napas</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:11:54 +0700</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Iswandy Rusli</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Pengunjung dilaporkan sempat pingsan dan karyawan mengalami sesak napas saat kebakaran Mal Nipah Makassar.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611497/kebakaran-mal-nipah-makassar-pengunjung-pingsan-hingga-karyawan-sesak-napas</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/kebakaran-terjadi-di-mal-nipah-makassar-1786291264697_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4 Hal Kasus Kematian Sutrimo Setelah Keluarga Buka Suara</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:44:19 +0700</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Keluarga melaporkan kematian Sutrimo ke polisi untuk kepastian hukum. Sutrimo ditemukan meninggal di klinik keantikan di Jakarta dalam kondisi mulut berbusa.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611494/4-hal-kasus-kematian-sutrimo-setelah-keluarga-buka-suara</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/polisi-masih-mendalami-penyebab-tewasnya-pria-bernama-sutrimo-di-depan-klinik-kecantikan-mordent-di-jaksel-penyebab-kematian-s-1785156176528_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Harga Minyak Mendidih Lagi Dekati US$ 85/Barel</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:30:57 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Harga minyak mentah Brent tercatat naik US$ 1,20, atau 1,44%, menjadi US$ 84,79 per barel.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8611498/harga-minyak-mendidih-lagi-dekati-us-85-barel</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/13/emas-minyak-membara-usai-israel-serang-iran-1749816526884_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Laptop hingga Uang Tunai Tertinggal di Kereta, Segini Nilainya</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:00:52 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Barang berharga tersebut antara lain handphone, tablet, laptop, perhiasan, uang tunai, serta perangkat elektronik dan barang pribadi bernilai lainnya.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611332/laptop-hingga-uang-tunai-tertinggal-di-kereta-segini-nilainya</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/momen-prabowo-jajal-ka-nusantara-explorer-1785389903881_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sebesar Ini Perputaran Duit Judol Saat Piala Dunia</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:30:28 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Berdasarkan data PPATK, tercatat deposit judol terkait Piala Dunia mencapai Rp 1,02 triliun dalam lebih dari 6 juta transaksi.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611329/sebesar-ini-perputaran-duit-judol-saat-piala-dunia</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/05/judi-online_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tokopedia &amp;amp; Shopee Refund Dana Pedagang Bertahap Usai Pajak Ditunda</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Tokopedia dan Shopee juga telah berkomitmen mengembalikan pajak yang telah dipungut dari pedagang pada periode 1-5 Agustus kemarin.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611328/tokopedia-shopee-refund-dana-pedagang-bertahap-usai-pajak-ditunda</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/03/04/5394c5b5-e2e8-4cc6-b022-29b973e633f2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ruben Onsu Ungkap Hal yang Paling Dirindukan dari Anak-anak</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:08:00 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ruben Onsu mengungkap kerinduan mendalam kepada anak-anaknya di tengah persoalan hak asuh. Ia merindukan momen sederhana dan komunikasi yang terjalin.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611449/ruben-onsu-ungkap-hal-yang-paling-dirindukan-dari-anak-anak</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ruben-onsu-dan-sarwendah-1785990958341_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Prabowo Panggil Dirut Pertamina ke Hambalang Bahas Ini</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:26:54 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Prabowo Subianto memanggil Dirut Pertamina untuk membahas program energi nasional dan restrukturisasi BUMN, termasuk efisiensi dan pengurangan birokrasi.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260810065358-532-1390409/prabowo-panggil-dirut-pertamina-ke-hambalang-bahas-ini</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/06/presiden-buka-taklimat-awal-tahun-saat-retret-hambalang-1767693968817_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>IHSG Berpeluang Gagah Awali Pekan Ini</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:55:03 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Analis memperkirakan IHSG berpeluang melanjutkan penguatan pada perdagangan hari ini setelah naik 1,04 persen dan didukung peningkatan volume pembelian.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260810063657-92-1390405/ihsg-berpeluang-gagah-awali-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/04/23/9a58e76b-c36f-402f-8254-37b730807eaf_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Jejeran Pilihan Saham Berpeluang Cuan Pekan Ini</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:31:10 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>IHSG menguat 1,04 persen di level 6.409 dengan transaksi Rp16,46 triliun. Proyeksi pergerakan saham untuk pekan depan menunjukkan potensi penguatan terbatas.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260810061710-92-1390401/jejeran-pilihan-saham-berpeluang-cuan-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/03/24/ihsg-turun-ke-level-5000-1742799150138_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Wilayah Priangan Jawa Barat Senin, 10 Agustus 2026: Cerah dan Berawan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:34:51 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) merilis prakiraan cuaca untuk wilayah Priangan, Jawa Barat, pada Senin (10/8/2026).</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866141/prakiraan-cuaca-wilayah-priangan-jawa-barat-senin-10-agustus-2026-cerah-dan-berawan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5NsvRAfKVVqlNUGVnYRGovtF7v4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-8.jpg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Dea Annisa Resmi Dipersunting Mazaki Ahmad, Mahar Uang Tunai Senilai Rp2,9 Juta</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:28:33 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Dea Annisa resmi menikah dengan aktor Mazaki Ahmad. Akad nikah digelar outdoor dengan mahar tunai Rp2.921.996.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866140/dea-annisa-resmi-dipersunting-mazaki-ahmad-mahar-uang-tunai-senilai-rp29-juta</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c3jJDvNp76kBsTihvTTvj_r8Rdc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/dea-annisa-fokus-pada-karir_20200907_205837.jpg</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tragedi Drag Race Maut Kotamobagu, Polisi Olah TKP Dalami Penyebab Kecelakaan dan Kelalaian Panitia</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:27:21 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Polres Kotamobagu turun tangan menyelidiki insiden penyebab kecelakaan dalam Drag Race Maut yang tewaskan 7 orang dan 9 luka, Minggu (9/8/2026).</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866139/tragedi-drag-race-maut-kotamobagu-polisi-olah-tkp-dalami-penyebab-kecelakaan-dan-kelalaian-panitia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/AXdgAr9Iw3PgL4auFlOtiwlS1HI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kecelakaan-Drag-Race-dan-Drag-Bike-di-kotamobagu.jpg</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Di Balik Transfer Junior Cristiano Ronaldo, Al Nassr Tak Bisa Belanja Lagi akibat Duit Ludes</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:07:31 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Transfer junior Cristiano Ronaldo di Portugal, Samu Costa bisa jadi yang terakhir karena uang  belanja Al Nassr untuk musim panas 2026 sudah habis.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866138/di-balik-transfer-junior-cristiano-ronaldo-al-nassr-tak-bisa-belanja-lagi-akibat-duit-ludes</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Cyib7FLfUSF10TPgO8ouC9PoF_0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-klub-Liga-Arab-Saudi-Al-Nassr.jpg</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Bandung Raya Senin, 10 Agustus 2026: Kota Bandung Cerah</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:05:42 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Simak prakiraan cuaca wilayah Bandung Raya pada Senin (10/8/2026). Cuaca di seluruh wilayah Bandung Raya diprakirakan cerah, termasuk Kota Bandung.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866137/prakiraan-cuaca-bandung-raya-senin-10-agustus-2026-kota-bandung-cerah</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lDgUVS5zQ1sLN8t3mHbweeriZkY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-xx.jpg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>7 Tewas dan 9 Luka dalam Drag Race Kotamobagu Sulut, Polisi Selidiki Keselamatan Acara</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:58:51 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Panitia siap bertanggung jawab terhadap para korban, termasuk menanggung biaya pengobatan</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866136/7-tewas-dan-9-luka-dalam-drag-race-kotamobagu-sulut-begini-kata-panitia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/irpXgcKMI0KzK9jgyk8KGbe5jMA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/drag-race-kotamobagu-tabrak-penonton.jpg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Denny Sumargo Berharap Polemik Ruben Onsu dan Sarwendah Segera Selesai : Aku Stres</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:55:21 +0700</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Denny Sumargo berharap Ruben Onsu segera bertemu anak-anak dan polemik dengan Sarwendah bisa mereda.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866135/denny-sumargo-berharap-polemik-ruben-onsu-dan-sarwendah-segera-selesai-aku-stres</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ik23waLzTdDpWPovuqWu3mZdce4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Denny-Sumargo-1-03082026.jpg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Kesehatan Saluran Cerna Anak Berkaitan dengan Tumbuh Kembang Otak, Kepala BPOM Ungkap Bukti Ilmiah</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:54:45 +0700</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Kesehatan saluran cerna anak berkaitan dengan sistem imun dan perkembangan otak, terutama pada 1.000 Hari Pertama Kehidupan (HPK).</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866134/kesehatan-saluran-cerna-anak-berkaitan-dengan-tumbuh-kembang-otak-kepala-bpom-ungkap-bukti-ilmiah</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/xy8YPWuuJK5tvjDcqn1s754Ljkg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/5-gangguan-pencernaan-anak-yang-sering-terjadi-dan-pencegahannya.jpg</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Daftar 7 Korban Tewas dan 9 Luka Dihantam Mobil Pembalap Tian Ngantung, Panitia Janji Tanggung Jawab</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:52:25 +0700</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Daftar lengkap 7 korban tewas dan 9 luka akibat diseruduk mobil pembalap Tian Ngantung dalam ajang Drag Race di Kotamubagu Minggu (9/8/2026).</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866133/daftar-7-korban-tewas-dan-9-luka-dihantam-mobil-pembalap-tian-ngantung-panitia-janji-tanggung-jawab</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/sdtdONAMpybx_mtcJWcZYFFaWCI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/drage-race-kotamogaku-kecelakaan-tabrak-penonton.jpg</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PSSI Minta Maaf atas Kegagalan Timnas Indonesia di Piala AFF 2026, Evaluasi Segera Dilakukan</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:47:29 +0700</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PSSI melalui Yunus Nusi meminta maaf atas kegagalan Timnas Indonesia melaju ke semifinal Piala AFF 2026 dan janji lakukan evaluasi.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866132/pssi-minta-maaf-atas-kegagalan-timnas-indonesia-di-piala-aff-2026-evaluasi-segera-dilakukan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XnwHrLgh_9fjfJVEBcVvY288K5U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Skuad-Timnas-Indonesia-berdiskusi-bersama-sebelum-pertandingan-melawan-Vietnam.jpg</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mal Nipah Makassar Terbakar, Tak Ada Korban Jiwa</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:43:42 +0700</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Pihak manajemen juga menjelaskan awal mula kebakaran, titik api dari luar ruangan.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866131/mal-nipah-makassar-terbakartak-ada-korban-jiwa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/agcpkJPhibG2HYwEc7hsXBKRlyg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Seorang-pria-menjadi-sorotan-di-tengah-kebakaran-di-Mal-Nipah-Makassar.jpg</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Kronologi dan Sosok Pembalap Tian Ngantung yang Tabrak Penonton Drag Race di Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:32:13 +0700</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Tian Ngantung, pembalap terlibat kecelakaan Drag Race di Upai, Kotamobagu sebanyak 7 orang tewas dan 9 luka-luka akibat tragedi maut itu.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866130/kronologi-dan-sosok-pembalap-tian-ngantung-yang-tabrak-penonton-drag-race-di-kotamobagu</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8gdAtas3R9JuWqaIQxN4FApmqWo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pembalap-tian-ngantung-laka-drag-race-kotamubagu.jpg</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Denny Sumargo Tak Kecewa Ruben Onsu Tak Hadiri Podcastnya Tapi Bicara di Kanal Deddy Corbuzier</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:30:15 +0700</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Denny Sumargo bicara soal keputusan Ruben Onsu tak hadiri mendatangi podcastnya tapi memilih menemui Deddy Corbuzier.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866129/denny-sumargo-tak-kecewa-ruben-onsu-tak-hadiri-podcastnya-tapi-bicara-di-kanal-deddy-corbuzier</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4R39igLvVKxFx-kgiW4STstZIMc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ruben-sarwednah-densu.jpg</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ketegangan Neymar dengan Santos Picu Isu Bersatunya MSN di Inter Miami</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:23:04 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Inter Miami disebut berpeluang kembali persatukan MSN di tengah kabar ketegangan Neymar dengan Santos FC</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866128/ketegangan-neymar-dengan-santos-picu-isu-bersatunya-msn-di-inter-miami</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/sCpIPtKiR2NTjJ5VCaXgyFD1vOg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Neymar-Kembali-Bermain-usai-Absen-1-Tahun-Akibat-Cedera_20241022_083117.jpg</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Kota Sorong Hari Ini, Senin 10 Agustus 2026: Cerah dan Berawan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:19:00 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>BMKG memprakirakan, Kota Sorong, Provinsi Papua Barat Daya akan cerah dan berawan pada Senin (10/8/2026).</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866127/prakiraan-cuaca-kota-sorong-hari-ini-senin-10-agustus-2026-cerah-dan-berawan</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/V8VPFaStexZIHk2XEOtMdpkKhgQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Cuaca-Berawan-di-Indonesia.jpg</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Korea Masters Tuntas, Perang Bintang Badminton Siap Menggebrak Kejuaraan Dunia BWF 2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:06:04 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Korea Masters 2026 tuntas, agenda badminton bakal berlanjut ke Kejuaraan Dunia BWF 2026 yang akan dihelat pada 17-23 Agustus pekan depan.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866126/korea-masters-tuntas-perang-bintang-badminton-siap-menggebrak-kejuaraan-dunia-bwf-2026</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/sRRV5VlVttmMJFoEPVXGJ1bmX9U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/FajarFikri-Terhenti-di-Babak-32-Besar_20260603_183918.jpg</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>INDEF Dorong Pemerintah Terapkan Kebijakan Outward Looking Kalau Mau Tumbuh 8 Persen</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:51:14 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Lida Puspaningtyas</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Ekonom Senior Institute for Development of Economics and Finance (Indef) Didik J. Rachbini mengkritisi kebijakan ekonomi pemerintah di bawah kepemimpinan Prabowo Subianto yang cenderung berorientasi ke dalam...</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjj0qr502/indef-dorong-pemerintah-terapkan-kebijakan-outward-looking-kalau-mau-tumbuh-8-persen</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/070594900-1740478240-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cek Rute dan Cara Naik Bus Sekolah Jakarta</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:31:25 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Sebanyak 235 bus sekolah gratis melayani 50 rute di Jakarta untuk membantu pelajar berangkat dan pulang sekolah.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265916/cek-rute-dan-cara-naik-bus-sekolah-jakarta</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/nS50Kld92vp5bVkOH2I0PBgHZkM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/3560138/original/068350600_1630651083-20210903-Bus-Sekolah-3.jpg</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Menyusuri Lorong Bawah Tanah MRT Jakarta</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:45:34 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Stasiun MRT Monas Fase 2A kini hampir rampung, dengan sejumlah fasilitas unik yang disiapkan untuk penumpang.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265906/menyusuri-lorong-bawah-tanah-mrt-jakarta</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/5X34BRxyCRjjPlLTfVqOcrZ4V_s=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9319895/original/030201600_1786318411-1_94mUKbE-fG6vHj63F3tVnA.jpg</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Maldini Sebut Guardiola Sudah Rancang Formasi untuk Timnas Italia</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:50:27 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Paolo Maldini menyatakan Pep Guardiola hampir menerima tawaran melatih Timnas Italia.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/10/07481698/maldini-sebut-guardiola-sudah-rancang-formasi-untuk-timnas-italia</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/34FJNFqHBCLZAnqjq-CPLZBiTHg=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/05/24/6a131b1d6c7b3.jpg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Pakta Makkah: Menekan Iran, Mengimbangi AS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:50:27 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Pakta Makkah berusaha memaksa Iran mengubah kalkulasi politik perangnya dengan menciptakan pertahanan kolektif dan mempersempit ruang manuver Teheran.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/10/072300970/pakta-makkah--menekan-iran-mengimbangi-as</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/-3xngfZtXbwe4jCNnV8NEnVQdMo=/0x0:1800x1200/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2026/08/02/6a6f2e61e8350.jpg</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tekno</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Induk TikTok Siapkan Model AI Terbesar dari China</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:50:27 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Bila terwujud, model ini akan menjadi model AI terbesar yang pernah dikembangkan perusahaan China, dan berpotensi menyaingi model tercanggih Anthropic</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://tekno.kompas.com/read/2026/08/10/07000087/induk-tiktok-siapkan-model-ai-terbesar-dari-china</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/RruQ0jqJwkJg8bcVQRCHboRHvlc=/186x0:1200x676/1200x675/filters:watermark(data/photo/2026/01/30/697c816a7af9e.png,0,-0,1)/data/photo/2026/06/05/6a2257b04f98c.webp</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I63"/>
+  <autoFilter ref="A1:I112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5697,8 +5697,4238 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Trump mau akhiri perang dengan Iran meski tanpa kesepakatan nuklir</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:04:36 +0700</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump secara pribadi melontarkan gagasan untuk mengakhiri perang dengan Iran meski ...</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687103/trump-mau-akhiri-perang-dengan-iran-meski-tanpa-kesepakatan-nuklir</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/XxjpbeE000612_20260620_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Menlu Mesir desak Israel tarik pasukan sepenuhnya dari Gaza</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:01:53 +0700</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Menteri Luar Negeri Mesir Badr Abdelatty pada Minggu menekankan pentingnya menerapkan seluruh ketentuan yang telah ...</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687101/menlu-mesir-desak-israel-tarik-pasukan-sepenuhnya-dari-gaza</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/thumbs_b_b39e1a6a973e661feeb3926a2ec52632.jpg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pemkot Jakut berupaya menemukan kasus Tuberkulosis cegah penularan</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:01:25 +0700</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Jakarta Utara terus berupaya menemukan kasus Tuberkulosis (TB) sebagai upaya pencegahan ...</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687099/pemkot-jakut-berupaya-menemukan-kasus-tuberkulosis-cegah-penularan</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_4756.jpeg</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Trump isyaratkan peralihan ke tekanan ekonomi terhadap Iran</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:00:19 +0700</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat (AS) Donald Trump, Minggu (9/8) mengisyaratkan kesiapan negaranya untuk ...</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687097/trump-isyaratkan-peralihan-ke-tekanan-ekonomi-terhadap-iran</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/thumbs_b_c_7585b7a40076b45ff76a5da72d4e66da.jpg</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BBMKG: Waspada potensi rob di enam pesisir Bali pada 11=17 Agustus</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:58:17 +0700</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Balai Besar Meteorologi Klimatologi dan Geofisika (BBMKG) Wilayah III Denpasar meminta masyarakat mewaspadai potensi ...</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687096/bbmkg-waspada-potensi-rob-di-enam-pesisir-bali-pada-1117-agustus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_104959.jpg</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Mojtaba Khamenei muncul pertama kali di depan publik dan media</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:57:13 +0700</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Pemimpin Tertinggi Iran Mojtaba Khamenei bertemu Presiden Masoud Pezeshkian, Minggu (9/8) guna membahas ...</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687095/mojtaba-khamenei-muncul-pertama-kali-di-depan-publik-dan-media</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/09/XxjpbeE000022_20260309_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sedikitnya 11 tewas dalam penembakan terpisah di Cape Town, Afsel</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:50:26 +0700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Sedikitnya 11 orang tewas dalam tiga insiden penembakan terpisah di wilayah metropolitan Cape Town, Afrika Selatan, ...</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687092/sedikitnya-11-tewas-dalam-penembakan-terpisah-di-cape-town-afsel</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/08/InShot_20251108_111309960.jpg</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Paus Leo desak ruang diplomasi dalam konflik Ukraina</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:46:16 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Paus Leo XIV, Minggu (9/8) menyerukan agar diplomasi mendapat ruang dalam konflik Ukraina dan menekankan ...</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687091/paus-leo-desak-ruang-diplomasi-dalam-konflik-ukraina</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/17/thumbs_b_c_05e0e67ec243b575c0f4998f277901d2.jpg</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>IHSG menguat dipicu optimisme arah "dovish" bank sentral global</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:42:11 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin bergerak menguat dipicu oleh optimisme arah ...</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687089/ihsg-menguat-dipicu-optimisme-arah-dovish-bank-sentral-global</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IHSG-ditutup-menguat-65-94-poin-070826-Fah-2.jpg</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Kemenimipas-Kemenkes gelar pemeriksaan katarak dan CKG sambut HUT RI</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:42:06 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Kementerian Imigrasi dan Pemasyarakatan bersama Kementerian Kesehatan melaksanakan pemeriksaan katarak dan cek ...</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687087/kemenimipas-kemenkes-gelar-pemeriksaan-katarak-dan-ckgsambut-hut-ri</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001854577.jpg</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Israel gempur desa di Lebanon Selatan dengan artileri, serangan udara</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:42:03 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Tentara Israel menggempur desa-desa di Lebanon selatan dengan artileri dan serangan udara, Minggu (9/8), sementara ...</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687085/israel-gempur-desa-di-lebanon-selatan-dengan-artileri-serangan-udara</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/thumbs_b_c_44d942499a723724c9911a3f1b4d8b35.jpg</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sebelum Sang Saka Merah Putih berkibar</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:36:47 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Pukul 04.00 WIB, ketika sebagian besar anak seusia mereka masih terlelap, 76 calon Pasukan Pengibar Bendera Pusaka ...</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687083/sebelum-sang-saka-merah-putih-berkibar</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/Latihan-gabungan-Paskibraka-Nasional-2026-080826-Bay-1.jpg</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BNSP lakukan penyaksian uji pertama LSP guna perkuat kompetensi 80 SDM</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:35:41 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Badan Nasional Sertifikasi Profesi (BNSP) melakukan penyaksian uji pertama terhadap proses asesmen yang dilakukan enam ...</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687079/bnsp-lakukan-penyaksian-uji-pertama-lsp-guna-perkuat-kompetensi-80-sdm</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-07.19.13.jpeg</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Empat orang tewas dalam insiden kekerasan di Chicago, Amerika Serikat</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:32:25 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Empat orang tewas dalam insiden penembakan dan penikaman yang terjadi secara terpisah sepanjang malam di Chicago, ...</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687077/empat-orang-tewas-dalam-insiden-kekerasan-di-chicago-amerika-serikat</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/29/ilustrasi-penembakan-di-Michigan-AS.jpg</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BPK: BSSN jadi contoh lembaga yang responsif</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:23:59 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Anggota I Badan Pemeriksa Keuangan (BPK) Nyoman Adhi Suryadnyana menyatakan Badan Siber dan Sandi Negara (BSSN) menjadi ...</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687076/bpk-bssn-jadi-contoh-lembaga-yang-responsif</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-06-at-15.21.23.jpeg</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BPK: Semua K/L di lingkungan pemeriksaan Ditjen PKN I dapat opini WTP</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:21:10 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Anggota I Badan Pemeriksa Keuangan (BPK) Nyoman Adhi Suryadnyana menyatakan seluruh kementerian/lembaga (K/L) di ...</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687075/bpk-semua-k-l-di-lingkungan-pemeriksaan-ditjen-pkn-i-dapat-opini-wtp</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-06-at-15.17.41.jpeg</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Perkuat pelayanan, SuperApp Polri hadirkan fitur layanan darurat 110</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:20:23 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Polri terus memperkuat kualitas pelayanan kepada masyarakat melalui pemanfaatan teknologi digital, salah satunya ...</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687073/perkuat-pelayanan-superapp-polri-hadirkan-fitur-layanan-darurat-110</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000087528.jpg</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Hentikan Desley, Tammara kuasai kelas menengah putri IBF dan WBO</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:18:57 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Petinju Tammara Thibeault menghentikan perlawanan Desley Robinson untuk menguasai kelas menengah putri (72.5kg) ...</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687071/hentikan-desley-tammara-kuasai-kelas-menengah-putri-ibf-dan-wbo</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_090052.jpg</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Rupiah pada Senin pagi menguat jadi Rp17.810 per dolar AS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:16:46 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 87 poin atau 0,49 persen ...</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687067/rupiah-pada-senin-pagi-menguat-jadi-rp17810per-dolar-as</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821211.jpg</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Aktivitas gunung Lewotolok menurun, status tetap Level II</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:15:44 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Pos Pengamat Gunung Lewotolok melaporkan, aktivitas vulkanik Gunung Ile Lewotolok di Kabupaten Lembata, Nusa Tenggara ...</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687064/aktivitas-gunung-lewotolok-menurun-status-tetap-level-ii</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Ile-Lewotolok.jpg</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Coolita Luncurkan FAST Media Alliance Pertama di Indonesia Bersama Sejumlah Stasiun TV Terkemuka</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:15:34 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Aliansi industri pertama di Indonesia yang berfokus pada FAST (Free Ad-supported Streaming TV) resmi diluncurkan di ...</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687063/coolita-luncurkan-fast-media-alliance-pertama-di-indonesia-bersama-sejumlah-stasiun-tv-terkemuka</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Coolita-Luncurkan-FAST-Media-Alliance.jpg</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>IHSG Senin dibuka menguat 30,95 poin ke posisi 6.440,6</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:14:58 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 30,95 poin atau 0,48 ...</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687059/ihsg-senin-dibuka-menguat-3095-poin-ke-posisi-64406</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IHSG-ditutup-menguat-65-94-poin-070826-Fah-2.jpg</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Harga emas Antam pada Senin ini stabil di angka Rp2,690 juta/gr</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:13:08 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Harga emas Antam di laman Logam Mulia, yang dikutip di Jakarta, Senin pukul 9.01 WIB, menunjukkan kondisi tak ...</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687056/harga-emas-antam-pada-senin-ini-stabil-di-angka-rp2690-juta-gr</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/03/inflasi-kalimantan-tengah-mei-2026-2798825.jpg</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Menteri Ekraf: Film internasional diproduksi di RI berdampak positif</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:09:54 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Menteri Ekonomi Kreatif Teuku Riefky Harsya menilai proses produksi film internasional yang dilakukan di Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687053/menteri-ekraf-film-internasional-diproduksi-di-ri-berdampak-positif</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000456663.jpg</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Trump akui AS kurangi upaya negosiasi kesepakatan damai dengan Iran</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:08:34 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat (AS) Donald Trump, Minggu (9/8) mengakui bahwa pemerintahannya telah mengurangi ...</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687051/trump-akui-as-kurangi-upaya-negosiasi-kesepakatan-damai-dengan-iran</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/thumbs_b_c_2263c951fe4876ab38332a738c829d57-1.jpg</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Terpopuler, kebakaran di Bromo hingga pengembangan wisata yacth</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:05:43 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Beragam berita unggulan dimuat kanal Antaranews.com pada Senin, ada soal kebakaran di kawasan Gunung Bromo hingga ...</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687047/terpopuler-kebakaran-di-bromo-hingga-pengembangan-wisata-yacth</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Upaya-Pemadaman-Kebakaran-Hutan-Di-Kawasan-TNBTS-090826-IS-2.jpg</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Menteri LH imbau optimalisasi perdagangan karbon untuk masyarakat</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:02:45 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Menteri Lingkungan Hidup (LH) Moh Jumhur Hidayat meminta optimalisasi perdagangan karbon dan pengembangan ekowisata ...</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687044/menteri-lh-imbau-optimalisasi-perdagangan-karbon-untuk-masyarakat</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/DSC00844-11-1.jpg</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Parlemen Iran bahas RUU melarang kapal AS-Israel lewat Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:00:19 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Komisi Keamanan Nasional dan Kebijakan Luar Negeri Parlemen Iran menyetujui rancangan undang-undang (RUU) yang akan ...</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687040/parlemen-iran-bahas-ruu-melarang-kapal-as-israel-lewat-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/thumbs_b_c_b7099268d94f4d1f11b5ede1f17b74d1.jpg</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Alex Kawilarang melawan ketidakadilan, bukan Republik</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:51:58 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Kopral Satibi panik. Ia baru saja mendapatkan laporan warga mengenai kedatangan dua serdadu Belanda ke arah ...</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687036/alex-kawilarang-melawan-ketidakadilan-bukan-republik</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Kawilarang.jpg</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>BPK beri opini WTP kepada Kementerian PKP hingga Barantin</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:50:21 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Badan Pemeriksa Keuangan (BPK) memberikan opini wajar tanpa pengecualian (WTP) atas Laporan Keuangan (LK) Tahun 2025 ...</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687032/bpk-beri-opini-wtp-kepada-kementerian-pkp-hingga-barantin</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Anggota-BPK-Nyoman.jpeg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Pasukan pemerintah Yaman serang posisi Houthi di Provinsi Taizz</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:44:38 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Pasukan yang loyal kepada pemerintah Yaman yang diakui secara internasional menyerang posisi dan pasukan gerakan Ansar ...</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687028/pasukan-pemerintah-yaman-serang-posisi-houthi-di-provinsi-taizz</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/Tentara-Yaman.jpg</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>KI DKI dorong JIEP perkuat budaya keterbukaan informasi publik</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:34:11 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Komisi Informasi (KI) Provinsi DKI Jakarta mendorong PT Jakarta Industrial Estate Pulogadung (JIEP) untuk terus ...</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687027/ki-dki-dorong-jiep-perkuat-budaya-keterbukaan-informasi-publik</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000911949.jpg</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Menekraf: Inovasi kuliner-penerbitan buka nilai tambah ekraf baru</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:30:46 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Menteri Ekonomi Kreatif/Kepala Badan Ekonomi Kreatif (Ekraf), Teuku Riefky Harsya mendukung kolaborasi lintas subsektor ...</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687023/menekraf-inovasi-kuliner-penerbitan-buka-nilai-tambah-ekraf-baru</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000456629.jpg</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SIM Keliling tersedia di lima lokasi Jakarta pada Senin</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:20:14 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Direktorat Lalu Lintas (Ditlantas) Polda Metro Jaya masih membuka layanan Surat Izin Mengemudi (SIM) Keliling di lima ...</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687021/sim-keliling-tersedia-di-lima-lokasi-jakarta-pada-senin</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/Batas-Akhir-Dispensasi-Perpanjangan-SIM-31082020-gp-4.jpg</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Desain Samsung Galaxy Tab S12+ dan S12 Ultra dikabarkan mirip S11</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:11:21 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Desain Samsung Galaxy Tab S12+ dan Galaxy Tab S12 Ultra yang diperkirakan dirilis September 2026 dikabarkan ...</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687020/desain-samsung-galaxy-tab-s12-dan-s12-ultra-dikabarkan-mirip-s11</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/my-feature-galaxy-tab-s-550750764.jpg</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Umat Islam gelar doa keselamatan bangsa sambut HUT RI</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:02:00 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Umat Islam memanjatkan doa saat mengikuti doa keselamatan bangsa di Masjid Istiqlal, Jakarta.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687019/umat-islam-gelar-doa-keselamatan-bangsa-sambut-hut-ri</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Doa-Keselamatan-Bangsa-Di-Jakarta-090826-hma-2.jpg</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>KEK Tanjung Lesung dorong pengembangan sport fishing di Pandeglang</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:56:00 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pengelola Kawasan Ekonomi Khusus (KEK) Tanjung Lesung mendorong pengembangan sport fishing sebagai daya tarik wisata ...</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687004/kek-tanjung-lesung-dorong-pengembangan-sport-fishing-di-pandeglang</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000402845.jpg</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Saepul Ajukan Resign ke Bos Picok Tepat di Hari Pembunuhan Pria Depok</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:59:05 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pemilik usaha piscok di Depok menjelaskan bahwa Saepul, tersangka mutilasi, bukan lagi karyawannya. Saepul ajukan resign tepat di hari ia membunuh dan mutilasi.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611661/saepul-ajukan-resign-ke-bos-picok-tepat-di-hari-pembunuhan-pria-depok</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-pembunuhan-dan-mutilasi-pria-di-pancoran-mas-depok-ditangkap-subdit-resmob-polda-metro-jaya-1785915706525_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Momen Kocak Pria Tertidur di Etalase Museum Bikin Gubernur Sulut Kaget</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:55:52 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Fistel Mukuan</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Gubernur Sulut Yulius Selvanus terkejut  melihat pria tertidur di etalase gedung bekas Minahasa Raad. Dia berencana memperbaiki gedung bersejarah ini.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611658/momen-kocak-pria-tertidur-di-etalase-museum-bikin-gubernur-sulut-kaget</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/08/gubernur-sulawesi-utara-sulut-yulius-selvanus-memergoki-seorang-pria-tidur-di-dalam-etalase-1786180018810_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Bamsoet Ajak Komunitas Otomotif Jaga Soliditas dan Persatuan Bangsa</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:29:07 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Bambang Soesatyo, mengajak komunitas otomotif Indonesia untuk menjaga persatuan dan brotherhood, serta mendukung program pemerintah demi ketahanan nasional.</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611609/bamsoet-ajak-komunitas-otomotif-jaga-soliditas-dan-persatuan-bangsa</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bamsoet-ajak-komunitas-otomotif-jaga-soliditas-dan-persatuan-bangsa-1786328690337_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Evakuasi Dramatis 2 Pekerja Proyek Tertimpa Beton Turap di Jaktim</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:28:47 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Dua pekerja proyek normalisasi saluran air di Jakarta Timur tertimpa beton turap. Evakuasi dramatis berlangsung 3 jam, keduanya mengalami luka di kepala.</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611607/evakuasi-dramatis-2-pekerja-proyek-tertimpa-beton-turap-di-jaktim</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/petugas-suku-dinas-penanggulangan-kebakaran-dan-penyelamatan-gulkarmat-jakarta-timur-jaktim-mengevakuasi-dua-pekerja-proyek-no-1786311861874_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ogah Bayar, Sopir Xpander Tabrak Mobil hingga Hantam Palang GT Kalikangkung</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:26:54 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Tim detikJateng</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Mobil Mitsubishi Xpander menabrak mobil hingga menghantam palang GT Kalikangkung Semarang. Polisi menyebut sopir Xpander itu kabur karena tidak mau bayar tol.</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611604/ogah-bayar-sopir-xpander-tabrak-mobil-hingga-hantam-palang-gt-kalikangkung</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/08/viral-di-semarang-1786192394383_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Tembok Roboh Timpa Peserta Jalan Sehat di Sleman, 10 Orang Dilarikan ke RS</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:21:34 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Tim detikJogja</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Tembok pembatas roboh timpa peserta jalan sehat di Perum Minomartani, Ngaglik, Sleman. Sebanyak 10 orang dilarikan ke rumah sakit.</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611601/tembok-roboh-timpa-peserta-jalan-sehat-di-sleman-10-orang-dilarikan-ke-rs</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/tembok-roboh-saat-jalan-sehat-1786264342495_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PKS Dukung Pejabat Kabinet Tak Harus dari Partai, Ini Respons PDIP</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:55:10 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Mardani Ali Sera dari PKS mendukung Prabowo merekrut kabinet baru dengan kapasitas mumpuni. Reshuffle pasca 17 Agustus jadi hak prerogatif presiden.</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611574/pks-dukung-pejabat-kabinet-tak-harus-dari-partai-ini-respons-pdip</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/01/03/554f9ddb-f91b-4874-9d53-84512786f7b7_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Pria di Bantul Ditangkap Usai Kepergok Bawa Kopi Saset Isi Sabu</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:49:02 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Tim detikJogja</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Pria diciduk setelah kedapatan membawa narkoba jenis sabu di kawasan Bangunharjo, Sewon, Bantul. Kejadian itu pun sempat viral di media sosial.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611571/pria-di-bantul-ditangkap-usai-kepergok-bawa-kopi-saset-isi-sabu</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/08/sabu-diselipkan-dalam-kopi-saset-di-bantul-1786168388436_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Motor Tiba-tiba Terbakar hingga Hangus Tinggal Rangka di Jl Gatsu</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:48:29 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sebuah motor terbakar di Jalan Gatot Subroto, Jakarta Selatan, akibat korsleting listrik. Tidak ada korban jiwa, namun arus lalu lintas terhambat.</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611570/motor-tiba-tiba-terbakar-hingga-hangus-tinggal-rangka-di-jl-gatsu</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/motor-terbakar-hingga-hangus-tinggal-kerangka-di-jalan-gatot-subroto-tepatnya-dekat-mapolda-metro-jaya-1786326466752_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Polda Metro Koordinasi ke Polda Jateng Ekshumasi Jenazah Sutrimo</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:42:36 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap perkembangan kasus kematian Sutrimo di Jakarta. Polda Metro Jaya akan lakukan ekshumasi dan memanggil dokter yang menangani korban.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611566/polda-metro-koordinasi-ke-polda-jateng-ekshumasi-jenazah-sutrimo</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/30/kabidhumas-polda-metro-jaya-kombes-budi-hermanto-dok-istimewa-1782795010386_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Soal Isu Reshuffle Usai 17 Agustus, PKB Bicara Sinyal dari Istana</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:36:02 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>PKS usulkan menteri tidak harus dari parpol, PKB setuju keputusan menteri sepenuhnya hak prerogatif Presiden. Harapan figur menteri paham bidang tugasnya.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611549/soal-isu-reshuffle-usai-17-agustus-pkb-bicara-sinyal-dari-istana</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/22/ketua-dpp-pkb-daniel-johan-tangkapan-layar_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sederet Hal yang Sudah Diketahui dari Aksi Keji Saepul Pemutilasi</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:24:12 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Kasus pembunuhan dan mutilasi oleh Saepul terhadap pria K di Depok mengungkap fakta mengejutkan. Polisi masih dicari potongan tubuh korban.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611541/sederet-hal-yang-sudah-diketahui-dari-aksi-keji-saepul-pemutilasi</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/08/saepul-26-pelaku-mutilasi-pria-inisial-k-di-depok-diperiksa-di-polda-metro-jaya-1786191209681_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Mobil Oleng Keluar Jalur Hantam 3 Motor di Sleman, 2 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:18:34 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Tim detikJogja</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Kecelakaan maut di Moyudan, Sleman, melibatkan mobil dan tiga sepeda motor. Dua orang dilaporkan meninggal dunia.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611539/mobil-oleng-keluar-jalur-hantam-3-motor-di-sleman-2-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/avanza-tabrak-3-motor-di-sleman-1786265405883_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Gedung Advent Pertemuan di MT Haryono Tebet Kebakaran</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:17:46 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda gedung Advent di Tebet, Jakarta Selatan. Petugas damkar berhasil padamkan api dalam satu jam. Dugaan penyebabnya adalah kelistrikan.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611530/gedung-advent-pertemuan-di-mt-haryono-tebet-kebakaran</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/13/ilustrasi-api_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Jawaban dan Bantahan Yayasan Sekolah di Jaksel soal Temuan Ratusan Senjata</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:14:11 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Sebanyak 996 senjata ditemukan di sekolah swasta di Jakarta Selatan. Yayasan menjawab dan membantah pernyataan dari pihak eks ketua yayasan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611527/jawaban-dan-bantahan-yayasan-sekolah-di-jaksel-soal-temuan-ratusan-senjata</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/pendiri-yayasan-sekolah-swasta-di-jaksel-yang-ditemukan-senjata-adrialdetikcom-1786266610236_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>IYF 2026, Jasaraharja Putera Perkuat Pengelolaan Risiko Wisata Bahari</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:03:57 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Pengembangan sektor wisata bahari Indonesia memerlukan ekosistem yang mampu mendorong pertumbuhan ekonomi dan membutuhkan pengelolaan risiko yang terintegrasi.</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611546/iyf-2026-jasaraharja-putera-perkuat-pengelolaan-risiko-wisata-bahari</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/pengembangan-sektor-wisata-bahari-indonesia-memerlukan-ekosistem-yang-mampu-mendorong-pertumbuhan-ekonomi-dan-membutuhkan-peng-1786325597274_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Ditemukan Ratusan Senjata, Sekolah di Jaksel Terapkan PJJ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:58:00 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Trypama Randra</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Menteri PPPA, Arifah Fauzi prihatin atas temuan ratusan senjata, narkotika, dan CD porno di sekolah swasta di Pondok Pinang,</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611331/ditemukan-ratusan-senjata-sekolah-di-jaksel-terapkan-pjj</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/detik-pagi-ditemukan-ratusan-senjata-sekolah-di-jaksel-terapkan-pjj-1786285020763_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Tol Dalam Kota Cawang Arah Tebet Macet Senin Pagi</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:56:25 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Wilda Hayatun Nufus</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Lalu lintas (lalin) di Tol Dalam Kota macet dari Cawang arah Tebet pagi ini. Kemacetan akibat tingginya volume kendaraan.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611519/tol-dalam-kota-cawang-arah-tebet-macet-senin-pagi</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/06/24/d6cd5b81-129f-48c1-8362-a733abc0c2d5_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Petantang-petenteng Bang Jukir Jago Tambora yang Positif Narkoba</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:49:13 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Viral seorang jukir memaksa tarif hingga mengajak duel pengendara motor di Jalan Jembatan Lima, Tambora, Jakarta Barat. Bang jago itu kini dicokok polisi.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611518/petantang-petenteng-bang-jukir-jago-tambora-yang-positif-narkoba</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/jukir-liar-memaksa-tarif-hingga-ajak-duel-pemotor-di-jalan-jembatan-lima-tambora-jakarta-barat-1786273386183_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Dolar AS Pagi Ini Melemah ke Rp 17.810</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:29:27 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Nilai tukar dolar AS melemah terhadap Rupiah di level Rp 17.800. Pergerakan mata uang lainnya cenderung stagnan.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8611611/dolar-as-pagi-ini-melemah-ke-rp-17-810</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338270_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Hari Ini Naik atau Turun?</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:25:57 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Harga emas Antam stagnan di Rp 2.690.000 per gram. Rincian harga untuk berbagai ukuran juga disediakan, termasuk buyback di Rp 2.511.000 per gram.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611603/harga-emas-antam-hari-ini-naik-atau-turun</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/04/23/melihat-kilau-emas-yang-harganya-jatuh-dari-level-rp-2-juta-1745406997688_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>IHSG Dibuka Menguat di Awal Pekan</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:18:38 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) pagi ini dibuka di zona hijau. IHSG berada di level 6.400 saat pembukaan perdagangan.</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8611599/ihsg-dibuka-menguat-di-awal-pekan</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/19/ihsg-ditutup-menguat-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Rekomendasi Saham Hari Ini saat IHSG Menguat</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:56:42 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>RLCO incar pasar ekspor baru, SINI kembangkan tambang batu bara US$3,26 miliar, dan EAST bagikan dividen Rp2 per saham.</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8611575/rekomendasi-saham-hari-ini-saat-ihsg-menguat</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bursa-dan-valas-1786324946-1786324946707.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Dirut Pertamina Lapor Prabowo soal B50 hingga Persiapan Bioetanol</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:20:59 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Direktur Utama PT Pertamina (Persero) Simon Aloysius Mantiri bertemu Presiden Prabowo Subianto sore kemarin.</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8611540/dirut-pertamina-lapor-prabowo-soal-b50-hingga-persiapan-bioetanol</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/prabowo-panggil-dirut-pertamina-ke-hambalang-dok-instagram-1786303642467_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Gisela Cindy dan Sian Resmi Menikah, Ucap Janji Suci di Altar</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:09:46 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Aktris Gisela Cindy resmi menikah dengan Sian. Inilah momen sakral aktris yang kini memilih tinggal di Kanada itu.</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611531/gisela-cindy-dan-sian-resmi-menikah-ucap-janji-suci-di-altar</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/gisela-cindy-1786323615840_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Fitrop Ikut Mellow Sada Murung Lomba Ice Skating di Malaysia, tapi Happy Ending</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:03:48 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Artis Fitri Tropica atau Fitrop ikut deg-degan ketika Sada murung lomba ice skating di Malaysia. Namun, Sada bikin Fitrop menangis haru.</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611436/fitrop-ikut-mellow-sada-murung-lomba-ice-skating-di-malaysia-tapi-happy-ending</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/fitri-tropica-1786283509237_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Kemendagri dan ATR/BPN Integrasikan Data Pajak dan Bidang Tanah</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Kemendagri dan Kementerian ATR/BPN resmi mengintegrasikan data perpajakan dan pertanahan untuk menutup bocornya pendapatan daerah.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866180/kemendagri-dan-atrbpn-integrasikan-data-pajak-dan-bidang-tanah</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oACdedZMl7uJmG8R5DMgTabu-_A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Integrasi-data-Kemendagri-dan-Kementerian-ATR.jpg</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Apes Fabio Quartararo di Silverstone, Penalti 16 Detik Berujung Pulang Tanpa Poin</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:03:17 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Fabio Quartararo dikenai sanksi penalti 16 detik karena data tekanan ban yang tak terekam sepanjang balapan MotoGP 2026 di Silverstone, Inggris.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866179/apes-fabio-quartararo-di-silverstone-penalti-16-detik-berujung-pulang-tanpa-poin</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/VTbmWc2QhoSmEl-VoFtfPuixEA8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/fabio-quartararo-motogp-india-2023.jpg</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Zelenskyy: Korea Utara akan Kirim 50.000 Tentara ke Rusia</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:59:34 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Presiden Ukraina Volodymyr Zelenskyy mengatakan Korea Utara akan mengirim 50.000 tentara ke Rusia sebagai bagian dari dukungan terhadap perang.</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866178/zelenskyy-korea-utara-akan-kirim-50000-tentara-ke-rusia</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/OckoZz7XHDWLCUCgT7a3CVcqVJs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Z3L3NSKYY-345345433.jpg</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Telkom Tuntaskan Spin-Off InfraCo Tahap 2, Perkuat InfraNexia di Bisnis Wholesale Connectivity</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:54:31 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Pengalihan aset dan bisnis dengan total Rp85,7 triliun memperkuat InfraNexia dalam mengembangkan lebih dari 90 persen aset jaringan Telkom.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866177/telkom-tuntaskan-spin-off-infraco-tahap-2-perkuat-infranexia-di-bisnis-wholesale-connectivity</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Rv3B02tJ6U8ElZW_KNXI-V6yyhk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/InfraNexia-Jadi-Pilar-Utama-Bisnis-Wholesale-Connectivity-T.jpg</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Komisi XI DPR Tunggu Surpres untuk Fit and Proper Test Calon Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:52:55 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>DPR masih menunggu Surat Presiden (Surpres) kepada DPR terkait usulan nama calon Gubernur Bank Indonesia yang definitif.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866176/komisi-xi-dpr-tunggu-surpres-untuk-fit-and-proper-test-calon-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/_pqGaXZbbQkpPXU2Rr9VPOKklw8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Destry-Damayanti-Penjabat-Gubernur-BI.jpg</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Kronologi Drag Race Maut di Kotamobagu: Mobil Crash Usai Finis dan Tabrak Penonton, 7 Tewas</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:52:49 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Drag race di Kotamobagu berakhir tragedi, mobil crash usai finis menabrak penonton, tujuh orang tewas, belasan luka-luka.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866175/kronologi-drag-race-maut-di-kotamobagu-mobil-crash-usai-finis-dan-tabrak-penonton-7-tewas</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/irpXgcKMI0KzK9jgyk8KGbe5jMA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/drag-race-kotamobagu-tabrak-penonton.jpg</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5 Contoh Teks Doa Upacara 17 Agustus di Sekolah, Kantor, Kampus hingga RT/RW</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:51:43 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Simak kumpulan contoh teks doa upacara 17 Agustus dalam rangka memperingati HUT ke-81 RI pada kegiatan upacara bendera di sekolah, kantor hingga desa.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866174/5-contoh-teks-doa-upacara-17-agustus-di-sekolah-kantor-kampus-hingga-rtrw</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/6VjcqlpNVFLByknPk0gAqyyHXqw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/upacara-bendera-orang-tua-murid-sd-negeri-karangmekar-mandiri-1_20200317_183145.jpg</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Bukan karena Perceraian, Marshanda Sebut Anak Hancur saat Lihat Orang Tua Saling Menjatuhkan</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:47:20 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Marshanda menyebut penyebab anak hancur bukan karena perceraian orang tua, namun ketika ayah dan ibu mereka saling menjatuhkan.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866173/bukan-karena-perceraian-marshanda-sebut-anak-hancur-saat-lihat-orang-tua-saling-menjatuhkan</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/EAfm_oeo4kzS5l-vpQ_8MeYqn_w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Marshanda-di-kawasan-Senayan-128.jpg</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pemerintah Targetkan Bedah 400 Ribu Rumah Sepanjang 2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:42:53 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Tito berharap aturan teknis yang disiapkan dapat menjamin warga negara mendapatkan haknya tanpa proses yang berbelit-belit.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866172/pemerintah-targetkan-bedah-400-ribu-rumah-sepanjang-2026</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Sii878jA8GXObqlbSeacjvD6UWQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Tito-Karnavian-bakal-mengeksekusi.jpg</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Lantai 5 Gedung Pertemuan Advent Tebet Terbakar: Diduga Karena Masalah Listrik</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:27:58 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Petugas berhasil melokalisir api pada pukul 05.57 WIB. Proses pendinginan kemudian dimulai pada pukul 06.00 WIB.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866171/lantai-5-gedung-pertemuan-advent-tebet-terbakar-diduga-karena-masalah-listrik</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tDk7IObInGCnZb1nWhJ5FdYEj4Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-kebakarannnnnnnnnnnnnnnnnnnn.jpg</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Lutesha Ajak Publik Nonton Seni Merayu Tuhan, Singgung Kisah Pemuda yang Lalai Ibadah</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:25:28 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Lutesha mengajak publik menyaksikan Seni Merayu Tuhan. Film ini mengisahkan perjalanan spiritual Hikmah setelah kehilangan sang ibu.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866170/lutesha-ajak-publik-nonton-seni-merayu-tuhan-singgung-kisah-pemuda-yang-lalai-ibadah</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/6QDU-A5OOgZKMGf3STeqKDQEYbs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Lutesha-1-12062026.jpg</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sosok Guru SDN di Jambi Jadi Korban Bullying, Dua Kali Masuk IGD hingga Ditangani Psikiater</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:25:27 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Guru SDN di Jambi jadi korban bullying, dua kali masuk IGD, kondisi psikis memburuk hingga harus ditangani psikiater.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866169/sosok-guru-sdn-di-jambi-jadi-korban-bullying-dua-kali-masuk-igd-hingga-ditangani-psikiater</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/NGLrV12xH3sz2AQIMxFEX3j7Hsg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-bullying.jpg</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Foto-foto Aktris Fang Taozi Buatan AI, Kerutan Wajah dan Aktingnya Persis Manusia, Populer di China</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:21:05 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Ini adalah foto-foto aktris  buatan kecerdasan buatan (AI) yang persis manusia sungguhan.</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866168/foto-foto-aktris-fang-taozi-buatan-ai-kerutan-wajah-dan-aktingnya-persis-manusia-populer-di-china</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iQp77laSPNxju8tn3aFFRyjTvDM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Diberi-nama-Fang-Taozi-di-platfor-D.jpg</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Pelaku Penembakan di Festival Budaya Lembah Baliem Papua Diduga Anggota KKB Egianus Kogoya</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:14:03 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Dari penyelidikan sementara, pelaku diduga merupakan anggota Kelompok Kriminal Bersenjata pimpinan Egianus Kogoya.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866167/pelaku-penembakan-di-festival-budaya-lembah-baliem-papua-diduga-anggota-kkb-egianus-kogoya</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/qEyJ1F8EbobD-Yt2hKPIYq9rr5k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penembakan-di-Festival-Budaya-Lembah-Baliem-Jayawijaya-Papua-Pegunungan.jpg</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>MUI Buat Fatwa, Larang Pria Berbusana Wanita saat Karnaval HUT RI</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:11:13 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>MUI menerbitkan fatwa terkait larangan pria berbusana wanita saat karnaval 17 Agustusan. Fatwa ini terbit berlandaskan hadist Imam Bukhari.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866166/mui-buat-fatwa-larang-pria-berbusana-wanita-saat-karnaval-hut-ri</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ZJPch9XJ-U2BIVAWX4RWZFniLhQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-bendera-lgbt.jpg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5 Contoh Susunan Upacara HUT ke-81 RI 17 Agustus 2026 di Sekolah, Kantor, RT/RW hingga Desa</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:07:15 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Simak kumpulan contoh susunan upacara HUT ke-81 RI pada 17 Agustus 2026 di lingkungan sekolah, kantor, RT/RW, desa hingga kampus.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866165/5-contoh-susunan-upacara-hut-ke-81-ri-17-agustus-2026-di-sekolah-kantor-rtrw-hingga-desa</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0AURNJFFHjJ2KvayMAhKDCxLwzo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/UPACARA-HUT-KORPRI.jpg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum Sebut Rudy Tanoesoedibjo Jalani Check Up Kesehatan, KPK Panggil Ulang Besok</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:02:33 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Bambang Rudijanto Tanoesoedibjo alias Rudy Tanoe bantah kabar yang menyebut kliennya sengaja mangkir dari panggilan KPK.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866164/kuasa-hukum-sebut-rudy-tanoesoedibjo-jalani-check-up-kesehatan-kpk-panggil-ulang-besok</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XemIsTqUJx8_tk2AQZ3U8MRqlns=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/rudy-tanoesoedibjo-presiden-direktur-pt-dnr1.jpg</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Damai Batal, Ketua RT di Bandar Lampung Dipolisikan Perkara Jewer Bocah</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:56:49 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Like Yuanita dilaporkan ke Polresta Bandar Lampung oleh ayah salah satu korban, Doddy Kurnia Putra (40).</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866163/damai-batal-ketua-rt-di-bandar-lampung-dipolisikan-perkara-jewer-bocah</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/QUupo8KbLXEJnvK_WzEOCT4UGkQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PENGAKUAN-KETUA-RT.jpg</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Ongkang-ongkang dapat Cuan, Chelsea Diuntungkan Klausul Khusus Romelu Lukaku</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:55:36 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Transfer Romelu Lukaku ke Turki membawa rezeki nomplok hampir 100 miliar Rupiah bagi Chelsea.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866162/ongkang-ongkang-dapat-cuan-chelsea-diuntungkan-klausul-khusus-romelu-lukaku</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fol4LxzHkM4vpHaJ0rZ4fru28HI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Romelu-Lukaku-merayakan-gol-pertamanya-dalam-pertandingan-sepak-bola-Serie-A.jpg</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Lowongan Kerja PT Jamkrida Jakarta untuk Lulusan SMA dan S1, Buka 7 Posisi, Cek Syaratnya</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:55:18 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>PT Jamkrida Jakarta buka lowongan kerja sebanyak tujuh posisi untuk lulusan minimal SMA/sederajat dan S1, batas pendaftaran 18 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866161/lowongan-kerja-pt-jamkrida-jakarta-untuk-lulusan-sma-dan-s1-buka-7-posisi-cek-syaratnya</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/CLh8S1-7FaS_IR--cgW89FrrePQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PT-Jamkrida-Jakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga Pasok Layanan Avtur Untuk Raksasa Emirates A380</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:18:52 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Kedatangan Airbus A380 Emirates di Bandara Internasional Soekarno-Hatta pada Sabtu (8/8/2026) menjadi momentum bagi PT Pertamina Patra Niaga melalui Aviation Fuel Terminal (AFT) Soekarno-Hatta untuk menunjukkan kesiapan...</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjj7rg522/pertamina-patra-niagapasok-layanan-avtur-untukraksasa-emirates-a380</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/airbus-a380-emirates-di-bandara-internasional-soekarno-hatta-pada-sabtu_260810091835-158.jpeg</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Presiden Perintahkan PLN-Pertamina Segera Pangkas Anak-Cucu Perusahaan</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Presiden Prabowo Subianto memerintahkan jajarannya dan para petinggi BUMN, khususnya Pertamina dan PLN, untuk segera memangkas anak-cucu perusahaan beserta unit-unit usaha di bawahnya guna meningkatkan efisiensi dan produktivitas...</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjj4ws423/presiden-perintahkan-plnpertamina-segera-pangkas-anakcucu-perusahaan</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/090065900-1785763541-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sepekan Depan, Harga Emas Diprediksi Berada di Kisaran Rp 2,55-Rp 2,82 Juta per Gram</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:59:35 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Harga emas dan atau logam mulia diprediksi masih bergerak melandai dan cenderung naik pada sepekan ke depan. Diproyeksi pergerakan harga emas akan berada di kisaran Rp 2,55-Rp...</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjj43b423/sepekan-depan-harga-emas-diprediksi-berada-di-kisaran-rp-255rp-282-juta-per-gram</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/ilustrasi-emas-batangan-otoritas-jasa-keuangan-ojk-mengungkapkan-usaha_250222070434-420.jpg</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Pemerintah Integrasikan Data PBB, Pendapatan Daerah Dibidik Melonjak</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:04:00 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Kebijakan ini diharapkan mendongkrak Pendapatan Asli Daerah secara signifikan.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8265978/pemerintah-integrasikan-data-pbb-pendapatan-daerah-dibidik-melonjak</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/V6DrqodWzRPmJPb8FThkdzlcbLI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9319994/original/067677300_1786330997-b77f8770-6ab0-4251-a0d9-6df8cb18721e.jpg</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Dalam Kebisuan, Tarno Setia 20 Tahun Terakhir Menarik Perahu Tambangan di Sungai Cimanuk Indramayu</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:08:43 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Tarno, penyandang tuna wicara yang selama 20 tahun terakhir setia menjadi penarik perahu tambangan di Sungai Cimanuk Indramayu</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://bandung.kompas.com/read/2026/08/10/100654178/dalam-kebisuan-tarno-setia-20-tahun-terakhir-menarik-perahu-tambangan-di</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/mA7DWOibww0lWYUWozvc8iO-kn8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/09/6a788ca3a8a25.jpeg</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Tekno</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HP Xiaomi Redmi Note 17 dan Note 17 Pro Rilis di Indonesia Segera, Ini Buktinya</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:08:43 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Dua perangkat yang diduga Redmi Note 17 dan Redmi Note 17 Pro sudah masuk laman sertifikasi TKDN dan Postel di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://tekno.kompas.com/read/2026/08/08/19010087/hp-xiaomi-redmi-note-17-dan-note-17-pro-rilis-di-indonesia-segera-ini-buktinya</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/5zZzMjBZLbQM3Sm28ZxpOhUAH08=/243x65:1683x1025/1200x675/filters:watermark(data/photo/2026/01/30/697c816a7af9e.png,0,-0,1)/data/photo/2026/08/07/6a754a153edcc.png</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Gas Langka dan Mahal, Industri Tekstil Bangladesh Mulai Beralih ke Energi Terbarukan</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:08:43 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Krisis gas membuat pabrik tekstil Bangladesh beroperasi hingga 40 persen di bawah kapasitas dan mulai beralih ke biomassa serta energi surya.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/10/093500726/gas-langka-dan-mahal-industri-tekstil-bangladesh-mulai-beralih-ke-energi</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/8zhBGUa8ytFK5B1s9h4ICd30fvU=/513x155:2560x1520/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2025/05/04/6816eda4ddf99.jpeg</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I112"/>
+  <autoFilter ref="A1:I202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$327</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I202"/>
+  <dimension ref="A1:I327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9927,8 +9927,5887 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>BPS: Harga daging sapi di atas HAP pada awal Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:07:48 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pusat Statistik (BPS) Amalia Adininggar Widyasanti menyampaikan harga rata-rata secara nasional komoditas ...</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687209/bps-harga-daging-sapi-di-atas-hap-pada-awal-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/16/IMG_2971.jpeg</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>LPSK "jemput bola" untuk dampingi keluarga Sutrimo</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:07:14 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Lembaga Perlindungan Saksi dan Korban (LPSK) melakukan "jemput bola" untuk menjangkau keluarga almarhum ...</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687208/lpsk-jemput-bola-untuk-dampingi-keluarga-sutrimo</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000998509.jpg</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Liburan ke Jepang makin hemat dengan cashback 10% BRI Kartu Kredit JCB Platinum</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:01:43 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Merencanakan perjalanan impian ke Negeri Sakura kini terasa jauh lebih menyenangkan. Selain menikmati keindahan ...</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687205/liburan-ke-jepang-makin-hemat-dengan-cashback-10-bri-kartu-kredit-jcb-platinum</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/05/04/IMG_7422-copy.jpg</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Chichen Itza dan pesan Xi Jinping tentang dialog antarperadaban</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:00:29 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Di situs arkeologi Maya kuno Chichen Itza, Meksiko, piramida batu dan kuil-kuilnya masih menceritakan kisah sebuah ...</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687204/chichen-itza-dan-pesan-xi-jinping-tentang-dialog-antarperadaban</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CjkinzN000003_20260810_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Museum Tekstil hadirkan umbul-umbul "Caruban Nagari"</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:00:21 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Museum Tekstil bersama Himpunan Wastraprema (HWP) menghadirkan umbul-umbul Caruban Nagari, Bendera Kesultanan Cirebon ...</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687201/museum-tekstil-hadirkan-umbul-umbul-caruban-nagari</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000318615.jpg</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Hasil manis Raul Fernandez di Silverstone</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Pembalap TrackHouse Racing Raul Fernandez tampil solid dan memenangi balapan MotoGP Inggris di Sirkuit Silverstone, ...</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5687172/hasil-manis-raul-fernandez-di-silverstone</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810-Hasil-manis-Raul-Fernandez-di-Silverstone.jpg</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Eala kandas, Gauff dan Osaka melaju ke perempat final Toronto</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:42:41 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Petenis Filipina Alexandra Eala harus mengakhiri langkahnya di National Bank Open 2026 setelah kalah dari unggulan ...</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687199/eala-kandas-gauff-dan-osaka-melaju-ke-perempat-final-toronto</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_0159.jpeg</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>KSP: SNT upaya strategis hadirkan pendidikan bermutu hingga pelosok RI</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:39:28 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Kantor Staf Presiden (KSP) mengatakan penyelenggaraan Sekolah Nasional Terintegrasi (SNT) merupakan intervensi ...</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687196/ksp-snt-upaya-strategis-hadirkan-pendidikan-bermutu-hingga-pelosok-ri</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/MPLS-1.jpg</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Komisi XIII DPR duga ada dalang penyebar video hoaks demonstrasi</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:39:22 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi XIII DPR RI Andreas Hugo Pareira menduga ada dalang di balik beredarnya video-video hoaks yang ...</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687195/komisi-xiii-dpr-duga-ada-dalang-penyebar-video-hoaks-demonstrasi</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/04/wakil-ketua-komisi-XIII-DPR-RI-Andreas.jpg</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>PNM dorong usaha perempuan pesisir naik kelas lewat hilirisasi</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:39:00 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>nya pun tulang punggung keluarga di sini yang juga sangat aktif," ujar Muhaimin.
+Menurut Muhaimin, penguatan ...</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687193/pnm-dorong-usaha-perempuan-pesisir-naik-kelas-lewat-hilirisasi</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-9.18.41-AM.jpeg</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Pemkab Probolinggo edukasi warga dan terapkan EWS cegah karhutla Bromo</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:35:50 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten (Pemkab) Probolinggo menyiapkan langkah penguatan edukasi kepada masyarakat dan menerapkan sistem ...</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687191/pemkab-probolinggo-edukasi-warga-dan-terapkan-ews-cegah-karhutla-bromo</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-09-at-22.34.59-1-1200x630.jpeg</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Menghubungkan Dunia dengan Peluang Baru – Guangzhou Nansha Membangun Ekosistem Baru bagi Perdagangan Lintas Batas</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Departemen Publisitas Distrik Nansha
+Guangzhou, China (ANTARA/Xinhua-AsiaNet) – Baru-baru ini, tujuh jurnalis ...</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687187/menghubungkan-dunia-dengan-peluang-baru-guangzhou-nansha-membangun-ekosistem-baru-bagi-perdagangan-lintas-batas</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1-Nansha-District.jpg</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Menteri Arifah: Beri ruang bagi anak untuk belajar dan berkreasi</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:24:31 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Menteri Pemberdayaan Perempuan dan Perlindungan Anak (PPPA) Arifah Fauzi menekankan pentingnya komitmen untuk ...</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687184/menteri-arifah-beri-ruang-bagi-anak-untuk-belajar-dan-berkreasi</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-09.08.50.jpg</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>BPS: Kenaikan harga ayam ras di 188 daerah perlu diwaspadai</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:24:06 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pusat Statistik (BPS) Amalia Adininggar Widyasanti meminta pemerintah daerah mewaspadai kenaikan harga ...</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687183/bps-kenaikan-harga-ayam-ras-di-188-daerah-perlu-diwaspadai</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Inflasi-kaltim-periode-Juli-040826-AP-4.jpg</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Polisi jadwalkan pemeriksaan YouTuber Bigmo pada Senin siang</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:20:15 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menjadwalkan pemanggilan dan pemeriksaan terhadap seorang pembuat konten YouTube (YouTuber) bernama ...</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687179/polisi-jadwalkan-pemeriksaan-youtuber-bigmo-pada-senin-siang</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/9368b4fa-86bf-4254-b9cc-b5cff07d9e35.jpeg</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Padang Fashion Summit 2026 sebagai upaya dorong wastra Minangkabau tembus pasar internasional</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:16:45 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Model memperagakan busana karya desainer De Irma saat Padang Fashion Summit di Padang, Sumatera Barat, Minggu ...</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687177/padang-fashion-summit-2026-sebagai-upaya-dorong-wastra-minangkabau-tembus-pasar-internasional</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Padang-Fashion-Summit-2026-090826-Ief-3.jpg</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Roadmap perbankan dan Prabowonomics dalam bingkai komunikasi kritis</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:14:10 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Saya selalu waspada setiap kali angka pertumbuhan ekonomi dan peta jalan kebijakan dirilis bersamaan dalam satu ...</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687175/roadmap-perbankan-dan-prabowonomics-dalam-bingkai-komunikasi-kritis</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/ilustrasi_roadmap.jpg</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>OJK dan SRO resmi luncurkan instrumen investasi ETF Emas</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:12:13 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) bersama Self Regulatory Organization (SRO) resmi meluncurkan instrumen investasi Exchange ...</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687168/ojk-dan-sro-resmi-luncurkan-instrumen-investasi-etf-emas</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000722191.jpg</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Yili Group Mendorong Inovasi dan Kolaborasi untuk Ekosistem Susu Global yang Berkelanjutan pada World Dairy Congress 2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:11:01 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Yili Group
+Hohhot, China (ANTARA/Xinhua-AsiaNet) – World Dairy Congress 2026 resmi dibuka pada 1 Agustus di ...</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687165/yili-group-mendorong-inovasi-dan-kolaborasi-untuk-ekosistem-susu-global-yang-berkelanjutan-pada-world-dairy-congress-2026</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1-Hohhot-World-Dairy-Capital.jpg</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>AS tak khawatirkan penolakan Netanyahu soal rencana damai Gaza</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:09:44 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Pemerintahan Presiden AS Donald Trump tidak mengkhawatirkan penolakan Kepala Otoritas Israel Benjamin Netanyahu ...</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687164/as-tak-khawatirkan-penolakan-netanyahu-soal-rencana-damai-gaza</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/17/thumbs_b_c_67ee4d371d8bc8a93405db85a379f9f0.jpg</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Simak daftar selengkapnya harga emas di Pegadaian pada Senin</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:04:59 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Harga emas di laman Pegadaian yang dikutip di Jakarta, Senin, pukul 10.50 WIB, menunjukkan jenama Galeri24, Antam, dan ...</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687161/simak-daftar-selengkapnya-harga-emas-di-pegadaian-pada-senin</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/bazar-dan-literasi-emas-di-kendari-2828053.jpg</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Greenland tolak aktivitas perusahaan AS di tengah isu aneksasi</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:04:29 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Pemerintah Greenland memberikan "peringatan keras" kepada perusahaan minyak yang terkait dengan Presiden AS ...</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687157/greenland-tolak-aktivitas-perusahaan-as-di-tengah-isu-aneksasi</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/14/Greenland-salah-satu-semenanjung-Pulau.jpg</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Bareskrim bongkar dugaan peredaran narkoba di HH Club Batam</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:03:20 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Direktorat Tindak Pidana Narkoba Badan Reserse Kriminal Polri membongkar kasus dugaan peredaran narkoba di tempat ...</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687155/bareskrim-bongkar-dugaan-peredaran-narkoba-di-hh-club-batam</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000087539.jpg</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Delegasi ekonomi dan perdagangan Hainan mengunjungi Thailand dan Indonesia untuk meningkatkan kerja sama</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:54:42 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Thailand, yang diselenggarakan bersama oleh Pemerintah Provinsi Hainan dan Dewan Investasi Thailand (Board of ...</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687151/delegasi-ekonomi-dan-perdagangan-hainan-mengunjungi-thailand-dan-indonesia-untuk-meningkatkan-kerja-sama</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/MOU-signing-ceremony.jpg</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Bank BSN salurkan donasi Rp81 ribu dari setiap finisher Lilawangsa Run</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:52:22 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Lhokseumawe (ANTARA) – Bank Syariah Nasional (BSN) mengonversikan setiap peserta yang berhasil menyelesaikan BSN ...</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687148/bank-bsn-salurkan-donasi-rp81-ribu-dari-setiap-finisher-lilawangsa-run</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-10.37.36.jpeg</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Kebakaran landa warteg dan bengkel di Tambora Jakbar</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:51:15 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda warteg dan bengkel di Jalan Prof. Dr. Latumenten, RT 08/RW 09 Angke, Tambora, Jakarta Barat, pada ...</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687144/kebakaran-landa-warteg-dan-bengkel-di-tambora-jakbar</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260810-WA0003.jpg</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Kemenhan gelar Ziarah Nasional Veteran di TMP Kalibata</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:48:29 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Kementerian Pertahanan menggelar agenda Ziarah Nasional Veteran di Taman Makam Pahlawan (TMP) Kalibata, Jakarta, ...</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687140/kemenhan-gelar-ziarah-nasional-veteran-di-tmp-kalibata</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000478880.jpg</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Ben Shelton singkirkan Fonseca untuk ke perempat final ATP Montreal</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:48:21 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Juara bertahan Ben Shelton melaju ke perempat final National Bank Open 2026 di Montreal setelah mengalahkan petenis ...</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687139/ben-shelton-singkirkan-fonseca-untuk-ke-perempat-final-atp-montreal</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_0158.jpeg</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Babel bentuk posko siber percepat tangani karhutla</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:45:45 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Kepulauan Bangka Belitung membentuk posko siber kebakaran hutan dan lahan (karhutla) serta ...</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687136/babel-bentuk-posko-siber-percepat-tangani-karhutla</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/siaga-karhutla2.jpg</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Pemkot Jaksel imbau warga tidak bakar sampah untuk cegah kebakaran</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:45:17 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Administrasi Jakarta Selatan (Pemkot Jaksel) mengimbau warga tidak membakar sampah untuk mencegah ...</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687133/pemkot-jaksel-imbau-warga-tidak-bakar-sampah-untuk-cegah-kebakaran</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/kebakaran-permukiman-padat-jakarta-210125-aaa-2.jpg</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Anggota DPR hadirkan rumah singgah warga kurang mampu di Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:43:47 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Anggota Komisi VII DPR RI Hendry Munief menghadirkan Rumah Singgah H. Hendry Munief di Pekanbaru, Riau, untuk membantu ...</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687129/anggota-dpr-hadirkan-rumah-singgah-warga-kurang-mampu-di-pekanbaru</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001228392.jpg</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga layani pengisian avtur pesawat berbadan lebar</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:38:21 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>PT Pertamina Patra Niaga sukses melayani pengisian 92.901 liter bakar avtur pesawat berbadan lebar Airbus A380 untuk ...</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687128/pertamina-patra-niaga-layani-pengisian-avtur-pesawat-berbadan-lebar</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000406618.jpg</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Kemenhut perkuat transformasi perdagangan karbon yang inklusif</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:35:26 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) memperkuat transformasi pemanfaatan hutan melalui perdagangan karbon yang inklusif dan ...</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687127/kemenhut-perkuat-transformasi-perdagangan-karbon-yang-inklusif</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/11/381554.jpg</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>BPS: Penurunan IPH terjadi di 21 provinsi pada awal Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:30:53 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pusat Statistik (BPS) Amalia Adininggar Widyasanti menyampaikan terdapat 21 provinsi yang mencatat ...</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687123/bps-penurunan-iph-terjadi-di-21-provinsi-pada-awal-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_3727.jpeg</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>PIHPS catat harga cabai rawit Rp72.400/kg dan telur ayam Rp31.650/kg</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:23:35 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Pusat Informasi Harga Pangan Strategis (PIHPS) Nasional, yang dikelola Bank Indonesia, mencatat harga komoditas cabai ...</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687121/pihps-catat-harga-cabai-rawit-rp72400-kg-dan-telur-ayam-rp31650-kg</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/B49D97F8-30F1-48EB-98C4-578F3657C8B5.jpeg</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Kamera drone AL Inggris dilaporkan kirim data ke China</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:23:17 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Otoritas Inggris melaporkan bahwa kamera yang terpasang pada kendaraan permukaan nirawak (drone) Angkatan ...</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687120/kamera-drone-al-inggris-dilaporkan-kirim-data-ke-china</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/thumbs_b_c_d3052a5bb086c343c3be611c43f27c7e.jpg</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Pemkot Jaksel minta jajaran tertibkan spanduk dan PKL jelang HUT RI</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:21:28 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Administrasi Jakarta Selatan (Pemkot Jaksel) meminta jajaran kecamatan hingga RW menerbitkan spanduk ...</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687119/pemkot-jaksel-minta-jajaran-tertibkan-spanduk-dan-pkl-jelang-hut-ri</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001020865.jpg</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Rupiah membaik seiring posisi cadangan devisa RI yang relatif kuat</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:20:03 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 87 poin atau 0,49 persen ...</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687116/rupiah-membaik-seiring-posisi-cadangan-devisa-ri-yang-relatif-kuat</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/12/30/nilai-tukar-rupiah-tertinggi-se-asia-26082024-dr-05.jpg</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Menlu Iran: negosiasi dengan AS ditunda hingga pelanggaran berakhir</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:16:16 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Menteri Luar Negeri Iran Seyed Abbas Araghchi mengatakan pada Minggu (9/8) bahwa dimulainya kembali negosiasi antara ...</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687113/menlu-iran-negosiasi-dengan-as-ditunda-hingga-pelanggaran-berakhir</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CjkinzN000001_20260810_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Hizbullah desak Lebanon tolak berunding dengan Israel</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:15:52 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Hizbullah mendesak pemerintah Lebanon menghentikan perundingan langsung dengan Israel setelah Kementerian Luar Negeri ...</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687109/hizbullah-desak-lebanon-tolak-berunding-dengan-israel</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/thumbs_b_c_f9d71cf33f41f6bf740072e5508bb800.jpg</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Hamas tegaskan setia pada rencana perdamaian Gaza meski ditolak Israel</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:11:07 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Kelompok pejuang Palestina Hamas menegaskan komitmen mematuhi peta jalan untuk melanjutkan tahapan kedua rencana ...</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687105/hamas-tegaskan-setia-pada-rencana-perdamaian-gaza-meski-ditolak-israel</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/20/gaza_1.jpg</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Brankas Besar Isi Ekstasi Disita dari Kelab Malam 'Sarang' Narkoba Batam</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:03:35 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Tim gabungan Bareskrim Polri menggerebek kelab malam di Batam, menyita brankas berisi ekstasi. 53 orang diamankan untuk penyelidikan lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611859/brankas-besar-isi-ekstasi-disita-dari-kelab-malam-sarang-narkoba-batam</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kelab-malam-di-batam-kepri-digerebek-atas-dugaan-peredaran-narkoba-1786334168714_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Harga Sejumlah Kebutuhan Pokok Turun, Jabar Alami Deflasi 0,05 Persen</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:57:02 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Angga Laraspati</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Deflasi 0,05% terjadi di Jawa Barat pada Juli 2026 akibat turunnya harga bahan pokok. Ekspor Jabar surplus USD 13,79 miliar, didorong oleh pasar AS.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611845/harga-sejumlah-kebutuhan-pokok-turun-jabar-alami-deflasi-0-05-persen</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/19/meski-harga-naik-warga-tetap-padati-pasar-1773900434094_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Pamit Main ke Ortu, 3 Remaja di Depok Malah Terciduk Hendak Tawuran</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:53:44 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Tiga remaja ditangkap saat hendak tawuran di Depok. Polisi menyita celurit dan melakukan penyelidikan setelah laporan warga.</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611843/pamit-main-ke-ortu-3-remaja-di-depok-malah-terciduk-hendak-tawuran</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/01/04/b21d558e-c595-4bba-8042-536fa6d359fc_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Jelang Sidang Kasus Haji Eks Menag Yaqut, KPK Lanjut Panggil Biro Travel</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:51:24 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>KPK terus panggil petinggi travel menjelang sidang eks Menag Yaqut terkait kasus korupsi kuota haji. Sidang perdana dijadwalkan 11 Agustus di Jakarta.</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611842/jelang-sidang-kasus-haji-eks-menag-yaqut-kpk-lanjut-panggil-biro-travel</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/01/28/82d1f3eb-c607-4d17-abb9-2e460a5b5400_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Satlantas Polresta Sidoarjo Raih Penilaian Terbaik Manajemen Rekayasa Lalin</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:48:25 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Satlantas Polresta Sidoarjo raih penghargaan terbaik dalam Manajemen Rekayasa Lalu Lintas selama Operasi Ketupat Semeru 2026.</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611838/satlantas-polresta-sidoarjo-raih-penilaian-terbaik-manajemen-rekayasa-lalin</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/satlantas-polresta-sidoarjo-meraih-penghargaan-manajemen-rekayasa-lalin-terbaik-pada-operasi-ketupat-semeru-2026-1786337288028_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Gerhana Matahari Total 12 Agustus 2026 Jam Berapa? Cek Waktunya!</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:48:21 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Kanya Anindita Mutiarasari</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Gerhana Matahari Total akan terjadi pada 12 Agustus 2026. Apakah bisa dilihat dari Indonesia? Simak infonya.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611837/gerhana-matahari-total-12-agustus-2026-jam-berapa-cek-waktunya</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/04/09/potret-memukau-gerhana-matahari-di-as-dan-meksiko_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Bromo Tutup Total Imbas Kebakaran, Begini Cara Refund dan Reschedule Tiket</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:47:14 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Muhammad Aminudin</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Gunung Bromo masih berlangsung, kunjungan ditutup. Wisatawan bisa refund atau jadwal ulang tiket hingga 31 Desember 2026.</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611835/bromo-tutup-total-imbas-kebakaran-begini-cara-refund-dan-reschedule-tiket</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/situasi-di-bromo-saat-petugas-gabungan-berjibaku-memadamkan-api-1786337171880_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Viral Runner Up Raka Jatim 2026 Minta Pacar Aborsi, Terancam Disanksi</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:41:18 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Faiq Azmi</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Viral dugaan runner up Raka Raki Jatim 2026, TFR, minta pacar aborsi. Ikatan Raka Raki Jatim akan menindak tegas dan Disbudpar siapkan sanksi pencabutan gelar.</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611826/viral-runner-up-raka-jatim-2026-minta-pacar-aborsi-terancam-disanksi</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/runner-up-raka-raki-jawa-timur-2026-diduga-minta-pacar-aborsi-ke-singapura-1786280246592_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Waka Komisi III DPR Apresiasi BNN Bongkar Penyelundupan 1,3 Ton Ketamin</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:41:16 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi III DPR Rano Alfath apresiasi BNN atas penggagalan penyelundupan 1,3 ton ketamin.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611825/waka-komisi-iii-dpr-apresiasi-bnn-bongkar-penyelundupan-1-3-ton-ketamin</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/09/rano-alfath-1746801301728_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Karhutla Bromo Meluas, Komisi IV DPR Minta SOP Penanganan Diperbaiki</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:25:19 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi IV DPR, Alex Indra Lukman, soroti kebakaran hutan di Bromo. Ia minta perbaikan SOP dan penggunaan teknologi canggih untuk penanganan.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611803/karhutla-bromo-meluas-komisi-iv-dpr-minta-sop-penanganan-diperbaiki</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/03/07/wakil-ketua-komisi-iv-dpr-alex-indra-lukman-dok-istimewaalex-indra-1741317786581_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>HNW Apresiasi Terbitnya Peraturan Menteri Agama tentang Ditjen Pesantren</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:20:20 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Hidayat Nur Wahid apresiasi PMA Nomor 16 Tahun 2026, menandai pembentukan Ditjen Pesantren untuk dukung lembaga keagamaan dan santri di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611796/hnw-apresiasi-terbitnya-peraturan-menteri-agama-tentang-ditjen-pesantren</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/wakil-ketua-mpr-ri-hidayat-nur-wahid-hnw-1786335516456_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Pakai Helikopter, TNI Evakuasi Warga dari Konflik Ugimba Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:18:07 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Lisye Sri Rahayu</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Koops TNI Habema evakuasi warga di Distrik Ugimba, Papua Tengah, menggunakan helikopter.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611794/pakai-helikopter-tni-evakuasi-warga-dari-konflik-ugimba-intan-jaya</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/tni-evakuasi-warga-dari-konflik-di-ugimba-intan-jaya-papua-tengah-1786335405371_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo Diperiksa Polisi Buntut Ajak Anak Promosi Vape Siang Ini</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:17:20 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya jadwalkan klarifikasi YouTuber Bigmo terkait ajakan anak di bawah umur mempromosikan vape. Pemeriksaan berlangsung siang ini.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611790/youtuber-bigmo-diperiksa-polisi-buntut-ajak-anak-promosi-vape-siang-ini</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/youtuber-bigmo-diadukan-ke-polisi-karena-diduga-mengeksploitasi-anak-dalam-siaran-langsung-doktangkapan-layar-medsos-1785590766503_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Pemotor di Sleman Rusak Palang Pintu Perlintasan Saat Kereta Hendak Melintas</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:08:56 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Adji G Rinepta</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Pemuda berinisial S (24) nekat merusak palang pintu perlintasan kereta api (KA) di Banyumeneng, Banyuraden, Gamping, Sleman. S sudah diamankan polisi.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611784/pemotor-di-sleman-rusak-palang-pintu-perlintasan-saat-kereta-hendak-melintas</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/petugas-memperbaiki-palang-pintu-perlintasan-kereta-api-ka-di-banyumeneng-banyuraden-gamping-sleman-1786332362331_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Kronologi 2 Pekerja Proyek Tertimpa Beton Turap Drainase di Jaktim</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:06:13 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Dua pekerja proyek normalisasi saluran air tertimpa beton turap di Jakarta Timur (Jaktim). Beton itu disebut tiba-tiba roboh dan menimpa korban.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611780/kronologi-2-pekerja-proyek-tertimpa-beton-turap-drainase-di-jaktim</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dua-pekerja-proyek-normalisasi-saluran-air-tertimpa-beton-turap-di-jakarta-timur-jaktim-beton-itu-disebut-tiba-tiba-roboh-dan--1786334668781_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Istri Korban KM Mutiara Ikhlas Suami Belum Ditemukan, Minta Kejelasan Manifes</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:02:24 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Praditya Fauzi Rahman</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Munideh, istri sopir logistik korban terbakarnya KMP Mutiara Sentosa 2, berjuang menuntut kejelasan data manifes. Dia ikhlas, namun tetap meminta penyelidikan.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611773/istri-korban-km-mutiara-ikhlas-suami-belum-ditemukan-minta-kejelasan-manifes</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Bang Jago Kehabisan Bensin Peras Pengendara di SPBU Ciwidey, Pelaku Ditangkap</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:58:43 +0700</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Yuga Hassani</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Polisi menangkap 'Bang Jago' yang memalak di SPBU Ciwidey. Aksinya viral di media sosial, pelaku ditangkap setelah melarikan diri ke Karawang.</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611761/bang-jago-kehabisan-bensin-peras-pengendara-di-spbu-ciwidey-pelaku-ditangkap</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/08/tangkapan-layar-video-viral-soal-aksi-premanisme-di-spbu-ciwidey-1786185016418_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ASN Bandung Barat Klarifikasi soal Singgung Fee Proyek Saat Live TikTok</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:56:43 +0700</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Whisnu Pradana</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>ASN tersebut pun meminta maaf dan menanti sanksi.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611759/asn-bandung-barat-klarifikasi-soal-singgung-fee-proyek-saat-live-tiktok</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/asn-kbb-yang-melakukan-live-tiktok-saat-jam-kerja-minta-maaf-1786272528570_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Bareskrim Gerebek Kelab Malam di Batam Diduga 'Sarang' Narkoba</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:56:34 +0700</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Bareskrim Polri menggerebek kelab malam di Batam yang diduga sarang narkoba. 32 orang diamankan, termasuk manajemen tempat hiburan malam.</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611758/bareskrim-gerebek-kelab-malam-di-batam-diduga-sarang-narkoba</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kelab-malam-di-batam-kepri-digerebek-atas-dugaan-peredaran-narkoba-1786334168574_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Balap Liar di Parung Bogor Dibubarkan Polisi, 3 Motor Diangkut</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:47:36 +0700</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Polisi membubarkan sekelompok pemotor yang diduga hendak balap liar di Jalan Raya Parung, Bogor, Jawa Barat (Jabar). Sebanyak tiga unit motor diamankan.</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611749/balap-liar-di-parung-bogor-dibubarkan-polisi-3-motor-diangkut</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/polisi-membubarkan-sekelompok-pemotor-yang-diduga-hendak-balap-liar-di-jalan-raya-parung-bogor-jawa-barat-jabar-sebanyak-tiga--1786333616485_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Bamsoet Apresiasi Inovasi Tiffney Tyra di Pilmapres 2026</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:41:24 +0700</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Bambang Soesatyo mengapresiasi Tiffney Tyara Setyoko, juara Pilmapres Nasional 2026. Inovasi Smart Febrile Patch-nya berpotensi bantu skrining penyakit infeksi.</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611730/bamsoet-apresiasi-inovasi-tiffney-tyra-di-pilmapres-2026</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bamsoet-apresiasi-inovasi-tiffney-tyra-di-pilmapres-2026-1786333238972.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Jadi Masalah Bertahun-tahun di Depok, Banjir di Bulak Barat Akhirnya Surut</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:22:34 +0700</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Banjir di Kampung Bulak Barat, Cipayung, Depok, akhirnya surut. Banjir rutin di sana menjadi masalah Kota Depok selama bertahun-tahun.</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611698/jadi-masalah-bertahun-tahun-di-depok-banjir-di-bulak-barat-akhirnya-surut</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bulak-barat-1786331924537_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Waka MPR Dorong Pengakuan Hukum bagi Masyarakat Adat di Tanah Air</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:20:52 +0700</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR RI Lestari Moerdijat serukan pengakuan masyarakat adat di Indonesia. Dia menekankan pentingnya pengesahan RUU MHA untuk perlindungan hak mereka.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611690/waka-mpr-dorong-pengakuan-hukum-bagi-masyarakat-adat-di-tanah-air</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/28/wakil-ketua-mpr-ri-lestari-moerdijat-1761654592023_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Hakim Tolak Praperadilan Tersangka Kuota Haji Asrul Azis Terkait Penggeledahan</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:17:42 +0700</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Hakim menolak praperadilan terkait penggeledahan yang diajukan Ketua Umum Asosiasi Kesthuri Asrul Azis Taba dalam kasus korupsi kuota haji.</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611686/hakim-tolak-praperadilan-tersangka-kuota-haji-asrul-azis-terkait-penggeledahan</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/sidang-praperadilan-asrul-azis-muliadetikcom-1786331809679_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Saepul Ajukan Resign ke Bos Piscok Tepat di Hari Pembunuhan Pria Depok</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:59:05 +0700</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Pemilik usaha piscok di Depok menjelaskan bahwa Saepul, tersangka mutilasi, bukan lagi karyawannya. Saepul ajukan resign tepat di hari ia membunuh dan mutilasi.</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611661/saepul-ajukan-resign-ke-bos-piscok-tepat-di-hari-pembunuhan-pria-depok</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-pembunuhan-dan-mutilasi-pria-di-pancoran-mas-depok-ditangkap-subdit-resmob-polda-metro-jaya-1785915706525_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Siap-siap! Truk Obesitas Kena Denda Mulai Januari 2027</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:58:17 +0700</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Kemenhub luncurkan ETLE HUB untuk awasi truk ODOL. Sistem ini bertujuan wujudkan Zero ODOL 2027 dengan sanksi tegas mulai 1 Januari 2027.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611848/siap-siap-truk-obesitas-kena-denda-mulai-januari-2027</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menteri-perhubungan-menhub-dudy-purwagandhi-1786337809727_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Harga Daging Ayam Naik di 188 Daerah, Ini Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:39:22 +0700</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Ada 188 kabupaten/kota di Indonesia yang mengalami kenaikan harga daging ayam ras.</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611822/harga-daging-ayam-naik-di-188-daerah-ini-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/12/daging-ayam-mentah-1762926625592_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Bos Danantara Bicara soal Rencana IPO BUMN</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:30:21 +0700</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Proses pencatatan saham di pasar modal ini tengah berjalan di Danantara Asset Management (DAM).</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8611808/bos-danantara-bicara-soal-rencana-ipo-bumn</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/danantara-pandu-sjahrir-1784184162881_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Genjot Pasokan Energi di Jatim, Pertamina Optimalkan Potensi Gas Pangkah</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:26:24 +0700</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Pertamina optimalkan Wilayah Kerja Pangkah di Gresik untuk meningkatkan produksi minyak dan gas. Fokus pada eksplorasi dan pemanfaatan infrastruktur yang ada.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8611804/genjot-pasokan-energi-di-jatim-pertamina-optimalkan-potensi-gas-pangkah</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/genjot-pasokan-energi-di-jatim-pertamina-optimalkan-potensi-gas-pangkah-1786334925952_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Danantara soal Beli Saham BEI: Masih Proses</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:38:11 +0700</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Investasi (BPI) Daya Anagata Nusantara (Danantara) membenarkan telah mengajukan pembelian saham Bursa Efek Indonesia (BEI).</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8611723/danantara-soal-beli-saham-bei-masih-proses</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/chief-investment-officer-cio-bpi-danantara-pandu-sjahrir-1786332950999_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Pesawat Raksasa Airbus A380 Mendarat di Soetta, Isi 92.901 Liter Avtur</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:33:01 +0700</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga sukses isi 92.901 liter avtur ke Airbus A380 Emirates di Soekarno-Hatta, menunjukkan kesiapan layanan aviasi untuk pesawat besar.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8611720/pesawat-raksasa-airbus-a380-mendarat-di-soetta-isi-92-901-liter-avtur</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/pesawat-raksasa-1786332529825_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Produsen Buru-buru Tarik Stok, Bapanas Lanjut Usut Beras Fortifikasi Bermasalah</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:28:52 +0700</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Bapanas memastikan tindakan tegas pemerintah dalam pengawasan terkait peredaran beras fortifikasi atau beras dengan klaim gizi, masih terus berlanjut.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611714/produsen-buru-buru-tarik-stok-bapanas-lanjut-usut-beras-fortifikasi-bermasalah</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/28/pemerintah-pastikan-beras-hingga-daging-ayam-dalam-kondisi-surplus-1785222178147_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>RI Butuh Investasi Rp 8.705 T Tahun Depan, dari Mana Sumbernya?</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:21:07 +0700</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Keuangan (Wamenkeu), Juda Agung, menyebut Indonesia membutuhkan investasi besar di tahun depan.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8611689/ri-butuh-investasi-rp-8-705-t-tahun-depan-dari-mana-sumbernya</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/wakil-menteri-keuangan-wamenkeu-juda-agung-1786331256785_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Tinjau Jembatan Lumut Aceh, Wapres Gibran Dorong Penguatan Konektivitas</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:59:08 +0700</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Wakil Presiden Gibran meninjau proyek rehabilitasi Jembatan Lumut di Aceh Tengah. Proyek ini penting untuk infrastruktur dan ekonomi masyarakat setempat.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8611662/tinjau-jembatan-lumut-aceh-wapres-gibran-dorong-penguatan-konektivitas</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/wapres-gibran-tinjau-proyek-rehab-jembatan-lumut-garapan-hk-1786330539579.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Detail Pesta Pernikahan Dea Annisa dan Mazaki Ahmad yang Intimate</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:08:31 +0700</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Artis Dea Annisa resmi menikah dengan Mazaki Ahmad, Minggu (9/8/2026). Ini potret detail pernikahan Dea dan Zaki.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611864/detail-pesta-pernikahan-dea-annisa-dan-mazaki-ahmad-yang-intimate</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dea-annisa-1786337547046_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Gisel Pilih Jadi Bestie ke Gempi Ketimbang Interogasi</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:41:32 +0700</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Pingkan Anggraini</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Gisella Anastasia berbagi pengalaman mengasuh putrinya, Gempi, di era digital. Ia menekankan pentingnya komunikasi, dukungan emosional, dan gizi seimbang.</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611828/gisel-pilih-jadi-bestie-ke-gempi-ketimbang-interogasi</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/24/gisel-1782259166541_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Celine Evangelista Perlihatkan Panorama Bromo yang Gak Terimbas Kebakaran</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:05:37 +0700</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Celine Evangelista membawa anak-anaknya liburan ke kawasan Bromo, Jawa Timur. Celine memperlihatkan Bromo yang gak terimbas kebakaran.</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611629/celine-evangelista-perlihatkan-panorama-bromo-yang-gak-terimbas-kebakaran</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/celine-evangelista-1786328180330_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Davina Karamoy Rasakan Jadi Pelari Kalcer</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:26:15 +0700</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Artis Davina Karamoy mencoba lari. Ia meluapkan perasaannya.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611692/davina-karamoy-rasakan-jadi-pelari-kalcer</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/davina-karamoy-1786331881173_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Feby Febiola Comeback Akting Usai Belasan Tahun Vakum: Pressure Banget</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:05:47 +0700</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Aktris Feby Febiola comeback berakting usai vakum selama belasan tahun dari dunia akting. Kembali berakting di depan kamera Feby merasa ada tekanan.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611547/feby-febiola-comeback-akting-usai-belasan-tahun-vakum-pressure-banget</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/01/feby-febiola-1775025294009_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Penampakan Horor Hutan Kanada Dilahap Kobaran Api Kebakaran Hebat</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:11:35 +0700</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Kebakaran hebat melanda hutan Bald Range, Kanada, hingga memaksa sekitar 20 ribu orang dievakuasi pada Sabtu (8/8).</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810071726-139-1390413/penampakan-horor-hutan-kanada-dilahap-kobaran-api-kebakaran-hebat</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/api-lahap-hutan-bald-range-20-ribu-warga-dievakuasi-1786321531587_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>PM Malaysia Anwar Ibrahim Masuk Rumah Sakit</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:27:18 +0700</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Perdana Menteri Malaysia Anwar Ibrahim dilaporkan masuk rumah sakt pada Senin (10/8) usai bertemu Raja Malaysia Sultan Ibrahim Iskandar pada Sabtu (8/8).</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810111555-106-1390499/pm-malaysia-anwar-ibrahim-masuk-rumah-sakit</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/09/06/pm-malaysia-anwar-ibrahim_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Asosiasi Penerbang Malaysia soal Pilot Bawa Narkoba di RI: Aib Besar!</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:05:25 +0700</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Presiden Asosiasi Penerbang Malaysia, Kapten Ab Manan Mansor mengatakan pilot Mohd Saufi yang ditangkap di RI karena bawa narkoba adalah aib besar.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810101703-106-1390463/asosiasi-penerbang-malaysia-soal-pilot-bawa-narkoba-di-ri-aib-besar</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/detik-detik-pilot-maskapai-malaysia-ditangkap-bawa-sabu-1785750021111_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Amunisi Menipis Lawan Iran, AS Tekan Produsen Senjata Genjot Produksi</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:35:05 +0700</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Amerika Serikat menekan perusahaan produsen senjata untuk menggenjot produksi karena amunisi hingga rudal semakin menipis lawan Iran.</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810093359-134-1390449/amunisi-menipis-lawan-iran-as-tekan-produsen-senjata-genjot-produksi</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/04/22/pabrik-amunisi-as-banjir-pesanan-penuhi-kebutuhan-perang-ukraina-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Sultan Brunei Cabut Gelar Kerajaan Menantu karena Perilaku Tak Pantas</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:05:30 +0700</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Sultan Brunei cabut gelar kerajaan menantu perempuannya karena dinilai mencoreng nama baik institusi kerajaan.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810093716-106-1390450/sultan-brunei-cabut-gelar-kerajaan-menantu-karena-perilaku-tak-pantas</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/08/31/sultan-hassanal-bolkiah-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Keluarga Netanyahu Tuntut Sumpah Setia Semua Staf Kantor PM, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:35:05 +0700</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Keluarga Benjamin Netanyahu menuntut seluruh staff perdana menteri untuk menandatangani sumpah setia.</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810085323-120-1390435/keluarga-netanyahu-tuntut-sumpah-setia-semua-staf-kantor-pm-ada-apa</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/10/07/8593b370-5778-445c-a49a-305e75d51d84_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Tolak 15 Poin Usul Trump, Netanyahu Diam-diam Setuju Rekonstruksi Gaza</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:05:30 +0700</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>PM Israel Benjamin Netanyahu dikabarkan diam-diam menyetujui rekonstruksi Jalur Gaza rencana Board of Peace (BoP) meski menolak 15 poin usulan Donald Trump.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810083409-120-1390432/tolak-15-poin-usul-trump-netanyahu-diam-diam-setuju-rekonstruksi-gaza</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/08/israel-conflict-memorial-1780888036572_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Iran Ungkap Isi Pertemuan Terbaru Pezeshkian dan Mojtaba Khamenei</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:36:03 +0700</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Presiden Iran Pezeshkian disebut telah bertemu dengan Pemimpin Tertinggi Mojtaba Khamenei menjelang dimulainya tahun ketiga masa jabatannya pada akhir Juli ini.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810080916-120-1390427/iran-ungkap-isi-pertemuan-terbaru-pezeshkian-dan-mojtaba-khamenei</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/10/mojtaba-khamenei-1778379376204_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Pilot Ditangkap di RI Gegara Bawa Narkoba, Raja Malaysia Buka Suara</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:05:15 +0700</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Raja Malaysia Sultan Ibrahim memerintahkan pihak berwenang memperketat pengawasan di seluruh bandara hingga perbatasan negaranya.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810074728-106-1390419/raja-malaysia-minta-perketat-bandara-buntut-pilot-bawa-narkoba-di-ri</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/07/20/penobatan-sultan-ibrahim-iskandar-sebagai-raja-di-malaysia-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Apa Itu Pakta Pertahanan Makkah yang Diteken Saudi, Pakistan dan Turki?</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:35:20 +0700</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Arab Saudi, Pakistan, dan Turki menandatangani pakta pertahanan bersama di tengah meningkatnya ketegangan di Timur Tengah.</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810065204-120-1390408/apa-itu-pakta-pertahanan-makkah-yang-diteken-saudi-pakistan-turki</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/08/arab-saudi-pakistan-dan-turki-teken-pakta-pertahanan-bersama-1786186719034_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Pengusiran Besar-besaran, Kenapa Kanada Deportasi 3.323 Imigran India?</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:05:25 +0700</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Pemerintah Kanada memutuskan untuk melakukan deportasi sebanyak 3.323 imigran yang merupakan warga negara India.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810064346-134-1390407/pengusiran-besar-besaran-kenapa-kanada-deportasi-3323-imigran-india</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2017/02/21/a1254691-a0b0-4c28-83bd-5328ae7afa7b_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Tenaga Kesehatan dan Ahli Teknologi Eksodus dari Israel, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:35:15 +0700</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Warga kaya Israel, terutama pekerja di bidang teknologi dan perawatan kesehatan eksodus meninggalkan negeri zionis itu dalam jumlah yang meningkat tajam</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810061739-120-1390400/tenaga-kesehatan-ahli-teknologi-eksodus-dari-israel-ada-apa</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/10/10/bandara-ben-gurion-di-israel_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Api Hanguskan Puluhan Rumah di Empat Lawang Sumsel, Kerugian Capai Miliaran Rupiah</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:05:38 +0700</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Kebakaran hebat menghanguskan 20 rumah warga di Desa Landur, Empat Lawang, akibat dugaan korsleting listrik. Kerugian ditaksir mencapai Rp4 miliar.</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866248/api-hanguskan-puluhan-rumah-di-empat-lawang-sumsel-kerugian-capai-miliaran-rupiah</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Gqvc_cxUf4WNuq7lwHsnqabMcGU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kebakaran-di-kabupaten-empat-lawang.jpg</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Daripada Lancarkan Serangan, Trump Beri Isyarat Siap Mengandalkan Tekanan Ekonomi ke Iran</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:56:39 +0700</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Donald Trump disebut akan mengandalkan peningkatan tekanan ekonomi daripada langsung melancarkan serangan militer baru.</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866247/daripada-lancarkan-serangan-trump-beri-isyarat-siap-mengandalkan-tekanan-ekonomi-ke-iran</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fndRnDnJM2a6L6JVrj7RP-FEAjc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penutupan-Selat-Hormuz-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Pemerintah Resmi Cairkan Rp 18,9 Triliun ke 546 Pemda, Cegah Badai PHK P3K</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:55:36 +0700</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian mengumumkan pencairan dana sebesar Rp18,9 triliun untuk 546 pemerintah daerah.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866246/pemerintah-resmi-cairkan-rp-189-triliun-ke-546-pemda-cegah-badai-phk-p3k</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fCQdKpDn6HdMrLdPNWTvyCszidk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/defisit-anggaran-pemda-karena.jpg</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 10 SMA Kurikulum Merdeka Halaman 152 Edisi Revisi: Aktivitas 3.6</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:54:20 +0700</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban IPS kelas 10 SMA Kurikulum Merdeka Halaman 152 Edisi Revisi: Aktivitas 3.6.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866245/kunci-jawaban-ips-kelas-10-sma-kurikulum-merdeka-halaman-152-edisi-revisi-aktivitas-36</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DSga7wM08_0kQh0WIsFqhAjs6F8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Simak-kunci-jawaban-Informatika-Kelas-5-Halaman-139.jpg</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>30 Ide Lomba 17 Agustus Anak yang Seru dan Edukatif, Cocok untuk Perayaan HUT RI</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:52:50 +0700</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Simak kumpulan ide lomba 17 Agustus untuk anak-anak yang seru dan edukatif, mulai dari lomba balap kelereng hingga tebak gambar pahlawan.</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866244/30-ide-lomba-17-agustus-anak-yang-seru-dan-edukatif-cocok-untuk-perayaan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pSvKFu2La6RfqSpy0DkTfaLkPaw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/lomba-hut-kemerdekaan-ke-78-ri-di-apartemen-kalibata-city_20230818_160716.jpg</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu Personal - HRVY: Beautiful but She Dangerous</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:51:49 +0700</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Simak lirik dan terjemahan lagu Personal yang dipopulerkan oleh penyanyi asal Inggris, Harvey Leigh Cantwell atau dikenal sebagai HRVY.</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866243/terjemahan-lirik-lagu-personal-hrvy-beautiful-but-she-dangerous</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zLN77GXG_MWcQ27NDqNvGgp-QJs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-musik-ilustrasi-lirik-ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Jangan Panik Dulu jika Hasil Lab Abnormal saat MCU, Kenali Beberapa Faktor Ini Sebelum Takut</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:50:44 +0700</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Inilah beberapa faktor yang mempengaruhi hasil lab Medical Check-Up (MCU) menjadi abnormal. Jangan panik dulu, bukan tentu hasil yang buru.</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866242/jangan-panik-dulu-jika-hasil-lab-abnormal-saat-mcu-kenali-beberapa-faktor-ini-sebelum-takut</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ReM1Sj5n8MWiHA7Cby0Cx_9nzjo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Cek-Kesehatan-Pasca-Bulan-Puasa_20250410_173604.jpg</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Raih Penghargaan Kemanusiaan, Natasha Dematra: Kita Bisa Membuat Dunia Menjadi Lebih Baik</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:45:19 +0700</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Natasha Dematra raih Mother Teresa Award atas dedikasi mempromosikan perdamaian, toleransi, kemanusiaan, dan pemberdayaan generasi muda.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866241/raih-penghargaan-kemanusiaan-natasha-dematra-kita-bisa-membuat-dunia-menjadi-lebih-baik</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zvFHe1qJf9CqNUw3d46jnetoSQ8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Natasha-Dematra-menerima-Mother-Teresa-Award.jpg</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Hamas Terima Rencana 15 Poin Trump, Netanyahu Tolak: Gaza-Tepi Barat Tak Akan Jadi Negara Palestina</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:38:48 +0700</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Hamas menerima peta jalan 15 poin Trump untuk Gaza, tetapi Netanyahu menolaknya dan menegaskan tak ada negara Palestina selama ia berkuasa.</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866240/hamas-terima-rencana-15-poin-trump-netanyahu-tolak-gaza-tepi-barat-tak-akan-jadi-negara-palestina</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/G87T1T8FbGwfz8d70IG2pezr-vU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Perdana-Menteri-Benjamin-Netanyahu-8778999800.jpg</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Dipicu Uang Rp20 Ribu, Wanita di Palembang Laporkan Pacar atas Dugaan Penganiayaan</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:38:43 +0700</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Perempuan RO (24) lapor pacarnya HM ke Polrestabes Palembang atas dugaan penganiayaan dipicu persoalan uang Rp20 ribu via DANA.</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866239/dipicu-uang-rp20-ribu-wanita-di-palembang-laporkan-pacar-atas-dugaan-penganiayaan</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MZaQZ8ilhEA23NOJih870Ttf82U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-penganiayaan-siswa.jpg</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Jadwal PSG vs Aston Villa di Piala Super Eropa 2026: Les Parisiens Coba Ikuti Jejak Real Madrid</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:36:23 +0700</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>PSG dan Aston Villa siap membuka musim baru dengan duel perebutan Piala Super Eropa 2026 di Austria tengah pekan ini.</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866238/jadwal-psg-vs-aston-villa-di-piala-super-eropa-2026-les-parisiens-coba-ikuti-jejak-real-madrid</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0HFHC_4nUJUGcCjvIZFFMmckvUM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Para-pemain-Paris-Saint-Germain-PSG-merayakan-gelar-juara-Liga-Champions.jpg</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Trump Klaim Kesepakatan Iran Dekat, Teheran Bantah, Pengamat: Produksi Drone Digenjot 3 Kali Lipat</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:35:52 +0700</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Trump klaim kesepakatan Iran dekat, tetapi Teheran membantah perang segera berakhir dan justru menggenjot produksi drone 3 kali lipat.</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866237/trump-klaim-kesepakatan-iran-dekat-teheran-bantah-pengamat-produksi-drone-digenjot-3-kali-lipat</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pd58Lh0QZkuUPrM04LfPl7UxG4o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/residen-AS-Donald-Trump-Senin-27-Juli-2026-Foto-Res.jpg</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro Segera Hadir, Ini 12 Fitur Baru yang Dikabarkan Bakal Dibawa Apple</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:34:27 +0700</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro segera dirilis tahun ini. Menurut rumor, setidaknya ada 12 fitur baru yang dikabarkan bakal dibawa penerus iPhone 17 tersebut.</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/techno/7866236/iphone-18-pro-segera-hadir-ini-12-fitur-baru-yang-dikabarkan-bakal-dibawa-apple</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/EkaKJmACYZLOgeDv2PpgKh8CKQ4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Apple-terbaru-iPhone-18-Pro.jpg</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Hadiah Tak Biasa Prilly Latuconsina untuk Ulang Tahun Kekasih, Tanam 270 Pohon Kopi, Ini Maknanya</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:33:35 +0700</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Prilly Latuconsina beri hadiah tak biasa untuk kekasihnya, Omara Esteghlal.Kado ulang tahun yang diberikan bukan barang mewah  tapi tanaman kopi.</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866235/hadiah-tak-biasa-prilly-latuconsina-untuk-ulang-tahun-kekasih-tanam-270-pohon-kopi-ini-maknanya</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/F94d0_Gl8S03yLKr0Iq1Gy5BsSY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prilly-Latuconsina-dan-Omara-Esteghlal.jpg</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ShopeePay dan SPayLater Gelar Kompetisi Desain Batik, Dorong Kreativitas dan Pemberdayaan UMKM</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:57:02 +0700</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Sebagai layanan pembayaran digital dan layanan keuangan, ShopeePay dan SPayLater terus memperkuat komitmennya dalam mendukung pertumbuhan UMKM.</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866234/shopeepay-dan-spaylater-gelar-kompetisi-desain-batik-dorong-kreativitas-dan-pemberdayaan-umkm</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/o8oZK-EvdcxR80wS4dmhqBxLlGQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Shopee-Tribunnews_070826.jpg</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Cerita Borgol Tahanan Dilepas demi Bisa Peluk Anak dan Istrinya</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:24:27 +0700</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Viral aksi polisi di Polda Kaltim melepas borgol tahanan agar bisa memeluk anak dan istrinya. Tindakan humanis ini menuai banyak pujian.</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866233/cerita-borgol-tahanan-dilepas-demi-bisa-peluk-anak-dan-istrinya</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yxBCZcGMMEvpNScjmfowF9Sx-z8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/polisi-lepas-borgol-tahanan-sdfv.jpg</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Menakar Empat Arus Kekuatan di Luar Istana dalam Peta Politik Menuju 2029</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:24:14 +0700</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Empat arus kekuatan politik di luar istana jadi tantangan besar bagi Prabowo menuju 2029, ujian konsolidasi dan kepercayaan publik.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/tribunners/7866232/menakar-empat-arus-kekuatan-di-luar-istana-dalam-peta-politik-menuju-2029</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/JA5ve1DLrNRur56KMm9iJ5c6JIk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ilustrasi-pemilu1.jpg</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 10 SMA Kurikulum Merdeka Hal 151 Edisi Revisi: Konsep Diakronis Sinkronis</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:24:02 +0700</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban IPS kelas 10 SMA Kurikulum Merdeka Halaman 151 Edisi Revisi: Konsep Diakronis Sinkronis.</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866231/kunci-jawaban-ips-kelas-10-sma-kurikulum-merdeka-hal-151-edisi-revisi-konsep-diakronis-sinkronis</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/U9U0Ezm2sPloSaaCbS7kqX3m2cw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/suasana-hari-pertama-pembelajaran-tatap-muka-ptm-terbatas-di-kota-bogor-senin-18102021.jpg</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Youtuber Bigmo Diperiksa Terkait Kasus Dugaan Eksplotasi Anak Hari Ini di Polda Metro Jaya</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:23:32 +0700</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>YouTuber Muhammad Jannah alias Bigmo akan diperiksa terkait kasus dugaan eksploitasi anak dalam promosi produk rokok elektronik atau vape.</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866230/youtuber-bigmo-diperiksa-terkait-kasus-dugaan-eksplotasi-anak-hari-ini-di-polda-metro-jaya</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kVJ1JVg63OmX06VPzX6uBJAdK7g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bigmo-apa.jpg</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Hasil Sumur Baru Positif, Pertamina Perkuat Eksplorasi Migas di Wilayah Pangkah</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:23:17 +0700</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Di tengah kebutuhan energi industri yang terus tumbuh, Wilayah Kerja Pangkah di Gresik, Jawa Timur, dinilai berpeluang untuk menghasilkan gas bumi.</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pertamina/7866229/hasil-sumur-baru-positif-pertamina-perkuat-eksplorasi-migas-di-wilayah-pangkah</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-jm-DITicXhI5vDGtjf-7RCfsnA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pertamina-10082026.jpg</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Indeks Keyakinan Konsumen Turun pada Juli 2026, Daya Beli Lesu?</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Bank Indonesia (BI) merilis data Indeks Keyakinan Konsumen (IKK) pada Juli 2026 tercatat berada di angka 116,8, menurun dibandingkan dengan IKK pada bulan sebelumnya sebesar 117,8. Capaian...</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjfhg423/indeks-keyakinan-konsumen-turun-pada-juli-2026-daya-beli-lesu</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/025447800-1781348161-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ETF Emas Kantongi Kesesuaian Syariah, Bisa Jadi Alternatif Investasi</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Exchange Traded Fund (ETF) emas resmi diluncurkan di pasar modal Indonesia pada Senin pagi. Instrumen tersebut telah memperoleh kesesuaian prinsip syariah berdasarkan fatwa Dewan Syariah Nasional Majelis...</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjdzt423/etf-emas-kantongi-kesesuaian-syariah-bisa-jadi-alternatif-investasi</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260810113258-698.png</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Investor Pasar Modal Tembus 30,27 Juta, OJK Tekankan Integritas</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:21:18 +0700</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Jumlah investor pasar modal Indonesia telah mencapai 30,27 juta single investor identification (SID) hingga Agustus 2026. Otoritas Jasa Keuangan (OJK) menilai pertumbuhan tersebut perlu diikuti penguatan integritas...</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjdfi423/investor-pasar-modal-tembus-3027-juta-ojk-tekankan-integritas</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/kehadiran-presiden-prabowo-subianto-dinanti-di-pembukaan-perdagangan-bei_251231133318-629.jpeg</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Potensi Besar Gas Pangkah, Pertamina Dorong Produksi Gas Bumi untuk Industri Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:01:59 +0700</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, GRESIK -- Di tengah kebutuhan energi industri yang terus tumbuh, Pertamina melihat Wilayah Kerja Pangkah di Gresik, Jawa Timur (Jatim), bukan sekadar aset migas yang sudah berproduksi. 
+Kawasan...</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjcjb472/potensi-besar-gas-pangkah-pertamina-dorong-produksi-gas-bumi-untuk-industri-jawa-timur</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pertamina-menilai-wilayah-kerja-pangkah-gresik-jawa-timur-menyimpan_260810110007-798.jpeg</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Trump Isyaratkan Peralihan ke Tekanan Ekonomi terhadap Iran</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:34:23 +0700</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, WASHINGTON -- Presiden Amerika Serikat (AS) Donald Trump, Ahad (9/8/2026), mengisyaratkan kesiapan negaranya untuk mengandalkan tekanan ekonomi yang terus meningkat terhadap Iran, alih-alih segera melancarkan operasi militer baru, menurut...</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjb9b423/trump-isyaratkan-peralihan-ke-tekanan-ekonomi-terhadap-iran</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260708182638-646.png</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Juru Parkir Paksa Pemotor Bayar Rp 5 Ribu, Modus Beri Karcis Kedaluwarsa</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:09:56 +0700</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Juru parkir itu ditangkap kepolisian setelah korban melaporkan aksi pelaku. Hasil pemeriksaan, juru parkir itu positif narkoba.</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266080/juru-parkir-paksa-pemotor-bayar-rp-5-ribu-modus-beri-karcis-kedaluwarsa</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/P6yg3dWGU6mz0sJGtfBONfdTQ10=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320163/original/099167800_1786338586-71534.jpg</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo Diperiksa Polisi Siang Ini</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Bigmo melalui kuasa hukumnya memastikan akan hadir.</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266069/youtuber-bigmo-diperiksa-polisi-siang-ini</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/7XEaacjnNEYkRCn6aMu0EhXedMo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9315071/original/067471800_1785826081-95a329d9-bbfa-4973-8ee5-53fc7f4dc1f2.jpg</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>546 Daerah Dapat Tambahan Anggaran, Mendagri Beberkan Nasib Gaji PPPK</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:53:08 +0700</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Dana ini menjamin pembayaran gaji PPPK lancar, dan sisa anggaran dapat dimanfaatkan untuk pembangunan mendesak di wilayah.</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266066/546-daerah-dapat-tambahan-anggaran-mendagri-beberkan-nasib-gaji-pppk</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/LukoYBUSnDOQa7XdOg56BWMS6eA=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320140/original/004542800_1786337559-761905c4-1471-44da-a21e-a0db4cf27294.jpg</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Layanan Posyandu Jaga Kesehatan Balita di Aceh</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:21:24 +0700</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Sejumlah bayi mengikuti pemeriksaan kesehatan bulanan di Pos Pelayanan Terpadu (Posyandu) di Banda Aceh, Senin, 10 Agustus 2026. Dalam kegiatan tersebut, petugas kesehatan memberikan suplemen vitamin A sebagai bagian dari layanan pemenuhan kebutuhan kesehatan anak. Posyandu juga menyediakan penimbangan balita, pemantauan pertumbuhan dan perkembangan, imunisasi, pemeriksaan ibu hamil, serta penyuluhan mengenai gizi. Pelayanan tersebut menjadi salah satu upaya menjaga kesehatan anak dan mendukung pencegahan stunting melalui pemantauan sejak dini.</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8266036/layanan-posyandu-jaga-kesehatan-balita-di-aceh</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/rKYSxKj3zCzVtVl0qmyuUywxr_U=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320103/original/034260000_1786335675-pos1.jpg</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Mulai 17 Agustus, Urus Balik Nama Sertifikat Tanah Maksimal 10 Hari</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:28:35 +0700</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Tahap awal kebijakan ini akan diterapkan di 17 kabupaten/kota.</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266001/mulai-17-agustus-urus-balik-nama-sertifikat-tanah-maksimal-10-hari</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ol3kyth2VvFEUPy_ldqNBhw1N_Y=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320034/original/073447200_1786333008-c3de2af6-a756-4359-8e19-41568f4252f6.jpg</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>KSOP Janji Sanksi Kapal yang Angkut Rombongan Artis Jesicca Mila ke Pulau Padar</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:18:51 +0700</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Kapal yang memuat rombongan artis Jessica Mila diduga melanggar maklumat KSOP karena berlayar ke Pulau Padar, Labuan Bajo</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/10/121804578/ksop-janji-sanksi-kapal-yang-angkut-rombongan-artis-jesicca-mila-ke-pulau</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/z1HTC8s-9_hIBY1u7RUn8FhLpNY=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/03/30/69ca23d905933.png</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Ketika Dukungan Iran kepada Palestina Masuk ke Meja Perundingan</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:18:51 +0700</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Politik Iran terhadap Palestina berada di persimpangan antara prinsip ideologis, kepentingan strategis, dan kebutuhan diplomasi.</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/10/120300470/ketika-dukungan-iran-kepada-palestina-masuk-ke-meja-perundingan</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/KZ1SO18nwHzx-x-l6KsMlWZXbJ4=/0x0:2000x1333/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2025/11/02/6906be8a7e273.jpg</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Sering Heartburn Saat Deadline? Awas Kebiasaan Ngopi dan Nunda Makan Bikin Asam Lambung</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:18:51 +0700</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Awas, kebiasaan nunda makan dan konsumsi kopi berlebih bisa jadi sinyal GERD. Simak penjelasannya bersama pakar Mayapada Hospital Jakarta Timur.</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>https://health.kompas.com/read/26H10114638068/sering-heartburn-saat-deadline-awas-kebiasaan-ngopi-dan-nunda-makan-bikin-asam</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/27HzQcC-Bf88CdDLXdh4CHrIGSc=/0x0:1536x1024/1200x675/filters:watermark(data/photo/2026/01/30/697c819f9c086.png,0,-0,1)/data/photo/2026/08/10/6a794e85dc557.png</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I202"/>
+  <autoFilter ref="A1:I327"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$327</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$485</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I327"/>
+  <dimension ref="A1:I485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -15806,8 +15806,7436 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Timnas bola basket putra targetkan lolos dari fase grup AG 2026</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:04:07 +0700</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Tim nasional (timnas) bola basket putra Indonesia menargetkan untuk lolos dari fase penyisihan grup Asian Games (AG) ...</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687373/timnas-bola-basket-putra-targetkan-lolos-dari-fase-grup-ag-2026</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/07/30/19.jpg</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>OJK: Perdagangan karbon bagian dari ekosistem keuangan berkelanjutan</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:03:07 +0700</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) menilai perdagangan karbon merupakan salah satu bagian dari ekosistem keuangan ...</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687372/ojk-perdagangan-karbon-bagian-dari-ekosistem-keuangan-berkelanjutan</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/24/Target-Proyek-Karbon-Biru-Indonesia-Pada-2027-230326-Add-2.jpg</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>PT HCM Ads Media luncurkan mobil videotron bergerak untuk publikasi</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:02:35 +0700</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Komisaris PT HCM Ads Media Suryanto (kanan) bersama Direktur Utama PT HCM Ads Media Prasetyo Utomo (ketiga kiri), ...</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687368/pt-hcm-ads-media-luncurkan-mobil-videotron-bergerak-untuk-publikasi</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Peluncuran-mobile-videotron-bergerak-untuk-publikasi-100826-Bay-2.jpg</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Wamen ATR/BPN libatkan Tim Ekspedisi Patriot petakan persoalan tanah</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:02:34 +0700</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) melibatkan Tim Ekspedisi Patriot (TEP) 2026 ...</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687364/wamen-atr-bpn-libatkan-tim-ekspedisi-patriot-petakan-persoalan-tanah</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000674321.jpg</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>PKKMB UB fokus bina kesehatan mental 17.300 mahasiswa baru</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:01:56 +0700</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Pengenalan Kehidupan Kampus bagi Mahasiswa Baru (PKKMB) Universitas Brawijaya (UB) memfokuskan pada kesehatan mental ...</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687360/pkkmb-ub-fokus-bina-kesehatan-mental-17300-mahasiswa-baru</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/rektor3.jpeg</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Inggris kucurkan dana Rp3,12 triliun kembangkan kendaraan nol emisi</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:00:29 +0700</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Inggris mengumumkan pendanaan hampir 130 juta poundsterling (175 juta dolar AS/Rp3,12 triliun), Senin, untuk ...</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687359/inggris-kucurkan-dana-rp312-triliun-kembangkan-kendaraan-nol-emisi</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/11/03/73.jpg</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Pemerintah dorong pendalaman dan diversifikasi pembiayaan pasar modal</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:59:29 +0700</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto menyampaikan pemerintah akan terus mendorong penguatan ...</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687356/pemerintah-dorong-pendalaman-dan-diversifikasi-pembiayaan-pasar-modal</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000722479.jpg</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Danantara siapkan proses untuk miliki saham BEI</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:56:25 +0700</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Investasi Daya Anagata Nusantara (Danantara Indonesia) menyatakan tengah mempersiapkan proses upaya ...</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687352/danantara-siapkan-proses-untuk-miliki-saham-bei</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000722449.jpg</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Wamenperin yakin BRICS jadi ruang penguatan ekspor produk agro RI</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:54:08 +0700</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perindustrian (Wamenperin) Faisol Riza meyakini organisasi kerja sama ekonomi antarnegara BRICS ...</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687351/wamenperin-yakin-brics-jadi-ruang-penguatan-ekspor-produk-agro-ri</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-12.08.01_edit_367277361887704.jpg</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Prabowo kirim Surpres ke DPR ajukan Destry jadi Gubernur BI definitif</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:51:54 +0700</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengirim Surat Presiden (Surpres) ke DPR RI untuk mengajukan nama Destry Damayanti untuk ...</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687347/prabowo-kirim-surpres-ke-dpr-ajukan-destry-jadi-gubernur-bi-definitif</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001302379.jpg</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Dewa United perkuat lini tengah dengan gaet Ripal Wahyudi</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:51:43 +0700</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Dewa United memperkuat lini tengah dengan menggaet gelandang bertahan Ripal Wahyudi di bursa transfer musim panas ...</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687344/dewa-united-perkuat-lini-tengah-dengan-gaet-ripal-wahyudi</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_1289.jpg</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Kemenhut: Kunjungan taman nasional ditutup sesuai eskalasi karhutla</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:51:14 +0700</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) menyatakan kebijakan penutupan akses kunjungan ke kawasan taman nasional di Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687340/kemenhut-kunjungan-taman-nasional-ditutup-sesuai-eskalasi-karhutla</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/upaya-pemadaman-kebakaran-hutan-di-kawasan-tnbts-2837984.jpg</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>AS lanjutkan berbagi informasi intelijen dengan Ukraina</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:50:27 +0700</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Amerika Serikat akan terus memberikan informasi intelijen kepada Ukraina, termasuk untuk serangan terhadap ...</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687337/as-lanjutkan-berbagi-informasi-intelijen-dengan-ukraina</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_863dfec59d02271c214ef6081a1c041a.jpg</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>BPS: Harga bawang putih mulai turun dan relatif terkendali</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:48:52 +0700</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>nya sudah jauh relatif lebih baik, lebih kecil PR-nya," kata Amalia.
+Ia menambahkan, kondisi pasokan bawang ...</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687333/bps-harga-bawang-putih-mulai-turun-dan-relatif-terkendali</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_3689.jpeg</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Riset baterai nasional, Guru Besar UNS raih Indonesia Innovator Award</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:45:10 +0700</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Guru Besar Universitas Sebelas Maret (UNS) Surakarta Prof. Agus Purwanto meraih penghargaan Indonesia Innovator ...</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687332/riset-baterai-nasional-guru-besar-uns-raih-indonesia-innovator-award</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000474131.jpg</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Kalteng optimalkan satgas udara dan darat tangani karhutla</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:44:23 +0700</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Kalimantan Tengah (Kalteng) terus mengoptimalkan satuan tugas (satgas) udara maupun darat dalam ...</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687331/kalteng-optimalkan-satgas-udara-dan-darat-tangani-karhutla</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001737211.jpg</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Alasan Song Kang bergabung dalam "Four Hands, Two Sonatas"</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:43:53 +0700</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Aktor Korea Selatan Song Kang menceritakan mengenai keterlibatannya dalam drama terbarunya yakni "Four Hands, Two ...</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687329/alasan-song-kang-bergabung-dalam-four-hands-two-sonatas</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/07/01/WhatsApp-Image-2025-07-01-at-08.32.45.jpeg</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Menteri PPN: Hilirisasi sawit harus dibarengi penguatan sektor hulu</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:43:16 +0700</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Menteri Perencanaan Pembangunan Nasional (PPN)/Kepala Badan Perencanaan Pembangunan Nasional (Bappenas) Rachmat Pambudy ...</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687325/menteri-ppn-hilirisasi-sawit-harus-dibarengi-penguatan-sektor-hulu</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/rahmadsiexpo.jpg</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Kemenhut target pemulihan 15 ribu hektare ekosistem kritis tahun ini</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:40:24 +0700</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) menargetkan upaya pemulihan ekosistem seluas 15.000 hektare kawasan lahan kritis yang ...</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687321/kemenhut-target-pemulihan-15-ribu-hektare-ekosistem-kritis-tahun-ini</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_082227_121042.jpg</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz tembak seorang DPO KKB di Tembagapura</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:38:45 +0700</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Operasi Damai Cartenz 2026 bersama Satgas Amole melakukan upaya penegakan hukum terhadap Guspi Waker, ...</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687277/satgas-cartenz-tembak-seorang-dpo-kkb-di-tembagapura</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-10-131016.jpg</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>KPK jadwalkan pemeriksaan ulang Rudy Tanoe pada 11 Agustus</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:37:54 +0700</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) menjadwalkan pemeriksaan ulang terhadap tersangka kasus dugaan korupsi dalam ...</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687319/kpk-jadwalkan-pemeriksaan-ulang-rudy-tanoe-pada-11-agustus</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/12/14/1.jpg</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Java United tunjuk Fabio Lefundes sebagai pelatih kepala</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:36:23 +0700</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Java United FC menunjuk Fabio Lefundes sebagai pelatih kepala tim untuk menatap Super League 2026/2027.
+Lefundes ...</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687317/java-united-tunjuk-fabio-lefundes-sebagai-pelatih-kepala</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260809-WA0110.jpg</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Anggota DPR ingatkan pentingnya mitigasi dan wawasan kebencanaan</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:35:23 +0700</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Anggota Komisi VIII DPR RI asal Daerah Pemilihan (Dapil) XI Jawa Timur Ansari mengingatkan pentingnya melakukan ...</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687315/anggota-dpr-ingatkan-pentingnya-mitigasi-dan-wawasan-kebencanaan</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Mitigasi-Bencana.jpg</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>DPR kumpulkan Panglima TNI dan Kapolri bahas keamanan jelang HUT RI</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:33:58 +0700</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Wakil Ketua DPR RI Sufmi Dasco Ahmad bersama pimpinan komisi bidang pertahanan dan keamanan DPR RI mengumpulkan jajaran ...</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687313/dpr-kumpulkan-panglima-tni-dan-kapolri-bahas-keamanan-jelang-hut-ri</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001302374.jpg</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Bulog Papua salurkan bantuan pangan untuk 845 ribu penerima manfaat</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:33:54 +0700</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>ANTARA - Perum Bulog Kantor Wilayah Papua mulai menyalurkan bantuan pangan beras periode Juli hingga September 2026 ...</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687207/bulog-papua-salurkan-bantuan-pangan-untuk-845-ribu-penerima-manfaat</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-10-115451_1.jpg</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Karnaval budaya Festival Lembah Baliem</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:33:48 +0700</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Sejumlah peserta mengikuti karnaval budaya Festival Lembah Baliem ke-34 di Wamena, Kabupaten Jayawijaya, Papua ...</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687312/karnaval-budaya-festival-lembah-baliem</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Karnaval-Festival-Lembah-Baliem-100826-yef-7.jpg</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Menpora sebut kontrak ajang FIFA ASEAN Cup masih dinegosiasikan</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:31:42 +0700</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Menteri Pemuda dan Olahraga Erick Thohir menyebutkan kontrak pengaturan tuan rumah (host contrac) ajang FIFA ASEAN Cup ...</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687308/menpora-sebut-kontrak-ajang-fifa-asean-cup-masih-dinegosiasikan</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/kongres-biasa-pssi-2026-2833315.jpg</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Hingga Agustus, program pilah sampah Jakarta sudah capai 23,14 persen</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:27:55 +0700</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung Wibowo mengungkapkan bahwa hingga awal Agustus, tercatat program pilah sampah di ibu ...</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687307/hingga-agustus-program-pilah-sampah-jakarta-sudah-capai-2314-persen</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_6653.jpeg</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Film karya Kamila Andini akan ditayangkan di TIFF 2026</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:27:34 +0700</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Film karya sutradara dan penulis Kamila Andini yang berjudul "Empat Musim Pertiwi" ...</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687303/film-karya-kamila-andini-akan-ditayangkan-di-tiff-2026</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/ENP_TIFF-1-2.jpg</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Persita Tangerang resmi umumkan kedatangan Tyronne del Pino</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:27:18 +0700</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Klub BRI Super League Persita Tangerang resmi mengumumkan gelandang serang senior Tyronne del Pino pada bursa transfer ...</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687301/persita-tangerang-resmi-umumkan-kedatangan-tyronne-del-pino</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/27/Persib.jpg</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>BPBD: Sebanyak 28.222 jiwa di Banyumas terdampak kekeringan</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:26:37 +0700</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Badan Penanggulangan Bencana Daerah (BPBD) Kabupaten Banyumas, Jawa Tengah, mencatat sebanyak 28.222 jiwa dari 8.371 ...</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687300/bpbd-sebanyak-28222-jiwa-di-banyumas-terdampak-kekeringan</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/air-bersih-bms-090826.jpg</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Kemenimipas-Kemenkes sinergi tingkatkan layanan kesehatan di lapas</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:24:30 +0700</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Kementerian Imigrasi dan Pemasyarakatan (Kemenimipas) bersinergi dengan Kementerian Kesehatan (Kemenkes) meningkatkan ...</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687296/kemenimipas-kemenkes-sinergi-tingkatkan-layanan-kesehatan-di-lapas</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000012986.jpg</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Igor Tolic nilai kehadiran Loncar tambah opsi di lini belakang Persib</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:21:48 +0700</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Pelatih Persib Bandung Igor Tolic menilai kehadiran bek anyar Danijel Loncar menambah opsi di lini belakang tim ...</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687292/igor-tolic-nilai-kehadiran-loncar-tambah-opsi-di-lini-belakang-persib</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/lon.jpg</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>HCM Ads Media bawa informasi lewat media luar ruang bergerak LED-Go!</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:21:37 +0700</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>PT Hikmah Cakra Mulia (HCM Ads Media), perusahaan media Digital Out-of-Home (DOOH) yang berafiliasi dengan ANTARA ...</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687288/hcm-ads-media-bawa-informasi-lewat-media-luar-ruang-bergerak-led-go</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/4b5aa87f-73ca-4943-aca8-05f3a9a970a0.jpeg</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Pramono harap seluruh sampah di DKI terkelola 100 persen pada 2028</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:21:32 +0700</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung Wibowo berharap seluruh sampah di ibu kota dapat terkelola 100 persen pada ...</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687284/pramono-harap-seluruh-sampah-di-dki-terkelola-100-persen-pada-2028</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_6652.jpeg</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Kemenhut: Satgas Inovasi bukan untuk komersialisasi taman nasional</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:20:04 +0700</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) menegaskan pembentukan satuan tugas khusus (Satgas) Inovasi Pembiayaan Taman Nasional ...</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687280/kemenhut-satgas-inovasi-bukan-untuk-komersialisasi-taman-nasional</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_095048_113251.jpg</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Hendak tawuran, Polisi tangkap tiga remaja bawa senjata tajam di Depok</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:14:05 +0700</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Kepolisian Sektor (Polsek) Beji, Kota Depok, Jawa Barat, menangkap tiga orang remaja yang diduga hendak melakukan aksi ...</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687276/hendak-tawuran-polisi-tangkap-tiga-remaja-bawa-senjata-tajam-di-depok</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000912256.jpg</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Seskab Teddy terima Haji Isam bahas investasi hingga hilirisasi</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:12:22 +0700</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Sekretaris Kabinet (Seskab) Teddy Indra Wijaya menerima kedatangan pengusaha nasional Andi Syamsuddin Arsyad atau Haji ...</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687272/seskab-teddy-terima-haji-isam-bahas-investasi-hingga-hilirisasi</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000035208.jpg</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>KSP: Sekolah Terintegrasi tonggak baru ekosistem pendidikan nasional</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:10:26 +0700</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Kantor Staf Presiden (KSP) meluncurkan Sekolah Nasional Terintegrasi (SNT) 7 Kabupaten Bogor, Jawa Barat, bersamaan ...</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687271/ksp-sekolah-terintegrasi-tonggak-baru-ekosistem-pendidikan-nasional</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_3733.jpeg</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Veronica Tan: Perkuat keterwakilan perempuan hingga pemerintah desa</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:09:04 +0700</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Wakil Menteri (Wamen) Pemberdayaan Perempuan dan Perlindungan Anak Veronica Tan mengusulkan penguatan kepemimpinan dan ...</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687267/veronica-tan-perkuat-keterwakilan-perempuan-hingga-pemerintah-desa</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-09-at-09.55.27.jpg</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Panglima imbau masyarakat tak terprovokasi hoaks di media sosial</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:08:54 +0700</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Panglima TNI Jenderal TNI Agus Subiyanto mengimbau masyarakat tidak terprovokasi hoaks yang beredar di media sosial ...</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687264/panglima-imbau-masyarakat-tak-terprovokasi-hoaks-di-media-sosial</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/7d587659-5ff7-4b6d-8e27-e154b30de2b7.jpeg</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Pelaku UMKM bagikan 1.081 onde-onde sambut HUT kemerdekaan</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:06:16 +0700</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Seorang warga menunjukkan onde-onde yang dibagikan dalam rangka memperingati HUT ke-81 Republik Indonesia di ...</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687260/pelaku-umkm-bagikan-1081-onde-onde-sambut-hut-kemerdekaan</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Bagikan-1081-Onde-onde-100826-bcs-3.jpg</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Perpani siapkan 10 pemanah andalan bersaing pada Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Persatuan Panahan Indonesia (PB Perpani) menyiapkan sebanyak 10 pemanah andalan untuk bersaing meraih ...</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687257/perpani-siapkan-10-pemanah-andalan-bersaing-pada-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/pelatnas-panahan-jelang-asian-games-2026-2825267.jpg</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Gubernur: Pembangunan Sekolah Rakyat Pandeglang-Lebak rampung Mei 2027</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:02:20 +0700</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Banten mengungkapkan pembangunan gedung baru untuk program Sekolah Rakyat (SR) yang ...</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687256/gubernur-pembangunan-sekolah-rakyat-pandeglang-lebak-rampung-mei-2027</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000454937.jpg</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Koops TNI Habema evakuasi warga di tengah konflik Ugimba Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:59:41 +0700</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Koops TNI Habema mengevakuasi seorang warga lokal yang membutuhkan pertolongan saat melakukan patroli di Distrik ...</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687252/koops-tni-habema-evakuasi-warga-di-tengah-konflik-ugimba-papua-tengah</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001228610.jpg</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen: 1.360 murid angkatan pertama SNT siap ikuti MPLS</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:59:40 +0700</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Dasar dan Menengah (Kemendikdasmen) melaporkan sebanyak 1.360 murid angkatan pertama Sekolah ...</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687248/kemendikdasmen-1360-murid-angkatan-pertama-snt-siap-ikuti-mpls</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000231902.jpg</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>TNI evakuasi seorang warga dari wilayah rawan OPM</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:55:17 +0700</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Koops TNI Habema mengevakuasi seorang warga dari wilayah rawan aktivitas Organisasi Papua Merdeka (OPM), Minggu ...</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687244/tni-evakuasi-seorang-warga-dari-wilayah-rawan-opm</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001567611.jpg</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Kemenhut: Gajah mati di kebun sawit momentum benahi konservasi</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:55:13 +0700</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) menjadikan peristiwa kematian satu individu Gajah Sumatera ((Elephas maximus ...</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687240/kemenhut-gajah-mati-di-kebun-sawit-momentum-benahi-konservasi</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG20260810084342_112905.jpg</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Kejagung panggil 16 saksi dalam penyidikan kasus MBG</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:53:14 +0700</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Tim penyidik Jampidsus Kejaksaan Agung (Kejagung) memanggil 16 saksi dalam penyidikan kasus dugaan korupsi tata kelola ...</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687237/kejagung-panggil-16-saksi-dalam-penyidikan-kasus-mbg</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000087578.jpg</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Wamenkeu yakinkan investor soal kejelasan "underlying" ETF Emas</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:47:24 +0700</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Keuangan (Wamenkeu) Juda Agung meyakinkan para investor bahwa instrumen investasi Exchange Traded ...</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687236/wamenkeu-yakinkan-investor-soal-kejelasan-underlying-etf-emas</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000722261.jpg</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Praperadilan Tersangka Kuota Haji Ditolak, KPK: Penggeledahan Sesuai Prosedur</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:04:21 +0700</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>KPK menyambut baik putusan hakim yang menolak gugatan praperadilan Asrul Azis Taba terkait penggeledahan dalam kasus korupsi kuota haji.</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612080/praperadilan-tersangka-kuota-haji-ditolak-kpk-penggeledahan-sesuai-prosedur</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Seskab Teddy Terima Haji Isam, Bahas Hilirisasi hingga Energi</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:01:46 +0700</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Rolando Fransiscus Sihombing</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya bertemu pengusaha Haji Isam untuk membahas hilirisasi dan isu energi, memperkuat kolaborasi ekonomi nasional.</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612070/seskab-teddy-terima-haji-isam-bahas-hilirisasi-hingga-energi</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/seskab-teddy-menerima-haji-isam-1786345275109_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Polda Metro Ekshumasi Jenazah Sutrimo di Banyumas Rabu 12 Agustus</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:01:21 +0700</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya rencanakan ekshumasi jenazah Sutrimo, pria yang ditemukan tewas di Kebayoran Baru. Ekshumasi dijadwalkan pada 12 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612069/polda-metro-ekshumasi-jenazah-sutrimo-di-banyumas-rabu-12-agustus</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/polda-metro-jaya-menggelar-konferensi-pers-terkait-tindak-pidana-perdagangan-orang-tppo-pmi-ilegal-ke-libya-1784892641841_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Mensesneg Umumkan Tambahan 3.400 Undangan HUT RI di Istana</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:57:52 +0700</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi umumkan penambahan 3.400 undangan untuk HUT ke-81 RI di Istana. Antusiasme pendaftar mencapai 336.000 orang.</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612052/mensesneg-umumkan-tambahan-3-400-undangan-hut-ri-di-istana</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ilustrasi-upacara-hut-ri-di-istana-1785898929673_169.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Kemenimipas Gelar Operasi Katarak Gratis 81 Warga, Napi dan Petugas Lapas</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:56:39 +0700</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Kementerian Imigrasi adakan bakti kesehatan, operasi katarak, dan cek kesehatan gratis bagi 2.097 warga binaan.</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612051/kemenimipas-gelar-operasi-katarak-gratis-81-warga-napi-dan-petugas-lapas</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menteri-imipas-agus-andrianto-menghadiri-bakti-kesehatan-kemenimipas-1786344842735_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Menteri LH Siapkan Aturan Produsen Wajib Kelola Limbah Produk Kemasan</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:53:06 +0700</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Menteri LH Jumhur Hidayat soroti sampah plastik di RI. Siapkan aturan mewajibkan perusahaan kelola limbah hasil produk.</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612044/menteri-lh-siapkan-aturan-produsen-wajib-kelola-limbah-produk-kemasan</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menteri-lingkungan-hidup-lh-mohammad-jumhur-hidayat-1786341602514_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Hindari Kendaraan Lain, Mobil Tabrak Pemotor hingga Tewas di Bogor</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:51:35 +0700</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Kecelakaan tragis di Cileungsi, Bogor, melibatkan minibus dan pengendara motor. Korban, MDI, meninggal dunia setelah mengalami luka serius di kepala.</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612042/hindari-kendaraan-lain-mobil-tabrak-pemotor-hingga-tewas-di-bogor</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/02/ilustrasi-kecelakaan-1777698723734_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Bigmo Hadiri Pemeriksaan di Polda Metro soal Konten Promo Vape Ajak Anak</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:46:12 +0700</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo mendatangi Polda Metro Jaya untuk klarifikasi terkait ajakan anak di bawah umur mempromosikan liquid vape dalam siaran langsungnya.</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612038/bigmo-hadiri-pemeriksaan-di-polda-metro-soal-konten-promo-vape-ajak-anak</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/youtuber-bigmo-menghadiri-undangan-klarifikasi-di-polda-metro-terkait-konten-promosi-vape-mengajak-anak-di-bawah-umur-1786344350368_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Pramono Ungkap Gerakan Pilah Sampah Jakarta Capai 23,14%</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:43:45 +0700</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung mengungkap gerakan pilah sampah telah mencapai 23,14%.</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612035/pramono-ungkap-gerakan-pilah-sampah-jakarta-capai-23-14</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/gubernur-dki-jakarta-pramono-anung-1786344109705_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Denda Perusahaan yang Buang Sampah Sembarangan Rp 5 Juta</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:43:33 +0700</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung menegaskan sanksi tegas bagi perusahaan buang sampah sembarangan, termasuk denda dan ancaman penutupan usaha.</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612033/pemprov-dki-denda-perusahaan-yang-buang-sampah-sembarangan-rp-5-juta</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/gubernur-dki-jakarta-pramono-anung-1786344172145_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>18 Agustus 2026 Apakah Cuti Bersama? Cek SKB 3 Menteri</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:41:53 +0700</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Kanya Anindita Mutiarasari</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Tanggal 17 Agustus 2026 ditetapkan sebagai libur nasional untuk memperingati HUT RI. Apakah 18 Agustus 2026 cuti bersama?</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611920/18-agustus-2026-apakah-cuti-bersama-cek-skb-3-menteri</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/31/ilustrasi-kalender_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Ketua MPR Sambangi BPK, Beri Undangan Sidang Tahunan 14 Agustus</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:40:41 +0700</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani bersilaturahmi ke BPK RI, mengundang untuk Sidang Tahunan 14 Agustus. Diskusi fokus pada kinerja audit dan akuntabilitas keuangan.</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612032/ketua-mpr-sambangi-bpk-beri-undangan-sidang-tahunan-14-agustus</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/ketua-mpr-ahmad-muzani-kurniawan-fadilahdetikcom-1786344024711_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Mensesneg Respons Usulan PKS Rekrut Orang Luar Partai di Kabinet</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:39:46 +0700</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi merespons dukungan PKS untuk Presiden Prabowo merekrut kabinet baru. Ia terima masukan, namun belum ada pembahasan lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612030/mensesneg-respons-usulan-pks-rekrut-orang-luar-partai-di-kabinet</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/prasetyo-hadi-1784523183633_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Detik-detik Mobil Drag Race Tabrak Penonton di Sulut Hingga 8 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:36:41 +0700</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Fistel Mukuan</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Mobil peserta Drag Race Kotamobagu Championship 2026 bernama Tian Ngantung di Kota Kotamobagu, Sulawesi Utara (Sulut) hilang kendali dan menabrak penonton.</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612029/detik-detik-mobil-drag-race-tabrak-penonton-di-sulut-hingga-8-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/mobil-peserta-turnamen-tidar-drag-race-championship-2026-di-kotamobagu-hilang-kendali-menabrak-penonton-1786337882181_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Pemerintah Serahkan Surpres Terkait Calon Duta Besar ke DPR</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:24:05 +0700</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Pemerintah serahkan tiga surat presiden ke DPR, termasuk calon Gubernur BI Destry Damayanti. Prasetyo Hadi mengonfirmasi setelah rapat dengan Pimpinan DPR.</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612011/pemerintah-serahkan-surpres-terkait-calon-duta-besar-ke-dpr</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/prasetyo-hadi-1784523183633_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Pernikahan 'Sultan' di Grobogan Bikin Heboh, Maharnya GWM Tank hingga Ekskavator</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:15:57 +0700</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Ardian Dwi Kurnia</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Pernikahan 'sultan' di Grobogan menghebohkan jagat media sosial. Tak main-main, 'sultan' Grobogan memberi mahar sejumlah motor, mobil hingga ekskavator.</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612000/pernikahan-sultan-di-grobogan-bikin-heboh-maharnya-gwm-tank-hingga-ekskavator</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/pernikahan-sultan-grobogan-1786339192241_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Mensesneg Rapat Finalisasi Perpres Ojol Bareng Pimpinan DPR</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:15:20 +0700</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi memimpin rapat finalisasi Perpres ojol di DPR. Rapat melibatkan pimpinan DPR dan sejumlah menteri terkait.</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611999/mensesneg-rapat-finalisasi-perpres-ojol-bareng-pimpinan-dpr</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/prasetyo-hadi-1780894920309_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Gus Ipul Cek Langsung Kesiapan Tambakberas Sambut Peserta Muktamar NU</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:14:02 +0700</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Ketua Panitia Muktamar ke-35 NU, Gus Ipul, memeriksa kesiapan lokasi dan menata kamar peserta. Muktamar dijadwalkan 27-31 Agustus 2026 di Jombang.</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611997/gus-ipul-cek-langsung-kesiapan-tambakberas-sambut-peserta-muktamar-nu</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/gus-ipul-cek-langsung-kesiapan-tambakberas-sambut-peserta-muktamar-nu-1786342328974_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Kejagung Panggil 16 Saksi Korupsi MBG: Direktur Perusahaan hingga Yayasan</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:03:35 +0700</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Kejagung memenggil 16 orang saksi perkara korupsi dalam tata kelola program Makan Bergizi Gratis (MBG) pada Badan Gizi Nasional (BGN).</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611989/kejagung-panggil-16-saksi-korupsi-mbg-direktur-perusahaan-hingga-yayasan</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/13/ilustrasi-kejagung-1755064730615_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Menteri LH Usul Pemulung Diganti Jadi Pekerja Pemilah Sampah</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:01:01 +0700</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Menteri LH Jumhur Hidayat usulkan istilah pemulung diganti menjadi pekerja pemilah sampah. Dia dorong standar kompetensi untuk perlindungan sosial sektor ini.</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611970/menteri-lh-usul-pemulung-diganti-jadi-pekerja-pemilah-sampah</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menteri-lingkungan-hidup-lh-mohammad-jumhur-hidayat-1786341602514_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Mobil Ditabrak 2 Truk di Bekasi, Sopir Tewas-2 Penumpang Terluka</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:59:45 +0700</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Kecelakaan di Bantargebang, Bekasi, melibatkan mobil dan dua truk. Pengemudi mobil meninggal, dua penumpang mengalami luka-luka. Investigasi sedang berlangsung.</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611969/mobil-ditabrak-2-truk-di-bekasi-sopir-tewas-2-penumpang-terluka</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/04/11/ilustrasi-kecelakaan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Menaker: Pekerja Pemilah Sampah Dapat Diskon Iuran JKK-JKM Jadi Rp 8.400/Bulan</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:53:46 +0700</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan Yassierli umumkan diskon 50% iuran JKK dan JKM untuk pekerja informal sektor persampahan, mendukung perlindungan sosial hingga 2026.</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611957/menaker-pekerja-pemilah-sampah-dapat-diskon-iuran-jkk-jkm-jadi-rp-8-400-bulan</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menaker-yassierli-1786341206325_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Panglima TNI Ikut Rapat di DPR, Imbau Masyarakat Tak Mudah Terprovokasi</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:51:11 +0700</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Pimpinan DPR menggelar rapat koordinasi dengan pemerintah untuk membahas isu strategis. Panglima TNI imbau masyarakat tidak terprovokasi berita hoaks.</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611954/panglima-tni-ikut-rapat-di-dpr-imbau-masyarakat-tak-mudah-terprovokasi</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/panglima-tni-jenderal-agus-subiyanto-1786340972361_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Lantik Pengurus LPM RI, KDM Dorong Percepatan Pembangunan Desa</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:49:54 +0700</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Gubernur Jabar Dedi Mulyadi melantik Ahmad Doli Kurnia Tandjung sebagai Ketua Umum DPP LPM. Fokus pada pembangunan desa dan penanganan masalah sosial.</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611953/lantik-pengurus-lpm-ri-kdm-dorong-percepatan-pembangunan-desa</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kdm-ajak-lpm-jabar-berantas-judol-dan-perkuat-pembangungan-desa-1786340765426_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Gudang Gas Oplosan di Bogor Digerebek, 3 Pelaku Kabur Panjat Tembok</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:42:41 +0700</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Polisi menggerebek gudang pengoplosan gas bersubsidi di Bogor, mengamankan 152 tabung LPG dan barang bukti lainnya. Tiga pelaku melarikan diri.</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611942/gudang-gas-oplosan-di-bogor-digerebek-3-pelaku-kabur-panjat-tembok</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/polisi-menggerebek-gudang-diduga-tempat-pengolosan-gas-di-gunung-putri-bogor-1786340472898_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Layanan 110 Polri Kini Terintegrasi di Sepanjang Tol Jakarta-Cikampek</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:33:16 +0700</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Layanan call center Polri 110 kini terintegrasi di Tol Jakarta-Cikampek, memberikan respons cepat dan bebas pulsa untuk pengguna jalan dalam keadaan darurat.</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611921/layanan-110-polri-kini-terintegrasi-di-sepanjang-tol-jakarta-cikampek</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/layanan-110-polri-kini-terintegrasi-di-sepanjang-ruas-tol-jakarta-cikampek-1786339957486_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>KDM Ajak Insan Akademik Lahirkan Karya &amp;amp; Dampak Nyata bagi Masyarakat</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:30:17 +0700</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Angga Laraspati</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Gubernur Jabar Dedi Mulyadi dorong KAHMI untuk menghubungkan pemikiran akademik dengan tindakan nyata, menciptakan inovasi yang bermanfaat bagi masyarakat.</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611882/kdm-ajak-insan-akademik-lahirkan-karya-dampak-nyata-bagi-masyarakat</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kdm-ajak-insan-akademi-lahirkan-karya-dampak-nyata-bagi-masyarakat-1786338101434_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Mobil Drag Race Tabrak Penonton di Sulut, 8 Orang Tewas dan 9 Luka</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:29:09 +0700</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Fistel Mukuan</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Mobil drag race di Kotamobagu hilang kendali, menabrak penonton. Akibatnya, 8 orang meninggal dan 9 lainnya luka-luka.</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611917/mobil-drag-race-tabrak-penonton-di-sulut-8-orang-tewas-dan-9-luka</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/mobil-peserta-turnamen-tidar-drag-race-championship-2026-di-kotamobagu-hilang-kendali-menabrak-penonton-1786337882181_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Bareskrim Tangkap 2 Pengedar Narkoba di Bandung, 5 Kg Ganja Disita</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:26:39 +0700</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Dittipidnarkoba Polri menangkap dua pengedar narkoba di Bandung, menyita 5 kg ganja</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611911/bareskrim-tangkap-2-pengedar-narkoba-di-bandung-5-kg-ganja-disita</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/13/ilustrasi-bareskrim-polri-1755061127379_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Pria di Cileungsi Ditangkap Saat Ambil Pesanan Sabu, Sempat Ngaku Beli Nasgor</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:24:44 +0700</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Pria inisial AP ditangkap di Cileungsi karena terlibat jual beli narkoba jenis sabu. Pelaku berusaha mengelabui petugas dengan alasan membeli nasi goreng.</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611901/pria-di-cileungsi-ditangkap-saat-ambil-pesanan-sabu-sempat-ngaku-beli-nasgor</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/1a2bc536-7a6d-41d4-9f9e-6b6372576e53_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Gubernur &amp;amp; Kapolda Jabar Musnahkan Knalpot Brong hingga Tramadol</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:22:23 +0700</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Gubernur Jabar Dedi Mulyadi memusnahkan barang bukti kejahatan, termasuk knalpot brong dan narkoba. Polda Jabar aktif razia untuk stabilitas kamtibmas.</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611896/gubernur-kapolda-jabar-musnahkan-knalpot-brong-hingga-tramadol</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/gubernur-kapolda-jabar-musnahkan-knalpot-brong-hingga-trama-1786340101581.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>10 Ha Lahan Gunung Gede Hangus Usai 4 Hari Kebakaran, Sisa 4 Titik Api</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:16:26 +0700</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Ikbal</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Sekitar 10 hektare (ha) lahan di kawasan Kawah Wadon Gunung Gede Pangrango terdampak kebakaran dalam 4 hari ini. Jumlah titik api sudah berkurang.</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611890/10-ha-lahan-gunung-gede-hangus-usai-4-hari-kebakaran-sisa-4-titik-api</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/08/proses-pemadaman-kebakaran-di-gunung-gede-pangrango-1786169226162_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>KPK Minta Publik Ikut Pantau Sidang Perdana Eks Menag Yaqut 11 Agustus</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:51:24 +0700</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Sidang perdana kasus dugaan korupsi kuota haji yang menjerat mantan Menag Yaqut Cholil Qoumas dkk digelar besok. KPK meminta publik untuk ikut memantau.</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8611842/kpk-minta-publik-ikut-pantau-sidang-perdana-eks-menag-yaqut-11-agustus</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/01/28/82d1f3eb-c607-4d17-abb9-2e460a5b5400_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Trump Siapkan Proyek Fantastis, Renovasi Bandara Dulles Ditaksir US$22 Miliar</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:00:18 +0700</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Rengga Sancaya</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Trump mengusulkan renovasi besar-besaran Bandara Dulles di Virginia senilai US$22 miliar. Proyek ini diproyeksikan mengubah wajah bandara utama Washington.</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8611731/trump-siapkan-proyek-fantastis-renovasi-bandara-dulles-ditaksir-us-22-miliar</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/trump-siapkan-proyek-fantastis-renovasi-bandara-dulles-ditaksir-us22-miliar-1786333008902_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Kinerja LPS 2025: Menjaga Kepercayaan dan Stabilitas Keuangan</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:59:37 +0700</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Lembaga Penjamin Simpanan berkomitmen menjaga kepercayaan dan stabilitas keuangan, dengan pencapaian aset Rp 276,35 T dan WTP 12 tahun berturut-turut.</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infografis/d-8612057/kinerja-lps-2025-menjaga-kepercayaan-dan-stabilitas-keuangan</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/lembaga-penjamin-simpanan-berupaya-untuk-menjaga-kepercayaan-dan-mendukung-stabilitas-sistem-keuangan-1786345139438.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>DJP Buka Suara soal Pajak Rumah Kontrakan</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:32:26 +0700</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Pajak (DJP) Kementerian Keuangan (Kemenkeu) menanggapi rencana pemungutan pajak kepada pemilik rumah kontrakan pada 2027.</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612021/djp-buka-suara-soal-pajak-rumah-kontrakan</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2014/10/01/aba994a2-34ed-467e-b236-0838b109f70c_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Pemerintah Juga Usul Nama Anggota Dewan Komisioner Baru OJK</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:21:35 +0700</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Hari ini, pemerintah menyampaikan Surat Presiden untuk mengusulkan beberapa nama pejabat ke DPR.</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8612005/pemerintah-juga-usul-nama-anggota-dewan-komisioner-baru-ojk</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/mensesneg-prasetyo-hadi-1784623877619_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Punya 1,8 Miliar Penduduk, India Incar Mete hingga Pinang dari RI</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:20:19 +0700</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perindustrian Faisol Riza menyatakan India meminta Indonesia memperbesar ekspor produk agro. BRICS jadi peluang pasar potensial bagi Indonesia.</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611998/punya-1-8-miliar-penduduk-india-incar-mete-hingga-pinang-dari-ri</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/12/raup-cuan-dari-bisnis-kacang-mete_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>RI Impor Bawang Putih 229 Ribu Ton Sejak Awal Tahun, 98% dari China</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:13:10 +0700</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) melaporkan impor bawang putih sepanjang Januari hingga Juni 2026 mencapai 229,76 ribu ton.</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611995/ri-impor-bawang-putih-229-ribu-ton-sejak-awal-tahun-98-dari-china</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/27/meski-sudah-impor-harga-bawang-tetap-melonjak-naik-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Airlangga Sebut VOC Perusahaan Tercatat Pertama di Bursa</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:09:17 +0700</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian, Airlangga Hartarto, menyebut Vereenigde Oostindische Compagnie (VOC) adalah perusahaan tercatat pertama di dunia.</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8611992/airlangga-sebut-voc-perusahaan-tercatat-pertama-di-bursa</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/13/menko-perekonomian-airlangga-hartarto-1783940653691_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Pemerintah Resmi Usulkan Destry Damayanti Jadi Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:01:07 +0700</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Pemerintah resmi menyampaikan usulan calon Gubernur Bank Indonesia hari ini ke DPR.</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8611971/pemerintah-resmi-usulkan-destry-damayanti-jadi-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/potret-destry-damayanti-paparkan-hasil-rapat-kssk-usai-bertemu-prabowo-1785158889989_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Harga Daging Sapi Tembus Rp 180 Ribu/Kg!</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:29:11 +0700</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Contoh kedua adalah Kabupaten Melawi yang sudah harga (daging) sapinya 28,6% di atas HAP dan saat ini sudah menyentuh Rp 180.000 per kilogram, imbuhnya.</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611918/harga-daging-sapi-tembus-rp-180-ribu-kg</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/16/harga-daging-sapi-naik-jelang-lebaran-pasar-kramat-jati-tetap-ramai-1773637836352_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Buruh Mau Demo Akhir Agustus, Bawa Isu Upah Minimum-Outsourcing</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:25:18 +0700</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>KSPN dan buruh anggota Serikat Pekerja mandiri tingkat perusahaan akan melakukan aksi unjuk rasa di DPR dan Istana Negara.</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611894/buruh-mau-demo-akhir-agustus-bawa-isu-upah-minimum-outsourcing</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/15/buruh-demo-dpr-keluhkan-kecilnya-kenaikan-ump-1768461540644_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>ETF Emas RI Resmi Diluncurkan</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:19:13 +0700</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Potensi instrumen investasi ini disebut dapat mengungguli India dan Singapura.</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8611892/etf-emas-ri-resmi-diluncurkan</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/30/ihsg-rebound-usai-dua-hari-anjlok-seiring-pengunduran-diri-dirut-bei-1769748663323_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Dunia Makin Doyan Kopi RI, Ekspornya Tembus Rp 12,3 T</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:14:27 +0700</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Produk kopi dan teh Indonesia semakin diminati global. Ekspor kopi diproyeksi mencapai US$ 692 juta pada 2025.</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8611883/dunia-makin-doyan-kopi-ri-ekspornya-tembus-rp-12-3-t</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/15/target-ekspor-kopi-rp100-triliun-terus-dikejar-1784121762246_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Komentar Ngaco soal Pemerkosaan, Tokoh Sayap Kanan India Dtangkap</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Tokoh sayap kanan India dari Kerala, TG Mohandas, ditangkap polisi karena komentar ngaco soal ancaman pemerkosaan massal di demo Partai Kecoak.</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810103749-113-1390476/komentar-ngaco-soal-pemerkosaan-tokoh-sayap-kanan-india-dtangkap</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Isi 15 Poin Rencana Trump soal Gaza-Hamas yang Ditolak Netanyahu</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:15:04 +0700</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Isi 15 poin rencana Dewan Perdamaian bentukan Trump soal pelucutan senjata Hamas yang ditolak PM Israel Netanyahu.</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810112835-120-1390502/isi-15-poin-rencana-trump-soal-gaza-hamas-yang-ditolak-netanyahu</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/21/benjamin-netanyahu-dan-donald-trump-1779324448821_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Siapa Menantu Sultan Brunei yang Gelarnya Dicabut Kerajaan?</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:46:24 +0700</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Sultan Brunei mencabut gelar kerajaan menantunya Pengiran Raabi'atul Adawiyyah karena dianggap melakukan perilaku tidak pantas.</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810122733-106-1390531/profil-menantu-sultan-brunei-yang-gelarnya-dicopot-kerajaan</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/04/08/06696f31-4d67-417c-906e-a1b403140fa2_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>6 Begal Nasabah Bank di Bekasi Ditangkap Polisi, Terungkap Modus Pelaku</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:06:43 +0700</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Ditreskrimum Polda Metro Jaya menangkap enam pelaku pencurian dengan kekerasan atau begal yang menyasar nasabah bank.</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866304/6-begal-nasabah-bank-di-bekasi-ditangkap-polisi-terungkap-modus-pelaku</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/LjyICkcmYug3jUwbTO2khBZ9HdM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Dirreskrimum-Polda-Metro-Jaya-Kombes-Iman-Imanuddin-10082026.jpg</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Ratusan Siswa SD di Bandung Bakal Dipindahkan Sementara ke Sekolah Lain, SD 148 Cibaduyut: Kami Siap</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:06:27 +0700</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Lebih dari 900 siswa SDN 026 Bojongloa Bandung akan direlokasi sementara ke SDN 148 Cibaduyut imbas penyegelan sekolah oleh ahli waris.</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866303/ratusan-siswa-sd-di-bandung-bakal-dipindahkan-sementara-ke-sekolah-lain-sd-148-cibaduyut-kami-siap</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/USHwYtWQ_cYXuf3XTP5C77sjKtw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sdn-148-cibaduyut-kota-bandung-asdvc-awef.jpg</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>DJP Bantah Bakal Kenakan Pajak Baru bagi Pemilik Rumah Kontrakan pada 2027, Ini Penjelasanya</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:05:16 +0700</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Isu mengenai pemungutan pajak terhadap pemilik rumah kontrakan ini sebenarnya muncul dalam Forum Komunikasi Publik RUU APBN 2027.</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866302/djp-bantah-bakal-kenakan-pajak-baru-bagi-pemilik-rumah-kontrakan-pada-2027-ini-penjelasanya</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fWhsnZNTd9hRJbzcETeT2lZ3AuU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-pajak-17-juni.jpg</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Araujo Tinggal Tunggu Waktu ke Liverpool, Darwin Nunez Sudah Beri Ucapan Selamat</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:05:16 +0700</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Darwin Nunez bocorkan transfer Ronald Araujo ke Liverpool lewat ucapan selamat di media sosial.</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866301/araujo-tinggal-tunggu-waktu-ke-liverpool-darwin-nunez-sudah-beri-ucapan-selamat</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/auSfGFfzUQwduX1Vb0Vc3Yfa5Ng=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-klub-Inggris-Liverpool.jpg</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Dari Natuna hingga Papua, TBIG Targetkan 253.440 Penerima Manfaat Program Kesehatan</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:03:25 +0700</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>TBIG) mengawali program bakti sosial di wilayah tertinggal, terdepan, dan terluar (3T) dari Kabupaten Natuna, Kepulauan Riau.</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866300/dari-natuna-hingga-papua-tbig-targetkan-253440-penerima-manfaat-program-kesehatan</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/uU7qNpMBtjZDsSGj5-Xhm4XjWNM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/TBIG-program-kesehatan.jpg</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Kebakaran di Bromo, Pemerintah Gandeng Pemprov Jatim hingga TNI-Polri Percepat Pemadaman</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:00:54 +0700</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Pemerintah meminta masyarakat meningkatkan kewaspadaan selama kondisi cuaca kering berlangsung.</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866299/kebakaran-di-bromo-pemerintah-gandeng-pemprov-jatim-hingga-tni-polri-percepat-pemadaman</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/I7FifinIaIvYQRA6iqe8Vh96lKI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/man-Nasional-Bromo-Tengger-S.jpg</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Jejak Digital Pelaku Penembakan Thailand Terbongkar, Ternyata Pelajari Senjata dari Media Sosial</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:58:53 +0700</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Jejak digital remaja 14 tahun pelaku penembakan Thailand terungkap. Polisi menyebut ia belajar senjata lewat media sosial.</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866298/jejak-digital-pelaku-penembakan-thailand-terbongkar-ternyata-pelajari-senjata-dari-media-sosial</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/EEK0q3rG-ePVrPFD67WwzdJ5rp8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penembakan-di-sekolah-Thailand.jpg</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Jalani Klarifikasi Konten Live Libatkan Anak di Promosi Vape, Bigmo Genggam Tangan Sosok Ini</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:55:33 +0700</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo menjalani pemeriksaan dan klarifikasi di Polda terkait konten siaran langsung (live) promosi vape yang libatkan anak di bawah umur.</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866297/jalani-klarifikasi-konten-live-libatkan-anak-di-promosi-vape-bigmo-genggam-tangan-sosok-ini</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/z634Z4o8g6sBtTrT1gMcyGbiqGw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KLARIFIKASI-bigmo.jpg</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Alami Kerugian Rp500 Juta, Tasyi Athasyia Bongkar Kronologi 5 Tas Mewahnya Dijual Karyawan</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:55:10 +0700</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Mengalami kerugian mencapai Rp500 juta, Tasyi Athasyia membongkar kronologi karyawan menjual 5 tas mewah miliknya.</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866296/alami-kerugian-rp500-juta-tasyi-athasyia-bongkar-kronologi-5-tas-mewahnya-dijual-karyawan</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/qa3hJrJieEFbvAcNsStLKCuUrUs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Tasyi-Athasyia-berikan-klarifikasi-usai-dituding-jatuhkan-produk-UMKM.jpg</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Sinopsis Film Ice Cream Man, Teror Penjual Es Krim Misterius, Tayang 26 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:53:35 +0700</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Simak sinopsis film Ice Cream Man yang menceritakan teror penjual es krim mengubah anak-anak jadi agresif, tayang perdana pada 26 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866295/sinopsis-film-ice-cream-man-teror-penjual-es-krim-misterius-tayang-26-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/_-Sp9H7_-Hg4MSOHiEJuyH57CnU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-menonton-bioskop-22.jpg</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Selain Gubernur Bank Indonesia, Prabowo Kirim Surpres Calon Komisioner OJK dan Dubes ke DPR</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:49:06 +0700</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Menurut Prasetyo, pemerintah telah berkoordinasi dengan pimpinan DPR sebelum menyerahkan Surpres tersebut secara resmi.</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866294/selain-gubernur-bank-indonesia-prabowo-kirim-surpres-calon-komisioner-ojk-dan-dubes-ke-dpr</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/PT414fYLRnAWHtDnkUO1w8CXPnM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SURPRES-Mensesneg-Prasetyo-Hadi-4.jpg</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Penyebab Kematian Sutrimo Misterius, Susno Duadji Desak Polisi Temukan HP Korban: Ada Jejak di Situ</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:48:40 +0700</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Susno Duadji menjelaskan penyebab kematian Sutrimo tidak dapat dipastikan wajar atau tidak tanpa melalui pemeriksaan forensik.</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866293/penyebab-kematian-sutrimo-misterius-susno-duadji-desak-polisi-temukan-hp-korban-ada-jejak-di-situ</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/O2XNO1hBWHBOCs0uq_Nhqzro324=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/wawancara-khusus-dengan-mantan-kabareskrim-susno-duadji_20240708_220728.jpg</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Jadi Calon Tunggal Gubernur BI, Harta Destry Damayanti Tembus Rp100 M, Punya 12 Properti</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:47:43 +0700</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Destry Damayanti menjadi calon tunggal Gubernur BI yang diusulkan Prabowo ke DPR. Ini profil dan harta kekayaannya.</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866292/jadi-calon-tunggal-gubernur-bi-harta-destry-damayanti-tembus-rp100-m-punya-12-properti</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ntjUUEA4T_-Qh2QLDTDBkoTXSkQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/deputi-gubernur-senior-bi-destry-damayanti.jpg</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Panglima TNI Akui Hoaks Demo Agustus di Medsos Sangat Masif, Imbau Warga Tak Terprovokasi</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:46:57 +0700</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Panglima TNI Jenderal TNI Agus Subiyanto mengimbau seluruh elemen masyarakat tidak mudah terprovokasi berbagai isu demo di media sosial.</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866291/panglima-tni-akui-hoaks-demo-agustus-di-medsos-sangat-masif-imbau-warga-tak-terprovokasi</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/wVAf74jwJiMQmehSY6f9Srv7Kes=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Panglima-TNI-Jenderal-TNI-Agus-Subiyanto-10082026.jpg</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Cerita Teuku Ryzki Dulunya Canggung Habiskan Waktu Berdua dengan sang Ibu: Baru Bisa Setahun Ini</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:42:32 +0700</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Cerita Teuku Ryzki alias Kiki eks CJR yang dulunya canggung menghabiskan waktu berdua dengan sang ibu. Baru bisa menikmati waktu berdua setahun ini.</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866290/cerita-teuku-ryzki-dulunya-canggung-habiskan-waktu-berdua-dengan-sang-ibu-baru-bisa-setahun-ini</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DjXT2d-tKx5p6nTCuGuDHz_sBJw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Teuku-Rizky-saklasfaskfjsa.jpg</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Doa agar Selalu Qana'ah, Pandai Bersyukur atas Rahmat Allah SWT</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:41:15 +0700</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Muslim yang baik akan selalu qanaah atau pandai bersyukur atas segala rezeki dan rahmat dari Allah SWT. Berikut doa agar selalu qanaah dalam hidup.</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7866289/doa-agar-selalu-qanaah-pandai-bersyukur-atas-rahmat-allah-swt</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/UJseVnNEEr38odi54oX1s0PC7y4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DOA-SELALU-QANAAH-45643564.jpg</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Iran Tunjuk Eks Panglima IRGC Pimpin Dewan Keamanan, Pernah Sebut Hormuz Lebih Penting dari Bom Atom</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:39:29 +0700</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Iran tunjuk eks panglima IRGC Mohsen Rezaei pimpin Dewan Keamanan saat Hormuz memanas dan perang dengan AS belum menunjukkan tanda berakhir.</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866288/iran-tunjuk-eks-panglima-irgc-pimpin-dewan-keamanan-pernah-sebut-hormuz-lebih-penting-dari-bom-atom</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Njz516VavznisiQXcBOUf9S5m2w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/n-Mohsen-Rezaei-dalam-sebuah.jpg</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Lutesha Ungkap Cara Bangun Chemistry dengan Ari Irham di Film Seni Merayu Tuhan</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:38:07 +0700</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Lutesha Sadhewa mengungkap cara membangun chemistry terhadap Ari Irham di film Seni Merayu Tuhan, dengan intens melakukan proses reading.</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866287/lutesha-ungkap-cara-bangun-chemistry-dengan-ari-irham-di-film-seni-merayu-tuhan</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fM6s_krKQ6pGWPybw8n36kESzF4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ari-irham_.jpg</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Film Operasi Pesta Copet Tayang Perdana di Bioskop Mulai 15 Agustus 2026, Ini Sinopsis dan Pemainnya</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:35:27 +0700</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Film Operasi Pesta Copet tayang perdana di bioskop mulai 15 Agustus 2026, berikut sinopsis, daftar pemain, dan jadwal tayangnya di bioskop.</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866286/film-operasi-pesta-copet-tayang-perdana-di-bioskop-mulai-15-agustus-2026-ini-sinopsis-dan-pemainnya</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/741UGGMgGbJJbaYqHX_Ljju216w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Film-Bioskop-Ilustrasi.jpg</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Aset ETF Emas Resmi Diperdagangkan di BEI, Jadi Pilihan Baru Instrumen Investasi</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:34:27 +0700</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Kehadiran ETF emas di Indonesia sejalan dengan meningkatnya minat investor global terhadap produk investasi berbasis emas.</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866285/aset-etf-emas-resmi-diperdagangkan-di-bei-jadi-pilihan-baru-instrumen-investasi</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/VHFUuEfT835eXHUErlxWxlrEqVM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/IHSG-Ditutup-Menguat-Usai-Koreksi-Tajam_20260130_171645.jpg</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Asing Net Buy Rp393 Miliar di Sesi I, Ini Daftar Sahamnya</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:05:11 +0700</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>IHSG melemah di sesi I, ditutup di 6.378,40. Tekanan jual dari saham besar, meski investor asing mencatat net buy Rp393,71 miliar.</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810130111-17-757929/asing-net-buy-rp393-miliar-di-sesi-i-ini-daftar-sahamnya</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893111108_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Destry Damayanti Calon Tunggal Gubernur BI, Rupiah Makin Perkasa</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:50:27 +0700</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Rupiah semakin perkasa terhadap dolar Amerika Serikat (AS) pada perdagangan awal pekan.</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810133458-17-757941/destry-damayanti-calon-tunggal-gubernur-bi-rupiah-makin-perkasa</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342089_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Bos OJK Ungkap Bukti Pasar Modal RI Tangguh Masuk Usia 49 Tahun</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:15:10 +0700</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>OJK merayakan 49 tahun pasar modal Indonesia, menyoroti kemajuan infrastruktur dan pertumbuhan investor.</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810115209-17-757892/bos-ojk-ungkap-bukti-pasar-modal-ri-tangguh-masuk-usia-49-tahun</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893013553_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Demutualisasi BEI, Danantara Bakal Ikut Beli Saham?</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:00:03 +0700</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Demutualisasi Bursa Efek Indonesia (BEI) hampir rampung.</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810114502-17-757889/demutualisasi-bei-danantara-bakal-ikut-beli-saham</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/30/danantara-indonesia-cnbc-indonesiamuhammad-sabki-1751266532126_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Prabowo Usulkan Destry Damayanti Jadi Calon Tunggal Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:59:23 +0700</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto telah mengirimkan surat kepada Dewan Perwakilan Rakyat (DPR) terkait calon Gubernur Bank Indonesia (BI).</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810125724-17-757926/prabowo-usulkan-destry-damayanti-jadi-calon-tunggal-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/27/menteri-sekretaris-negara-prasetyo-hadi-saat-menyampaikan-konferensi-pers-di-bank-indonesia-jakarta-senin-2772026-1785117094422_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Semangat Tinggalkan Dolar AS, RI Lebih Pilih Tarik Utang dari China</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:45:32 +0700</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Kepercayaan investor terhadap Panda Bond sangat baik, tercermin dari rating AAA yang didapatkan dari lembaga pemeringkat di China.</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810113432-17-757884/semangat-tinggalkan-dolar-as-ri-lebih-pilih-tarik-utang-dari-china</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/aimenteri-koordinator-bidang-perekonomian-airlangga-hartarto-pada-konferensi-pers-di-jakarta-rabu-582026-1785971442706_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Sempat Terbang ke 6.462, IHSG Malah Merosot 0,49% di Akhir Sesi 1</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:30:29 +0700</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>IHSG melemah di sesi I, turun 31,25 poin ke 6.378,40. Tekanan jual dari saham besar seperti TLKM dan BMRI. Investor asing catat net buy Rp694,8 miliar.</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810120350-17-757898/sempat-terbang-ke-6462-ihsg-malah-merosot-049-di-akhir-sesi-1</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/01/13/ilustrasi-ihsg-cnbc-indonesia-tri-susilo_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Airlangga Pede Pasar ETF Emas RI Bisa Salib India dan Singapura</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:55:53 +0700</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Indonesia meluncurkan ETF Emas, instrumen investasi baru yang melacak harga emas. Diharapkan dapat memperkuat ekosistem pasar modal dan bullion nasional.</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810114916-17-757894/airlangga-pede-pasar-etf-emas-ri-bisa-salib-india-singapura</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/menko-pereknomian-airlangga-hartarto-saat-acara-peringatan-hut-ke-49-pasar-modal-indonesia-dan-peluncuran-produk-etf-emas-seni-1786330817178_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Perusahaan Terbesar di Dunia Tebar Dividen Malah Jadi Petaka</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:35:40 +0700</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Membagikan dividen biasanya menjadi kabar baik bagi investor. Namun, bagi perusahaan ini pembagian dividen justru pernah menjadi petaka.</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810102640-17-757866/perusahaan-terbesar-di-dunia-tebar-dividen-malah-jadi-petaka</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/02/17/voc_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Airlangga Singgung Sejarah VOC di Peringatan Pasar Modal RI</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:11:11 +0700</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Menko Airlangga Hartarto merayakan HUT ke-49 Pasar Modal Indonesia, menekankan pentingnya kepercayaan investor dan sejarah bursa, termasuk peran VOC.</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810101800-17-757863/airlangga-singgung-sejarah-voc-di-peringatan-pasar-modal-ri</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/menko-pereknomian-airlangga-hartarto-saat-acara-peringatan-hut-ke-49-pasar-modal-indonesia-dan-peluncuran-produk-etf-emas-seni-1786330817178_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>HUT Pasar Modal, RI Resmi Luncurkan ETF Emas</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:05:02 +0700</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Indonesia resmi meluncurkan produk Exchange Traded Fund (ETF) Emas bertepatan dengan peringatan 49 tahun diaktifkannya kembali Pasar Modal Indonesia.</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810101102-17-757854/hut-pasar-modal-ri-resmi-luncurkan-etf-emas</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019885_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Video: Batubara Tertekan Efek Pasokan India Naik-Harga Minyak Melonjak</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:58:23 +0700</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Harga Batubara Tertekan Imbas Pasokan India Naik - Harga Minyak Kembali Meroket</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810103613-19-757869/video-batubara-tertekan-efek-pasokan-india-naik-harga-minyak-melonjak</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/harga-batubara-tertekan-imbas-pasokan-india-naik-harga-minyak-kembali-meroket-1786333503971_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Harga Minyak Sentuh US$84,32, Selat Hormuz Masih Jadi Isu</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:50:26 +0700</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Harga minyak mentah kembali menguat pada perdagangan Senin (10/8/2026), setelah pasar kembali dibayangi ketidakpastian mengenai pembukaan Selat Hormuz.</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810100006-17-757845/harga-minyak-sentuh-us-8432-selat-hormuz-masih-jadi-isu</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/04/usa-oilproduction-1767530216300_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Video: Pasar Nantikan Pidato Prabowo - Rupiah Menguat ke Rp 17.800/USD</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:48:43 +0700</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>IHSG Menghijau dan Rupiah Melaju ke Level Rp 17.800 per Dolar AS</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810103619-19-757870/video-pasar-nantikan-pidato-prabowo--rupiah-menguat-ke-rp-17800-usd</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/ihsg-menghijau-rupiah-melaju-ke-level-rp-17800-per-dolar-as-1786333397489_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Wamenkeu Ungkap Warga Dunia Gila Emas, Simpan 4.025 Ton di 2025</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:30:50 +0700</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Menkeu Juda Agung apresiasi peluncuran ETF Emas di Indonesia. Dia berharap instrumen ini memperkuat ekosistem investasi emas nasional dan bersaing global.</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810094123-17-757843/wamenkeu-ungkap-warga-dunia-gila-emas-simpan-4025-ton-di-2025</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/wakil-menteri-keuangan-juda-agung-saat-acara-peringatan-hut-ke-49-pasar-modal-indonesia-dan-peluncuran-produk-etf-emas-senin-1-1786329754851_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Meski Up dan Down, Pasar Modal RI Sukses Serok Dana Rp 125 T hingga Juni</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:55:22 +0700</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Juda Agung menyatakan pasar modal Indonesia tetap kuat, berhasil mengumpulkan Rp 125 triliun. Peluncuran ETF Emas diharapkan memperdalam pasar.</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810093423-17-757841/meski-up-down-pasar-modal-ri-sukses-serok-dana-rp-125-t-hingga-juni</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/12/wakil-menteri-keuangan-wamenkeu-juda-agung-dalam-konferensi-pers-apbn-kita-di-jakarta-pada-rabu-11032026-1773280602014_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Bank Mandiri Gandeng Paramount Pacu Pertumbuhan Sektor Ini</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:37:01 +0700</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Bank Mandiri dan Paramount Enterprise menandatangani MoU untuk kolaborasi layanan perbankan terintegrasi, mendukung pengembangan kawasan properti berkelanjutan.</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810092932-17-757840/bank-mandiri-gandeng-paramount-pacu-pertumbuhan-sektor-ini</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/bank-mandiri-gandeng-paramount-1786329406143_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Video: Mengekor Penguatan Rupiah, IHSG Berhasil Melaju ke 6.400-an</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:28:07 +0700</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Mengekor Penguatan Rupiah, IHSG Berhasil Melaju ke Level 6.400-an</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810092109-19-757831/video-mengekor-penguatan-rupiah-ihsg-berhasil-melaju-ke-6400-an</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/mengekor-penguatan-rupiah-ihsg-berhasil-melaju-ke-level-6400-an-1786328878988_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>OJK Tetapkan Alex Widi Kristiono Sebagai Calon Komisaris BEI</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>OJK menetapkan Alex Widi Kristiono sebagai Calon Anggota Dewan Komisaris PT Bursa Efek Indonesia untuk masa jabatan 2024-2028, menunggu persetujuan RUPSLB.</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810091155-17-757828/ojk-tetapkan-alex-widi-kristiono-sebagai-calon-komisaris-bei</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018492_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>IHSG Dibuka Menguat 0,48% ke Level 6.440</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:05:50 +0700</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>IHSG menguat 0,48% pada 10 Agustus 2026, dengan transaksi Rp 156,53 miliar. Pekan ini, fokus pasar pada inflasi AS dan pidato Presiden Prabowo.</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810085004-17-757824/ihsg-dibuka-menguat-048-ke-level-6440</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019552_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Rupiah Dibuka Perkasa, Dolar AS Turun ke Rp17.800 Pagi Ini</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:03:38 +0700</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Rupiah membawa momentum positif dari akhir pekan lalu ke pembukaan perdagangan awal pekan.</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810082544-17-757823/rupiah-dibuka-perkasa-dolar-as-turun-ke-rp17800-pagi-ini</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342975_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>DSSA Alihkan hingga 9,63 Miliar Saham Treasuri per 10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:00:02 +0700</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>PT Dian Swastatika Sentosa (DSSA) akan menjual kembali 9,63 miliar lembar saham treasuri, setara 5% dari total saham, tanpa perlu RUPS.</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810082702-17-757801/dssa-alihkan-hingga-963-miliar-saham-treasuri-per-10-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/12/14/dok-dssa_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Intip 5 Rekomendasi Saham yang Potensi Kasih Cuan Hari Ini</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:55:31 +0700</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>IHSG menguat 1,04% pada 7 Agustus, didorong oleh BBRI dan DCII. Investor asing mencatatkan net buy Rp917,23 miliar. Rekomendasi saham juga disertakan.</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810082029-17-757798/intip-5-rekomendasi-saham-yang-potensi-kasih-cuan-hari-ini</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/market-1786324828-1786324829134_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Asing Net Buy Rp672 M Pekan Lalu, Kompak Borong 10 Saham Ini</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:45:36 +0700</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>IHSG tembus 6.400, naik 1,04% pada 8 Agustus 2026. Investor asing catat pembelian bersih Rp672,7 miliar. Simak 10 saham terfavorit asing!</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810083136-17-757803/asing-net-buy-rp672-m-pekan-lalu-kompak-borong-10-saham-ini</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893013553_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Bursa Asia Menguat, Investor Pantau Konflik Iran-AS dan Data Inflasi</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:26:53 +0700</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Bursa saham Asia-Pasifik menguat pada 10 Agustus 2026, didorong harapan kesepakatan AS-Iran dan prospek kebijakan suku bunga The Fed.</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810082412-17-757799/bursa-asia-menguat-investor-pantau-konflik-iran-as-data-inflasi</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/28/korea-composite-stock-price-index-kospi-1785212557381_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Asing Terciduk Diam-Diam Kompak Lego 10 Saham Ini Pekan Lalu</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:17:56 +0700</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>IHSG naik 1,04% ke 6.409,65 pada akhir pekan, mencatatkan kenaikan 2,78% dalam lima hari. Investor asing beli bersih Rp672,7 miliar.</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810081459-17-757797/asing-terciduk-diam-diam-kompak-lego-10-saham-ini-pekan-lalu</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893111052_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Usai Jakarta, Bali Ingin Terbitkan Obligasi Daerah-Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:05:59 +0700</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung pada awal pekan lalu, Selasa (4/8/2026) telah menerima kunjungan Gubernur Bali I Wayan Koster</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810054839-17-757768/usai-jakarta-bali-ingin-terbitkan-obligasi-daerah-ada-apa</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/11/30/balai-kota-jakarta-kantor-wagub-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Danantara Siapkan Investasi di BEI, Besaran Porsi Belum Diungkap</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:16:07 +0700</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Badan Pengelola Investasi Daya Anagata Nusantara (BPI Danantara) tengah menyiapkan keterlibatan dalam demutualisasi Bursa Efek Indonesia (BEI). Namun, Danantara belum mengungkapkan besaran dana maupun porsi kepemilikan...</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjiqv370/danantara-siapkan-investasi-di-bei-besaran-porsi-belum-diungkap</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/086861200-1785491449-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Isuzu Perkenalkan Konsep Modifikasi Traga Menjadi Salon Berjalan</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:58:26 +0700</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, TANGERANG -- Area kargo kendaraan niaga dapat dimanfaatkan menjadi ruang usaha bergerak. Konsep tersebut ditunjukkan melalui Isuzu Traga Putri Salon Studio, kendaraan yang dimodifikasi menjadi salon berjalan dan...</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjhxe348/isuzu-perkenalkan-konsep-modifikasi-traga-menjadi-salon-berjalan</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/kendaraan-modifikasi-isuzu-traga-putri-salon_260810125539-967.jpeg</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Hilirisasi Bauksit Diklaim Buka Jalan Pengembangan Mineral Strategis Nasional</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, PONTIANAK — Hilirisasi bauksit dinilai membuka jalan bagi Indonesia untuk mengembangkan mineral strategis bernilai tambah sekaligus memperkuat fondasi industri nasional. Pengembangan tersebut tidak hanya diarahkan pada peningkatan produksi...</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjed5522/hilirisasi-bauksit-diklaim-buka-jalan-pengembangan-mineral-strategis-nasional</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/wakil-direktur-utama-mind-id-dany-amrul_260810114108-418.jpeg</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Hadir di GIIAS 2026, Gotion Dukung Pertumbuhan Industri EV Indonesia</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Fernan Rahadi</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- GAIKINDO Indonesia International Auto Show 2026 (GIIAS 2026) baru-baru ini digelar di ICE BSD City, Jakarta. Pada ajang ini, Gotion menampilkan solusi EV battery sekaligus menunjukkan kapabilitas...</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjje75291/hadir-di-giias-2026-gotion-dukung-pertumbuhan-industri-ev-indonesia</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/gaikindo-indonesia-international-auto-show-2026-giias-2026-baru-baru_260810113658-874.jpg</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Seskab Teddy Ungkap Isi Pertemuan dengan Haji Isam</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:05:58 +0700</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Pertemuan Seskab Teddy dengan Haji Isam digelar di kantor Sekretariat Kabinet, Jakarta, Minggu (9/8/2026).</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266201/seskab-teddy-ungkap-isi-pertemuan-dengan-haji-isam</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/NcvsnS2lsOHcFPZz-ZyIXdFyWC0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320330/original/095804500_1786345554-Screenshot_20260810_125908_Instagram.jpg</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Istana Kirim 3 Surpres ke DPR</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:44:24 +0700</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi mengatakan, pemerintah telah mengirimkan tiga surat presiden (surpres) ke DPR. Soal apa saja?</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266176/istana-kirim-3-surpres-ke-dpr</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/gHbesCjp-SNAzXm496ZCYwbc5s0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320299/original/065432400_1786344095-mensesneg.jpg</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Panglima TNI Beberkan Isi Rapat Tertutup dengan Pimpinan DPR</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Panglima TNI Jenderal Agus Subiyanto menegaskan keamanan nasional tetap terjaga pasca rapat dengan pimpinan DPR.</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266124/panglima-tni-beberkan-isi-rapat-tertutup-dengan-pimpinan-dpr</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/rD3ueMTqt3nI5n9Y9DV2HbCXMo0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320239/original/070492200_1786341140-c57a18a3-9595-4171-9ddf-5e5fedc25804.jpg</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>LPSK Jemput Bola Kasus Sutrimo, Ada Opsi Perlindungan Darurat</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>LPSK berkoordinasi dengan Polda Metro Jaya dan akan menjangkau keluarga Sutrimo untuk menawarkan perlindungan serta pendampingan hukum.</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266104/lpsk-jemput-bola-kasus-sutrimo-ada-opsi-perlindungan-darurat</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/-fx7HAZbdkTLuLva3_Hw8lwALys=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9308334/original/005435400_1785137531-64336.jpg</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Hari Ini Kejagung Panggil 16 Saksi MBG, Berikut Daftarnya</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Tim penyidik Kejaksaan Agung (Kejagung) memeriksa 16 saksi dari berbagai pihak dalam kasus dugaan korupsi tata kelola MBG.</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266099/hari-ini-kejagung-panggil-16-saksi-mbg-berikut-daftarnya</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/DlwAJOqLV_-r41sBicc0mvVyObg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9295697/original/095241300_1783939446-53527.jpg</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Penjelasan Pemilik Kedai Piscok Terkait Kasus Mutilasi Mantan Karyawan</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:28:24 +0700</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Pemilik kedai meminta masyarakat untuk tidak menyudutkan usahanya. Menurutnya, tindakan dilakukan Saepul tidak berkaitan dengan usaha tersebut.</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266096/penjelasan-pemilik-kedai-piscok-terkait-kasus-mutilasi-mantan-karyawan</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/xHpjC_cUgQOQJtph4-ap0p6MoPQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320187/original/026750100_1786339702-piscok.jpg</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Pemerintah Pusat Cairkan Rp 18,9 Triliun ke 546 Daerah, Ada DAU dan DBH</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:10:38 +0700</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian menyebutkan, pemerintah pusat sudah mencairkan Rp 18,6 triliun ke 546 daerah demi memenuhi kapasitas fiskal setiap daerah.</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/10/14071381/pemerintah-pusat-cairkan-rp-189-triliun-ke-546-daerah-ada-dau-dan-dbh</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Vjif6kp29CwgBi-wnwMXvPx5uQw=/0x0:4096x2731/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/03/6a705dc58e177.jpeg</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Bus Sekolah Gratis Banyumas Tambah Koridor 4, Ini Rute dan Jadwalnya</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:10:38 +0700</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Untuk koridor Kalibagor-Banyumas melayani titik jemput di Desa Kalibagor, Desa Pajerukan, Desa Suro, Desa Srowot, Desa Kaliori.</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/10/135800978/bus-sekolah-gratis-banyumas-tambah-koridor-4-ini-rute-dan-jadwalnya</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Rf5l5Eu4KLHoxYvUCOKwuZUfHoA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79673e5bcc9.jpg</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Pimpinan DPR, Mensesneg, Panglima TNI, dan Kapolri Bahas Keamanan Agustus</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:10:38 +0700</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Pimpinan DPR RI rapat bersama pihak eksekutif dan Polri serta TNI untuk membahas keamanan Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/10/13371731/pimpinan-dpr-mensesneg-panglima-tni-dan-kapolri-bahas-keamanan-agustus</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/sWDY09veNKvRSi1KkmyOV1nW_-4=/0x0:780x390/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2015/06/22/1506282011-fot01.JPG18-780x390.jpg</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I327"/>
+  <autoFilter ref="A1:I485"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$485</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$602</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I485"/>
+  <dimension ref="A1:I602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -23234,8 +23234,5507 @@
         </is>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Peternak di Temanggung bagikan ribuan ayam, tuntut solusi harga pakan</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:03:42 +0700</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>ANTARA - Paguyuban peternak ayam membagikan 5.500 ekor ayam secara gratis kepada masyarakat di jalan protokol di ...</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687560/peternak-di-temanggung-bagikan-ribuan-ayam-tuntut-solusi-harga-pakan</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PETERNAK-DI-TEMANGGUNG-BAGIKAN-RIBUAN-AYAM-TUNTUT-SOLUSI-HARGA-PAKAN.jpg</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>BB TNBTS tutup seluruh jalur akses ke Bromo</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:03:19 +0700</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Kondisi jalur wisata pascakebakaran di kawasan Taman Nasional Bromo Tengger Semeru (TNBTS), Kabupaten Pasuruan, Jawa ...</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687612/bb-tnbts-tutup-seluruh-jalur-akses-ke-bromo</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Penutupan-Wisata-Bromo-100826-IS-5.jpg</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Pemerintah koordinasi padamkan kebakaran hutan</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:59:24 +0700</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan pemerintah telah melakukan koordinasi lintas lembaga sebagai upaya ...</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687611/pemerintah-koordinasi-padamkan-kebakaran-hutan</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/penutupan-akses-wisata-bromo-akibat-kebakaran-2838377.jpg</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Ekonom: Daya beli kelas menengah bawah kunci ekonomi semester II</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:58:58 +0700</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Ekonom Institute for Development of Economics and Finance (INDEF) M Rizal Taufikurahman menilai daya beli masyarakat, ...</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687607/ekonom-daya-beli-kelas-menengah-bawah-kunci-ekonomi-semester-ii</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/05/pertumbuhan-ekonomi-indonesia-pada-kuartal-i-2026-2784808.jpg</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Hakteknas, Mendiktisaintek ingin kampus ciptakan perusahaan global</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:58:52 +0700</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Menteri Pendidikan Tinggi, Sains, dan Teknologi (Mendiktisaintek) Brian Yuliarto mengungkapkan visi ambisius agar ...</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687605/hakteknas-mendiktisaintek-ingin-kampus-ciptakan-perusahaan-global</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000474193.jpg</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Padi Biosalin panen perdana di Batang, lahan rob mulai produktif</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:57:18 +0700</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>ANTARA - Lahan terdampak rob di Desa Depok, Kabupaten Batang, Jawa Tengah, mulai menghasilkan panen padi biosalin. ...</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687577/padi-biosalin-panen-perdana-di-batang-lahan-rob-mulai-produktif</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PADI-BIOSALIN-PANEN-PERDANA-DI-BATANG-LAHAN-ROB-MULAI-PRODUKTIF.jpg</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Kuliner khas Indonesia dijadikan inspirasi koleksi pada pin sandal</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:54:34 +0700</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Sejumlah jajanan kuliner khas Indonesia dijadikan inspirasi untuk koleksi jibbitz charm atau pin hiasan kecil ...</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687600/kuliner-khas-indonesia-dijadikan-inspirasi-koleksi-pada-pin-sandal</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-13.55.48.jpeg</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>OJK tangani 124 kasus pasar modal, 89 masih diperiksa</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:53:32 +0700</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) menangani 124 kasus melalui pemeriksaan khusus di bidang pasar modal hingga 7 Agustus ...</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687599/ojk-tangani-124-kasus-pasar-modal-89-masih-diperiksa</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000179246.jpg</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Bandung dan Jakarta siap jadi tuan rumah FIFA ASEAN Cup 2026</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:51:33 +0700</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Bandung dan Jakarta siap menjadi dua kota tuan rumah penyelenggaraan ajang FIFA ASEAN Cup 2026 yang bergulir untuk ...</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687595/bandung-dan-jakarta-siap-jadi-tuan-rumah-fifa-asean-cup-2026</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/464936.jpg</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Kemenperin bidik produk unggulan agro penuhi potensi pasar global</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:48:45 +0700</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Kementerian Perindustrian (Kemenperin) membidik penguatan produk artisan agro unggulan nasional untuk memenuhi potensi ...</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687592/kemenperin-bidik-produk-unggulan-agro-penuhi-potensi-pasar-global</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-12.08.01_edit_367277361887704_1.jpg</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Danantara siapkan IPO BUMN dalam 6-12 bulan ke depan</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:48:25 +0700</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Investasi Daya Anagata Nusantara (Danantara Indonesia) menyatakan akan menyiapkan penawaran umum ...</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687588/danantara-siapkan-ipo-bumn-dalam-6-12-bulan-ke-depan</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000722643.jpg</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Menpar: RI masif jalin kolaborasi global perkuat daya saing pariwisata</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:48:17 +0700</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Menteri Pariwisata Widiyanti Putri Wardhana menyatakan bahwa pemerintah masif menjalin kolaborasi dengan pihak dari ...</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687584/menpar-ri-masif-jalin-kolaborasi-global-perkuat-daya-saing-pariwisata</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/08/Presiden-Prabowo-dan-PM-India-kunjungi-Candi-Prambanan-080726-bay-01_2.jpg</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Cerahkan peradaban dengan nanoteknologi</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:45:10 +0700</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Indonesia tidak kekurangan riset nanoteknologi. Di berbagai perguruan tinggi dan lembaga penelitian, kita dapat ...</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687580/cerahkan-peradaban-dengan-nanoteknologi</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000555744.png</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Kemnaker perkuat "link and match" pendidikan-industri berbasis data</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:35:43 +0700</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) memperkuat upaya penyelarasan dan keterkaitan (link and match) antara dunia ...</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687576/kemnaker-perkuat-link-and-match-pendidikan-industri-berbasis-data</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/b0d38a8c-5a7a-4f11-a64e-5613f4936d97.jpeg</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>HUT RI, Kantor Kelurahan Kuningan Timur dihiasi ornamen barang bekas</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:33:47 +0700</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Kantor Kelurahan Kuningan Timur, Kecamatan Setiabudi, Jakarta Selatan, dihiasi dengan ornamen-ornamen berbahan barang ...</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687573/hut-ri-kantor-kelurahan-kuningan-timur-dihiasi-ornamen-barang-bekas</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001021234.jpg</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Polisi tangkap enam perampok spesialis nasabah bank di DKI dan Bekasi</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:30:08 +0700</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Subdirektorat Kejahatan dan Kekerasan (Subdit Jatanras) Direktorat Reserse Kriminal Umum Polda Metro Jaya menangkap ...</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687571/polisi-tangkap-enam-perampok-spesialis-nasabah-bank-di-dki-dan-bekasi</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000912431.jpg</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>RI bakal gandeng New Hope Fintech fasilitasi pembiayaan bagi BUM Desa</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:30:02 +0700</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Kementerian Desa dan Pembangunan Daerah Tertinggal mengatakan, akan berkolaborasi dengan New Hope Financial Technology ...</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687569/ri-bakal-gandeng-new-hope-fintech-fasilitasi-pembiayaan-bagi-bum-desa</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-14.21.55.jpeg</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Topan Dolphin picu evakuasi 1,5 juta warga di pesisir China timur</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:27:50 +0700</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Lebih dari 1,5 juta orang dievakuasi ke tempat aman akibat topan Dolphin yang menerjang pesisir China timur dengan ...</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687565/topan-dolphin-picu-evakuasi-15-juta-warga-di-pesisir-china-timur</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/Peringatan-Merah-Topan-Dolphin-090826-WX-1.jpg</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Pendidikan vokasi jadi kunci siapkan SDM industri transportasi</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:26:59 +0700</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Perkembangan teknologi kendaraan menuntut industri transportasi tidak hanya menyiapkan produk dan infrastruktur, tetapi ...</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5687561/pendidikan-vokasi-jadi-kunci-siapkan-sdm-industri-transportasi</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-14.12.15.jpeg</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>OJK menunggu tinjauan MSCI di tengah "freeze" indeks Indonesia</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:23:43 +0700</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) menunggu hasil tinjauan indeks MSCI pada 12 Agustus 2026 di tengah masih berlakunya ...</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687556/ojk-menunggu-tinjauan-msci-di-tengah-freeze-indeks-indonesia</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000179219.jpg</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Pimpin Konsorsium ABMN, Asuransi Jasindo Serahkan Klaim Rp 17,6 Miliar kepada Kementerian Agama</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:20:43 +0700</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) — PT Asuransi Jasa Indonesia (Persero) atau lebih dikenal dengan Asuransi Jasindo selaku Ketua ...</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687552/pimpin-konsorsium-abmn-asuransi-jasindo-serahkan-klaim-rp-176-miliar-kepada-kementerian-agama</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-14.32.40.jpeg</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>BI: Indeks Keyakinan Konsumen Juli 2026 berada pada level optimis</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:19:49 +0700</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) melaporkan Indeks Keyakinan Konsumen (IKK) Juli 2026 yang berada pada level optimis (indeks ...</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687548/bi-indeks-keyakinan-konsumen-juli-2026-berada-pada-level-optimis</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/IMG_6691-1.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Ekonom: Destry Damayanti sosok tepat lanjutkan kepemimpinan BI</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:18:36 +0700</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai keputusan Presiden Prabowo mengusulkan Destry ...</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687544/ekonom-destry-damayanti-sosok-tepat-lanjutkan-kepemimpinan-bi</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/Pelibatan-Danantara-KSSK-270726-hma-14.jpg</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Kemenhut lepasliarkan 15 burung air di TWA Angke Jakarta</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:15:20 +0700</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan melepasliarkan 15 ekor burung air di Taman Wisata Alam (TWA) Angke, Jakarta Utara, Senin, sebagai ...</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687540/kemenhut-lepasliarkan-15-burung-air-di-twa-angke-jakarta</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_103744_112819.jpg</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Menpar sebut pariwisata RI tumbuh positif berkat strategi adaptif</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:15:13 +0700</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Menteri Pariwisata Widiyanti Putri Wardhana menyebut sektor pariwisata Indonesia sepanjang semester I 2026 di berbagai ...</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687537/menpar-sebut-pariwisata-ri-tumbuh-positif-berkat-strategi-adaptif</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/peningkatan-kunjungan-wisman-ke-ntt-2836131.jpg</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>BNI-Presetiya Mulya bekerja sama perkuat ekosistem keuangan kampus</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:15:04 +0700</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>PT Bank Negara Indonesia (Persero) Tbk atau BNI dan Universitas Prasetiya Mulya bekerja sama untuk memperkuat penetrasi ...</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687536/bni-presetiya-mulya-bekerja-sama-perkuat-ekosistem-keuangan-kampus</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-10.46.17.jpeg</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>BPK nilai LK Kementerian ESDM dan Kemenko IPK telah disajikan wajar</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:13:50 +0700</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Pelaksana Tugas (Plt) Anggota IV Badan Pemeriksa Keuangan (BPK) RI Nyoman Adhi Suryadnyana menyatakan Laporan Keuangan ...</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687533/bpk-nilai-lk-kementerian-esdm-dan-kemenko-ipk-telah-disajikan-wajar</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-09.17.17.jpeg</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Para panahan Indonesia berlaga di India sebelum ke Asian Para Games</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:12:31 +0700</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Tim para panahan Indonesia akan berlaga pada turnamen di India sebelum mereka berangkat ke Jepang untuk bermain di ...</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687529/para-panahan-indonesia-berlaga-di-india-sebelum-ke-asian-para-games</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/DSC_3586A.jpg</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Kuasa hukum: Dari 432 saksi, tidak ada yang bilang Yaqut terima uang</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:11:58 +0700</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Kuasa hukum mantan Menteri Agama Yaqut Cholil Qoumas, Mellisa Anggraini, mengatakan tidak ada satu pun dari 432 orang ...</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687527/kuasa-hukum-dari-432-saksi-tidak-ada-yang-bilang-yaqut-terima-uang</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_8342.jpg</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Ken Swagumilang raih dua emas di Para-meter Archery Indonesia Open</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:10:43 +0700</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Atlet para panahan Indonesia Ken Swagumilang meraih dua emas saat ia terjun dalam turnamen panahan bertajuk Para-meter ...</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687524/ken-swagumilang-raih-dua-emas-di-para-meter-archery-indonesia-open</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/DSC_7239A.jpg</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Ripal Wahyudi akan anggap semua laga bersama Dewa United seperti final</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:09:00 +0700</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Pemain baru Dewa United Banten FC Ripal Wahyudi akan menganggap semua laga bersama timnya seperti final, karena ia ...</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687521/ripal-wahyudi-akan-anggap-semua-laga-bersama-dewa-united-seperti-final</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/09/semen-padang-menang-atas-psbs-2747679.jpg</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Kemenhut ungkap modus jual beli kawasan hutan lindung di Sulsel</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:07:12 +0700</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) berhasil mengungkapkan modus jual beli kawasan hutan lindung yang digarap secara ...</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687517/kemenhut-ungkap-modus-jual-beli-kawasan-hutan-lindung-di-sulsel</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/writer_12.jpeg</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Ketua MPR sebut tren opini WTP pemerintah semakin baik</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:06:50 +0700</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani menyebut pengelolaan keuangan negara menunjukkan tren yang semakin baik setelah adanya ...</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687515/ketua-mpr-sebut-tren-opini-wtp-pemerintah-semakin-baik</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001302471.jpg</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Istana prioritaskan pendaftar baru saksikan upacara HUT Ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:06:17 +0700</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan pemerintah memprioritaskan pendaftar baru untuk menyaksikan upacara ...</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687512/istana-prioritaskan-pendaftar-baru-saksikan-upacara-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_6312.jpeg</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Paulo Ricardo siap berikan 100 persen kemampuannya untuk Garudayaksa</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:05:23 +0700</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Bek anyar Garudayaksa FC Paulo Ricardo mengaku siap memberikan 100 persen kemampuannya untuk timnya setelah ia ...</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687508/paulo-ricardo-siap-berikan-100-persen-kemampuannya-untuk-garudayaksa</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/24/Persija-Jakarta-Kalahkan-Semen-Padang-230526-MRH-9.jpg</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>HCM Ads Media luncurkan LED-Go! perluas publikasi videotron bergerak</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:05:08 +0700</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>ANTARA - PT HCM Ads Media meluncurkan mobile videotron LED-Go! sebagai inovasi baru layanan publikasi, informasi, dan ...</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687444/hcm-ads-media-luncurkan-led-go-perluas-publikasi-videotron-bergerak</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-10-141933.jpg</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Bidan jangan takut ambil bertindak medis selama sesuai SOP</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:03:45 +0700</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Wali Kota Samarinda, Kalimantan Timur, Andi Harun menegaskan para bidan tidak perlu takut dalam menjalankan ...</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687504/bidan-jangan-takut-ambil-bertindak-medis-selama-sesuai-sop</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_3727_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Ketika pendidikan tidak membedakan latar belakang siswa</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:00:32 +0700</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Berjajar piagam penghargaan melengkapi pemandangan dinding di sebuah ruangan yang tidak terlalu luas, tapi terasa adem ...</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687501/ketika-pendidikan-tidak-membedakan-latar-belakang-siswa</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_120911.jpg</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>PERURI raih penghargaan atas reputasi perusahaan teknologi sekuriti</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:00:22 +0700</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>PERURI meraih penghargaan Indonesia Public Relations Awards (Popular Companies) 2026 kategori Security Technology dalam ...</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687497/peruri-raih-penghargaan-atas-reputasi-perusahaan-teknologi-sekuriti</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260810-WA0015.jpg</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Bantuan pasokan air di 492 titik kekeringan</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Kementerian Pekerjaan Umum (Kemen PU) menyalurkan bantuan air bersih di 492 titik lokasi yang mengalami kekeringan ...</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5686964/bantuan-pasokan-air-di-492-titik-kekeringan</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810-Bantuan-pasokan-air-di-492-titik-kekeringan.jpg</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Kemenko PM meluncurkan program mobilisasi nilai ekonomi mangrove</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:59:54 +0700</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Kementerian Koordinator Bidang Pemberdayaan Masyarakat (Kemenko PM) dan Universitas Indonesia (UI) meluncurkan ...</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687495/kemenko-pm-meluncurkan-program-mobilisasi-nilai-ekonomi-mangrove</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810_100627.jpg</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>AS-Israel bahas perbedaan soal pelaksanaan rencana Gaza</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:59:47 +0700</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Amerika Serikat (AS) dan Israel tengah membahas perbedaan di antara kedua negara terkait mekanisme dan jadwal ...</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687492/as-israel-bahas-perbedaan-soal-pelaksanaan-rencana-gaza</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Dubes-AS-untuk-PBB-Mike-Waltz.jpg</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Kepala BRIN tegaskan tak semua masalah harus diatasi teknologi canggih</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:59:44 +0700</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Kepala Badan Riset dan Inovasi Nasional (BRIN) Arif Satria mengatakan tidak semua persoalan di masyarakat harus ...</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687491/kepala-brin-tegaskan-tak-semua-masalah-harus-diatasi-teknologi-canggih</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000474161.jpg</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Marc Marquez sebut ada permasalahan dengan motornya dalam GP Inggris</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:58:27 +0700</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Pembalap Ducati Lenovo Marc Marquez menyebut ada permasalahan dengan motornya dalam MotoGP Inggris yang berlangsung di ...</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687489/marc-marquez-sebut-ada-permasalahan-dengan-motornya-dalam-gp-inggris</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/mtogp.jpg</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Wamenkomdigi dorong manfaatkan teknologi digital untuk berbagi ilmu</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:57:44 +0700</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Komunikasi dan Digital Angga Raka Prabowo mendorong memanfaatkan perkembangan teknologi digital ...</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687488/wamenkomdigi-dorong-manfaatkan-teknologi-digital-untuk-berbagi-ilmu</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/36fee7a6-0b65-4ee6-a6ef-d438709afcc0.jpeg</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen mulai kegiatan MPLS Sekolah Nasional Terintegrasi</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:57:36 +0700</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Dasar dan Menengah (Kemendikdasmen) memulai rangkaian kegiatan Masa Pengenalan Lingkungan ...</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687487/kemendikdasmen-mulai-kegiatan-mpls-sekolah-nasional-terintegrasi</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000232038.jpg</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Kemenpar berkoordinasi dengan pemda terkait insiden semasa FBLB 2026</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:56:00 +0700</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Kementerian Pariwisata (Kemenpar) berkoordinasi dengan Pemerintah Daerah (Pemda) Kabupaten Jayawijaya di Provinsi Papua ...</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687483/kemenpar-berkoordinasi-dengan-pemda-terkait-insiden-semasa-fblb-2026</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Karnaval-Festival-Lembah-Baliem-100826-yef-1.jpg</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Kemenhan komitmen tingkatkan kesejahteraan veteran perang</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:52:51 +0700</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Kementerian Pertahanan berkomitmen meningkatkan kesejahteraan para veteran perang pada Hari Veteran Nasional Tahun ...</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687481/kemenhan-komitmen-tingkatkan-kesejahteraan-veteran-perang</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000479227.jpg</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>PERDAMI: Deteksi dini mata juling cegah risiko mata malas pada anak</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:51:49 +0700</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Perhimpunan Dokter Spesialis Mata Indonesia (PERDAMI) Jaya menggarisbawahi perlunya deteksi dini untuk mengidentifikasi ...</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687480/perdami-deteksi-dini-mata-juling-cegah-risiko-mata-malas-pada-anak</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-14.14.41.jpeg</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Lanal Lampung gagalkan penyelundupan 1.437 liter miras ilegal</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:49:30 +0700</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Tim Satgas BKO Pangkalan TNI Angkatan Laut (Lanal) Lampung menggagalkan penyelundupan 1.437 liter minuman beralkohol ...</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687477/lanal-lampung-gagalkan-penyelundupan-1437-liter-miras-ilegal</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001144494.jpg</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Polisi dalami izin ekskul sekolah di Jaksel soal temuan "airsoft gun"</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:23:36 +0700</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya mendalami keabsahan serta perizinan kegiatan ekstrakurikuler (ekskul) di salah satu sekolah di ...</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687428/polisi-dalami-izin-ekskul-sekolah-di-jaksel-soal-temuan-airsoft-gun</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000912381.jpg</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Progres LRT Jakarta Fase 1B sudah 97,99 persen, rampung Agustus</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:18:05 +0700</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>PT Waskita Karya (Persero) Tbk menyampaikan realisasi pembangunan konstruksi Light Rail Transit (LRT) Jakarta Fase 1B ...</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687411/progres-lrt-jakarta-fase-1b-sudah-9799-persen-rampung-agustus</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000318799_1.jpg</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Waka Komisi II DPR Bahtra Serap Aspirasi-Bagikan Sembako di Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:53:28 +0700</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi II DPR RI, Bahtra Banong, kunjungi tiga desa di Kolaka Timur untuk menyerap aspirasi masyarakat dan menyerahkan paket sembako.</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612339/waka-komisi-ii-dpr-bahtra-serap-aspirasi-bagikan-sembako-di-kolaka-timur</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bahtra-1786351977091_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>6 Perampok Pegawai Koperasi di Bekasi Diringkus, Ini Peran Para Pelaku</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:46:01 +0700</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Polisi menangkap enam pelaku perampokan bersenjata tajam di Cibitung, Bekasi. Mereka memiliki peran berbeda, dari pengamat hingga eksekutor.</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612318/6-perampok-pegawai-koperasi-di-bekasi-diringkus-ini-peran-para-pelaku</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/perampokan-nasabah-bank-di-siang-bolong-di-cibitung-bekasi-1786238003822_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Wamenkes Puji Kemenimipas Inisiatif CKG Masyarakat hingga Warga Binaan</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:31:22 +0700</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Wamenkes Benyamin memuji Kemenimipas atas inisiatif cek kesehatan gratis. Ia dorong masyarakat untuk periksa kesehatan secara proaktif, bukan hanya saat sakit.</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612287/wamenkes-puji-kemenimipas-inisiatif-ckg-masyarakat-hingga-warga-binaan</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/wamenkes-benyamin-paulus-octavianus-bersama-menteri-imipas-agus-andrianto-1786350504235_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Bank Mandiri-Paramount Perkuat Sinergi Bisnis Properti dan Layanan KPR</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:28:38 +0700</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Bank Mandiri dan Paramount menjalin kolaborasi untuk layanan perbankan terintegrasi, mendukung pengembangan properti berkelanjutan.</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612284/bank-mandiri-paramount-perkuat-sinergi-bisnis-properti-dan-layanan-kpr</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bank-mandiri-1786350481721_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Polda Metro Usut Kasus Sutrimo, Selidiki Dugaan Meninggal Tak Wajar</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:26:06 +0700</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menyelidiki kematian Sutrimo di depan klinik kecantikan. Polisi akan menyelidiki laporan dugaan kematian tak wajar Sutrimo.</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612278/polda-metro-usut-kasus-sutrimo-selidiki-dugaan-meninggal-tak-wajar</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dirkrimum-polda-metro-jaya-kombes-iman-imanuddin-1786346609303_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>KPK Periksa Istri Bos Blueray Terkait Pengembangan Kasus Bea Cukai</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:12:45 +0700</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>KPK terus melakukan pemeriksaan terhadap sejumlah saksi dalam pengembangan perkara korupsi importasi pada Ditjen Bea Cukai Kemenkeu.</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612234/kpk-periksa-istri-bos-blueray-terkait-pengembangan-kasus-bea-cukai</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Mensesneg Ungkap Isi Rapat Bareng Panglima-Kapolri di DPR</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:03:12 +0700</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi mengungkap hasil rapat koordinasi dengan DPR, TNI, dan Polri terkait persiapan HUT ke-81 RI dan pengamanan yang telah dilakukan.</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612222/mensesneg-ungkap-isi-rapat-bareng-panglima-kapolri-di-dpr</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/prasetyo-hadi-1784523183633_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>5 Tahun Berjalan, Alfamidi Berangkatkan Umrah 101 Karyawan Berprestasi</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:00:29 +0700</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Alfamidi berangkatkan 101 karyawan terbaik untuk umrah sebagai penghargaan atas dedikasi dan kontribusi mereka. Program ini sudah berjalan lima tahun.</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612214/5-tahun-berjalan-alfamidi-berangkatkan-umrah-101-karyawan-berprestasi</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/5-tahun-berjalan-alfamidi-berangkatkan-umrah-101-karyawan-berprestasi-1786348791560_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Sopir Taksi Online yang Cabuli Penumpang di Jakbar Jadi Tersangka</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:59:30 +0700</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Sopir taksi online (taksol) berinisial ARA (54) ditetapkan sebagai tersangka kasus pencabulan terhadap penumpang di Jakbar. Polisi juga menahan tersangka ARA.</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612210/sopir-taksi-online-yang-cabuli-penumpang-di-jakbar-jadi-tersangka</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/10/2c3bc144-0858-4a1e-9d59-2ef31566d27d_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Usut Kematian Sutrimo, Polda Metro Periksa 24 Saksi</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:55:15 +0700</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya mengusut kematian Sutrimo, pria yang ditemukan tewas di Kebayoran Baru. Sebanyak 24 saksi telah diperiksa.</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612203/usut-kematian-sutrimo-polda-metro-periksa-24-saksi</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dirkrimum-polda-metro-jaya-kombes-iman-imanuddin-1786346609303_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Identitas 8 Korban Tewas dalam Kecelakaan Drag Race di Kotamobagu Sulut</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:46:09 +0700</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Fistel Mukuan</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Kecelakaan tragis di turnamen Drag Race Kotamobagu mengakibatkan 8 tewas dan 9 luka-luka.</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612186/identitas-8-korban-tewas-dalam-kecelakaan-drag-race-di-kotamobagu-sulut</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kecelakaan-tragis-di-turnamen-drag-race-kotamobagu-mengakibatkan-8-orang-tewas-dan-9-lainnya-luka-luka-1786339477151_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>IPM Jawa Barat 2025 Capai 75,90 Poin, Tertinggi dalam 5 Tahun</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:45:14 +0700</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Indeks Pembangunan Manusia (IPM) Jabar 2025 mencapai 75,90 poin, tumbuh 1,31%. Peningkatan ini didukung oleh kesehatan, pendidikan, dan pengurangan kemiskinan.</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612144/ipm-jawa-barat-2025-capai-75-90-poin-tertinggi-dalam-5-tahun</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/13/gedung-sate-1763009965930_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Menimbang Bahaya dan Efisiensi Wacana Pilkada Tanpa Wakil</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:44:09 +0700</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>20detik Signature</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Sejauh mana wacana ini akan mempengaruhi soliditas koalisi di level daerah?</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612053/menimbang-bahaya-dan-efisiensi-wacana-pilkada-tanpa-wakil</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/detiksore-10-agustus-2026-1786345030084_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Mensesneg Minta Pemadaman Karhutla Bromo Dilakukan Sekeras-kerasnya</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:40:04 +0700</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi bahas karhutla di Bromo dan Kalimantan dalam rapat dengan DPR. Ia imbau masyarakat waspada dan koordinasi pemadaman terus dilakukan.</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612177/mensesneg-minta-pemadaman-karhutla-bromo-dilakukan-sekeras-kerasnya</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/mensesneg-prasetyo-hadi-foto-anggi-muliawatidetikcom-1786347543781_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Gelar Operasi Katarak dan Cek Kesehatan Gratis, Menimipas Beri 2 Pesan Ini</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:33:35 +0700</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Menteri Imigrasi membuka bakti kesehatan operasi katarak dan cek kesehatan gratis bagi warga hingga napi.  Pihaknya ingin melindungi hak kesehatan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612159/gelar-operasi-katarak-dan-cek-kesehatan-gratis-menimipas-beri-2-pesan-ini</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menteri-imipas-1786347052859_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Lelang di BPA Kejagung: Limit Terendah HP Rp 3.000, Tertinggi Tanah Rp 9,1 M</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:31:49 +0700</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>BPA Kejagung menggelar lelang serentak dengan limit terendah Rp 3.000 untuk ponsel dan tertinggi Rp 9,1 miliar untuk tanah.</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612156/lelang-di-bpa-kejagung-limit-terendah-hp-rp-3-000-tertinggi-tanah-rp-9-1-m</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kejagung-gelar-lelang-serentak-1786345984841_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Nilai Mahar Ekskavator hingga GWM Tank dari 'Sultan' Grobogan Capai Rp 2 M</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:26:22 +0700</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Ardian Dwi Kurnia</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Rico Putra Roberto Syah (23) mempersunting gadis pujaan hatinya, Laella Nur Fadhilah (20), dengan mahar alat berat ekskavator, sejumlah motor hingga mobil.</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612142/nilai-mahar-ekskavator-hingga-gwm-tank-dari-sultan-grobogan-capai-rp-2-m</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/mahar-pernikahan-di-grobogan-1786344143170_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Sopir Taksi Online Bersimpuh Minta Ampun Usai Cabuli Penumpang di Jakbar</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:25:34 +0700</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Seorang penumpang wanita diduga menjadi korban pelecehan sopir taksi online (taksol) di Jakbar. Pria sopir taksol tersebut telah diserahkan ke pihak kepolisian.</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612140/sopir-taksi-online-bersimpuh-minta-ampun-usai-cabuli-penumpang-di-jakbar</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/17/ilustrasi-rawan-pelecehan-seksual-taksi-online_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Kasus Kematian Sutrimo Naik Penyidikan, Dugaan Pembunuhan Berencana Diusut</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:24:27 +0700</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Kasus kematian Sutrimo di Jakarta Selatan meningkat ke tahap penyidikan. Polda Metro Jaya akan ekshumasi jenazah untuk mengungkap penyebab kematian.</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612137/kasus-kematian-sutrimo-naik-penyidikan-dugaan-pembunuhan-berencana-diusut</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dirkrimum-polda-metro-jaya-kombes-iman-imanuddin-1786346609303_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Pemprov Jabar Kawal Program 3 Juta Rumah Berjalan Efektif &amp;amp; Tepat Sasaran</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:20:41 +0700</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Pemprov Jabar berkomitmen mengawal Program 3 Juta Rumah dengan transparansi dan akuntabilitas, memastikan hunian layak bagi masyarakat yang membutuhkan.</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612113/pemprov-jabar-kawal-program-3-juta-rumah-berjalan-efektif-tepat-sasaran</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/03/geliat-hunian-subsidi-bekasi-dorong-target-program-3-juta-rumah-1772534928428_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Bareskrim Bongkar Penyelundupan 12 Kg Ganja dalam Paket Pakaian Anak</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:18:19 +0700</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Dittipidnarkoba Polri membongkar penyelundupan 12.135 gram ganja dalam truk ekspedisi dari Lampung ke Lombok</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612110/bareskrim-bongkar-penyelundupan-12-kg-ganja-dalam-paket-pakaian-anak</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bareskrim-bongkar-penyelundupan-12-kg-ganja-dok-istimewa-1786347507289_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Kejagung Gelar Lelang Serentak, Potensi Pemulihan Aset Negara Rp 289,3 M</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:14:58 +0700</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Badan Pemulihan Aset Kejagung RI menggelar lelang serentak untuk memulihkan aset negara. Kegiatan ini melibatkan 365 kejaksaan negeri.</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612105/kejagung-gelar-lelang-serentak-potensi-pemulihan-aset-negara-rp-289-3-m</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kejagung-gelar-lelang-serentak-1786345984756_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>ParagonCorp Dorong Riset Beauty Berbasis Sains Lewat Multi-Omics</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:08:49 +0700</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>ParagonCorp dan Corpora Science kolaborasi riset kecantikan berbasis sains. Fokus pada pendekatan multi-omics untuk inovasi produk yang relevan di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612098/paragoncorp-dorong-riset-beauty-berbasis-sains-lewat-multi-omics</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/paragoncorp-dorong-riset-beauty-berbasis-sains-lewat-multi-omics-1786345584385.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Handi Tewas Disekap dan Dianiaya di Sumedang, 15 Orang Diamankan</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:08:18 +0700</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Dwiky Maulana Velayati</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Pria asal Bandung, Handi (40) tewas usai diduga disekap dan dianiaya sejumlah orang di Kabupaten Sumedang, Jawa Barat.</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612095/handi-tewas-disekap-dan-dianiaya-di-sumedang-15-orang-diamankan</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/05/15/ilustrasi-pengeroyokan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Bigmo Irit Bicara Sebelum Jalani Pemeriksaan Dugaan Eksploitasi Anak</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:47:16 +0700</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo mendatangi Polda Metro Jaya terkait dugaan eksploitasi anak untuk promosi vape. Bigmo masih irit bicara sebelum diperiksa.</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612187/bigmo-irit-bicara-sebelum-jalani-pemeriksaan-dugaan-eksploitasi-anak</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bigmo-1786347973337_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Intip Foto Prewedding Romantis Felicia Tissue dan Calon Suami di Singapura</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:04:14 +0700</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Selebritas Felicia Tissue membagikan foto prewedding romantis bareng calon suami. Intip yuk momennya.</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611813/intip-foto-prewedding-romantis-felicia-tissue-dan-calon-suami-di-singapura</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/felicia-tissue-1786336097462_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Cita-cita Joanna Adelaide Zhang Gapai Fashion Internasional</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:55:10 +0700</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Joanna Adelaide Zhang, model muda serius meniti karier sebagai model. Ia aktif mengembangkan diri dan berambisi berkontribusi di industri fashion.</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612048/cita-cita-joanna-adelaide-zhang-gapai-fashion-internasional</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/joanna-adelaide-zhang-1786344847009_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Move On Bikin Dahlia Poland Lebih Happy, Cerita Mendalam soal Rangga Azies</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:06:26 +0700</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Pesinetron Dahlia Poland menjalin hubungan asmara dengan Rangga Azies. Dahlia menceritakan soal sosok Rangga.</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611982/move-on-bikin-dahlia-poland-lebih-happy-cerita-mendalam-soal-rangga-azies</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dahlia-poland-1786341189141_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Istri Ridho Illahi Sampai Masuk Rumah Sakit Gegara Dilaporkan</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:34:17 +0700</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Ridho Illahi dan istri dilaporkan atas dugaan doxing. Ia membantah tuduhan dan mengklaim sebagai korban penipuan. Ridho minta polisi usut tuntas kasus ini.</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611718/istri-ridho-illahi-sampai-masuk-rumah-sakit-gegara-dilaporkan</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/02/ridho-ilahi-1780378742153_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Pemain Timnas Dihujat Usai Gagal di AFF, Sekjen PSSI: Bully Saya, Ketum, dan Exco Saja</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:04:44 +0700</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Sejumlah pemain, seperti Rizky Ridho dan Shayne Pattynama menjadi sasaran hujatan warganet setelah skuad Merah Putih gagal melaju ke semifinal.</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866395/pemain-timnas-dihujat-usai-gagal-di-aff-sekjen-pssi-bully-saya-ketum-dan-exco-saja</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/S3Gk6ZMA8cwnXTfLfIU457lOEKY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/RESPON-KEKESALAN-SUPORTER-Sekretaris-Jenderal-PSSI-Yunus-Nusi.jpg</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Daya Saing Indonesia di Pasar Global Tak Cukup Bertumpu pada Regulasi, Perlu Institusi yang Kuat</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:04:41 +0700</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Sandiaga Uno: daya saing RI butuh institusi kredibel, bukan sekadar regulasi, untuk jamin keberlanjutan di pasar global.</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866394/daya-saing-indonesia-di-pasar-global-tak-cukup-bertumpu-pada-regulasi-perlu-institusi-yang-kuat</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1tZhdWrBDjJGHwKJYbuIwZp3BmI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/parapuan-tekstil1jpg-20250313045608.jpg</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Survei BI: Keyakinan Konsumen Juli 2026 Turun di Level 116,8</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:00:07 +0700</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Keyakinan tertinggi berasal dari kelompok usia 20-30 tahun dengan IKK 122,9 dan pengeluaran di atas Rp5 juta dengan IKK 121,2.</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866393/survei-bi-keyakinan-konsumen-juli-2026-turun-di-level-1168</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/O_cWjD8PKOltHmJKejl9Vf6Z2_U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-Bank-Indonesia-di-gedung-Bank-Indonesia.jpg</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Kasus Kapolresta Banda Aceh Masih Misteri Hampir Sepekan, Eks Kompolnas: Munculkan Spekulasi Publik</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:00:06 +0700</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Eks Komisioner Kompolnas, Poengky Indarti menyebut tidak transparannya Polri dalam mengungkap kasus itu bisa menimbulkan beragam spekulasi.</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866392/kasus-kapolresta-banda-aceh-masih-misteri-hampir-sepekan-eks-kompolnas-munculkan-spekulasi-publik</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-x6OZX7zgEAtmwNMMW-J7x43Ig8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Profil-Kombes-Pol-Andi-Kirana-Kapolresta-Banda-Aceh-yang-Diperiksa-Mabes-Polri-Hartanya-Rp369-Juta.jpg</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Di Depan Romo Magnis, Susi Pudjiastuti Kritik Kebijakan Ekspor Benih Lobster dan Tambang</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:59:45 +0700</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Susi Pudjiastuti, menyampaikan kritik berbagai kebijakan pengelolaan sumber daya alam yang dinilainya melenceng jauh dari prinsip keberlanjutan.</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866391/di-depan-romo-magnis-susi-pudjiastuti-kritik-kebijakan-ekspor-benih-lobster-dan-tambang</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/w6G-ZSeZpORi61IccKHaV-264ks=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Susi-Pudjiastuti-2026081.jpg</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Menpora Erick Thohir: Sepakbola Indonesia Sudah Bangkit, FIFA ASEAN Jadi Momentum Berikutnya</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:59:43 +0700</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Pernyataan Erick tersebut disampaikan setelah Presiden Prabowo Subianto sebelumnya mengungkapkan kesedihannya terhadap prestasi sepak bola</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866390/menpora-erick-thohir-sepakbola-indonesia-sudah-bangkit-fifa-asean-jadi-momentum-berikutnya</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1a7ILPPDpySjbwe7SeQea4Z15Rg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Timnas-Indonesia-Dicukur-Timnas-Vietnam-3-0_20260804_065849.jpg</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Aksi Pecah Kaca Mobil di Cikarang Selatan Digagalkan Korban, Laptop Jadi Barang Bukti</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:59:16 +0700</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Unit Reskrim Polsek Cikarang Selatan berhasil meringkus pelaku yang berinisial A (31) setelah aksinya dipergoki oleh korban dan warga sekitar.</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866389/aksi-pecah-kaca-mobil-di-cikarang-selatan-digagalkan-korban-laptop-jadi-barang-bukti</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/A-CEzVYKH-6NVNQuz5KSQjA2IG8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pecah-kaca12344.jpg</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Pentingnya Integritas, Profesionalisme hingga Kejujuran Bagi para Calon Advokat</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:58:50 +0700</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Menurut Asido, besaran honorarium yang diterima advokat akan sebanding dengan tingkat profesionalisme dan integritas yang dimiliki.</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866388/pentingnya-integritas-profesionalisme-hingga-kejujuran-bagi-para-calon-advokat</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MzWZ4bUGYvz5t9CGIoqCSpTiilc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ketua-DPC-Peradi-Jakarta-Barat-Jakbar-Suhendra-Asido-Hutabarat-21.jpg</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 7 Halaman 86 Kurikulum Merdeka Edisi Revisi: Aktivitas 6</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:57:18 +0700</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban mata pelajaran IPS Kelas 7 Halaman 86 Kurikulum Merdeka terdapat tugas Aktivitas 6 pada Tema 2.</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866387/kunci-jawaban-ips-kelas-7-halaman-86-kurikulum-merdeka-edisi-revisi-aktivitas-6</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/I26CNXmBVbp-YSqMKF_baAJSXHw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SISWA-SMP-BELAJAR-11.jpg</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Malaysia Kena Mental Jumpa Vietnam di Semifinal, Media Lokal Isyaratkan Bendera Putih</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:56:59 +0700</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Media lokal Malaysia memberikan sorotan tajam soal peluang Harimau Malaya melewati hadangan Vietnam di semifinal Piala AFF 2026.</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866386/malaysia-kena-mental-jumpa-vietnam-di-semifinal-media-lokal-isyaratkan-bendera-putih</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-98ggpKRB1uB5i4St1EJXG_XyiE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Aksi-pemain-naturalisasi-Malaysia-asal-Brasil-Endrick-melawan-Myanmar-di-Piala-AFF-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2.500 Pelari dan Puluhan UMKM Bakal Ramaikan GBK Akhir Pekan Ini</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:56:46 +0700</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Sebanyak 2.500 pelari dijadwalkan ambil bagian dalam lomba lari 5 kilometer, sementara lebih dari 50 tenant UMKM akan mengisi area Pasar Rakyat.</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866385/2500-pelari-dan-puluhan-umkm-bakal-ramaikan-gbk-akhir-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MHSNL8zy_dsHnwng0j92OIefER0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Konferensi-pers-Sabana-Fun-Run-5K.jpg</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>TNI AL Gagalkan Penyelundupan 1,3 Ton Ketamin di Kepulauan Riau, BNN: Kapal Berangkat dari Myanmar</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:54:53 +0700</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Irjen Pol. Aswin Sipayung mengungkap, narkoba jenis ketamin itu berangkat dari Myanmar, tetapi bahan bakunya bisa jadi berasal dari negara lain.</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866384/tni-al-gagalkan-penyelundupan-13-ton-ketamin-di-kepulauan-riau-bnn-kapal-berangkat-dari-myanmar</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8HBTVeSs3DE5EfXgfrdHUnDLAYg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ketamin-smuggled-in-kepri.jpg</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Sempat Dikira Batu, Bangkai Kapal Romawi Berusia 2.100 Tahun Ditemukan di Lepas Pantai Sisilia</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:53:13 +0700</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Bangkai kapal Romawi berusia 2.000 tahun ditemukan di Sisilia dengan ratusan amphora, jangkar timah, dan jejak perdagangan kuno</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866383/sempat-dikira-batu-bangkai-kapal-romawi-berusia-2100-tahun-ditemukan-di-lepas-pantai-sisilia</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GSBoeFwvYhxfMltzaa9rqVR4pP4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kapalromawi111111.jpg</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>HUT ke-81 RI, Aturan Ganjil Genap Jakarta Ditiadakan pada Senin, 17 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:51:16 +0700</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Ganjil genap Jakarta ditiadakan pada Senin, 17 Agustus 2026 karena bertepatan dengan hari libur nasional HUT ke-81 Kemerdekaan RI.</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866382/hut-ke-81-ri-aturan-ganjil-genap-jakarta-ditiadakan-pada-senin-17-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tOn_FEwviage4IeYPaG0pAtLxPc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ganjil-Genap-Jakarta-Ditiadakan-17-Agustus-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Sukses Gelar Intimate Concert di Solo, Sandhy Sondoro Ungkap Rencana Manggung di Berlin</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:50:32 +0700</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Sukses menggelar intimate concert di Solo, Sandhy Sondoro mengungkap rencananya manggung di Berlin, Jerman.</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866381/sukses-gelar-intimate-concert-di-solo-sandhy-sondoro-ungkap-rencana-manggung-di-berlin</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/uyyHX7_ufaGmAtUxQud4zKsjaz8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penyanyi-Sandhy-Sondoro-saat-berkunjung-ke-Kota-Solo.jpg</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Buruh Temui Cak Imin, Berharap PKB Kawal Penyusunan RUU Ketenagakerjaan yang Berkeadilan</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:48:31 +0700</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Dalam pertemuan, seluruh pimpinan konfederasi buruh menyampaikan materi usulan RUU Ketenagakerjaan yang telah disusun oleh Tim Perumus KBPBI.</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866380/buruh-temui-cak-imin-berharap-pkb-kawal-penyusunan-ruu-ketenagakerjaan-yang-berkeadilan</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/jjhDevOwhBOf3GoT-gyXvkMns3o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KBPBI-bertemu-Ketua-Umum-Partai-Kebangkitan-Bangsa-PKB-Muhaimin-Iskandar.jpg</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Menpora: FIFA ASEAN Dapat Restu Presiden Prabowo, Siap Bergulir di Jakarta dan Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:47:17 +0700</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Saat ini, pemerintah masih melakukan sinkronisasi terkait sejumlah poin dalam host contract dengan FIFA.</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866379/menpora-fifa-asean-dapat-restu-presiden-prabowo-siap-bergulir-di-jakarta-dan-jawa-barat</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0eancXCVg1b2Aj7dFU9LvB2XTRo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/FIFA-ASEAN-CUP-2026-Erick-Thohir.jpg</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Anak Sering Memiringkan Kepala Saat Menonton TV? Bisa Jadi Tanda Mata Juling</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:45:19 +0700</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Posisi kepala yang terus-menerus miring bisa menjadi salah satu tanda adanya gangguan penglihatan, termasuk mata juling atau strabismus.</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866378/anak-sering-memiringkan-kepala-saat-menonton-tv-bisa-jadi-tanda-mata-juling</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/dbdzpoPuf6w-ALb48UZw4faQCBo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mom-and-kids-usia-pas-bagi-anak-menonton-film-horor_20210127_150945.jpg</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Alexander Isak Mulai Buktikan Harga Rp2,9 Triliun, Liverpool Justru Punya Masalah di Lini Belakang</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:40:51 +0700</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Striker Liverpool, Alexander Isak mulai tunjukkan ketajamannya meski kalah 2-3 dari AS Monaco di pramusim.</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866377/alexander-isak-mulai-buktikan-harga-rp29-triliun-liverpool-justru-punya-masalah-di-lini-belakang</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/auSfGFfzUQwduX1Vb0Vc3Yfa5Ng=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-klub-Inggris-Liverpool.jpg</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Luka di 16 Besar Kanada Open 2026, Alex Eala dan Sabalenka Akhirnya Tumbang</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:39:53 +0700</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Petenis putri Filipina, Alex Eala, tumbang di babak 16 besar Kanada Open 2026 setelah kalah dari Belinda Bencic.</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866376/luka-di-16-besar-kanada-open-2026-alex-eala-dan-sabalenka-akhirnya-tumbang</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0fq3TCb3sGuyya0TZ8FScanSb4k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Alex-Eala-Janice-Tjen-Abu-Dhabi-Open-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Jakarta Kejar 100 Persen Layanan Air Perpipaan, 7.000 Km Pipa Baru Disiapkan</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:00:36 +0700</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Jakarta menargetkan cakupan layanan air perpipaan mencapai 100 persen pada 2029, sehingga pembangunan jaringan baru perlu digenjot dalam beberapa tahun ke depan. PAM Jaya menyiapkan sekitar 7.000...</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjq0u416/jakarta-kejar-100-persen-layanan-air-perpipaan-7000-km-pipa-baru-disiapkan</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/sambungan-air-perpipaan-pam-jaya-di-salah-satu-rumah_260611193346-578.jpeg</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Proyek LRT Jakarta Fase 1B Capai 97,99 Persen, Siap Masuk Tahap Akhir</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:48:52 +0700</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Direktur Operasi II Waskita Karya Paulus Budi Kartiko memastikan percepatan penyelesaian konstruksi Light Rail Transit (LRT) Jakarta Fase 1B rute Velodrome-Manggarai. Budi menyebut realisasi pembangunannya sudah...</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjptg370/proyek-lrt-jakarta-fase-1b-capai-9799-persen-siap-masuk-tahap-akhir</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260714130637-315.png</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Destry Damayanti Jadi Calon Tunggal Gubernur BI?</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:29:03 +0700</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Menteri Sekretaris Negara (Mensesneg) RI Prasetyo Hadi membocorkan posisi Gubernur Bank Indonesia (BI) akan diisi oleh sosok Destry Damayanti. Destry disebut merupakan calon tunggal, berdasarkan Surat...</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjowf370/destry-damayanti-jadi-calon-tunggal-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_250706154127-373.png</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Harga Gabah Naik, Kebijakan Bulog Pacu Petani Penajam Paser Utara Garap Sawah</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:00:49 +0700</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Erdy Nasrul</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Kebijakan Perum Bulog menyerap gabah kering panen (GKP) petani dengan harga Rp 6.500 per kilogram (kg) memacu semangat petani di Kabupaten Penajam Paser Utara, Kalimantan Timur, untuk kembali...</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjnld451/harga-gabah-naik-kebijakan-bulog-pacu-petani-penajam-paser-utara-garap-sawah</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/070704400-1785595198-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Danantara Housing Expo 2026, BRI Pimpin Kolaborasi Himbara Perkuat Pembiayaan Perumahan</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:50:16 +0700</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Dwi Murdaningsih</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA - Danantara akan menggelar Danantara Housing Expo 2026 sebagai bagian dari dukungan terhadap Program 3 Juta Rumah untuk memperluas akses masyarakat terhadap kepemilikan rumah. Pameran yang berlangsung pada...</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjn3s368/danantara-housing-expo-2026-bri-pimpin-kolaborasi-himbara-perkuat-pembiayaan-perumahan</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/danantara-akan-menggelar-danantara-housing-expo-2026-sebagai-bagian_260810144933-492.jpeg</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Survei IPO: Menteri Bahlil Masuk Tiga Besar Menteri Berkinerja Terbaik</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:38:00 +0700</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia masuk dalam jajaran menteri yang mendapat penilaian positif dari masyarakat berdasarkan survei terbaru Indonesia Political Opinion (IPO)....</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjeai522/survei-ipo-menteri-bahlil-masuk-tiga-besar-menteri-berkinerja-terbaik</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260414182044-589.png</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Digitalisasi Inspeksi Jadi Bagian Pembenahan Standar Keamanan Kendaraan Niaga Hino</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:18:00 +0700</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, TANGERANG — Kualitas kendaraan niaga tidak hanya ditentukan oleh performa mesin dan sasis. Proses pemeriksaan sebelum kendaraan diserahkan kepada pelanggan serta pembangunan bodi juga menjadi bagian penting untuk menjamin...</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjl55348/digitalisasi-inspeksi-jadi-bagian-pembenahan-standar-keamanan-kendaraan-niaga-hino</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/hino-meluncurkan-bus-rm-280-abs-retarder-di-giias_260809230919-332.jpeg</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Mensesneg Tanggapi Isu Demo Besar Agustus: Everything is Okay</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:30:39 +0700</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Panglima kembali memastikan, TNI menjamin keamanan masyarakat di seluruh Indonesia.</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266318/mensesneg-tanggapi-isu-demo-besar-agustus-everything-is-okay</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/R0kp0oU3zMOP5Ak0nHwSztd5bkc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4147188/original/080928900_1662370991-WhatsApp_Image_2022-09-05_at_16.35.03.jpeg</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Polisi Ekshumasi Jenazah Sutrimo Rabu Lusa</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:21:51 +0700</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Sutrimo ditemukan tak sadarkan diri kemudian meninggal di depan Klinik Mordent, kawasan Kebayoran Baru.</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266312/polisi-ekshumasi-jenazah-sutrimo-rabu-lusa</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/-fx7HAZbdkTLuLva3_Hw8lwALys=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9308334/original/005435400_1785137531-64336.jpg</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>336 Ribu Orang 'War Ticket' Upacara HUT RI di Istana, Pendaftar Baru Diprioritaskan</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:14:18 +0700</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Panitia juga menambah blok baru yang dapat menambah sekitar 3.400 tamu undangan.</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266299/336-ribu-orang-war-ticket-upacara-hut-ri-di-istana-pendaftar-baru-diprioritaskan</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/_br72lp4vVWS5CLZakL8R6QgFI4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/7767979/original/011455400_1780578714-IMG_3908__1_.jpeg</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>336 Ribu Orang Berebut Ikut Upacara HUT RI di Istana, Kuota Ditambah</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:00:55 +0700</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Pihak Istana akhirnya menambah jumlah kuota pendaftar agar semakin banyak masyarakat umum dapat mengikuti upacara HUT ke-81 RI.</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266280/336-ribu-orang-berebut-ikut-upacara-hut-ri-di-istana-kuota-ditambah</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/xd05yL1gtFEzgEEMh1AEfsGlgYk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5318121/original/001265800_1755424797-WhatsApp_Image_2025-08-17_at_13.20.59_dea7c4b9.jpg</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Nusron Pasang Aturan Baru di BPN, Pelanggar SOP Bisa Dipecat</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Nusron Wahid menyiapkan sanksi berjenjang hingga pemecatan bagi pelanggar SOP. Layanan balik nama ditarget rampung maksimal 10 hari mulai 17 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266235/nusron-pasang-aturan-baru-di-bpn-pelanggar-sop-bisa-dipecat</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/U9kYHo2CdlvOK5De-Tc6x-0ZTbY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320349/original/059905900_1786345958-c3de2af6-a756-4359-8e19-41568f4252f6.jpg</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Cerita Siti Khodijah Orang Tertua di Indonesia, Usianya 120 Tahun</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:27:16 +0700</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Siti Khodijah lahir pada 12 Februari 1906.</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266229/cerita-siti-khodijah-orang-tertua-di-indonesia-usianya-120-tahun</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/xwjChc-Gi5-CxfXayQGu4Np5IzM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320358/original/009109700_1786346832-WhatsApp_Image_2026-08-10_at_14.13.17.jpeg</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>3 Anak Meninggal Suspek Rabies di Buleleng, Cakupan Vaksinasi Anjing Baru 31,91 Persen</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:10:33 +0700</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Tiga anak di Buleleng meninggal akibat suspek rabies sepanjang 2026. Tingginya kasus gigitan hewan dan rendahnya vaksinasi jadi alarm bahaya.</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>https://denpasar.kompas.com/read/2026/08/10/160729678/3-anak-meninggal-suspek-rabies-di-buleleng-cakupan-vaksinasi-anjing-baru</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/6iPjUOAoSwNhbIjjLVCAE1mQ7qs=/0x5:993x667/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2023/06/20/649137319ddc5.jpg</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>PDAM Mati 2 Hari di Indramayu, Warga sampai Beli Air Galon, Berangkat Kerja Tanpa Mandi</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:10:33 +0700</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Aliran PDAM di sejumlah wilayah Indramayu mati dua hari akibat Sungai Cimanuk menyusut drastis. Warga sampai membeli air galon untuk mandi.</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>https://bandung.kompas.com/read/2026/08/10/155404078/pdam-mati-2-hari-di-indramayu-warga-sampai-beli-air-galon-berangkat-kerja</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/y7sfy-APJaCQ4soTX4PNYEEaaKk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a799056e1e63.jpeg</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2 Orang di Jateng Ditangkap, Diduga Produksi dan Suplai Uang Palsu via Facebook</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:10:33 +0700</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Polisi membongkar jaringan produksi dan peredaran uang palsu di Jawa Tengah yang dijual via Facebook.</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/10/153517578/2-orang-di-jateng-ditangkap-diduga-produksi-dan-suplai-uang-palsu-via</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/P99V0U2lG97xa_y2PcwTKikfWxA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a798aebb20ff.jpeg</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I485"/>
+  <autoFilter ref="A1:I602"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$602</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$719</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I602"/>
+  <dimension ref="A1:I719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -28733,8 +28733,5507 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Hoaks! Rakyat geruduk rumah Jokowi dan temukan bunker Rp6.000 triliun</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:53:56 +0700</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan video di Facebook menarasikan bahwa Polri menemukan bunker ...</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687819/hoaks-rakyat-geruduk-rumah-jokowi-dan-temukan-bunker-rp6000-triliun</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/10/153B6907-ED2B-46A5-8E90-414E524125C4.jpeg</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Wamenkes ingin klinik lapas-rutan ikut layani cek kesehatan gratis</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:53:31 +0700</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Kesehatan Benjamin Paulus Octavianus meminta klinik kesehatan di lembaga pemasyarakatan (lapas) dan rumah ...</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687815/wamenkes-ingin-klinik-lapas-rutan-ikut-layani-cek-kesehatan-gratis</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000012985.jpg</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>IBOS Expo 2026 hadirkan 100 lebih peluang bisnis bagi masyarakat</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:52:58 +0700</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Pameran peluang bisnis The 2nd Indonesia Brand &amp; Business Opportunity Show (IBOS Expo) 2026 resmi dibuka di Bekasi, ...</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687812/ibos-expo-2026-hadirkan-100-lebih-peluang-bisnis-bagi-masyarakat</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-09-at-4.55.56-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Hoaks! Komdigi blokir pemberitaan aksi demonstrasi Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:52:35 +0700</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan video di Facebook menampilkan foto seperti aksi demonstrasi ...</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687811/hoaks-komdigi-blokir-pemberitaan-aksi-demonstrasi-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/IMG_20251027_100820.jpg</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Target produksi tebu Lampung capai 11 juta ton pada 2026</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:52:26 +0700</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Dinas Perkebunan (Disbun) Provinsi Lampung menyatakan bahwa target produksi tebu di provinsi tersebut pada 2026 ...</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687809/target-produksi-tebu-lampung-capai-11-juta-ton-pada-2026</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260810-WA0028-1_1.jpg</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Hoaks! Aturan tilang baru 2026, denda tilang naik hingga 150 persen</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:50:52 +0700</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menampilkan foto anggota Komisi Percepatan ...</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687805/hoaks-aturan-tilang-baru-2026-denda-tilang-naik-hingga-150-persen</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/11/penggunaan-alat-tilang-etle-mobile-di-kota-bogor-2726774.jpg</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>FMIPA UI siap petakan nilai karbon mangrove hitung potensi ekonomi</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Dekan Fakultas Matematika dan Ilmu Pengetahuan Alam Universitas Indonesia (UI) Tito Latif Indra menyatakan kesiapan ...</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687803/fmipa-ui-siap-petakan-nilai-karbon-mangrove-hitung-potensi-ekonomi</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810_094601.jpg</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Angkutan Batu Bara KAI Cetak Rekor Bulanan Tertinggi 2026, Capai 5,13 Juta Ton pada Juli</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:49:46 +0700</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) mencatat volume angkutan batu bara sebesar 5.127.674 ton pada Juli 2026, menjadi ...</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687797/angkutan-batu-bara-kai-cetak-rekor-bulanan-tertinggi-2026-capai-513-juta-ton-pada-juli</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/angkutan-batu-bara.jpg</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Mengejar ketertinggalan realisasi, Pemkab Nagan Raya bentuk tim PRR</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:49:42 +0700</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kabupaten Nagan Raya, Aceh, bentuk Tim Satgas Percepatan Rehabilitasi dan Rekonstruksi (PRR) yang ...</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687731/mengejar-ketertinggalan-realisasi-pemkab-nagan-raya-bentuk-tim-prr</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENGEJAR-KETERTINGGALAN-REALISASI-PEMKAB-NAGAN-RAYA-BENTUK-TIM-PRR.jpg</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Houthi klaim serangan rudal, drone ke pasukan yang didukung Saudi</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:49:29 +0700</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Kelompok Houthi Yaman pada Minggu (9/8) mengklaim telah melancarkan serangan berskala besar menggunakan rudal balistik ...</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687793/houthi-klaim-serangan-rudal-drone-ke-pasukan-yang-didukung-saudi</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000004006.jpg</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Mengadu ke DPRD DIY, peternak ayam petelur bagikan ayam ke warga</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:47:31 +0700</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>ANTARA - Ribuan Ayam Petelur dibagikan secara gratis kepada warga dan wisatawan di ruas jalan Malioboro, Senin (10/8). ...</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687748/mengadu-ke-dprd-diy-peternak-ayam-petelur-bagikan-ayam-ke-warga</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENGADU-KE-DPRD-DIY-PETENAK-AYAM-PETELUR-BAGIKAN-AYAM-KE-WARGA_2.jpg</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Persib latihan di Bali</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:45:20 +0700</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Persib menggelar latihan di Bali sebagai bagian dari persiapan menghadapi musim 2026/2027, mulai 11 Agustus hingga 19 ...</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687791/persib-latihan-di-bali</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_9043.jpeg</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>BNPB: Penanganan gempa Yogyakarta pembelajaran penting kebencanaan</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:45:18 +0700</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Deputi Bidang Sistem dan Strategi Badan Nasional Penanggulangan Bencana (BNPB Raditya Jati mengatakan penanganan gempa ...</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687787/bnpb-penanganan-gempa-yogyakarta-pembelajaran-penting-kebencanaan</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_171519.jpg</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Polri tetapkan lima tersangka peredaran narkoba di Five Stars Bali</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:43:00 +0700</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Direktorat Tindak Pidana Narkoba (Dittipidnarkoba) Bareskrim Polri menetapkan lima tersangka dalam kasus dugaan ...</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687785/polri-tetapkan-lima-tersangka-peredaran-narkoba-di-five-stars-bali</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000087617.jpg</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>BNPB sebut sepuluh provinsi dikepung karhutla</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:42:49 +0700</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Fenomena kebakaran hutan dan lahan (karhutla) mengepung belasan kabupaten/kota di sepuluh provinsi Indonesia sepanjang ...</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687784/bnpb-sebut-sepuluh-provinsi-dikepung-karhutla</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Penutupan-Wisata-Bromo-100826-IS-1.jpg</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Klok tegaskan timnas akan belajar dari kegagalan pada Piala AFF</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:40:03 +0700</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Gelandang timnas Indonesia Marc Klok menyatakan Garuda akan belajar dari kegagalan dalam  Piala AFF 2026 setelah ...</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687781/klok-tegaskan-timnas-akan-belajar-dari-kegagalan-pada-piala-aff</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833572.jpg</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>KPEI catat nilai penyelesaian transaksi harian bursa naik 48 persen</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:39:24 +0700</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>PT Kliring Penjaminan Efek Indonesia (KPEI) mencatat rata-rata nilai penyelesaian transaksi harian bursa mencapai ...</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687779/kpei-catat-nilai-penyelesaian-transaksi-harian-bursa-naik-48-persen</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000179267.jpg</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>PM Inggris umumkan langkah atasi diskon sesat dan jebakan langganan</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:38:49 +0700</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Perdana Menteri (PM) Inggris Andy Burnham pada Minggu (9/8) mengumumkan langkah-langkah untuk menindak diskon yang ...</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687777/pm-inggris-umumkan-langkah-atasi-diskon-sesat-dan-jebakan-langganan</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CjkinzN000010_20260810_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Pekerja informal sektor persampahan dapat diskon iuran JKK-JKM</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:37:45 +0700</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli mengatakan pemerintah memberikan pelindungan jaminan sosial bagi pekerja ...</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687776/pekerja-informal-sektor-persampahan-dapat-diskon-iuran-jkk-jkm</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/e3f92f77-7f7c-44e4-b5c3-c4048ec96cbd.jpeg</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Prabowo perintahkan penanganan maksimal karhutla saat El Nino</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:37:14 +0700</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menginstruksikan penanganan kebakaran hutan dan lahan (karhutla) secara maksimal dan ...</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687772/prabowo-perintahkan-penanganan-maksimal-karhutla-saat-el-nino</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000403254.jpg</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Mahasiswa raih juara hadirkan perangkat pemantau berbasis keringat</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:36:15 +0700</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Mahasiswi Fakultas Kedokteran, Tiffney Tyara Setyoko, meraih juara pertama program sarjana pemilihan mahasiswa ...</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687769/mahasiswa-raih-juara-hadirkan-perangkat-pemantau-berbasis-keringat</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Universitas-Pelita-Harapan-FK-UPH.jpeg</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Konsumen mulai tinggalkan patokan lama dalam memilih kaca film</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:35:52 +0700</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Produsen kaca film asal Jepang, Wincos menilai adanya perubahan cara pandang konsumen dalam menentukan pilihan untuk ...</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5687767/konsumen-mulai-tinggalkan-patokan-lama-dalam-memilih-kaca-film</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/FOTO-5-1.jpg</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Menhub: Perpres ojol hanya atur kendaraan roda dua</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:34:22 +0700</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi mengatakan peraturan presiden (perpres) terkait ojek daring (ojol) ...</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687765/menhub-perpres-ojol-hanya-atur-kendaraan-roda-dua</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/4813a59c-936d-477b-b01b-f0a126d4b2fe.jpeg</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>IHSG ditutup melemah seiring sentimen domestik dan global</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:33:35 +0700</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin sore ditutup melemah seiring adanya kombinasi ...</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687763/ihsg-ditutup-melemah-seiring-sentimen-domestik-dan-global</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/ihsg-ditutup-menguat-6594-poin-2836668.jpg</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Iran sebut pembicaraan Selat Hormuz dengan Oman berjalan konstruktif</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:31:14 +0700</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Iran pada Senin mengatakan bahwa perundingan dengan Oman terkait jalur pelayaran melalui Selat Hormuz berlangsung ...</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687759/iran-sebut-pembicaraan-selat-hormuz-dengan-oman-berjalan-konstruktif</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1001014481.jpg</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>UB terima 57 mahasiswa asing program "full degree" dari 35 negara</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:26:39 +0700</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Wakil Rektor Bidang Akademik (WR I) Universitas Brawijaya (UB), Prof Dr Imam Santoso mengatakan bahwa kampus tersebut ...</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687755/ub-terima-57-mahasiswa-asing-program-full-degree-dari-35-negara</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/mabaub.jpeg</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Farhan: Husein Sastranegara kini berstatus bandar udara internasional</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:25:14 +0700</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Wali Kota Bandung Muhammad Farhan menyebut Bandara Husein Sastranegara Bandung kini berstatus menjadi bandar udara ...</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687753/farhan-husein-sastranegara-kini-berstatus-bandar-udara-internasional</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/6d752650-be28-4984-b3cb-9f90954255cf.jpeg</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Pemerintah berupaya padamkan karhutla lewat modifikasi cuaca</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:24:30 +0700</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Politik dan Keamanan (Menko Polkam) Djamari Chaniago mengatakan pemerintah tengah berupaya ...</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687752/pemerintah-berupaya-padamkan-karhutla-lewat-modifikasi-cuaca</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/rakor-penanganan-kebakaran-hutan-dan-lahan-2838473.jpg</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Istana tambah 3.400 kuota upacara HUT RI, pendaftaran buka Selasa</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:21:36 +0700</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan tambahan 3.400 kuota masyarakat untuk mengikuti Upacara HUT Ke-81 ...</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687744/istana-tambah-3400-kuota-upacara-hut-ri-pendaftaran-buka-selasa</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_1020.jpeg</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Dekranasda Jakpus perluas pasar UMKM lewat "Goes to Mall"</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:20:37 +0700</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Dewan Kerajinan Nasional Daerah (Dekranasda) Jakarta Pusat memanfaatkan kegiatan Dekranasda Goes to Mall sebagai ruang ...</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687741/dekranasda-jakpus-perluas-pasar-umkm-lewat-goes-to-mall</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000835771.jpg</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Pemkab Madiun percepat layanan izin usaha lewat program Jempol Mas Har</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:20:29 +0700</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten (Pemkab) Madiun, Jawa Timur, mempercepat layanan perizinan usaha bagi masyarakat dengan ...</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687737/pemkab-madiun-percepat-layanan-izin-usaha-lewat-program-jempol-mas-har</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/jempol-mas-har.jpeg</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Wisatawan terdampak penutupan Bromo bisa minta pengembalian dana</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:20:08 +0700</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Kementerian Pariwisata mengatakan wisatawan yang telah membeli tiket daring untuk kunjungan ke kawasan Gunung Bromo ...</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687735/wisatawan-terdampak-penutupan-bromo-bisa-minta-pengembalian-dana</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-15.54.09.jpeg</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>"Petal" milik Ariana Grande masuk daftar nomor 1 Billboard 200</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:17:41 +0700</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Penyanyi Ariana Grande berhasil meraih album nomor 1 melalui album ke delapan miliknya "Petal" pada tangga ...</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687728/petal-milik-ariana-grande-masuk-daftar-nomor-1-billboard-200</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_0569.jpeg</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Iraola tak puas dengan permainan Liverpool</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:15:04 +0700</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Pelatih kepala Liverpool Andoni Iraola manyatakan tak puas dengan permainan timnya setelah kalah 2-3 dari AS Monaco ...</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687727/iraola-tak-puas-dengan-permainan-liverpool</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/10/25/20191025-liverpool-01.jpg</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Inspektorat temukan Rp13 miliar pengeluaran BUMD tanpa laporan</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:10:18 +0700</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Inspektorat Provinsi Papua Barat menemukan pengeluaran sekitar Rp13 miliar tanpa laporan pertanggungjawaban dalam ...</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687723/inspektorat-temukan-rp13-miliar-pengeluaran-bumd-tanpa-laporan</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/25097.jpg</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>TNBTS sebut penataan JLKT capai 65 persen dan ditarget selesai Oktober</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:09:54 +0700</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Balai Besar Taman Nasional Bromo Tengger Semeru (TNBTS) menyebut proses penataan Jalur Lingkar Kaldera Tengger (JLKT) ...</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687721/tnbts-sebut-penataan-jlkt-capai-65-persen-dan-ditarget-selesai-oktober</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001411454.jpg</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Ini alasan Pramono pilih Transjakarta kelola transportasi ke Pulau Seribu</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:07:13 +0700</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung Wibowo mengaku menginginkan agar transportasi ke Pulau Seribu dikelola oleh ...</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687720/ini-alasan-pramono-pilih-transjakarta-kelola-transportasi-ke-pulau-seribu</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_6663.jpeg</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Arifah: Satuan Pendidikan Ramah Anak, untuk lingkungan pendidikan aman</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:03:22 +0700</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Menteri Pemberdayaan Perempuan dan Perlindungan Anak Arifah Fauzi menekankan pentingnya sekolah menerapkan sistem ...</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687716/arifah-satuan-pendidikan-ramah-anak-untuk-lingkungan-pendidikan-aman</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/WhatsApp-Image-2026-08-06-at-07.47.25.jpeg</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Wamenkes: Operasi katarak gratis beri asa 500 warga Banyumas Raya</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:03:00 +0700</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Kesehatan Dante Saksono Harbuwono mengatakan sebanyak 500 warga di wilayah Banyumas Raya, Jawa Tengah, ...</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687715/wamenkes-operasi-katarak-gratis-beri-asa-500-warga-banyumas-raya</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/17861586896a769e61794212.32822214.jpg</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Pemkot Jakpus minta pengembang segera sertifikatkan aset fasos fasum</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:01:50 +0700</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Administrasi Jakarta Pusat (Jakpus) meminta pengembang agar segera menyertifikatkan lahan ...</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687711/pemkot-jakpus-minta-pengembang-segera-sertifikatkan-aset-fasos-fasum</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000835733.jpg</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Kunjungan ke media pemeran Film Bisikan Desa Gringsing</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:59:19 +0700</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Aktris Aghniny Haque (kiri), Fatmah Faisal Nahdi (tengah), dan Wida Hesti Putri (kanan) berpose saat media visit ke ...</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687709/kunjungan-ke-media-pemeran-film-bisikan-desa-gringsing</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Media-visit-pemeran-film-Bisikan-Desa-Gringsing-100826-TAL-2.jpg</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Dubes UEA: Operasi katarak pulihkan penglihatan, bangun kemandirian</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:56:59 +0700</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Duta Besar Uni Emirat Arab (UEA) untuk Indonesia Abdulla Salem Al Dhaheri mengatakan, operasi katarak bukan hanya ...</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687707/dubes-uea-operasi-katarak-pulihkan-penglihatan-bangun-kemandirian</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/17861599386a76a34254e6f8.41673327.jpg</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Tiga tahun berkarya, Garuda TV gelar "Mahayuga" sebagai langkah baru</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:55:46 +0700</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Garuda TV merayakan Hari Ulang Tahun (HUT) ke-3 bertajuk "Mahayuga" yang menjadi momentum untuk melihat ...</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687703/tiga-tahun-berkarya-garuda-tv-gelar-mahayuga-sebagai-langkah-baru</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/36fee7a6-0b65-4ee6-a6ef-d438709afcc0.jpeg</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Gulkarmat padamkan kebakaran lahan di dekat Stasiun Kampung Bandan</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:55:04 +0700</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Petugas Suku Dinas Penanggulangan Kebakaran dan Penyelamatan (Sudin Gulkarmat) Jakarta Utara dan Kepulauan Seribu ...</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687700/gulkarmat-padamkan-kebakaran-lahan-di-dekat-stasiun-kampung-bandan</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_4784.jpeg</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Komisi VII DPR ingin turis asing tak hanya kenal Bali dan Labuan Bajo</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:54:18 +0700</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Komisi VII DPR RI mendorong pengembangan destinasi pariwisata di wilayah Nusa Tenggara Barat (NTB) agar terjadi ...</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687699/komisi-vii-dpr-ingin-turis-asing-tak-hanya-kenal-bali-dan-labuan-bajo</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001446513.jpg</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Pemkab Jayawijaya dorong pelestarian budaya melalui karnaval</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:53:29 +0700</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten (Pemkab) Jayawijaya, Papua Pegunungan melalui Dinas Kebudayaan dan Pariwisata (Disbudpar) setempat ...</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687695/pemkab-jayawijaya-dorong-pelestarian-budaya-melalui-karnaval</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/MG_7541.jpg</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Ribuan warga Ceuta gelar unjuk rasa tuntut solusi krisis migran</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:52:56 +0700</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Ribuan warga mengikuti aksi unjuk rasa yang digelar oleh empat komunitas agama utama di Ceuta, Spanyol, untuk menuntut ...</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687693/ribuan-warga-ceuta-gelar-unjuk-rasa-tuntut-solusi-krisis-migran</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/thumbs_b_c_61b9b5a45b45b992cb574d4b0b9e38a2.jpg</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Pemkot Cilegon pastikan tak ada data ganda penerima manfaat MBG</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:52:24 +0700</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Cilegon memastikan tak ada data ganda penerima manfaat pada program Makan Bergizi Gratis (MBG) ...</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687665/pemkot-cilegon-pastikan-tak-ada-data-ganda-penerima-manfaat-mbg</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-CILEGON-PASTIKAN-TAK-ADA-DATA-GANDA-PENERIMA-MANFAAT-MBG.jpg</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Lima tim Indonesia bidik juara FFWS SEA 2026 Fall di Surabaya</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:52:04 +0700</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Lima tim Indonesia akan memburu gelar juara Free Fire World Series Southeast Asia (FFWS SEA) 2026 Fall yang berlangsung ...</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687692/lima-tim-indonesia-bidik-juara-ffws-sea-2026-fall-di-surabaya</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Kick-off-FFWS-SEA-2026-Fall.jpeg</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>BNPB: Pemadaman kebakaran Gunung Bromo diperluas ke 2 titik hari ini</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:51:42 +0700</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Kepala Badan Nasional Penanggulangan Bencana (BNPB) Suharyanto mengatakan pemadaman kebakaran hutan dan lahan ...</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687691/bnpb-pemadaman-kebakaran-gunung-bromo-diperluas-ke-2-titik-hari-ini</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810_151713.jpg</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>1.147 Personel Paspampres Dikerahkan untuk Pengamanan Rangkaian HUT Ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:36:17 +0700</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>1.147 Paspampres dikerahkan untuk mengamankan HUT ke-81 RI. Apel kesiapan dipimpin Danpaspampres, dengan dukungan alutsista modern dan strategi proaktif.</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612549/1-147-personel-paspampres-dikerahkan-untuk-pengamanan-rangkaian-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/apel-pasukan-paspampres-untuk-pengamanan-vvip-di-hut-ke-81-ri-senin-1082026-1786358097581_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Jelang Sidang Tahunan, Sultan Najamudin Tegaskan Peran DPD Wakili Daerah</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:27:52 +0700</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Fara Difa Alfeni</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Ketua DPD RI Sultan Baktiar Najamudin menegaskan STSB DPR RI-DPD RI sebagai momentum memperkuat komitmen pembangunan merata di seluruh Indonesia.</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612530/jelang-sidang-tahunan-sultan-najamudin-tegaskan-peran-dpd-wakili-daerah</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dpd-ri-1786357625050_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>BULOG: Stok Beras 5,25 Juta Ton Tersebar di Seluruh Gudang Indonesia</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:11:50 +0700</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Inkana Izatifiqa R. Putri</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Perum BULOG mencatat stok beras 5,25 juta ton per 9 Agustus 2026, hasil penyerapan gabah petani. Target penyerapan 4 juta ton setara beras optimis tercapai.</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612506/bulog-stok-beras-5-25-juta-ton-tersebar-di-seluruh-gudang-indonesia</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/bulog-1786356691344_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Menko Polkam Duga Kebakaran di Gunung Bromo karena Human Error</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:10:17 +0700</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago menduga kebakaran hutan di Bromo akibat human error. Pengunjung mungkin lupa memadamkan api untuk menghangatkan diri.</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612503/menko-polkam-duga-kebakaran-di-gunung-bromo-karena-human-error</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menko-polkam-djamari-chaniago-1786354297702_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Modus Perampok Pegawai Koperasi di Bekasi, Korban Diintai Sejak di Bank</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:07:26 +0700</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap para pelaku berkomplot merampok pegawai koperasi di Cibitung. Korban diintai sejak transaksi di bank.</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612497/modus-perampok-pegawai-koperasi-di-bekasi-korban-diintai-sejak-di-bank</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/perampokan-nasabah-bank-di-siang-bolong-di-cibitung-bekasi-1786238003822_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Duel Maut 2 WNA Asal Afrika di Jakpus Dipicu Utang Usaha Bumbu Masakan</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:05:23 +0700</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Dua WNA asal Afrika terlibat duel di kafe kawasan Jakpus hingga menyebabkan salah satunya tewas. Perkelahian itu dipicu masalah utang-piutang.</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612494/duel-maut-2-wna-asal-afrika-di-jakpus-dipicu-utang-usaha-bumbu-masakan</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/07/ee5711ef-e911-45b4-8c03-0f958db2a558_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Wamenkes Kaget RS Pemasyarakatan Cipinang Buka Layanan untuk Masyarakat Umum</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:02:19 +0700</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Wamenkes Benyamin terkejut dengan layanan RSU Pemasyarakatan Jakarta yang melayani masyarakat umum. RS ini memiliki 26 ranjang untuk umum dan 60 untuk napi.</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612491/wamenkes-kaget-rs-pemasyarakatan-cipinang-buka-layanan-untuk-masyarakat-umum</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/wamenkes-benyamin-paulus-saat-berkunjung-cipinang-jakarta-timur-jaktim-pada-senin-1062026-1786355977544_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Pemerintah Waspadai Karhutla di 6 Provinsi, Siagakan 43 Helikopter</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:49:41 +0700</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Pemerintah mewaspadai karhutla di enam provinsi di tengah ancaman El Nino kuat. Sebanyak 43 helikopter disiagakan untuk mendukung operasi penanganan karhutla.</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612468/pemerintah-waspadai-karhutla-di-6-provinsi-siagakan-43-helikopter</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menko-polkam-djamari-chaniago-1786355344338_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Menko Polkam Ungkap 107 Ribu Ha Lahan Terbakar: El Nino Percepat Perambatan</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:33:59 +0700</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Menteri Djamari Chaniago mengungkapkan lebih dari 107 ribu hektare hutan terbakar di Indonesia akibat fenomena El Nino.</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612445/menko-polkam-ungkap-107-ribu-ha-lahan-terbakar-el-nino-percepat-perambatan</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menko-polkam-djamari-chaniago-1786354297702_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Kebakaran Dekat Stasiun Kampung Bandan, Perjalanan KRL Sempat Terganggu</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:32:22 +0700</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Kebakaran alang-alang terjadi di dekat Stasiun Kampung Bandan, Jakarta Utara (Jakut). Perjalanan kereta rel listrik (KRL) sempat terganggu.</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612439/kebakaran-dekat-stasiun-kampung-bandan-perjalanan-krl-sempat-terganggu</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kebakaran-alang-alang-terjadi-di-dekat-stasiun-kampung-bandan-jakarta-utara-jakut-perjalanan-kereta-rel-listrik-krl-sempat-ter-1786354296171_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Bareskrim Polri Tangkap 3 Wanita Kurir Narkoba di Riau, 10 Kg Sabu Disita</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:31:57 +0700</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Bareskrim Polri menangkap tiga wanita kurir narkoba di Pekanbaru, Riau. Dari penangkan itu polisi menyita sabu 10 kg dengan nilai Rp 18 miliar.</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612438/bareskrim-polri-tangkap-3-wanita-kurir-narkoba-di-riau-10-kg-sabu-disita</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/10-kg-sabu-disita-dari-penangkapan-3-wanita-kurir-di-pekanbaru-riau-1786354222036_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Pihak Eks Ketua Yayasan Jelaskan Klaim Senjata di Sekolah Jaksel untuk Ekskul</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:27:59 +0700</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Kadek Melda Luxiana</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Kasus ratusan senjata di sekolah swasta Pondok Pinang berlanjut. Yayasan minta bukti ke pihak eks kepala yayasan terkait peruntukan senjata untuk eskul.</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612431/pihak-eks-ketua-yayasan-jelaskan-klaim-senjata-di-sekolah-jaksel-untuk-ekskul</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2 WNA Asal Afrika Baku Hantam di Kafe Jakpus, 1 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:25:21 +0700</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Seorang WN asal Kamerun tewas usai berduel dengan WN Nigeria di salah satu kafe di kawasan Jakarta Pusat.</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612425/2-wna-asal-afrika-baku-hantam-di-kafe-jakpus-1-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/02/01/garis-polisi-dipasang-di-swalayan-modern-di-desa-teloyo-kecamatan-wonosari-klaten-yang-dibobolilustrasi-garis-polisi_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Perpres Rampung Sebelum 17 Agustus, Driver Ojol Bakal Jadi UMKM</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:24:57 +0700</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi targetkan finalisasi Perpres transportasi online sebelum 17 Agustus 2026. Status ojol akan diakui sebagai UMKM dengan insentif.</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612423/perpres-rampung-sebelum-17-agustus-driver-ojol-bakal-jadi-umkm</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/10/ilustrasi-driver-ojol-1762782634885_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Perkuat Pertanahan, Kemendagri &amp;amp; ATR/BPN Teken SEB tentang Layanan BPHTB</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:11:37 +0700</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian dan Menteri ATR/BPN Nusron Wahid menandatangani SEB untuk integrasi data BPHTB, meningkatkan layanan pertanahan dan pendapatan daerah.</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612388/perkuat-pertanahan-kemendagri-atr-bpn-teken-seb-tentang-layanan-bphtb</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kemendagri-1786353063733.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>ABG 17 Tahun di Parung Bogor Curi Angsa, Hasil Jualnya buat Beli Miras</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:08:45 +0700</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Polisi menangkap remaja berusia 17 tahun karena mencuri angsa milik warga di Parung, Bogor, Jawa Barat (Jabar).</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612381/abg-17-tahun-di-parung-bogor-curi-angsa-hasil-jualnya-buat-beli-miras</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/angsa-yang-dicuri-remaja-di-parung-bogor-dok-istimewa-1786352544014_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Melawan, 2 dari 6 Perampok Pegawai Koperasi di Bekasi Ditembak Polisi</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:08:35 +0700</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Polisi menangkap enam pelaku perampokan bersenjata tajam di Cibitung. Dua pelaku melawan saat ditangkap.</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612383/melawan-2-dari-6-perampok-pegawai-koperasi-di-bekasi-ditembak-polisi</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/02/05/821773bd-9e66-4096-8978-ba6bbbb8a87e_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Alasan 'Sultan Muda' di Grobogan Beri Mahar Ekskavator-GMW Tank ke Istri</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:03:20 +0700</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Ardian Dwi Kurnia</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Pria di Grobogan Rico Putra menikahi Laella dengan mahar alat berat senilai miliaran. Alasannya memberikan mahar berat ke itu karena ingin tampil berbeda.</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612362/alasan-sultan-muda-di-grobogan-beri-mahar-ekskavator-gmw-tank-ke-istri</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/pernikahan-sultan-grobogan-1786339192241_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Pansus RUU Daerah Kepulauan Matangkan Skema Dana Khusus Kepulauan</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:02:41 +0700</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Anggota Pansus RUU Daerah Kepulauan, Alimudin, dorong Dana Khusus untuk percepat pembangunan. Fokus pada hak masyarakat lokal dan kearifan adat.</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612361/pansus-ruu-daerah-kepulauan-matangkan-skema-dana-khusus-kepulauan</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dpr-ri-1786352519104_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>IHSG Ditutup Tergelincir ke 6.365</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:38:27 +0700</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) hari ini ditutup di zona merah. Sempat dibuka menghijau, IHSG berbalik arah hingga ditutup melemah di level 6.300-an.</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8612457/ihsg-ditutup-tergelincir-ke-6-365</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/19/ihsg-ditutup-menguat-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Survei BPS: 69,57% Orang RI Melek Keuangan, 93,61% Punya Akses</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:35:26 +0700</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) merilis Hasil Survei Nasional Literasi dan Inklusi Keuangan (SNLIK) Tahun 2026.</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8612447/survei-bps-69-57-orang-ri-melek-keuangan-93-61-punya-akses</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/06/08/27c435f4-ea8b-4528-9cf7-9833a8d3583d_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>MSCI Mau Umumkan Rebalancing Saham, OJK: Kita Harap Fair</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:30:55 +0700</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) buka suara jelang Tinjauan Indeks Agustus 2026 (August 2026 Index Review) MSCI.</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8612436/msci-mau-umumkan-rebalancing-saham-ojk-kita-harap-fair</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/28/bei-terapkan-trading-halt-imbas-ihsg-anjlok-1769587530913_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Profil Destry Damayanti, Calon Tunggal Gubernur BI Pilihan Prabowo</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:22:44 +0700</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Destry Damayanti diusulkan sebagai calon tunggal Gubernur Bank Indonesia oleh Prabowo Subianto. Ia memiliki latar belakang kuat di sektor moneter dan ekonomi.</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612410/profil-destry-damayanti-calon-tunggal-gubernur-bi-pilihan-prabowo</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/20/deputi-gubernur-senior-bi-destry-damayanti-1747729609306_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Ompreng MBG Wajib Diberi Label Batas Waktu Konsumsi Mulai Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:54:40 +0700</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Mulai pekan depan, setiap wadah atau ompreng makanan MBG wajib diberi label batas waktu konsumsi.</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612342/ompreng-mbg-wajib-diberi-label-batas-waktu-konsumsi-mulai-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/27/32-ribu-pegawai-inti-mbg-bakal-diangkat-jadi-asn-pppk-1769488598657_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Mau Mudik Nataru? Tol Baru Siap Dibuka, Ini Lokasinya</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:27:47 +0700</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>PT Jasa Marga siapkan ruas tol untuk arus Nataru 2026/2027. Beberapa ruas akan beroperasi fungsional, termasuk Probolinggo-Situbondo dan Jogja-Bawen.</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8612283/mau-mudik-nataru-tol-baru-siap-dibuka-ini-lokasinya</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/04/arus-lalu-lintas-di-tol-cipularang-saat-arus-balik-libur-nataru-1767517746995_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>OJK Usut 89 Kasus Pasar Modal</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:19:00 +0700</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) mencatat 124 kasus pelanggaran di pasar modal.</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8612262/ojk-usut-89-kasus-pasar-modal</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/06/30/logo-ojk_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Pertamina Sulap Sumur Lama Jadi 'Mesin' Gas, Produksi Tembus 6,7 MMSCFD</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:59:09 +0700</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Pertamina EP Limau sukses tingkatkan produksi gas dari sumur L5A-309 menjadi 6,7 MMSCFD. Ini rekor gas sales tertinggi, optimalkan potensi sumur eksisting.</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8612208/pertamina-sulap-sumur-lama-jadi-mesin-gas-produksi-tembus-6-7-mmscfd</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/05/pertamina-ep-1780666670110_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>China-Rusia Incar Proyek Kereta Kalimantan, Jalurnya Bisa ke IKN</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:53:47 +0700</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan Dudy Purwagandhi mengungkapkan minat investor China dan Rusia untuk proyek Trans Kalimantan Railway. Rute masih dalam pembahasan.</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612198/china-rusia-incar-proyek-kereta-kalimantan-jalurnya-bisa-ke-ikn</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/05/19/9e97dcc2-0649-4403-86c3-d9f9dfc676c6_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>BEI &amp;amp; OJK Buka Suara soal Masjid Istiqlal Masuk Bursa Efek</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:37:48 +0700</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>BEI dan OJK buka suara mengenai kabar Masjid Istiqlal masuk ke ekosistem Bursa Efek Indonesia (BEI) melalui pengelolaan wakaf produktif.</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612173/bei-ojk-buka-suara-soal-masjid-istiqlal-masuk-bursa-efek</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/19/ihsg-ditutup-menguat-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Seskab Teddy Kopi Darat Bareng Haji Isam, Ini yang Dibahas</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:09:31 +0700</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Pengusaha nasional Andi Syamsuddin Arsyad alias Haji Isam menemui Sekretaris Kabinet Teddy Indra Wijaya.</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612100/seskab-teddy-kopi-darat-bareng-haji-isam-ini-yang-dibahas</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/seskab-teddy-menerima-haji-isam-1786345275109_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Kapal Terbakar 3 Kali, Operator KM Mutiara Sentosa II Terancam Dicabut Izinnya</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:06:22 +0700</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan Dudy Purwagandhi siapkan sanksi tegas untuk PT Atosim Lampung Pelayaran setelah insiden kebakaran KM Mutiara Sentosa II di Madura.</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612084/kapal-terbakar-3-kali-operator-km-mutiara-sentosa-ii-terancam-dicabut-izinnya</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menteri-perhubungan-menhub-dudy-purwagandhi-1786337809924_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Kerap Terlibat Kecelakaan, Menhub Dudy Pertimbangkan Cabut Izin Operasional KMP Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:45:22 +0700</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Sebanyak 62 korban berhasil dievakuasi dari Pulau Masalembu ke Surabaya menggunakan KN Masalembo pada Selasa (4/8).</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866451/kerap-terlibat-kecelakaan-menhub-dudy-pertimbangkan-cabut-izin-operasional-kmp-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/qg7kga7TZ21luOTGpk7cUHseBm0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/p-Madura-KMP-Mutiara-Se.jpg</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Pesantren Dinilai Jadi Ruang Membangun Persaudaraan Lintas Daerah dan Latar Belakang Sosial</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:41:58 +0700</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Pesantren jadi ruang belajar agama sekaligus membangun persaudaraan lintas daerah, kata Anggota DPR Gerindra Kawendra Lukistian.</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866450/pesantren-dinilai-jadi-ruang-membangun-persaudaraan-lintas-daerah-dan-latar-belakang-sosial</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/TXK7HHuS52g9oaOeNlI9TWw2-w4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Anggota-DPR-RI-Kawendra-Lukistian-menilai-pesantren-bukan-hanya-tempat-belajar-agama.jpg</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>2 Pasal Belum Final, Pemerintah Targetkan Perpres Ojol Terbit Sebelum 17 Agustus</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:41:49 +0700</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Perpres Ojol ditargetkan terbit sebelum 17 Agustus, tetapi dua pasal masih difinalisasi. Apa yang belum tuntas?</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866449/2-pasal-belum-final-pemerintah-targetkan-perpres-ojol-terbit-sebelum-17-agustus</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vs3yeW0xLeRf6BfKSxoFKZDTDB0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menteri-UMKM-Maman-Abdurrahman-memberikan-keterangan-di-Kompleks-Parlemen-Senayan.jpg</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Sambut HUT ke-81 RI, PDIP Hidupkan Visi 'Nation Building' Bung Karno Lewat Soekarno Cup 2026</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:38:30 +0700</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Turnamen ini lahir dari keyakinan bahwa olahraga merupakan jalan utama dalam membentuk karakter bangsa.</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866448/sambut-hut-ke-81-ri-pdip-hidupkan-visi-nation-building-bung-karno-lewat-soekarno-cup-2026</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lNT1J3vaNqCErzEP94viOTBtP0Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/soekarno-cup-dibukaaaaaa.jpg</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>UEFA, AFC dan Concacaf Bersatu Jatuhkan Vonis ke Gianni Infantino sebagai Presiden FIFA</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:37:31 +0700</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>UEFA, AFC dan Concacaf bersatu menjatuhkan vonis kepada Gianni Infantino sebagai Presiden FIFA.</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866447/uefa-afc-concacaf-bersatu-jatuhkan-vonis-ke-gianni-infantino-sebagai-presiden-fifa</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MTmlwsBy-Mu_GqtMeJn5WRx_bwQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/presiden-fifa-gianni-infantino-kiri-berbicara-di-samping-presiden-conmebol.jpg</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Kumpulan Lirik Lagu Nasional Indonesia, Cocok Dinyanyikan untuk Menyambut Hari Kemerdekaan</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:35:22 +0700</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Hari Kemerdekaan akan segera tiba, untuk menyambut perayaan HUT RI, masyarakat biasanya akan menyanyikan dan memutar lagu-lagu nasional Indonesia.</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866446/kumpulan-lirik-lagu-nasional-indonesia-cocok-dinyanyikan-untuk-menyambut-hari-kemerdekaan</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/VXqq3vcoZEsR8hlMTzxY0rvEAHM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/upacara-hut-kemerdekaan-ri-di-ibu-kota-nusantara.jpg</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Kejagung Lelang Barang Rampasan Hasil Korupsi, dari Ponsel Senilai Rp3 Ribu hingga Tanah Rp9 Miliar</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:32:17 +0700</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>BPA Kejaksaan melelang sejumlah barang hasil rampasan tindak pidana korupsi dengan limit harga dari senilai Rp 3 Ribu hingga Rp 9 miliar.</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866445/kejagung-lelang-barang-rampasan-hasil-korupsi-dari-ponsel-senilai-rp3-ribu-hingga-tanah-rp9-miliar</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ol7mYObgATeSlkw_ydFpbCMUa_E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kepala-Badan-Pemulihan-Aset-BPA-Kejaksaan-RI-Patris-Yusrian-Jaya-soal-lelang-serentak.jpg</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Gara-gara Main Film Seni Merayu Tuhan, Teuku Ryzki Sadar Pentingnya Luangkan Waktu untuk sang Ibu</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:31:40 +0700</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Teuku Ryzki mengungkap pelajaran berharga berkat membintangi film Seni Merayu Tuhan yakni betapa pentingnya meluangkan waktu untuk sang ibu.</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866444/gara-gara-main-film-seni-merayu-tuhan-teuku-ryzki-sadar-pentingnya-luangkan-waktu-untuk-sang-ibu</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DjXT2d-tKx5p6nTCuGuDHz_sBJw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Teuku-Rizky-saklasfaskfjsa.jpg</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu Empty Space - The Story So Far: I Dwell On It Nightly</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:29:24 +0700</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Berikut ini merupakan terjemahan lirik lagu Empty Space yang dipopulerkan oleh grup band The Story So Far.</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866443/terjemahan-lirik-lagu-empty-space-the-story-so-far-i-dwell-on-it-nightly</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tEq9lHSi3zC8-tIEQ99J9IcoxD8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>WN Kamerun Tewas usai Dianiaya WN Nigeria di Kafe Jakpus, Dipicu Masalah Utang Piutang</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:29:15 +0700</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>WNA Kamerun tewas dianiaya WNA Nigeria di Jakarta Pusat. Polisi menyebut kasus ini dipicu persoalan utang piutang</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866442/wn-kamerun-tewas-usai-dianiaya-wn-nigeria-di-kafe-jakpus-dipicu-masalah-utang-piutang</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pyDmB2XRo3PNuyW2H_r5WgVYNZk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ilustrasi-penganiayaan-bocah.jpg</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban Bahasa Indonesia Kelas 9 Halaman 74, 75 Edisi Revisi Latihan 7: Denotatif/Konotatif</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:29:13 +0700</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Kunci jawaban Bahasa Indonesia kelas 9 halaman 74, 75 SMP, MTs Kurikulum Merdeka Edisi Revisi, Latihan 7: Analisislah kata apakah Denotatif/Konotatif.</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866441/kunci-jawaban-bahasa-indonesia-kelas-9-halaman-74-75-edisi-revisi-latihan-7-denotatifkonotatif</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7B1zrSNCtP-Dwq2UVQZPaG5g6uw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/siswa-smpn-1-jakarta-ikuti-unbk_20190422_120847.jpg</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Houthi Vs Saudi Kian Panas, Kilang Aramco Kembali Dirudal, Apa Dampaknya bagi Timur Tengah?</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:28:04 +0700</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Jika serangan berlanjut dan menyasar lebih banyak fasilitas energi, dampaknya tidak hanya akan dirasakan oleh Arab Saudi dan Yaman</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866440/houthi-vs-saudi-kian-panas-kilang-aramco-kembali-dirudal-apa-dampaknya-bagi-timur-tengah</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/BpjkJKxMsMAzfzDf9Zv45K5kVDY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kilang-minyak-Aramco-di-Jazan-Arab-Saudi-dirudal-Houthi.jpg</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Klaim 'Restu Istana' Jelang Muktamar ke-35 NU Jadi Sorotan, Miftah Maulana: Hormati Marwah Ulama</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:26:51 +0700</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Muktamar ke-35 NU diharapkan dapat berlangsung tanpa kepentingan pragmatisme politik.</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866439/klaim-restu-istana-jelang-muktamar-ke-35-nu-jadi-sorotan-miftah-maulana-hormati-marwah-ulama</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/u6VQw4xEXQ2n56EBduEIetmPM4g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pondok-Pesantren-Bahrul-Ulum-Tambakberas.jpg</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Rahasia Real Madrid Jor-joran di Bursa Transfer 2026, Pendapatan Los Blancos Tembus Rp25 Triliun</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:26:34 +0700</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Di balik jor-joran Real Madrid pada bursa transfer musim panas 2026, terdapat kekuatan finansial yang catatkan pendapatan €1,221 miliar musim lalu.</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866438/rahasia-real-madrid-jor-joran-di-bursa-transfer-2026-pendapatan-los-blancos-tembus-rp25-triliun</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/E54RA_I8M15KG7G9nmg6eXOU94s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-klub-Real-Madrid.jpg</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Soroti Mental Anak, Nanda Persada Minta Ruben Onsu dan Sarwendah Stop Saling Serang di Medsos</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:22:39 +0700</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Nanda Persada soroti mental anak, minta Ruben Onsu dan Sarwendah untuk stop saling serang di media sosial.</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866437/soroti-mental-anak-nanda-persada-minta-ruben-onsu-dan-sarwendah-stop-saling-serang-di-medsos</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/B0PjO6TU4zWsvX1GGG1dLTB_lgA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mediasi-ruben-onsu.jpg</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Pelajar SMA Terserempet KRL dan Jatuh ke Rel di Stasiun Jurangmangu, Perjalanan Kereta Terganggu</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:17:18 +0700</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Salah seorang penumpang KRL Commuter Line bernama Amel katakan detik-detik seorang pelajar yang tersambar lalu jatuh ke bawah rel kereta api tersebut.</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866436/pelajar-sma-terserempet-krl-dan-jatuh-ke-rel-di-stasiun-jurangmangu-perjalanan-kereta-terganggu</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/xyZeYL4h6OLW4VhaaILfhCNJEMk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Stasiun-Jurangmangu-pelajar-SMA-terserempet-KRL.jpg</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Menko Polkam: 107 Ribu Hektare Hutan dan Lahan Terbakar, 6 Provinsi Prioritas Penanganan</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:16:48 +0700</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Pemerintah mewaspadai enam provinsi yang memiliki potensi karhutla tinggi di tengah fenomena El Nino saat ini.</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866435/menko-polkam-107-ribu-hektare-hutan-dan-lahan-terbakar-6-provinsi-prioritas-penanganan</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/i_QJegsL6fpnK0Za9UKKMCHN140=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/karhutla-menko-polkam-bicaraaa.jpg</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>BoostAD Hadirkan Brand Activation Spektakuler Rayakan 5 Tahun SeaBank</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:15:54 +0700</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>BoostAD Hadirkan Brand Activation Spektakuler untuk Rayakan 5 Tahun SeaBank melalui Integrasi Experiential Marketing, Giant Installation, dan DOOH.</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866434/boostad-hadirkan-brand-activation-spektakuler-rayakan-5-tahun-seabank</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/FpAtPGaXko07BPhFroqAaRXkBZ0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/boostad_seabank.jpg</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>995 Benda Mirip Senjata di Sekolah Jaksel Bukan Senjata Api, Polisi Selidiki Dokumen Kepemilikan</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:15:21 +0700</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Pihak kepolisian tengah menyelidiki kepemilikan hingga dokumen barang-barang tersebut.</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866433/995-benda-mirip-senjata-di-sekolah-jaksel-bukan-senjata-api-polisi-selidiki-dokumen-kepemilikan</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/enu60eSCVJ1ALLFEmi5pFfeMTg4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/996-senjata-di-sebuah-sekolah-kawasan-Pondok-Pinang-32010.jpg</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Turnamen Padel Dorong Gaya Hidup Sehat dan Pengenalan Wastra Nusantara</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:14:48 +0700</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>WBI ajak generasi muda mengenal kekayaan wastra sebagai identitas budaya Indonesia.</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866432/turnamen-padel-dorong-gaya-hidup-sehat-dan-pengenalan-wastra-nusantara</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/TWPJ0NG_LT9_OceAuMK-KxRjySc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/WBI-padel-nihhh.jpg</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Makin Melek Finansial, Indeks Literasi dan Inklusi Keuangan Nasional Meningkat</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:27:58 +0700</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Badan Pusat Statistik (BPS) bersama Otoritas Jasa Keuangan (OJK) dan Lembaga Penjamin Simpanan (LPS) merilis data terbaru dalam Survei Nasional Literasi dan Inklusi Keuangan (SNLIK) Tahun...</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjuem370/makin-melek-finansial-indeks-literasi-dan-inklusi-keuangan-nasional-meningkat</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260810172531-932.png</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Ekonom: Daya Beli Kelas Menengah ke Bawah Jadi Kunci Pertumbuhan Ekonomi Semester II</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:51:16 +0700</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Ekonom Institute for Development of Economics and Finance (INDEF) M Rizal Taufikurahman menilai daya beli masyarakat, khususnya kelas menengah ke bawah menjadi kunci penting untuk menjaga...</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjspg370/ekonom-daya-beli-kelas-menengah-ke-bawah-jadi-kunci-pertumbuhan-ekonomi-semester-ii</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/022678600-1681475661-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Ekonom Nilai Destry Damayanti Tepat untuk Jaga Kesinambungan Kebijakan Moneter BI</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:24:43 +0700</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai keputusan Presiden Prabowo mengusulkan Destry Damayanti sebagai calon tunggal Gubernur Bank Indonesia merupakan pilihan yang tepat untuk menjaga...</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjrh7370/ekonom-nilai-destry-damayanti-tepat-untuk-jaga-kesinambungan-kebijakan-moneter-bi</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/019389400-1697710276-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Pramono Siapkan 2 Lapangan untuk Latihan Tim FIFA ASEAN Cup 2026</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:36:04 +0700</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Jakarta memberikan dukungan penuh terhadap pelaksanaan FIFA ASEAN Cup 2026.</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266478/pramono-siapkan-2-lapangan-untuk-latihan-tim-fifa-asean-cup-2026</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/jCkpFHKBOJ-dQJPzluS6qdh0Cio=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320604/original/015508500_1786358142-IMG_3493.jpg</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Pramono Harap STY Bawa Persija Juara saat Jakarta Genap 500 Tahun</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:35:46 +0700</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Momentum lima abad Jakarta dinilai menjadi kesempatan istimewa bagi Persija untuk mempersembahkan prestasi tertinggi bagi warga Ibu Kota.</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266477/pramono-harap-sty-bawa-persija-juara-saat-jakarta-genap-500-tahun</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/c0gZYiGT5jI3QIHMXvieij2OcWs=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5296511/original/053367500_1753591984-WhatsApp_Image_2025-07-27_at_11.22.57_447f6612.jpg</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap 6 Pelaku Begal Pegawai Koperasi di Bekasi</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:28:53 +0700</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Dua pelaku ditembak saat ditangkap karena melakukan perlawanan.</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266469/polisi-tangkap-6-pelaku-begal-pegawai-koperasi-di-bekasi</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/0veQbZL8lIBvsKKqgvO_SwzVtZA=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5495661/original/092534400_1770388302-IMG_0188.jpeg</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Kebakaran Bromo Diduga Akibat Human Error, Ini Kata Menko Polkam</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:15:37 +0700</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Suhu udara yang dingin di kawasan Gunung Bromo membuat pengunjung maupun wisatawan terkadang menyalakan api.</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266456/kebakaran-bromo-diduga-akibat-human-error-ini-kata-menko-polkam</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/YrtttGzeZHH8HE7tuvgwTieHrgM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317574/original/027541400_1786022250-br5.jpg</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Alasan Pramono Alihkan Transportasi Kepulauan Seribu ke Transjakarta</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:10:24 +0700</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Selama ini transportasi menuju Kepulauan Seribu sepenuhnya dikelola Dinas Perhubungan (Dishub) DKI Jakarta.</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266451/alasan-pramono-alihkan-transportasi-kepulauan-seribu-ke-transjakarta</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/GI039Q3nifF9zEGLxxjUP9PXZMM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5335066/original/065564400_1756786528-Pemprov_DKI_dan_Warga_Gotong_Royong_Pulihkan_Jakarta_3.jpg</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Karhutla Meluas, Istana Minta Warga Jangan Bikin Percikan Api</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:04:22 +0700</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Imbauan itu disampaikan setelah pemerintah mencatat masih banyak titik api di sejumlah wilayah.</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266442/karhutla-meluas-istana-minta-warga-jangan-bikin-percikan-api</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/YvrpqS7tuAdTpN8MCTYWZwlW4Lc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9319451/original/083208200_1786251327-WhatsApp-Image-2026-08-05-at-09.18.39.jpeg.jpg</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Rakor Karhutla Bahas Penanganan Lahan Terdampak Seluas 107 Ribu Hektare</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:58:08 +0700</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Pemerintah mencatat lebih dari 107 ribu hektare lahan terdampak kebakaran hutan dan lahan (karhutla) hingga awal Agustus 2026. Menko Polkam Djamari Chaniago mengatakan pemerintah terus melakukan penanganan melalui operasi udara dan darat. Upaya tersebut dilakukan untuk mengendalikan titik kebakaran dan mencegah meluasnya dampak karhutla. Dalam operasi udara, pemerintah mengerahkan sekitar 43 helikopter. Selain itu, sebanyak 10 hingga 15 pesawat fixed-wing disiapkan untuk dikerahkan sesuai kebutuhan di wilayah terdampak. Djamari menyampaikan perkembangan penanganan karhutla tersebut seusai rapat koordinasi di Jakarta, Senin (10/8/2026). Rapat turut dihadiri Menteri Kehutanan Raja Juli Antoni, Menteri Lingkungan Hidup M Jumhur Hidayat, serta Kepala BNPB Letjen TNI Suharyanto.</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8266432/rakor-karhutla-bahas-penanganan-lahan-terdampak-seluas-107-ribu-hektare</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/bMnzMjRbOU-DNkdbk2J65Xo93Ek=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320552/original/005825600_1786355838-men1.jpg</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Polisi Periksa 24 Saksi, Kasus Kematian Sutrimo Naik ke Penyidikan</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:39:49 +0700</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Penyidik Polda Metro Jaya juga telah menerima pelimpahan perkara kematian Sutrimo dari Polrestabes Banyumas dan Bareskrim Polri.</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266421/polisi-periksa-24-saksi-kasus-kematian-sutrimo-naik-ke-penyidikan</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Ac0CwWSgaQOzoD0dmfbEg4_UyMk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9312458/original/059177100_1785493658-IMG_1805.jpg</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Menko Polkam Sebut Kebakaran Bromo Tinggal 1-2 Titik Api</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:31:02 +0700</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago memastikan penanganan kebakaran Gunung Bromo tertangani dengan baik.</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266411/menko-polkam-sebut-kebakaran-bromo-tinggal-1-2-titik-api</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/TooXLhwgWwS4wlj_i3dbqLKA6Ew=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320535/original/066895900_1786354017-IMG_6886.jpeg</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Mensesneg: Sampai Hari Ini Belum Ada Rencana Reshuffle</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:07:50 +0700</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Prabowo belum memutuskan melakukan reshuffle.</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266373/mensesneg-sampai-hari-ini-belum-ada-rencana-reshuffle</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/_br72lp4vVWS5CLZakL8R6QgFI4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/7767979/original/011455400_1780578714-IMG_3908__1_.jpeg</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Potensi Transaksi Art Toys Indonesia di Korea Capai Rp 17 Miliar</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:00:21 +0700</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Para kreator tersebut bertemu langsung dengan sedikitnya 400 pembeli potensial selama pameran berlangsung.</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/10/175959226/potensi-transaksi-art-toys-indonesia-di-korea-capai-rp-17-miliar</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/4SrgqUsprJIuUf78hvwDN7HQhGc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/10/6a79aaa5bc21b.jpg</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Ilusi Kendali: Ketika Belanja Jadi Cara Kita Menolak Realitas Ekonomi</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:00:21 +0700</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Ekonomi sedang sulit. Pengeluaran harus dihemat. Tetapi mengapa kita masih membeli kopi, skincare, parfum, lipstik, atau makanan favorit?</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/10/17405821/ilusi-kendali-ketika-belanja-jadi-cara-kita-menolak-realitas-ekonomi</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/hL2p1kBm3Qq1iGxSR7nzJQxx6Dk=/0x0:780x520/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/03/16/69b80376d449b.jpeg</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Wamenhaj Sidak di Kantor Jaktim: Tak Boleh Ada Praktik Rugikan Jemaah</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:00:21 +0700</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Wakill Menteri Haji dan Umrah, Dahnil Anzar Simanjuntak, melakukan inspeksi mendadak atau sidak ke Kantor Kemenhaj di</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/10/17263771/wamenhaj-sidak-di-kantor-jaktim-tak-boleh-ada-praktik-rugikan-jemaah</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/hJl-Y-hI93Ovu6mrnHQAfZst0qk=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79a2e2a965b.jpeg</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I602"/>
+  <autoFilter ref="A1:I719"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$719</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$794</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I719"/>
+  <dimension ref="A1:I794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -34232,8 +34232,3533 @@
         </is>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Mario Aji syukuri hasil GP Inggris</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:39:31 +0700</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Pembalap Moto2 Mario Aji mensyukuri hasil GP Inggris 2026, Minggu (9/8), ketika menuntaskan balapan di peringkat ke-22, ...</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687912/mario-aji-syukuri-hasil-gp-inggris</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/Latihan-pembalap-nasional-Moto2-dan-Moto3-di-Mandalika-210726-AS-8.jpg</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Jerman perketat pemulangan migran</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:36:42 +0700</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Jerman dilaporkan mempertegas sikapnya terkait pemulangan migran dan ingin melanjutkan kembali transfer migran ke ...</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687907/jerman-perketat-pemulangan-migran</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/06/create-antaranews-logo.jpg</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Kementan siapkan kapal pengiriman 200 sapi perah demi swasembada susu</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:35:46 +0700</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian (Kementan) menyiapkan Kapal Motor (KM) Camara Nusantara I untuk mengangkut 200 sapi perah bunting ...</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687903/kementan-siapkan-kapal-pengiriman-200-sapi-perah-demi-swasembada-susu</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/7AE4ED87-1327-4F74-A776-1B732F18C9F6.jpeg</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Menkopolkam minta Kalteng dan Kalbar hentikan izin pembakaran lahan</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:35:13 +0700</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Politik dan Keamanan (Menkopolkam) Djamari Chaniago meminta pemerintah daerah Kalimantan ...</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687900/menkopolkam-minta-kalteng-dan-kalbar-hentikan-izin-pembakaran-lahan</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810_150224.jpg</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>PSSI prihatin kritik negatif terhadap Justin Hubner dan keluarganya</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Persatuan Sepak Bola Seluruh Indonesia (PSSI) menyatakan prihatin terhadap munculnya kritik negatif terhadap pemain ...</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687899/pssi-prihatin-kritik-negatif-terhadap-justin-hubner-dan-keluarganya</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/timnas-indonesia-dikalahkan-vietnam-di-piala-aff-2833631.jpg</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Pramono Anung: Pemulung Bantargebang didaftarkan BPJS Ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:32:44 +0700</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>ANTARA - Gubernur Jakarta Pramono Anung Wibowo mengungkapkan sebanyak 4.000 pemulung di Tempat Pengolahan Sampah ...</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687847/pramono-anung-pemulung-bantargebang-didaftarkan-bpjs-ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_RAMONO-ANUNG-PEMULUNG-BANTARGEBANG.jpg</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Karhutla meluas, BMKG ungkap mengapa belum bisa laksanakan OMC</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:29:23 +0700</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mengungkapkan Operasi Modifikasi Cuaca (OMC) untuk membantu ...</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687895/karhutla-meluas-bmkg-ungkap-mengapa-belum-bisa-laksanakan-omc</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/patroli-kebakaran-hutan-dan-lahan-melalui-udara-di-kalteng-2834369.jpg</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Pemkot Ambon gelar lomba Jukulele, sokong kreativitas generasi muda</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:23:51 +0700</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>ANTARA - Wakil Wali kota Ambon Ely Toisuta membuka lomba Jukulele di Taman Budaya kota Ambon, Maluku, Senin ...</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687656/pemkot-ambon-gelar-lomba-jukulele-sokong-kreativitas-generasi-muda</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-AMBON-GELAR-LOMBA-JUKULELE-SOKONG-KREATIVITAS-GENERASI-MUDA_1.jpg</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Dekranasda DKI tegaskan karya Nusantara harus hadir di ruang perkotaan</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:20:19 +0700</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Kerajinan Nasional Daerah (Dekranasda) DKI Jakarta Hani Pramono menegaskan karya tradisional dan produk ...</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687889/dekranasda-dki-tegaskan-karya-nusantara-harus-hadir-di-ruang-perkotaan</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000835766.jpg</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Kejagung periksa tujuh saksi terkait kasus TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:16:55 +0700</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Tim Penyidik Kejaksaan Agung (Tim 9) memeriksa tujuh saksi dalam proses penyidikan kasus dugaan tindak pidana pencucian ...</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687885/kejagung-periksa-tujuh-saksi-terkait-kasus-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000087297.jpg</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Kasus temuan senjata, KPAI terima aduan dari sekolah dan yayasan</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:16:10 +0700</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Komisi Perlindungan Anak Indonesia (KPAI) menerima pengaduan resmi dari pihak yayasan dan sekolah terkait,  ...</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687881/kasus-temuan-senjata-kpai-terima-aduan-dari-sekolah-dan-yayasan</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/tanggapan-pihak-sekolah-terkait-temuan-senjata-di-sekolah-2837852.jpg</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Danpaspampres pimpin gelar kesiapan pasukan rangkaian HUT Ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:14:06 +0700</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Komandan Pasukan Pengamanan Presiden (Danpaspampres) Mayjen TNI Edwin Adrian Sumantha memimpin Apel Gelar Kesiapan ...</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687877/danpaspampres-pimpin-gelar-kesiapan-pasukan-rangkaian-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_4888.jpg</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Pemerintah fokus tangani karhutla di enam provinsi rawan</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:13:53 +0700</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Pemerintah memfokuskan penanganan kebakaran hutan dan lahan (karhutla) di enam provinsi yang paling rawan, yakni Riau, ...</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687873/pemerintah-fokus-tangani-karhutla-di-enam-provinsi-rawan</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/rakor-penanganan-kebakaran-hutan-dan-lahan-2838469.jpg</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>BEI catat tambahan 9,9 juta investor dalam 7,5 bulan</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:13:38 +0700</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>PT Bursa Efek Indonesia (BEI) mencatat penambahan sekitar 9,9 juta investor pasar modal dalam kurun 7,5 bulan pada 2026 ...</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687869/bei-catat-tambahan-99-juta-investor-dalam-75-bulan</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000179366.jpg</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Polsek Sawah Besar amankan WNA pelaku penganiayaan di Pasar Baru</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:12:30 +0700</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Pusat melalui Polsek Sawah Besar mengamankan seorang warga negara asing (WNA) asal Nigeria ...</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687867/polsek-sawah-besar-amankan-wna-pelaku-penganiayaan-di-pasar-baru</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/1000000143.jpg</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>APBD Perubahan Jatim 2026 prioritaskan pelayanan publik-infrastruktur</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:11:04 +0700</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Jawa Timur memprioritaskan penguatan sektor pelayanan publik, pendidikan, kesehatan, dan ...</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687864/apbd-perubahan-jatim-2026-prioritaskan-pelayanan-publik-infrastruktur</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1343790.jpg</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Dorongan transparansi dan independensi BPKH terus menguat</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:10:57 +0700</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Rancangan Undang-Undang (RUU) tentang Perubahan atas Undang-Undang Nomor 34 Tahun 2014 tentang Pengelolaan Keuangan ...</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687863/dorongan-transparansi-dan-independensi-bpkh-terus-menguat</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/21/pembagian-biaya-hidup-kepada-jch-embarkasi-makassar-2775924.jpg</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>ITERA-ITB kolabirasi program fast track S1-S2 jadi Lima tahun</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:10:40 +0700</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Institut Teknologi Sumatera (ITERA) berkolaborasi dengan Institut Teknologi Bandung (ITB) melalui Jalur Kerja Sama ...</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687860/itera-itb-kolabirasi-program-fast-track-s1-s2-jadi-lima-tahun</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001143937.jpg</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Produsen robot China Unitree buka pemesanan IPO respons minat investor</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:09:19 +0700</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Produsen robot asal China, Unitree Robotics, pada Senin (10/8) membuka periode pemesanan untuk penawaran umum perdana ...</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687859/produsen-robot-china-unitree-buka-pemesanan-ipo-respons-minat-investor</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CjkinzN000011_20260810_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Kim Ji Won sumbangkan 100 juta won untuk RS dan ringankan pengobatan</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:08:49 +0700</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Aktris Korea Selatan Kim Ji Won menyumbangkan 100 juta won atau Rp1,26 miliar rupiah (asumsi kurs Rp12,64) untuk ...</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687857/kim-ji-won-sumbangkan-100-juta-won-untuk-rs-dan-ringankan-pengobatan</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/02/17/KimJiwon.jpg</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Perluas layanan, PAM Jaya akan bangun 7.000 km jaringan pipa</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:07:33 +0700</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Perusahaan Air Minum (PAM) Jaya akan membangun sekitar 7.000 kilometer (km) jaringan pipa baru dalam beberapa tahun ke ...</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687856/perluas-layanan-pam-jaya-akan-bangun-7000-km-jaringan-pipa</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_6665.jpeg</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Pegadaian resmi jadi satu-satunya Bullion Bank Underlying Provider ETF Emas di Indonesia</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:06:16 +0700</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Memasuki babak baru pengembangan ekosistem investasi emas di Indonesia, Exchange Traded Fund (ETF) Emas resmi ...</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687855/pegadaian-resmi-jadi-satu-satunya-bullion-bank-underlying-provider-etf-emas-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Peluncuran-ETF-Emas.jpg</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Kebun Raya Bogor kembangkan wisata berbasis pengalaman</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:05:35 +0700</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Kebun Raya Bogor mengembangkan konsep wisata berbasis pengalaman dengan mengajak pengunjung mengenal dan mempelajari ...</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687851/kebun-raya-bogor-kembangkan-wisata-berbasis-pengalaman</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1003328073.jpg</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Tim Ekspedisi Patriot latih UMKM di Manokwari olah matoa jadi dodol</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:03:14 +0700</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Tim Ekspedisi Patriot Universitas Airlangga (Unair) Surabaya melatih pelaku usaha mikro kecil dan menengah (UMKM) ...</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687843/tim-ekspedisi-patriot-latih-umkm-di-manokwari-olah-matoa-jadi-dodol</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/25132.jpg</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Kemenhub catat 1,35 juta kendaraan angkutan barang patuhi aturan</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:00:42 +0700</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan (Kemenhub) mencatat sekitar 1,3 juta kendaraan angkutan barang telah mematuhi ketentuan dimensi ...</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687841/kemenhub-catat-135-juta-kendaraan-angkutan-barang-patuhi-aturan</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/8243E8DC-E87A-4F8A-A69B-8E852D26B953.jpeg</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Aksi TNI AL gagalkan penyelundupan 1,3 ton narkoba</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>TNI Angkatan Laut bersama tim gabungan menggagalkan upaya penyelundupan 1,3 ton narkoba jenis ketamin dari kapal asing ...</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5687724/aksi-tni-al-gagalkan-penyelundupan-13-ton-narkoba</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810-Aksi-cepat-gagalkan-penyelundupan-1-3-ton-narkoba_2.jpg</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Kurir SPX kembalikan uang Rp92 juta akibat salah transfer</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:57:30 +0700</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Seorang kurir SPX Express, Syarif Husein Akbar, mengembalikan uang sebesar Rp92 juta milik pelanggan yang salah ...</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687837/kurir-spx-kembalikan-uang-rp92-juta-akibat-salah-transfer</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-5.14.22-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Hoaks! Pendaftaran upacara HUT Ke-81 RI di Istana Merdeka berbayar</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:56:45 +0700</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menarasikan bahwa masyarakat yang ingin mengikuti ...</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687833/hoaks-pendaftaran-upacara-hut-ke-81-ri-di-istana-merdeka-berbayar</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/19/edit-CBS_7400.jpg</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Polinela-Unila terapkan IoT dan PLTS untuk penyiraman kebun terong</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:56:41 +0700</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Politeknik Negeri Lampung (Polinela) bersama Universitas Lampung (Unila) Polinela menerapkan sistem penyiraman ...</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687831/polinela-unila-terapkan-iot-dan-plts-untuk-penyiraman-kebun-terong</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_1729.jpeg</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Kegiatan otomotif semakin lekat dengan industri kreatif</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:56:33 +0700</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Budaya kustom atau custome culture sejak beberapa tahun silam, telah menunjukkan fenomena yang bersinggungan dengan ...</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5687827/kegiatan-otomotif-semakin-lekat-dengan-industri-kreatif</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-16.44.24.jpeg</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Hoaks! Mendes Yandri minta warung desa ditutup agar warga belanja di Kopdes</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:55:18 +0700</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan video berdurasi delapan detik di Facebook menampilkan Menteri ...</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687823/hoaks-mendes-yandri-minta-warung-desa-ditutup-agar-warga-belanja-di-kopdes</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/IMG_20260801_172518.jpg</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Keluarga Sutrimo Pertanyakan Formulir Kronologi-Dompet dan HP yang Tak kembali</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:11:33 +0700</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Anang Firmansyah</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Kuasa hukum keluarga Sutrimo mengungkap awalnya tidak menaruh kecurigaan apa pun saat menerima jenazah Sutrimo.</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612621/keluarga-sutrimo-pertanyakan-formulir-kronologi-dompet-dan-hp-yang-tak-kembali</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kuasa-hukum-keluarga-sutrimo-aan-rohaeni-saat-memberikan-keterangan-kepada-wartawan-usai-melapor-ke-polresta-banyumas-sabtu-88-1786357485293_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Soekarno Cup 2026 Bentuk Komitmen PDIP Ciptakan Bibit Muda Sepakbola RI</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:08:35 +0700</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Faiq Azmi</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Turnamen Soekarno Cup 2026 resmi dimulai, diikuti 16 provinsi. PDIP berkomitmen mencari bibit pesepakbola muda untuk masa depan sepakbola Indonesia.</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612618/soekarno-cup-2026-bentuk-komitmen-pdip-ciptakan-bibit-muda-sepakbola-ri</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/soekarno-cup-2026-1786211228302.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Satpam Five Stars Bali Sempat Kabur Bawa Ekstasi Saat Hendak Ditangkap Polisi</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:03:07 +0700</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Direktorat Narkoba Polri menangkap 53 orang di kelab malam Five Stars Bali terkait peredaran narkoba. Penyelidikan melibatkan teknik Under Cover Buy.</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612614/satpam-five-stars-bali-sempat-kabur-bawa-ekstasi-saat-hendak-ditangkap-polisi</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/bareskrim-polri-mengungkap-peredaran-di-five-stars-denpasar-bali-dan-mengamankan-53-orang-1786079431797_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Pria di Kuningan Tega Bunuh Ibu gegara Kesal Dibangunkan Salat Subuh</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:51:44 +0700</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Fahmi Labibnajib</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Seorang pria di Kuningan tega membunuh ibunya lantaran kesal dibangunkan salat subuh. Pelaku ditangkap polisi setelah melarikan diri ke Brebes.</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612591/pria-di-kuningan-tega-bunuh-ibu-gegara-kesal-dibangunkan-salat-subuh</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/12/ilustrasi-pembunuhan-1754995633409_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Kronologi Duel Maut 2 WNA Asal Afrika Dipicu Utang di Kafe Jakpus</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:50:59 +0700</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Dua WNA berduel di salah satu kafe kawasan Jakpus hingga mengakibatkan salah satunya tewas. Polisi telah menangkap WN Nigeria terkait duel maut itu.</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612589/kronologi-duel-maut-2-wna-asal-afrika-dipicu-utang-di-kafe-jakpus</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dua-wna-berduel-di-salah-satu-kafe-kawasan-jakpus-hingga-mengakibatkan-salah-satunya-tewas-polisi-telah-menangkap-wn-nigeria-t-1786359032609_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Inflasi Juli 2026 Capai 2,88 Persen, Mendagri Sebut Masih Rentang Ideal</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:49:39 +0700</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Fara Difa Alfeni</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian menyatakan inflasi Juli 2026 sebesar 2,88% masih ideal. Ia minta Pemda waspada terhadap daerah dengan inflasi tinggi.</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612586/inflasi-juli-2026-capai-2-88-persen-mendagri-sebut-masih-rentang-ideal</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kemendagri-1786358338269.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Mendikdasmen soal Temuan 995 Senjata di Sekolah Jaksel: Sedang Dicari Jalan Keluar</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:41:12 +0700</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Mendikdasmen Abdul Mu'ti menanggapi temuan 995 senjata di sekolah Jaksel. Dia berkomitmen menjadikan sekolah aman sambil mencari solusi bersama pihak terkait.</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612561/mendikdasmen-soal-temuan-995-senjata-di-sekolah-jaksel-sedang-dicari-jalan-keluar</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/mendikdasmen-abdul-muti-1784547333294_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Bima Arya Minta Pemda Perkuat Sistem Penanganan Kekerasan Perempuan-Anak</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:39:18 +0700</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Wamendagri Bima Arya tegaskan dukungan Kemendagri untuk penguatan sistem penanganan kekerasan terhadap perempuan &amp; anak melalui integrasi dan pembiayaan memadai</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612556/bima-arya-minta-pemda-perkuat-sistem-penanganan-kekerasan-perempuan-anak</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kemendagri-1786358338343_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Puan Maharani Minta Kebakaran Bromo Segera Ditangani Total</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:39:14 +0700</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Ketua DPR Puan Maharani mendesak pemerintah tangani kebakaran hutan di Bromo dan Palangka Raya. Keselamatan masyarakat dan pemulihan ekosistem jadi prioritas.</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612555/puan-maharani-minta-kebakaran-bromo-segera-ditangani-total</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/20/puan-maharani-dok-youtube-setpres-1779247794648_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Destry Damayanti Calon Tunggal Gubernur BI, Airlangga Bilang Begini</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:30:46 +0700</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto mengatakan sosok Destry bukanlah orang baru.</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8612628/destry-damayanti-calon-tunggal-gubernur-bi-airlangga-bilang-begini</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/13/menko-perekonomian-airlangga-hartarto-1783940653691_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Art Toys RI Berpeluang Cuan Rp 17 Miliar dari Pasar Korea Selatan</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:01:06 +0700</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Art toys Indonesia berpotensi meraih Rp 17 miliar dari pasar Korea Selatan. Pameran URBAN BREAK &amp; TOY CON SEOUL 2026 menarik perhatian besar pembeli.</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612612/art-toys-ri-berpeluang-cuan-rp-17-miliar-dari-pasar-korea-selatan</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/18/pameran-hong-kong-art-toys-2024-jakarta-digelar-di-mall-of-indonesia-jakarta-utara-hingga-24-november-2024-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Pegadaian Jadi Satu-satunya Bullion Bank Underlying Provider ETF Emas RI</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:58:29 +0700</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Peluncuran ETF Emas di Indonesia menandai langkah baru dalam investasi emas, memperluas akses masyarakat melalui pasar modal dan sinergi industri bullion.</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8612607/pegadaian-jadi-satu-satunya-bullion-bank-underlying-provider-etf-emas-ri</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/pegadaian-1786359492880_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Rumah Kontrakan dan Wacana Pajak 2027</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:58:10 +0700</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Rifkianto Nugroho</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>DJP memastikan belum ada program pajak khusus bagi pemilik rumah kontrakan pada 2027, meski pemerintah berencana memperluas basis perpajakan.</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8612474/rumah-kontrakan-dan-wacana-pajak-2027</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/rumah-kontrakan-dalam-wacana-perluasan-basis-pajak-wacana-perluasan-pajak-dan-rumah-kontrakan-1786355268864.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Jonathan Frizzy Bentuk Badan demi Penampilan</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:10:24 +0700</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Jonathan Frizzy kembali bersinar setelah kasus vape ilegal. Kini, ia aktif sebagai brand ambassador dan affiliator, sambil fokus pada kebugaran tubuhnya.</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612260/jonathan-frizzy-bentuk-badan-demi-penampilan</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/03/jonathan-frizzy-1772514298397_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Keseruan Kylie Jenner Rayakan Ultah dengan Pesta Serba Pink</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:07:18 +0700</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Selebritas Kylie Jenner baru saja merayakan ulang tahunnya yang ke-29 dengan meriah. Begini keseruannya.</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8611884/keseruan-kylie-jenner-rayakan-ultah-dengan-pesta-serba-pink</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kylie-jenner-1786338705752_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Augie Fantinus Happy Syuting Bapakmu Kiper</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:47:27 +0700</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Film Bapakmu Kiper tayang 3 September 2026. Augie Fantinus berbagi pengalaman syuting dan kecintaannya pada sepakbola dalam film ini.</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/movie/d-8612461/augie-fantinus-happy-syuting-bapakmu-kiper</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/augie-fantinus-1786354925017_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Momen Aldi Taher Peluk Vokalis Jet di Panggung Jadi Sorotan</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:12:20 +0700</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Aldi Taher tiba-tiba aja naik ke atas panggung dan memeluk vokalis Jet, Nic Cester. Momen itu menuai sorotan.</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612119/momen-aldi-taher-peluk-vokalis-jet-di-panggung-jadi-sorotan</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/aldi-taher-1786345749578_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Mata Juling Mendadak pada Orang Dewasa, Waspadai Sinyal Diabetes, Hipertensi, hingga Gangguan Saraf</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:24:59 +0700</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Penyakit sistemik seperti diabetes dan hipertensi dapat memicu gangguan pada saraf yang mengatur pergerakan mata.</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866480/mata-juling-mendadak-pada-orang-dewasa-waspadai-sinyal-diabetes-hipertensi-hingga-gangguan-saraf</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oYC7Eu25ziOyR3hKvcJU_h4-zIA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bakti-sosial-operasi-mata-juling-jec_20231015_172841.jpg</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Dari Pengintai hingga Eksekutor, Begini Peran Komplotan Begal Bekasi</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:23:29 +0700</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Enam pelaku membagi tugas saat mengincar nasabah bank di Bekasi, dari mengamati target hingga mengeksekusi korban.</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866479/dari-pengintai-hingga-eksekutor-begini-peran-komplotan-begal-bekasi</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0rBKhvLskYx-2WBQEOKl8okIBJo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pengendara-motor-menjadi-korban-perampokan-bersenjata-tajam-di-Tokma-Cibitung-Bekasi.jpg</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Khariq Anhar Tertunduk dan Geleng-geleng Kepala Dituntut 6 Bulan Penjara Tekait Kasus Timpa Teks</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:23:20 +0700</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Khariq Anhar tertunduk dan menggeleng-gelengkan kepala setelah tuntutan 6 bulan penjara terhadap dirinya dibacakan jaksa penuntut umum</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866478/khariq-anhar-tertunduk-dan-geleng-geleng-kepala-dituntut-6-bulan-penjara-tekait-kasus-timpa-teks</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vaPH1NzCY8A7jHYj-ZNhGO_Q3pE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Khariq-Anhar-tertunduk-dan-menggeleng-gelengkan-kepala.jpg</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu Disenchanted - My Chemical Romance: If I'm So Wrong</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:19:53 +0700</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Berikut ini merupakan terjemahan lirik lagu Disenchanted yang dipopulerkan oleh grup band My Chemical Romance.</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866477/terjemahan-lirik-lagu-disenchanted-my-chemical-romance-if-im-so-wrong</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zLN77GXG_MWcQ27NDqNvGgp-QJs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-musik-ilustrasi-lirik-ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>NSHE Jalankan Revegetasi di Pembangunan PLTA Batangtoru Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:19:16 +0700</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Pembangunan PLTA Batangtoru dilakukan beriringan dengan revegetasi, pemantauan lingkungan dan pembangunan jembatan arboreal.</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866476/nshe-jalankan-revegetasi-di-pembangunan-plta-batangtoru-tapanuli-selatan</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/O_v98bwH_ZfAzpTpMfQtuTxJYhc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kegiatan-revegetasi-PT-North-Sumatera-Hydro-Energy-PT-NSHE.jpg</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Salah Tekstur MPASI Bisa Bikin Anak Sulit Mengunyah dan Menelan, Ini Kata Dokter Gigi Anak</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:19:10 +0700</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Tekstur MPASI tidak sesuai kemampuan anak dapat membuat anak sulit mengunyah dan menelan, orang tua sebaiknya tidak buru-buru, ini penjelasan dokter.</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866475/salah-tekstur-mpasi-bisa-bikin-anak-sulit-mengunyah-dan-menelan-ini-kata-dokter-gigi-anak</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/nVKQQ_L9VD82UiYOZ_otjUt-4Mc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-bayi-ilustrasi-mpasi.jpg</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Bigmo Sowan ke Keluarga Anak yang Terlibat Livestreaming, Minta Maaf ke Orang Tua Mereka</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:18:53 +0700</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Bigmo mendatangi keluarga anak-anak tersebut sebagai bentuk iktikad baik setelah kejadian live streaming yang menjadi polemik.</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866474/bigmo-sowan-ke-keluarga-anak-yang-terlibat-livestreaming-minta-maaf-ke-orang-tua-mereka</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MB1ZiNQ6NK2dGnKcwEd1QqaGYkc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Bigmo-1-10082026.jpg</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Noda Gigi Belum Tentu Karies, Begini Cara Bedakan dengan Gigi Berlubang</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:16:43 +0700</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Noda pada gigi belum tentu tanda karies. Kenali perbedaan noda akibat kopi, teh, rokok dengan gigi berlubang menurut dokter gigi.</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866473/noda-gigi-belum-tentu-karies-begini-cara-bedakan-dengan-gigi-berlubang</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fHcmJWiZ5D6iDxXn5TaUg_EZ5rc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/siswa-sd-SIKAT-GIGI-1.jpg</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Discover Nusantara: Rayakan Semangat Kemerdekaan melalui Ragam Budaya, Kuliner dan Ekonomi Kreatif</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:15:50 +0700</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Sebanyak 24 provinsi membawa seni, wastra, kuliner, dan produk UMKM ke Jakarta lewat Discover Nusantara dalam rangkaian HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866472/discover-nusantara-rayakan-semangat-kemerdekaan-melalui-ragam-budaya-kuliner-dan-ekonomi-kreatif</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/G_zb50yF9zVZ2vqBtLJLiAs5shE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/diskafer111111.jpg</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Inflasi Juli 2026 Capai 2,88 Persen, Mendagri Tito: Masih dalam Rentang Ideal</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:14:01 +0700</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Mendagri Tito mengapresiasi tingkat inflasi secara year on year (yoy) pada Juli 2026 yang tercatat sebesar 2,88 persen.</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kilas-kementerian/7866471/inflasi-juli-2026-capai-288-persen-mendagri-tito-masih-dalam-rentang-ideal</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/71B_xWOFzKOREG94sS3z4gO4gHw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mendagri-Tito-Karnavian-Senin-108.jpg</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Buntut Live Streaming Vape Libatkan Anak, Bigmo Diperiksa Polisi dan Akui Kesalahannya</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:12:22 +0700</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Saat live streaming, Bigmo diduga menyebut salah satu brand liquid vape atau rokok elektrik ketika berinteraksi dengan anak-anak di bawah umur.</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866470/buntut-live-streaming-vape-libatkan-anak-bigmo-diperiksa-polisi-dan-akui-kesalahannya</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kVJ1JVg63OmX06VPzX6uBJAdK7g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bigmo-apa.jpg</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Jadi Calon Tunggal Gubernur BI, Destry Damayanti Dihadapkan Tantangan Jaga Rupiah dan Independensi</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:11:39 +0700</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Koordinasi antara BI dan pemerintah memang penting, tetapikoordinasi tersebut tidak boleh menghilangkan independensi bank sentral.</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866469/jadi-calon-tunggal-gubernur-bi-destry-damayanti-dihadapkan-tantangan-jaga-rupiah-dan-independensi</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/65Lo5yaCMnnV5UuorcZ5wxSBZwE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penjabat-Gubernur-Bank-Indonesia-BI-Destry-Damayanti-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>'NATO Timur Tengah' Bentukan Arab Saudi-Pakistan-Turki Jadi Ancaman atau Sekutu Bagi Iran?</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:07:47 +0700</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Paradoksnya, salah satu kemungkinan jangka panjang justru adalah Iran masuk ke dalam arsitektur keamanan regional tersebut.</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866468/nato-timur-tengah-bentukan-arab-saudi-pakistan-turki-jadi-ancaman-atau-sekutu-bagi-iran</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/sKTjW2IWme_tj-rBEFT9DF7gqhA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PAKTA-PERTAHANAN-Bendera-Arab-Saudi-Pakistan-dan-Turki.jpg</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Misteri Kematian Winda Lorenza, Saksi KPK yang Sempat Terima Apartemen dan Jam Tangan Mewah</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:06:36 +0700</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Winda Lorenza Gowasa, mantan istri polisi yang meninggal dunia di Medan disebut pernah diperiksa KPK terkait kasus suap pejabat Bea Cukai.</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866467/misteri-kematian-winda-lorenza-saksi-kpk-yang-sempat-terima-apartemen-dan-jam-tangan-mewah</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/qz6cNS9JQnwE8G3U7M2BKGZF1Ng=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mantan-istri-polisi-di-medan.jpg</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Tumbang Usia Syuting, Dimas Aditya Ngoyo Gym 6 Hari Sepekan dan Tidur 3 Jam Demi Urang Bunian</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:05:43 +0700</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Kesehatan Dimas Aditya menurun usai syuting film horor Urang Bunian. Bahkan ia harus menjalani pengobatan ke Malaysia.</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866466/tumbang-usia-syuting-dimas-aditya-ngoyo-gym-6-hari-sepekan-dan-tidur-3-jam-demi-urang-bunian</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Xyon9h6AXxUCv24WjA1iHGIj3vI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Dimas-Aditya-1-10082026.jpg</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Bima Arya Dorong Penguatan Sistem Penanganan Kekerasan terhadap Perempuan dan Anak di Daerah</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:05:40 +0700</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Kemendagri berkomitmen mendukung penguatan sistem penanganan kekerasan terhadap perempuan dan anak di daerah melalui integrasi antarsistem.</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kilas-kementerian/7866465/bima-arya-dorong-penguatan-sistem-penanganan-kekerasan-terhadap-perempuan-dan-anak-di-daerah</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/gsRVQtShNuekIBhrXILzSPyvI8I=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wamendagri-Bima-Arya-Senin-108.jpg</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Rusa Bawean di Ambang Kepunahan, Habitat Menyusut hingga Ancaman Anjing, DiCaprio-Bezos Turun Tangan</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:01:54 +0700</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Rusa Bawean hanya hidup di Pulau Bawean dan kini terancam punah. Populasinya terbatas, sementara habitat dan ruang hidupnya terus tertekan</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866464/rusa-bawean-di-ambang-kepunahan-habitat-menyusut-hingga-ancaman-anjing-dicaprio-bezos-turun-tangan</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/m78o3AHLbf_lw9austaCyXD-NTQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/rusabawean1111111.jpg</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>30 Banner Malam Tirakatan 17 Agustus 2026, Pilihan Desain Kreatif dan Meriah untuk Perayaan HUT RI</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:01:51 +0700</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Banner malam tirakatan berfungsi sebagai dekorasi acara, dengan desain yang dapat disesuaikan dengan tema dan suasana perayaan.</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866463/30-banner-malam-tirakatan-17-agustus-2026-pilihan-desain-kreatif-dan-meriah-untuk-perayaan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/26sTuo-0R_YY-xflIjfKv94m6ak=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/acara-malam-tirakatan-313.jpg</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Potensi Cuaca di Indonesia Periode 11 – 17 Agustus 2026: Puncak Fenomena El Nino</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:59:17 +0700</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Simak potensi curah hujan di Indonesia selama periode 11 – 17 Agustus 2026, hujan semakin jarang terjadi namun kini menuju puncak fenomena El Nino.</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866462/potensi-cuaca-di-indonesia-periode-11-17-agustus-2026-puncak-fenomena-el-nino</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5NsvRAfKVVqlNUGVnYRGovtF7v4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-8.jpg</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Menko Polkam: Karhutla Bisa Pengaruhi Karier Pangdam dan Kapolda</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:58:41 +0700</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Menko Polkam menegaskan keberhasilan mengendalikan karhutla menjadi ukuran kinerja Pangdam dan Kapolda di daerah.</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866461/menko-polkam-karhutla-bisa-pengaruhi-karier-pangdam-dan-kapolda</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Hd-phEqUAJjjJpVJ0H0S_SSBao8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menko-Polkam-Djamari-Chaniago-seusai-memimpin-rapat-di-Kemenko-Polkam.jpg</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Investor Pasar Modal Bertambah 9,9 Juta, Tembus 30,27 Juta di 2026</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:36:24 +0700</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — PT Bursa Efek Indonesia (BEI) mencatat penambahan sekitar 9,9 juta investor pasar modal dalam 7,5 bulan pada 2026. Dengan penambahan tersebut, jumlah investor pasar modal mencapai...</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjxko370/investor-pasar-modal-bertambah-99-juta-tembus-3027-juta-di-2026</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/030039500-1769669495-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Gamer Diajak Belajar Investasi dari Strategi Bermain Esports</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Perkembangan esports membuka ruang baru untuk mengenalkan literasi keuangan kepada generasi muda yang akrab dengan ekosistem digital. Kemampuan membaca situasi, menyusun strategi, dan menjaga disiplin dalam permainan...</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjrdu416/gamer-diajak-belajar-investasi-dari-strategi-bermain-esports</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260810162512-347.png</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Kejagung Periksa 7 Saksi Terkait Kasus TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:42:50 +0700</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Penyidik memanggil sebanyak 13 orang untuk dimintai keterangan terkait perkara TPPU Febrie Adriansyah, namun hanya tujuh orang yang memenuhi panggilan.</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266530/kejagung-periksa-7-saksi-terkait-kasus-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/AdibnpaOlQuNR5w3Be37I-wjLuE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320653/original/012439900_1786362162-71890.jpg</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Paspampres Siapkan Alutsista hingga Anti-Drone untuk HUT Ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:03:37 +0700</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Apel juga digelar untuk memastikan kesiapan 1.147 personel Paspampres serta alutsista.</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266503/paspampres-siapkan-alutsista-hingga-anti-drone-untuk-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/t1n1mNvr-bfeza8C8BfMprtF0SU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320627/original/023592100_1786359807-IMG-20260810-WA0024.jpg</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Pahitnya Potensi Panen Kopi Petani Purwakarta, Buah Dicuri hingga Pohon Ditebang</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:44:57 +0700</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Petani kopi Purwakarta menghadapi tahun terberat 2026. Produksi anjlok akibat kemarau, serangan hama, dan pencurian brutal rusak tanaman.</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>https://bandung.kompas.com/read/2026/08/10/184339678/pahitnya-potensi-panen-kopi-petani-purwakarta-buah-dicuri-hingga-pohon</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Fy21nFSmTLXq0H6vR6y80198Gwg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79a63632afc.jpeg</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Kecewa pada FIFA, 3 Konfederasi Mau Bikin Turnamen Tandingan Piala Dunia</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:44:57 +0700</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Tiga konfederasi sepak bola mulai membahas pembentukan kompetisi di luar FIFA, menyusul memburuknya hubungan dengan Gianni Infantino.</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/10/183041970/kecewa-pada-fifa-3-konfederasi-mau-bikin-turnamen-tandingan-piala-dunia</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/IjxOcautHznQ5BXDNwmgTWzUQn0=/0x0:4992x3328/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2026/06/16/6a308dcc235ea.jpg</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>PSSI Rencanakan Timnas Indonesia Hadapi Peserta Piala Dunia 2026</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:44:57 +0700</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia berpeluang melawan negara Piala Dunia 2026 di FIFA Matchday.</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/10/18080448/pssi-rencanakan-timnas-indonesia-hadapi-peserta-piala-dunia-2026</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/HPAIDi_2V8Fg5mjy9PlQyJOLwvw=/113x0:1136x682/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/06/09/6a281a5adcd81.jpeg</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I719"/>
+  <autoFilter ref="A1:I794"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$794</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$886</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I794"/>
+  <dimension ref="A1:I886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -37757,8 +37757,4332 @@
         </is>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Pemerintah kerahkan 43 helikopter untuk operasi udara tangani karhutla</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:39:25 +0700</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah kini mewaspadai ancaman El Nino kuat yang diperkirakan melanda Indonesia pada awal September hingga ...</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687981/pemerintah-kerahkan-43-helikopter-untuk-operasi-udara-tangani-karhutla</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_PEMERINTAH-KERAHKAN-43-HELIKOPTER-UNTUK-OPERASI-UDARA-TANGANI-KARHUTLA.jpg</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Kejati NTB banding atas vonis bebas tiga anggota DPRD</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:38:03 +0700</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Kejaksaan Tinggi Nusa Tenggara Barat mengajukan banding atas putusan bebas tiga anggota DPRD NTB dalam perkara ...</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688008/kejati-ntb-banding-atas-vonis-bebas-tiga-anggota-dprd</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/gedung-kejati-ntb-2.jpg</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Angka kebangkrutan perusahaan di Jepang pada Juli tembus 1.000</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:36:25 +0700</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Angka kebangkrutan perusahaan di Jepang pada Juli melampaui 1.000 kasus untuk bulan kedua berturut-turut, seiring ...</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688007/angka-kebangkrutan-perusahaan-di-jepang-pada-juli-tembus-1000</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CjkinzN000012_20260810_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Fatmah Nahdi ungkap tantangan peran di film "Bisikan Desa Gringsing"</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:32:11 +0700</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Aktris Fatmah Nahdi mengungkap tantangan memerankan karakter Fatimah dalam film terbaru berjudul "Bisikan Desa ...</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688005/fatmah-nahdi-ungkap-tantangan-peran-di-film-bisikan-desa-gringsing</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_184226-3.jpg</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Sulsel siapkan forum dan satgas pangan atasi harga pakan ternak ayam</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:30:52 +0700</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Sulawesi Selatan menyiapkan sejumlah langkah untuk merespons keluhan peternak ayam petelur ...</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687951/sulsel-siapkan-forum-dan-satgas-pangan-atasi-harga-pakan-ternak-ayam</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SULSEL-SIAPKAN-FORUM-DAN-SATGAS-PANGAN-ATASI-HARGA-PAKAN-TERNAK-AYAM.jpg</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Perbasi kembali panggil pemain untuk Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:30:31 +0700</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Dewan Pengurus Pusat Persatuan Bola Basket Seluruh Indonesia (DPP Perbasi) kembali memanggil empat pemain untuk ...</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688003/perbasi-kembali-panggil-pemain-untuk-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/WhatsApp-Image-2026-07-30-at-19.44.26.jpeg</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Sekelompok anjing "PAW Patrol" bakal ramaikan bioskop pada 14 Agustus</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:27:14 +0700</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Kru Paw Patrol yang beranggotakan sekelompok anjing akan berlaga dalam film "PAW Patrol:The Dino Movie" yang ...</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687999/sekelompok-anjing-paw-patrol-bakal-ramaikan-bioskop-pada-14-agustus</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/photo_6325543407836664781_y.jpg</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Pengadilan China selesaikan kasus tabrakan antarkapal di Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:25:04 +0700</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Pengadilan maritim China berhasil memediasi sengketa yang timbul akibat tabrakan antara dua kapal asing di dekat Selat ...</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687997/pengadilan-china-selesaikan-kasus-tabrakan-antarkapal-di-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CjkinzN000009_20260810_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>BNPB siagakan operasi darat dan OMC di 6 provinsi rawan karhutla</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:24:53 +0700</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) menyiagakan pasukan operasi darat dan operasi modifikasi cuaca (OMC) di ...</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687993/bnpb-siagakan-operasi-darat-dan-omc-di-6-provinsi-rawan-karhutla</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/20260810_151712.jpg</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Sebanyak 65 personel damkar padamkan kebakaran toko buah di Priok</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:24:37 +0700</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Sebanyak 65 personel pemadam kebakaran dikerahkan memadamkan kebakaran toko buah yang berlokasi di Jalan Bisma Raya, ...</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687992/sebanyak-65-personel-damkar-padamkan-kebakaran-toko-buah-di-priok</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/17/1000938564.jpg</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Konektivitas Menuju Kepulauan Seribu Menguat, Commuter Line Hubungkan Perjalanan dari Daratan Jakarta</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:22:18 +0700</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Rencana Pemerintah Provinsi DKI Jakarta memperkuat layanan transportasi menuju Kepulauan Seribu mulai 2027 membuka ...</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687989/konektivitas-menuju-kepulauan-seribu-menguat-commuter-line-hubungkan-perjalanan-dari-daratan-jakarta</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Stasiun-Angke-pic.jpg</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>KAI: Manggarai disiapkan perkuat konektivitas transportasi Jakarta</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:22:11 +0700</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) menyiapkan Stasiun Manggarai untuk memperkuat konektivitas transportasi Jakarta ...</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687988/kai-manggarai-disiapkan-perkuat-konektivitas-transportasi-jakarta</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/7E0EA540-666C-42EB-BB88-6C0E1868B9B3.jpeg</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Hotel Borobudur gelar "Discover Nusantara" sambut HUT Kemerdekaan RI</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:22:08 +0700</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Hotel Borobudur Jakarta menggelar program "Discover Nusantara" sepanjang Agustus 2026 dalam rangka menyambut ...</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687985/hotel-borobudur-gelar-discover-nusantara-sambut-hut-kemerdekaan-ri</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260810-WA0016.jpg</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>162 Ribu Pergerakan Pelanggan per Hari, Manggarai Disiapkan Menguatkan Konektivitas Transportasi Jakarta</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:19:30 +0700</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) memandang Stasiun Manggarai memiliki peran strategis dalam perkembangan sistem ...</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687979/162-ribu-pergerakan-pelanggan-per-hari-manggarai-disiapkan-menguatkan-konektivitas-transportasi-jakarta</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Stasiun-Manggarai-pic.jpg</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Pluang catat investor saham AS tumbuh enam kali lipat dalam tiga tahun</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:17:23 +0700</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – Pluang mencatat jumlah investor saham Amerika Serikat (AS) yang aktif bertransaksi setiap ...</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687976/pluang-catat-investor-saham-as-tumbuh-enam-kali-lipat-dalam-tiga-tahun</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Aplikasi-Pluang.jpg</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Polda Bengkulu tangkap pemilik gudang oplosan MinyaKita</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:16:05 +0700</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Subdit I Indagsi Ditreskrimsus Polda Bengkulu menangkap HS (37), warga Jakarta, yang diduga sebagai pemilik gudang ...</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687972/polda-bengkulu-tangkap-pemilik-gudang-oplosan-minyakita</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_162750.jpg</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Papua Barat pulihkan Rp29 miliar dan serahkan 24 temuan ke APH</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:16:04 +0700</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Inspektorat Provinsi Papua Barat menyerahkan penanganan 24 temuan terkait pengelolaan anggaran pada 2025 kepada aparat ...</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687969/papua-barat-pulihkan-rp29-miliar-dan-serahkan-24-temuan-ke-aph</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/25098.jpg</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Polisi olah TKP di sekolah temuan senjata dan narkoba di Jaksel</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:14:36 +0700</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Kepolisian melakukan olah tempat kejadian perkara (TKP) di sekolah temuan 995 airsoft gun dan narkoba di kawasan Pondok ...</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687965/polisi-olah-tkp-di-sekolah-temuan-senjata-dan-narkoba-di-jaksel</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001021514.jpg</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Kejati NTB periksa eks dirut bank syariah terkait pinjaman Rp11 miliar</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:11:35 +0700</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Kejaksaan Tinggi Nusa Tenggara Barat memeriksa mantan Direktur Utama bank syariah milik pemerintah daerah, Kukuh ...</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687961/kejati-ntb-periksa-eks-dirut-bank-syariah-terkait-pinjaman-rp11-miliar</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/jubir-kejati-ntb-harun.jpg</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>BKSDA turunkan tim nekropsi bangkai gajah sumatra di Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:08:23 +0700</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Balai Konservasi Sumber Daya Alam (BKSDA) Aceh menurunkan tim dokter hewan melakukan bedah bangkai atau nekropsi gajah ...</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687957/bksda-turunkan-tim-nekropsi-bangkai-gajah-sumatra-di-aceh-tamiang</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/gajah-mati-aceh-tamiang.jpg</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Rudenim Tanjungpinang deportasi 25 warga negara Vietnam</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:06:42 +0700</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Rumah Detensi Imigrasi (Rudenim) Pusat Tanjungpinang, Kepulauan Riau, mendeportasi 25 warga negara Vietnam yang ...</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687955/rudenim-tanjungpinang-deportasi-25-warga-negara-vietnam</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/inbound2795638213678190306.jpg</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Menhut pastikan penguatan antisipasi karhutla saat fenomena El Nino</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:06:05 +0700</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan (Menhut) Raja Juli Antoni mengatakan pemerintah memperkuat antisipasi kebakaran hutan dan lahan ...</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687952/menhut-pastikan-penguatan-antisipasi-karhutla-saat-fenomena-el-nino</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_182710.jpg</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Kemenimipas gandeng Kemenkes gelar CKG di Lapas Cipinang sambut HUT RI</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:01:50 +0700</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>ANTARA - Kementerian Imigrasi dan Pemasyarakatan (Imipas) berkolaborasi dengan Kementerian Kesehatan (Kemenkes) ...</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687923/kemenimipas-gandeng-kemenkes-gelar-ckg-di-lapas-cipinang-sambut-hut-ri</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KEMENIMIPAS-GANDENG-KEMENKES-GELAR-CKG-DI-LAPAS-CIPINANG-SAMBUT-HUT-RI.jpg</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Sekolah Nasional Terintegrasi IKN beroperasi perdana dengan 82 siswa</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:58:42 +0700</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>ANTARA - Sekolah Nasional Terintegrasi (SNT) di Ibu Kota Nusantara (IKN) memulai kegiatan perdana setelah ...</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687800/sekolah-nasional-terintegrasi-ikn-beroperasi-perdana-dengan-82-siswa</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SEKOLAH-NASIONAL-TERINTEGRASI-IKN-BEROPERASI-PERDANA-DENGAN-82-SISWA.jpg</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo beri dukungan penuh untuk restorasi ekosistem</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:58:10 +0700</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan Raja Juli Antoni mengungkapkan bahwa Presiden Prabowo Subianto memberikan dukungan penuh terhadap ...</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687947/presiden-prabowo-beri-dukungan-penuh-untuk-restorasi-ekosistem</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/01/1000638883.jpg</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Mendagri dan Menteri ATR/BPN percepat layanan BPHTB lewat SEB</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:55:51 +0700</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri Muhammad Tito Karnavian dan Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional Nusron ...</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687943/mendagri-dan-menteri-atr-bpn-percepat-layanan-bphtb-lewat-seb</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000583242.jpg</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Kakorbinmas Polri dorong Bhabinkamtibmas perkuat pendekatan warga</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:53:58 +0700</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Kepala Korps Pembinaan Masyarakat (Kakorbinmas) Baharkam Polri Irjen Pol Mardiyono mendorong Bhabinkamtibmas memperkuat ...</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687940/kakorbinmas-polri-dorong-bhabinkamtibmas-perkuat-pendekatan-warga</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/489818.jpg</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Luncuran lava pijar Gunung Karangetang tak jangkau permukiman warga</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:50:56 +0700</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Penyelidik Bumi Ahli Muda, Balai Pemantauan Gunung Api dan Mitigasi Bencana Gerakan Tanah Sulawesi Maluku, Sandy ...</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687936/luncuran-lava-pijar-gunung-karangetang-tak-jangkau-permukiman-warga</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001994877.jpg</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>PT JIEP dorong transparansi untuk perkuat kepercayaan publik</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:48:49 +0700</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>PT Jakarta Industrial Estate Pulogadung (Perseroda) atau PT JIEP mendorong keterbukaan informasi publik sebagai salah ...</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687933/pt-jiep-dorong-transparansi-untuk-perkuat-kepercayaan-publik</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/InShot_20260810_180458343.jpg</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>AFC, UEFA dan Concacaf surati FIFA tolak FFE</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:48:02 +0700</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Konfederasi sepak bola Asia (AFC0, Eropa  (UEFA) dan (Amerika Utara, Amerika Tengah, Karibia (Concacaf) ...</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687932/afc-uefa-dan-concacaf-surati-fifa-tolak-ffe</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/06/Peresmian-Kantor-FIFA-Jakarta-101123-hma-08.jpg</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Polresta Palu periksa sembilan saksi kasus pembunuhan satu keluarga</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Polresta Palu, Sulawesi Tengah, telah memeriksa sembilan saksi dalam kasus pembunuhan satu keluarga di Jalan PDAM, ...</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687929/polresta-palu-periksa-sembilan-saksi-kasus-pembunuhan-satu-keluarga</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260810-WA0007-1.jpg</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>X dikabarkan ubah skema monetisasi untuk kreator tekan orisinal konten</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:47:15 +0700</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Platform jejaring sosial milik pebisnis Elon Musk, X dikabarkan akan melakukan perubahan skema monetisasi terhadap ...</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687927/x-dikabarkan-ubah-skema-monetisasi-untuk-kreator-tekan-orisinal-konten</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/08/Logo-X.jpg</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>HUT pertama Kodam XXII/Tambun Bungai teguhkan pertahanan Kalteng</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:47:14 +0700</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>ANTARA - Peringatan HUT pertama Kodam XXII/Tambun Bungai menjadi momentum memperkuat komitmen menjaga pertahanan dan ...</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687836/hut-pertama-kodam-xxii-tambun-bungai-teguhkan-pertahanan-kalteng</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/HUT-PERTAMA-KODAM-XXII-TAMBUN-BUNGAI-TEGUHKAN-PERTAHANAN-KALTENG.jpg</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Bulog sebut stok beras 5,25 juta ton tersebar seluruh gudang Indonesia</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:45:14 +0700</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Perum Bulog menegaskan stok cadangan beras pemerintah (CBP) secara nasional yang dikelola mencapai 5,25 juta ton, ...</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687920/bulog-sebut-stok-beras-525-juta-ton-tersebar-seluruh-gudang-indonesia</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/EC556D40-7F50-4F3D-BFA5-0B17C15F0154.jpeg</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Pengadilan Tinggi Surabaya terapkan sidang elektronik tingkat banding</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:44:29 +0700</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>ANTARA - Pengadilan Tinggi Surabaya mulai menerapkan sidang elektronik untuk seluruh perkara tingkat banding, termasuk ...</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687687/pengadilan-tinggi-surabaya-terapkan-sidang-elektronik-tingkat-banding</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PENGADILAN-TINGGI-SURABAYA-TERAPKAN-SIDANG-ELEKTRONIK-TINGKAT-BANDING_1.jpg</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Sekolah anak-anak desa terpencil di Kerinci</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:43:58 +0700</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Sejumlah murid berjalan meninggalkan sekolah usai mengikuti kegiatan belajar mengajar di SDN 226/III Renah Kasah, ...</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5687917/sekolah-anak-anak-desa-terpencil-di-kerinci</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Semangat-sekolah-anak-anak-desa-terpencil-Kerinci-100826-ws-6.jpg</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Mensesneg serahkan surpres terkait Gubernur BI kepada DPR</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:43:04 +0700</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Sekretaris Negara Prasetyo Hadi menyerahkan tiga Surat Presiden (Surpres) kepada DPR RI, di Kompleks ...</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687891/mensesneg-serahkan-surpres-terkait-gubernur-bi-kepada-dpr</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENSESNEG-SERAHKAN-SURPRES-TERKAIT-GUBERNUR-BI-KEPADA-DPR.jpg</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Aghniny Haque jajal syuting di kompleks Iskandar Malaysia Studios</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:42:15 +0700</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Aktris Indonesia Aghniny Haque dan Hesti Putri membagikan pengalaman menjajal proses syuting film "Bisikan Desa ...</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5687915/aghniny-haque-jajal-syuting-di-kompleks-iskandar-malaysia-studios</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_130330.jpg</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Pencapaian Alikka Kalistha Usai Ultah ke-22: Happy Masuk TV!</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:09:51 +0700</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Selebgram Alikka Kalistha mengungkapkan salah satu pencapaian. Kebetulan ia baru juga ulang tahun.</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612013/pencapaian-alikka-kalistha-usai-ultah-ke-22-happy-masuk-tv</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/alikka-kalistha-1786343086146_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Vietnam Layak Waspada, Kans Malaysia Ciptakan Dejavu Masa Lalu di Semifinal Piala AFF 2026</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:26:43 +0700</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Timnas Vietnam harus menaruh waspada terhadap Malaysia yang bakal jadi lawan mereka di semifinal Piala AFF 2026.</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866508/vietnam-layak-waspada-kans-malaysia-ciptakan-dejavu-masa-lalu-di-semifinal-piala-aff-2026</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0ZYdO2i7sJNRdAvkLPBImQFZQSw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Nguyen-Quang-Hai-Vietnam-Piala-AFF-2024-1612.jpg</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Resmikan Gol Perdana Berbaju Real Madrid, Carlos Espi Terus Jalani Proses</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:24:36 +0700</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Pemain depan anyar Real Madrid, Carlos Espi, mencetak gol perdananya bagi Los Blancos saat berhadapan dengan Ferencvaros di laga uji coba.</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866507/resmikan-gol-perdana-berbaju-real-madrid-carlos-espi-terus-jalani-proses</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/KSajdTxa1ppoHKZQfARaD3lvLBw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemain-baru-Real-Madrid-Carlos-Espi.jpg</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Kaisar Naruhito dan Permaisuri Masako Batalkan Liburan, Sumbangkan Dana Bantuan untuk Kumamoto</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:23:59 +0700</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Kaisar Naruhito dan Permaisuri Masako menyalurkan bantuan bagi korban Gempa Kumamoto 2026. Keluarga Kekaisaran juga membatalkan agenda</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866506/kaisar-naruhito-dan-permaisuri-masako-batalkan-liburan-sumbangkan-dana-bantuan-untuk-kumamoto</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/eMRqsPN4yuuhvRDv1V0dYQkWps4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/naruhito111111.jpg</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Khariq Anhar Wisuda di Tengah Tuntutan 6 Bulan: “Semoga Dapat Kerja, Bukan Penjara”</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:23:52 +0700</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Dituntut enam bulan penjara pada 10 Agustus, Khariq akan wisuda 18 Agustus sebelum kembali ke ruang sidang.</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866505/khariq-anhar-wisuda-di-tengah-tuntutan-6-bulan-semoga-dapat-kerja-bukan-penjara</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8fRftMALcqsKVRKz4f9OCapaRjA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Terdakwa-Khariq-Anhar-kuasa-hukum-usai-sidang-tuntutan-kasus-timpa-teks.jpg</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Jejak Gagasan Destry Damayanti Calon Gubernur BI saat Fit and Proper Test di Komisi XI DPR</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:19:29 +0700</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Gagasannya mencakup stabilitas rupiah, kebijakan moneter, makroprudensial, sistem pembayaran digital, pasar keuangan, dan UMKM.</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866504/jejak-gagasan-destry-damayanti-calon-gubernur-bi-saat-fit-and-proper-test-di-komisi-xi-dpr</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c1C0qZ4ZTdcn1wQcewDcdVgY3Sk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/destry-damayanti-deputi-gubernur-senior-dgs-bank-indonesia.jpg</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>SUV  T2 i-DM Punya Garansi Kendaraan 6 Tahun Tanpa Batasan Kilometer</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:18:21 +0700</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Perusahaan menyiapkan pusat distribusi suku cadang seluas 2.000 meter persegi yang mencakup 31.000 item parts.</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7866503/suv-t2-i-dm-punya-garansi-kendaraan-6-tahun-tanpa-batasan-kilometer</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XfO4wACdahOFt6ItkTY6iL2cBmE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Paparan-teknologi-SUV-Jetour-T2-i-DM-di-GIIAS-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Masa Depan Pangkalan Rusia di Suriah Ditentukan dalam 3 Bulan, Ini Perubahannya</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:12:36 +0700</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Pemerintah Suriah mengumumkan telah mencapai kesepakatan dengan Rusia mengenai masa depan kedua fasilitas tersebut.</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866502/masa-depan-pangkalan-rusia-di-suriah-ditentukan-dalam-3-bulan-ini-perubahannya</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/cepEmntAKDHO6SS1JIcGlTjHW6c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/selongsong-bom-serangan-udara-Israel-di-Suriah.jpg</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Kebakaran Hutan dan Lahan Meluas, Pemerintah Minta Masyarakat Tingkatkan Kewaspadaan</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:04:34 +0700</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Pemerintah berharap kewaspadaan masyarakat dapat membantu mencegah munculnya titik api baru.</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866501/kebakaran-hutan-dan-lahan-meluas-pemerintah-minta-masyarakat-tingkatkan-kewaspadaan</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/j2S7gAqYm6hUyXDc9EsEv3NLcUc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Karhutla-Bromo-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Jelang HUT ke-81 RI, Pemerintah Siapkan Bantuan Beras Tahap II untuk 33,24 Juta KPM</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:01:17 +0700</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Pemerintah akan kembali menyalurkan Bantuan Pangan Beras Tahap II kepada 33,24 juta keluarga penerima manfaat (KPM) di seluruh Indonesia.</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866500/jelang-hut-ke-81-ri-pemerintah-siapkan-bantuan-beras-tahap-ii-untuk-3324-juta-kpm</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Sn2AzBvrauTN9Mxi4xaVbPHeLE8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-beras-di-gudang.jpg</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Transportasi Kepulauan Seribu Beralih ke TransJakarta, Fahira Soroti 6 Hal Ini</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Tantangan utama transportasi Kepulauan Seribu adalah memastikan warga memperoleh layanan publik yang setara dengan masyarakat di wilayah lainnya</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866499/transportasi-kepulauan-seribu-beralih-ke-transjakarta-fahira-soroti-6-hal-ini</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/VW5HtMPTQmzbHprUzB8VxR5P0a4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/fahiraidris111111.jpg</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Flores Besok Selasa 11 Agustus 2026: Bajawa Diprediksi Kabut Asap</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:00:08 +0700</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Berikut detail prakiraan cuaca di beberapa kota terkenal di Flores untuk Selasa (11/8/2026) dilansir dari BMKG.</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866498/prakiraan-cuaca-flores-besok-selasa-11-agustus-2026-bajawa-diprediksi-kabut-asap</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/OhzEZi8-TThzoLbcoQWSjHOkPjE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pantai-pink-pulau-komodo-labuan-bajo-manggarai-barat-ntt.jpg</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>43.805 Pekerja Kena PHK Januari-Juli 2026, Terbanyak di Jabar</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:59:44 +0700</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Sebanyak 43 ribu lebih pekerja di Indonesia harus menghadapi pemutusan hubungan kerja (PHK) sepanjang Januari-Juli 2026.</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866497/43805-pekerja-kena-phk-januari-juli-2026-terbanyak-di-jabar</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fI4dy5xULfqtZz8Z5nhadxzCVNI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/angka-phk-di-jabar232.jpg</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Pulihkan Pasokan Semen di Aceh, SMGR Optimalisasi Produksi dan Distribusi</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:57:07 +0700</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>SMGR tetap berupaya maksimal dalam menjaga ketersediaan produk di berbagai titik penjualan walaupun perusahaan tengah mengalami tekanan</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866496/pulihkan-pasokan-semen-di-aceh-smgr-optimalisasi-produksi-dan-distribusi</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/twtsLeG6muRZCGg9ncrkUqlVtBA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SMGR-pasokan-semen-Aceh.jpg</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Mengenal Gejala Superflu, Lengkap dengan Penyebab dan Cara Mencegahnya</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:55:13 +0700</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Superflu merupakan istilah yang dikaitkan dengan influenza, berikut gejala, faktor penyebab, hingga cara mencegahnya berikut ini.</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866495/mengenal-gejala-superflu-lengkap-dengan-penyebab-dan-cara-mencegahnya</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yvYBk7Mj-zTlRR51mwpwa8LWo7E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Cek-kesehatan-gratis-di-Colomadu-Tohudan.jpg</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Israel Tolak Penarikan Pasukan Sebelum Hamas Dilucuti, Rencana Damai Gaza Terancam</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:54:30 +0700</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Pemerintah Israel menilai penarikan pasukan sebelum pelucutan senjata selesai dapat menciptakan risiko keamanan baru.</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866494/israel-tolak-penarikan-pasukan-sebelum-hamas-dilucuti-rencana-damai-gaza-terancam</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/67KE1S1-igdGhTGm1JEcCY0c8Uk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ANGGOTA-BRIGADE-AL-QASSAM-wr24324234234.jpg</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>ABK Indonesia Berusia 20 Tahun Hilang, Diduga Jatuh dari Kapal Kontainer di Perairan Ehime Jepang</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:52:19 +0700</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>ABK Indonesia berusia 20 tahun hilang diduga jatuh ke laut dari kapal kontainer di lepas pantai Ehime, Jepang. Tim SAR masih mencari</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866493/abk-indonesia-berusia-20-tahun-hilang-diduga-jatuh-dari-kapal-kontainer-di-perairan-ehime-jepang</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GYWEhOLACcBdVWWBSG7xROAPsa4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tkptenggelam1111.jpg</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Nasib Tian Ngantung Pembalap Drag Race Tabrak Penonton hingga 8 Orang Tewas, Wajah Dipenuhi Perban</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:52:09 +0700</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Drag race di Kotamobagu berujung maut, mobil pembalap menabrak penonton hingga 8 orang tewas dan 9 lainnya terluka.</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866492/nasib-tian-ngantung-pembalap-drag-race-tabrak-penonton-hingga-8-orang-tewas-wajah-dipenuhi-perban</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/AXdgAr9Iw3PgL4auFlOtiwlS1HI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kecelakaan-Drag-Race-dan-Drag-Bike-di-kotamobagu.jpg</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Malang-Batu Besok, Selasa 11 Agustus 2026: Batu Lebih Dingin, Malang 30 Derajat</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:47:23 +0700</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Cuaca Malang dan Batu besok diprakirakan cerah berkabut hingga udara kabur, suhu Malang mencapai 30 derajat Celsius.</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866491/prakiraan-cuaca-malang-batu-besok-selasa-11-agustus-2026-batu-lebih-dingin-malang-30-derajat</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/eu4A6cMigDB3AsrpfAl0TfCYo68=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/alun-alun-kota-malang-april-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Jelang HUT ke-81 RI, Istana Pastikan Aman, TNI Wanti-wanti Hoaks</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:45:51 +0700</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Jelang HUT ke-81 RI, Istana memastikan pengamanan siap. Panglima TNI mengingatkan warga mewaspadai hoaks dan isu provokatif.</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866490/jelang-hut-ke-81-ri-istana-pastikan-aman-tni-wanti-wanti-hoaks</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/b9Hcqv7iS4vvK6LuL2i9t4rjFXQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Presiden-Prabowo-Subianto-Gibran-Rakabuming-Prasetyo-Hadi-Muhaimin-Iskandar-di-Halim.jpg</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum Febrie Adriansyah Minta Kejagung RI Tak Hindari Sidang Gugatan Praperadilan</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:44:39 +0700</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Kejagung RI selaku salah satu termohon dalam gugatan praperadilan Febrie Adriansyah diminta untuk bersedia hadir di persidangan.</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866489/kuasa-hukum-febrie-adriansyah-minta-kejagung-ri-tak-hindari-sidang-gugatan-praperadilan</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/eQh7NUBPd1a5LZJ7hmRGe9FD4wA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Febrie-Adriansyah-Jalani-Pemeriksaan-Lanjutan-Kasus-TPPU_20260807_134205.jpg</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Destry Calon Tunggal Gubernur BI, Airlangga Beri Komentar Tak Terduga</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:25:54 +0700</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Airlangga Hartanto buka suara soal Destry Damayanti menjadi calon tunggal Gubernur definitif Bank Indonesia (BI).</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810181654-17-758058/destry-calon-tunggal-gubernur-bi-airlangga-beri-komentar-tak-terduga</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/aimenteri-koordinator-bidang-perekonomian-airlangga-hartarto-pada-konferensi-pers-di-jakarta-rabu-582026-1785971442706_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Jelang Review MSCI Agustus 2026, OJK Bilang Gini</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>OJK berharap MSCI mencabut pembekuan saham Indonesia dalam tinjauan 12 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810170312-17-758042/jelang-review-msci-agustus-2026-ojk-bilang-gini</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/07/15/ilustrasi-bursa-cnbc-indonesiaandrean-kristianto-4_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Efek 'Sulap' Prabowo, Valuasi Emiten BUMN Ini Melonjak Drastis</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:52:46 +0700</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>PT Timah Tbk (TINS) mencatat laba usaha Rp3,48 triliun di Semester I 2026, meningkat signifikan. Target produksi logam hingga 25.000 ton diharapkan tercapai.</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810183732-17-758071/efek-sulap-prabowo-valuasi-emiten-bumn-ini-melonjak-drastis</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/08/25/timah-balok-siap-jual-cnbc-indonesiafirda-dwi-muliawati-1756098257458_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Danantara Bisa Jadi Pemegang Saham BEI, OJK Masih Godok Aturan</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>OJK mengungkap rencana demutualisasi BEI dan keterlibatan BPI Danantara sebagai pemegang saham.</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810145436-17-757986/danantara-bisa-jadi-pemegang-saham-bei-ojk-masih-godok-aturan</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/03/26/ilustrasi-ojk-cnbc-indonesiafaisal-rahman-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Bukan Cuma Uang, Wakaf di Istiqlal Bisa Berupa Saham</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:55:10 +0700</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia memperkenalkan program wakaf dan sedekah melalui pasar modal, termasuk saham dan reksa dana, untuk mendukung filantropi Islam.</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810142935-17-757976/bukan-cuma-uang-wakaf-di-istiqlal-bisa-berupa-saham</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019885_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Tantangan Besar Destry-Calon Gubernur BI di Tengah Gejolak Global</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:25:06 +0700</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Destry Damayanti menjadi calon tunggal Gubernur Bank Indonesia (BI) pilihan Presiden Prabowo Subianto.</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810143206-17-757969/tantangan-besar-destry-calon-gubernur-bi-di-tengah-gejolak-global</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/08/07/5771d0f6-119c-445f-808c-6c2f636386f8_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Video: Calon Tunggal Gubernur BI hingga IHSG Anjlok Lagi ke 6.300-an</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:22:24 +0700</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Calon Tunggal Gubernur BI hingga IHSG Anjlok Lagi ke Level 6.300-an</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810165854-19-758037/video-calon-tunggal-gubernur-bi-hingga-ihsg-anjlok-lagi-ke-6300-an</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/calon-tunggal-gubernur-bi-hingga-ihsg-anjlok-lagi-ke-level-6300-an-1786357244157_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Video: Sinyal Suku Bunga Tinggi BI dan The Fed, Bos MI Ungkap Efeknya</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:58:12 +0700</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Sinyal Suku Bunga Tinggi BI dan The Fed, Bos MI Ungkap Efeknya IHSG hingga SBN</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810155822-19-758002/video-sinyal-suku-bunga-tinggi-bi-the-fed-bos-mi-ungkap-efeknya</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/sinyal-suku-bunga-tinggi-bi-the-fed-bos-mi-ungkap-efeknya-ihsg-hingga-sbn-1786352623714_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>IHSG Ambruk 0,69%, Dua Saham Ini Jadi Beban</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:35:17 +0700</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>IHSG ditutup melemah di level 6.365,37 pada hari ini, Senin (10/8/2026).</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810161653-17-758017/ihsg-ambruk-069-dua-saham-ini-jadi-beban</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/19/ilustrasi-orang-berdoa-dengan-latar-belakang-bursa-saham-indonesia-di-bursa-efek-indonesia-jakarta-selasa-1952026-1779182674119_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Video: Prabowo Usul Destry Jadi Gubernur BI, Pasar Respons Begini</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:14:57 +0700</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Prabowo Usulkan Destry Damayanti Jadi Gubernur BI, Pasar Respon Positif</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810160015-19-758003/video-prabowo-usul-destry-jadi-gubernur-bi-pasar-respons-begini</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/prabowo-usulkan-destry-damayanti-jadi-gubernur-bi-pasar-respon-positif-1786352735826_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Universitas Tempatkan Dana di Sukuk Negara: Hasilkan Beasiswa-Riset</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:50:10 +0700</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan (Kemenkeu) mengungkapkan manfaat dari surat berharga syariah negara (SBSN) atau Sukuk Negara</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810132119-17-757937/universitas-tempatkan-dana-di-sukuk-negara-hasilkan-beasiswa-riset</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/22/direktur-pembiayaan-syariah-djppr-kementerian-keuangan-deni-ridwan-saat-menyampaikan-pemaparan-dalam-sesi-educational-class-di-1779456376570_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Duit Investor Menguap, SpaceX Bakar Rp288 T Cuma buat AI</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:45:32 +0700</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Elon Musk mengalami momen tak terduga saat roket SpaceX menghantam Bulan. Pendapatan SpaceX melonjak, namun kerugian tetap membayangi.</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810153232-17-757992/duit-investor-menguap-spacex-bakar-rp288-t-cuma-buat-ai</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/13/roket-spacex-falcon-9-dan-pesawat-ruang-angkasa-dragon-lepas-landas-dalam-misi-crew-12-nasa-ke-stasiun-luar-angkasa-internasio-1770990649346_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Danantara Mau Bawa BUMN Melantai di BEI, Pandu: Buat Tambah Likuiditas</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:43:28 +0700</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>BPI Danantara rencanakan IPO sejumlah BUMN di BEI untuk meningkatkan likuiditas pasar. Perusahaan seperti Pelindo dan Angkasa Pura akan dilibatkan.</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810154057-17-757995/danantara-mau-bawa-bumn-melantai-di-bei-pandu-buat-tambah-likuiditas</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/19/chief-investment-officer-cio-danantara-pandu-sjahrir-menyampaikan-paparan-dalam-acara-big-alpha-business-summit-2025-di-jakart-1766116798744_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>OJK Bakal Punya Bos Baru, Prabowo Hari Ini Kirim Surpres ke DPR</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:30:03 +0700</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Pemerintah memperluas kewenangan OJK untuk mengawasi Bursa Mineral dan Komoditas Strategis mulai 2027.</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810140608-17-757952/ojk-bakal-punya-bos-baru-prabowo-hari-ini-kirim-surpres-ke-dpr</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/03/26/ilustrasi-ojk-cnbc-indonesiafaisal-rahman-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>BRI Perkuat Pembiayaan Perumahan dalam Danantara Housing Expo 2026</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:14:15 +0700</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Danantara Housing Expo 2026 hadir untuk mendukung Program 3 Juta Rumah, menawarkan 200.000 unit hunian dan solusi pembiayaan</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810150534-17-757988/bri-perkuat-pembiayaan-perumahan-dalam-danantara-housing-expo-2026</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/danantara-housing-expo-1786349470824_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Rupiah Menguat 4 Hari Beruntun, Dolar AS Turun ke Rp17.750</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:06:00 +0700</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah berhasil menutup perdagangan awal pekan dengan penguatan tajam melawan dolar Amerika Serikat (AS).</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810144853-17-757977/rupiah-menguat-4-hari-beruntun-dolar-as-turun-ke-rp17750</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/09/25/petugas-menjunjukkan-mata-uang-dolar-amerika-serikat-as-dan-rupiah-di-vip-money-changer-jakarta-kamis-2592025-1758794525604_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Video: Transaksi Bursa Berjangka Diramal Masih Bisa Naik 60% di 2026</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:53:55 +0700</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Volatilitas Masih Tinggi, Transaksi Bursa Berjangka 2026 Diramal Masih Bisa Naik 60%</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810141600-19-757957/video-transaksi-bursa-berjangka-diramal-masih-bisa-naik-60-di-2026</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/perdagangan-perak-saham-as-di-bursa-berjangka-kian-marak-di-2026-apa-pendorongnya-1786347672100_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Airlangga dan Bos Pajak Pertimbangkan Potensi Pajak ETF Emas Direvisi</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:45:35 +0700</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Menko Airlangga Hartarto koordinasi dengan Kemenkeu terkait revisi pajak untuk Electronic Gold Receipt. Harapannya, transaksi ETF emas meningkat.</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810122756-17-757914/airlangga-bos-pajak-pertimbangkan-potensi-pajak-etf-emas-direvisi</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/menko-pereknomian-airlangga-hartarto-saat-acara-peringatan-hut-ke-49-pasar-modal-indonesia-dan-peluncuran-produk-etf-emas-seni-1786330817178_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Awas! Michael Burry Wanti-wanti Crash 1987 Terulang Lagi</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:35:03 +0700</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Investor legendaris Michael Burry tetap bertahan dengan posisi jual meski SdanP 500 mencetak rekor. Ia peringatkan potensi kejatuhan pasar seperti 1987.</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810131347-17-757934/awas-michael-burry-wanti-wanti-crash-1987-terulang-lagi</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/11/michael-burry-dimitrios-kambouris-getty-images-north-america-getty-images-via-afp-1778480233916_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Video: Rupiah Makin Perkasa dan Menguat ke Rp 17.700-an per Dolar AS</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:34:49 +0700</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Rupiah Makin Perkasa dan Menguat ke Rp 17.700-an per Dolar AS</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810142639-19-757965/video-rupiah-makin-perkasa-menguat-ke-rp-17700-an-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/rupiah-makin-perkasa-menguat-ke-rp-17700-an-per-dolar-as-1786347234430_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Airlangga Soroti Pajak 'PPN dan PPh' dari Transaksi EGR</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:15:47 +0700</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Menko Airlangga Hartarto dorong perlakuan pajak untuk transaksi Electronic Gold Receipt (EGR) guna pengembangan ETF emas di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810135234-17-757950/airlangga-soroti-pajak-ppn-dan-pph-dari-transaksi-egr</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/menko-pereknomian-airlangga-hartarto-saat-acara-peringatan-hut-ke-49-pasar-modal-indonesia-dan-peluncuran-produk-etf-emas-seni-1786330817178_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Video: ETF Emas Resmi Diluncurkan, Wamenkeu Titip Tiga Pesan</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:15:03 +0700</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>ETF Emas Resmi Diluncurkan, Wamenkeu Titip Tiga Pesan</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810124636-19-757918/video-etf-emas-resmi-diluncurkan-wamenkeu-titip-tiga-pesan</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/etf-emas-resmi-diluncurkan-wamenkeu-titip-tiga-pesan-1786344716395_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Perubahan Teknologi Makin Cepat, Perusahaan IT Genjot Adaptasi AI</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:31:39 +0700</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Perkembangan teknologi yang semakin cepat mendorong perusahaan teknologi informasi (IT) memperkuat kemampuan adaptasi, terutama dalam menghadapi perkembangan artificial intelligence (AI). Perubahan yang sebelumnya berlangsung dalam hitungan tahun...</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjk04r416/perubahan-teknologi-makin-cepat-perusahaan-it-genjot-adaptasi-ai</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/kecerdasan-buatan-atau-ai-ilustrasi-lebih-dari-200-tokoh_250924111739-212.jpg</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Pembangunan Tol Layang Ancol Timur-Pluit Capai 44,12 Persen, Ditargetkan Beroperasi 2028</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Pembangunan Jalan Tol Harbour Road II (HBR II) terus berjalan dengan progres konstruksi mencapai 44,12 persen per awal Agustus 2026. Ruas tol layang Ancol Timur-Pluit tersebut ditargetkan...</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjsfd416/pembangunan-tol-layang-ancol-timurpluit-capai-4412-persen-ditargetkan-beroperasi-2028</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260810164713-634.png</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Bigmo Dicecar 40 Pertanyaan, Akui Salah Promosi Vape Ajak Anak</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:28:14 +0700</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Bigmo menjalani pemeriksaan selama sekitar empat jam.</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266554/bigmo-dicecar-40-pertanyaan-akui-salah-promosi-vape-ajak-anak</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/fU5Qq94_Eb5gSrPjGZ_wg7oj-oc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320661/original/015938000_1786364749-71853.jpg</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Menko Polkam ke Pangdam dan Kapolda: Karhutla Tentukan Karier Anda</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:17:33 +0700</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Menurut Djamari, keberhasilan penanganan karhutla diukur dari kemampuan aparat mengendalikan titik api.</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266551/menko-polkam-ke-pangdam-dan-kapolda-karhutla-tentukan-karier-anda</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/v65nxNPh494cmWMnnl7ST70epHM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320658/original/015286800_1786364252-IMG_8200.jpeg</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Strategi Pemerintah Cegah Asap Karhutla Menyebar ke Negara Tetangga</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:09:25 +0700</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Pemerintah pun menanti kemunculan awan hujan untuk menjalankan Operasi Modifikasi Cuaca (OMC).</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266548/strategi-pemerintah-cegah-asap-karhutla-menyebar-ke-negara-tetangga</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/drley7BU6pBcGwJIxbChDJ5cnqM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320657/original/072138100_1786363761-IMG_8202.jpeg</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>BPA Gelar Lelang Serentak: Limit Terendah Rp 3 Ribu, Tertinggi Rp 9,1 Miliar</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:05:26 +0700</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Setiap rupiah yang berhasil dipulihkan BPA Kejaksaan merupakan hak negara dan masyarakat yang wajib dikembalikan.</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266544/bpa-gelar-lelang-serentak-limit-terendah-rp-3-ribu-tertinggi-rp-91-miliar</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/95nxxVphs6VNs9nq8KsRTLg5sE0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320656/original/022231000_1786363519-WhatsApp_Image_2026-08-10_at_16.13.38.jpeg</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Karhutla Meluas, 107.000 Hektare Lahan di Indonesia Terbakar</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:39:27 +0700</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Fenomena El Nino atau kemarau yang melanda Indonesia saat ini mempercepat terjadinya kebakaran hutan dan lahan (karhutla).</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266493/karhutla-meluas-107000-hektare-lahan-di-indonesia-terbakar</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/52ERORkc0kbwgpNk-Zs71NbkIyk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320558/original/015050400_1786355841-men6.jpg</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Panglima TNI Minta Warga Tak Terprovokasi Isu Medsos</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:19:15 +0700</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Panglima TNI Jenderal Agus Subiyanto menegaskan keamanan nasional tetap terjaga pasca rapat dengan pimpinan DPR.</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266124/panglima-tni-minta-warga-tak-terprovokasi-isu-medsos</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/rD3ueMTqt3nI5n9Y9DV2HbCXMo0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320239/original/070492200_1786341140-c57a18a3-9595-4171-9ddf-5e5fedc25804.jpg</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>KPK Tahan 4 Tersangka Kasus Pengadaan Iklan Bank BJB</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:44:32 +0700</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>KPK menahan 4 tersangka kasus korupsi pengadaan iklan fiktif di Bank BJB yang merugikan negara Rp 222 miliar, satu tersangka lain belum ditahan.</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/10/19435331/kpk-tahan-4-tersangka-kasus-pengadaan-iklan-bank-bjb</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/469bCMWHgGRvW4sa8pM0mm9-QYY=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79c41e45066.jpeg</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Dua JPO Tak Terintegrasi di Rasuna, Ketika Kepentingan Berbeda Bertemu di Satu Kawasan</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:44:32 +0700</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Dua JPO di Rasuna tak terintegrasi meski berdiri berdekatan. Pengamat menilai perbedaan aset dan kepentingan jadi tantangan.</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/10/19231931/dua-jpo-tak-terintegrasi-di-rasuna-ketika-kepentingan-berbeda-bertemu-di</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/P807KvISkgYTpCrYkWD_L6vlU6M=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/04/6a716628f297a.jpg</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>China-Rusia Langsung "Melek" Saat Amunisi AS Terkuras di Perang Iran</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:44:32 +0700</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Rangkaian pengeboman dan operasi pertahanan Amerika selama lebih dari 5 bulan melawan Iran menguras ribuan rudal presisi bernilai jutaan dollar AS.</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>https://internasional.kompas.com/read/2026/08/10/190000870/china-rusia-langsung-melek-saat-amunisi-as-terkuras-di-perang-iran</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/lYO_7LPMZNLZPppdjChIiVnV0pI=/0x0:2000x1333/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a7972125450a.jpg</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I794"/>
+  <autoFilter ref="A1:I886"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$886</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1067</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I886"/>
+  <dimension ref="A1:I1067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -42081,8 +42081,8515 @@
         </is>
       </c>
     </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Seskab: Prestasi atlet panjat tebing wujud nyata mengisi kemerdekaan</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:08:14 +0700</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyebut prestasi atlet panjat tebing Indonesia di panggung dunia sebagai salah ...</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688163/seskab-prestasi-atlet-panjat-tebing-wujud-nyata-mengisi-kemerdekaan</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000035210.jpg</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Kemensos apresiasi Sumenep siapkan lahan untuk Sekolah Rakyat permanen</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:07:14 +0700</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial mengapresiasi Pemerintah Kabupaten Sumenep, Jawa Timur telah menyiapkan lahan seluas 7,1 hektare ...</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688159/kemensos-apresiasi-sumenep-siapkan-lahan-untuk-sekolah-rakyat-permanen</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-20.30.24.jpeg</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Liman unggulan pertama dalam World Tour Lausanne 2026</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:06:50 +0700</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Tim Liman dari Serbia menjadi unggulan pertama dalam perebutan gelar juara  3x3 World Tour Lausanne 2026 di Place ...</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688157/liman-unggulan-pertama-dalam-world-tour-lausanne-2026</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000478563.jpg</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>​KAI Daop 6 Yogyakarta sediakan layanan Wi-Fi gratis di 33 stasiun</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:06:38 +0700</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) Daerah Operasi (Daop) 6 Yogyakarta menyediakan fasilitas jaringan Wi-Fi gratis di ...</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688155/kai-daop-6-yogyakarta-sediakan-layanan-wi-fi-gratis-di-33-stasiun</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000047034.jpg</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Syuting di Johor, para pemeran Bisikan Desa Gringsing berburu cokelat</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:04:40 +0700</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Proses syuting film Indonesia terbaru "Bisikan Desa Gringsing" di kompleks Iskandar Malaysia Studios, Johor, ...</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688151/syuting-di-johor-para-pemeran-bisikan-desa-gringsing-berburu-cokelat</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_130945.jpg</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Martin kian percaya diri setelah GP Inggris</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:03:08 +0700</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Pembalap Aprilia Racing Jorge Martin menyatakan kian percaya diri setelah memperoleh hasil positif dari MotoGP Inggris ...</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688149/martin-kian-percaya-diri-setelah-gp-inggris</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/11/06/Jorge-Martin-Juara-MotoGP-Mandalika-290924-Ak-19.jpg</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Pemulihan pertanian pascabencana di Aceh capai 49 persen</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:59:40 +0700</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>ANTARA - Realisasi pemulihan area pertanian dan perkebunan di Provinsi Aceh yang terdampak bencana akhir tahun lalu ...</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688108/pemulihan-pertanian-pascabencana-di-aceh-capai-49-persen</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_31_24_07.Still481.jpg</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Polisi ungkap peredaran etomidate yang tewaskan anggota TNI</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:59:38 +0700</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>ANTARA - Polda Aceh mengungkap kasus peredaran narkotika jenis baru berupa cartridge atau vape getar mengandung ...</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688128/polisi-ungkap-peredaran-etomidate-yang-tewaskan-anggota-tni</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_33_16_23.Still482.jpg</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Bedah rumah orang tua siswa Sekolah Rakyat mulai jalan di Madura</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:58:00 +0700</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Program bedah rumah orang tua siswa Sekolah Rakyat hasil kolaborasi Kementerian Sosial dan Kementerian Perumahan dan ...</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688145/bedah-rumah-orang-tua-siswa-sekolah-rakyat-mulai-jalan-di-madura</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-20.36.08.jpg</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Kebakaran yang menganggu KRL di Jakut diduga akibat puntung rokok</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:57:36 +0700</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Kebakaran lahan yang ditumbuhi alang-alang di dekat Stasiun Kampung Bandan, Ancol, Pademangan, Jakarta Utara, yang ...</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688144/kebakaran-yang-menganggu-krl-di-jakut-diduga-akibat-puntung-rokok</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_4802.jpeg</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Bulog Jatim sewa 269 gudang tambahan perkuat cadangan pangan</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:56:29 +0700</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Perum Bulog memperkuat kapasitas penyimpanan cadangan pangan di Jawa Timur dengan menyewa 269 gudang tambahan, termasuk ...</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688140/bulog-jatim-sewa-269-gudang-tambahan-perkuat-cadangan-pangan</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/476563.jpg</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>KP2MI-IOM siapkan pembaruan kerja sama pelindungan pekerja migran</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:56:26 +0700</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Kementerian Pelindungan Pekerja Migran Indonesia (KP2MI) dan Organisasi Internasional untuk Migrasi (IOM) tengah ...</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688137/kp2mi-iom-siapkan-pembaruan-kerja-sama-pelindungan-pekerja-migran</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000682934.jpg</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Polda Aceh gagalkan peredaran 50 ribu butir ekstasi</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:55:47 +0700</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Tim Opsnal Direktorat Reserse Narkoba Polda Aceh menggagalkan peredaran 50 ribu butir ekstasi, 2.495 kartrid atau vape ...</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688136/polda-aceh-gagalkan-peredaran-50-ribu-butir-ekstasi</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/konpres-narkoba-polda-aceh_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Kementerian PKP beri perhatian seniman Bali lewat bangun rusun</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:48:34 +0700</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Kementerian Perumahan dan Kawasan Permukiman (PKP) memberikan perhatian kepada seniman Bali lewat pembangunan rumah ...</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688135/kementerian-pkp-beri-perhatian-seniman-bali-lewat-bangun-rusun</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_0795.jpeg</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Pemerintah deteksi dini penyakit tuberkulosis warga binaan lewat CKG</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>ANTARA - Kementerian Imigrasi dan Pemasyarakatan (Imipas) dan Kementerian Kesehatan (Kemenkes) menggelar Cek Kesehatan ...</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687973/pemerintah-deteksi-dini-penyakit-tuberkulosis-warga-binaan-lewat-ckg</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMERINTAH-DETEKSI-DINI-PENYAKIT-TUBERKULOSIS-WARGA-BINAAN-LEWAT-CKG.jpg</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Polda Sumut tangkap tiga tersangka jaringan pengedar 169,6 kg ganja</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:46:48 +0700</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>ANTARA - Direktorat Reserse Narkoba Polda Sumatera Utara berhasil mengungkap tindak pidana narkoba jenis ganja seberat ...</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688097/polda-sumut-tangkap-tiga-tersangka-jaringan-pengedar-1696-kg-ganja</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/POLDA-SUMUT-TANGKAP-TIGA-TERSANGKA-JARINGAN-PENGEDAR-169-6-KG-GANJA.jpg</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>BNN integrasikan edukasi antinarkoba di 598 SD Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:45:33 +0700</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Badan Narkotika Nasional (BNN) menyiapkan implementasi Integrasi Kurikulum Anti Narkoba (IKAN) di 598 sekolah dasar di ...</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688131/bnn-integrasikan-edukasi-antinarkoba-di-598-sd-kabupaten-magelang</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_183712.jpg</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>SIG perkuat produksi-distribusi jaga pasokan semen di Aceh</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:41:43 +0700</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Badan Usaha Milik Negara (BUMN) bidang industri semen dan solusi bahan bangunan PT Semen Indonesia (Persero) Tbk (SIG) ...</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688125/sig-perkuat-produksi-distribusi-jaga-pasokan-semen-di-aceh</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000179430.jpg</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>AS kirim 16 ton air minum untuk korban gempa di Kumamoto</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:40:57 +0700</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Kedutaan Besar Amerika Serikat di Tokyo menyatakan bahwa Pasukan AS di Jepang (USFJ) telah mengirimkan bantuan air ...</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688123/as-kirim-16-ton-air-minum-untuk-korban-gempa-di-kumamoto</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gempa-Bumi-Di-Kumamoto-Jepang-310726-JH-3.jpg</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Triathlon siapkan enam atlet untuk Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:40:39 +0700</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Pengurus Pusat (PP) Federasi Triathlon Indonesia (FTI) menyiapkan tiga atlet putra dan tiga atlet putri untuk mengikuti ...</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688119/triathlon-siapkan-enam-atlet-untuk-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/03/15/Olahraga.jpg</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>KI DKI kembangkan layanan penyelesaian sengketa informasi</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:38:53 +0700</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Komisi Informasi (KI) DKI Jakarta terus mengembangkan layanan Penyelesaian Sengketa Informasi secara elektronik serta ...</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688116/ki-dki-kembangkan-layanan-penyelesaian-sengketa-informasi</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000318932.jpg</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Polres Cimahi ungkap peredaran 506.116 butir OKT ilegal</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:35:39 +0700</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Polres Cimahi, Jawa Barat, bersama Kodim 0609/Cimahi dan Pemerintah Kota Cimahi mengungkap peredaran 506.116 butir obat ...</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688112/polres-cimahi-ungkap-peredaran-506116-butir-okt-ilegal</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/490355.jpg</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Kemenimipas ingin klinik lapas layani CKG masyarakat umum</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:35:28 +0700</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Kementerian Imigrasi dan Pemasyarakatan (Kemenimipas) berupaya meningkatkan fasilitas klinik di lembaga pemasyarakatan ...</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688111/kemenimipas-ingin-klinik-lapas-layani-ckg-masyarakat-umum</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000013000.jpg</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Bakom tegaskan keamanan nasional terkendali jelang HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:33:41 +0700</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyatakan stabilitas keamanan nasional dalam kondisi ...</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688104/bakom-tegaskan-keamanan-nasional-terkendali-jelang-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_3742.jpeg</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Persik matangkan persiapan hadapi Super League musim baru</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:32:50 +0700</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Persik terus mematangkan persiapan menghadapi Super League musim 2026/2027 dengan menjalani pemusatan latihan di Solo ...</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688100/persik-matangkan-persiapan-hadapi-super-league-musim-baru</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000903052.jpg</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Pemadaman karhutla di Riau terkendala angin kencang dan minim air</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:28:44 +0700</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Penanggulangan Bencana Daerah (BPBD) Riau, Senin (10/8), menyatakan upaya pemadaman kebakaran hutan dan ...</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688088/pemadaman-karhutla-di-riau-terkendala-angin-kencang-dan-minim-air</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_27_37_08.Still480.jpg</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Menko Polkam: karhutla di Bromo, TNGP, dan TNGR telah tertangani</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:24:57 +0700</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah memastikan karhutla yang terjadi di Taman Nasional Bromo Tengger Semeru (TNBTS) sudah tertangani ...</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688021/menko-polkam-karhutla-di-bromo-tngp-dan-tngr-telah-tertangani</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENKO-POLKAN-KARHUTLA-DI-BROMO-TNGP-DAN-TNGR-TELAH-TERTANGANI.jpg</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Pengajuan KUR UMKM hingga Rp100 juta tidak perlu agunan</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:24:37 +0700</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Pekerja menjemur ikan asin di salah satu tempat produksi ikan asin kering di Palembang, Sumatera Selatan, Senin ...</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5688096/pengajuan-kur-umkm-hingga-rp100-juta-tidak-perlu-agunan</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/Pengajuan-KUR-UMKM-tanpa-agunan-100826-Lmo-4.jpg</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Satgas ODC: Tim gabungan selidiki keterlibatan KKB EK-PN kasus penembakan di Walesi</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:24:30 +0700</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Kaops Damai Cartenz Irjen Pol Faizal Ramadhani mengatakan tim gabungan yang terdiri dari personel Polres Jayawijaya dan ...</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688093/satgas-odc-tim-gabungan-selidiki-keterlibatan-kkb-ek-pn-kasus-penembakan-di-walesi</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1002615041.jpg</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Baznas bekali 50 dhuafa di Kendal keterampilan menjahit siap kerja</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:23:36 +0700</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Sebanyak 50 mustahik di Kabupaten Kendal, Jawa Tengah mengikuti Program Amal Vokasi berupa pelatihan menjahit skema ...</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688091/baznas-bekali-50-dhuafa-di-kendal-keterampilan-menjahit-siap-kerja</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_200848.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>PDI Perjuangan gelar Soekarno Cup 2026 di Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:22:51 +0700</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>PDI Perjuangan menggelar turnamen sepak bola Soekarno Cup 2026 di Jawa Timur untuk menyambut HUT ke-81 Kemerdekaan ...</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688084/pdi-perjuangan-gelar-soekarno-cup-2026-di-jawa-timur</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000583156.jpg</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Erlina Christiana gabung TC timnas 3x3 putri untuk Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:21:44 +0700</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Erlina Christiana dipanggil Badan Tim Nasional (BTN) Dewan Pengurus Pusat Persatuan Bola Basket Seluruh Indonesia (DPP ...</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688081/erlina-christiana-gabung-tc-timnas-3x3-putri-untuk-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/WhatsApp-Image-2026-07-30-at-20.19.22.jpeg</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Nezar soroti ancaman siber akibat komputasi kuantum</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:20:23 +0700</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Komunikasi dan Digital Nezar Patria menyoroti ancaman siber baru dari perkembangan komputasi kuantum, ...</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688080/nezar-soroti-ancaman-siber-akibat-komputasi-kuantum</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/62ee266c-2fb7-41ae-bc9d-3fe033273da8.jpeg</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Tiga kali mangkir eks direktur BUMD Bekasi akhirnya ditahan</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:20:05 +0700</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Kejaksaan Negeri Kabupaten Bekasi, Jawa Barat, menahan mantan Direktur Usaha Perumda Tirta Bhagasasi berinisial AEZ ...</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688077/tiga-kali-mangkir-eks-direktur-bumd-bekasi-akhirnya-ditahan</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260810-018.jpg</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>ESDM sebut IMERC 2026 ajang tingkatkan kompetensi, Freeport juara umum</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:18:24 +0700</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Direktur Jenderal Mineral dan Batubara Kementerian ESDM, Tri Winarno mengatakan ajang kompetisi Indonesia Mining ...</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688073/esdm-sebut-imerc-2026-ajang-tingkatkan-kompetensi-freeport-juara-umum</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMERC-2026-4.jpeg</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Sudin KPKP Jakbar tangkap 2.000 lebih ekor ikan sapu-sapu selama 2026</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:18:08 +0700</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Suku Dinas Ketahanan Pangan, Kelautan dan Pertanian (Sudin KPKP) Jakarta Barat (Jakbar) menangkap dan memusnahkan 2.927 ...</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688069/sudin-kpkp-jakbar-tangkap-2000-lebih-ekor-ikan-sapu-sapu-selama-2026</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/IMG_20260703_203943.v1.jpg</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>LPS nilai Destry Damayanti punya 'paket lengkap' sebagai Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:17:22 +0700</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Komisioner Lembaga Penjamin Simpanan (LPS) Anggito Abimanyu menilai Destry Damayanti merupakan sosok yang ...</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688065/lps-nilai-destry-damayanti-punya-paket-lengkap-sebagai-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000674697.jpg</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Wamenhaj tegaskan tata kelola haji harus bersih dari penyimpangan</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:17:18 +0700</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Haji dan Umrah RI Dahnil Anzar Simanjuntak menegaskan komitmen lembaga yang dipimpinnya untuk ...</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688061/wamenhaj-tegaskan-tata-kelola-haji-harus-bersih-dari-penyimpangan</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000177409.jpg</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Sambut HUT RI, ratusan kampung di Solo lukis gapura agar semarak</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:12:22 +0700</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>ANTARA - Menjelang Hari Ulang Tahun ke-81 Kemerdekaan Republik Indonesia, wajah kampung-kampung di Kota Solo mulai ...</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687980/sambut-hut-ri-ratusan-kampung-di-solo-lukis-gapura-agar-semarak</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SAMBUT-HUT-RI-RATUSAN-KAMPUNG-DI-SOLO-LUKIS-GAPURA-AGAR-SEMARAK.jpg</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Kemdiktisaintek dorong penguatan sains untuk pelestarian tradisi lokal</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:11:51 +0700</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Tinggi, Sains, dan Teknologi (Kemdiktisaintek) mendorong penguatan dan implementasi budaya sains ...</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688059/kemdiktisaintek-dorong-penguatan-sains-untuk-pelestarian-tradisi-lokal</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-17.31.19_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Karhutla 107 ribu hektare belum ganggu negara tetangga</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:10:52 +0700</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Pemerintah menyatakan hingga Senin belum menerima laporan adanya negara tetangga yang terganggu asap kebakaran hutan ...</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688057/karhutla-107-ribu-hektare-belum-ganggu-negara-tetangga</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/rakor-penanganan-kebakaran-hutan-dan-lahan-2838477.jpg</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Jurnal SSRN catut Prabowo, Menteri Brian: Investigasi terus berjalan</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:09:26 +0700</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Menteri Pendidikan Tinggi, Sains, dan Teknologi (Mendiktisaintek) Brian Yuliarto menegaskan bahwa pihaknya terus ...</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688053/jurnal-ssrn-catut-prabowo-menteri-brian-investigasi-terus-berjalan</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_195335.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Mendagri: Inflasi Juli 2,88 persen, masih dalam rentang ideal</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:06:27 +0700</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri Muhammad Tito Karnavian menyebut tingkat inflasi tahunan pada Juli 2026 sebesar 2,88 persen masih ...</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688051/mendagri-inflasi-juli-288-persen-masih-dalam-rentang-ideal</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000583309.jpg</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Kasus dugaan eksploitasi anak, "streamer" Bigmo dicecar 40 pertanyaan</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:04:09 +0700</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Selebritas internet (streamer) Muhammad Jannah alias Bigmo dicecar sebanyak 40 pertanyaan oleh penyidik Subdirektorat ...</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688047/kasus-dugaan-eksploitasi-anak-streamer-bigmo-dicecar-40-pertanyaan</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000912638.jpg</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Menhub buka peluang investasi percepat pengembangan jaringan kereta RI</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:02:51 +0700</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi menegaskan pemerintah membuka peluang investasi dalam pengembangan ...</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688044/menhub-buka-peluang-investasi-percepat-pengembangan-jaringan-kereta-ri</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/8EF73156-C95F-4277-B176-1AE4CD3678D9.jpeg</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>BPS: Indeks literasi dan inklusi keuangan masyarakat meningkat di 2026</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:01:06 +0700</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) merilis hasil Survei Nasional Literasi dan Inklusi Keuangan (SNLIK) Tahun 2026 yang ...</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688040/bps-indeks-literasi-dan-inklusi-keuangan-masyarakat-meningkat-di-2026</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/0ef8d814-aa79-4507-81b7-57d3c70031f8.jpeg</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Qodari nilai pertumbuhan ekonomi 5,29 persen semakin berkualitas</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menilai pertumbuhan ekonomi Indonesia sebesar 5,29 persen ...</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688036/qodari-nilai-pertumbuhan-ekonomi-529-persen-semakin-berkualitas</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_3742_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Presiden dijadwalkan buka Muktamar ke-35 NU di Jombang</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:00:16 +0700</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto dijadwalkan membuka Muktamar ke-35 Nahdlatul Ulama (NU) pada 27 Agustus 2026 di Kabupaten ...</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688033/presiden-dijadwalkan-buka-muktamar-ke-35-nu-di-jombang</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000903043_1.jpg</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Koops TNI Habema bentangkan Merah Putih raksasa di Papua</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:59:00 +0700</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>ANTARA - Komando Operasi TNI Habema membentangkan bendera Merah Putih berukuran 120x80 meter di kawasan Paralayang ...</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5687935/koops-tni-habema-bentangkan-merah-putih-raksasa-di-papua</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KOOPS-TNI-HABEMA-BENTANGKAN-MERAH-PUTIH-RAKSASA-DI-PAPUA.jpg</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Ahli Metabolomics Universitas Jepang kenalkan pangan kesehatan</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:57:45 +0700</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Ahli Metabolomics dari The University of Osaka, Jepang Prof Sastia Prama Putri, memaparkan cara merancang pangan agar ...</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688032/ahli-metabolomics-universitas-jepang-kenalkan-pangan-kesehatan</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260810-WA0035.jpg</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Bapanas tegaskan usut tuntas dugaan kecurangan beras fortifikasi</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:53:29 +0700</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Badan Pangan Nasional (Bapanas) menegaskan pihaknya terus mengusut tuntas dugaan kecurangan beras fortifikasi melalui ...</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688028/bapanas-tegaskan-usut-tuntas-dugaan-kecurangan-beras-fortifikasi</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CD9F3F00-67C9-4E91-B56F-589D39B9E6D6_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Satgas PRR Pulihkan Akses Nagan Raya, Ekonomi Warga Kembali Bergerak</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:08:57 +0700</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Akfa Nasrulhak</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Akses masyarakat di Beutong Ateuh Banggalang, Aceh, pulih pascabencana. Satgas PRR fokus perbaikan jalan dan jembatan untuk kembalikan aktivitas ekonomi.</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612876/satgas-prr-pulihkan-akses-nagan-raya-ekonomi-warga-kembali-bergerak</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/satgas-prr-1786370542685_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Ngeri 2 Pekerja Proyek Tertimpa Beton Turap Drainase di Jaktim</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:07:12 +0700</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Dua orang pekerja tertimpa beton proyek normalisasi drainase di Jatinegara, Jakarta Timur. Tiga jam proses evakuasi berlangsung dramatis.</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612874/ngeri-2-pekerja-proyek-tertimpa-beton-turap-drainase-di-jaktim</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/dua-pekerja-proyek-normalisasi-saluran-air-tertimpa-beton-turap-di-jakarta-timur-jaktim-beton-itu-disebut-tiba-tiba-roboh-dan--1786334668781_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Bappisus Minta Warga Tak Asal Percaya Info di Medsos, Bicara AI-Deepfake</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:06:50 +0700</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Kepala Bappisus mengimbau masyarakat tidak terprovokasi oleh narasi demo besar di media sosial. Ia meminta untuk gunakan sumber berita kredibel sebagai rujukan.</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612873/bappisus-minta-warga-tak-asal-percaya-info-di-medsos-bicara-ai-deepfake</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/04/aris-marsudiyanto-1756965719862_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Keamanan Nasional Terkendali, Kabakom Minta Warga Bijak Sikapi Info Medsos</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:04:26 +0700</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Kepala Bakom RI, Muhammad Qodari, imbau masyarakat bijak dalam menerima informasi menjelang HUT ke-81 Kemerdekaan RI. Stabilitas keamanan terjaga.</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612871/keamanan-nasional-terkendali-kabakom-minta-warga-bijak-sikapi-info-medsos</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/09/kepala-bakom-m-qodari-serta-asisten-khusus-presiden-dirgayuza-dan-agung-gumilar-di-peluncuran-buku-presiden-solusi-digelar-di--1780940035746_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>KPK Tahan 4 Tersangka Kasus Iklan Bank di Jabar</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:47:35 +0700</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>KPK menahan empat tersangka korupsi pengadaan iklan di Jabar. Mereka ditahan per hari ini setelah ditetapkan sebagai tersangka sejak Maret 2025.</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612842/kpk-tahan-4-tersangka-kasus-iklan-bank-di-jabar</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kpk-menahan-empat-tersangka-kasus-korupsi-pengadaan-iklan-di-jawa-barat-jabar-senin-1082026-1786369633192_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Pemerintah Siapkan Tiga Skema, Pastikan PPPK di Daerah Tak Dirumahkan</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:37:14 +0700</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Pemerintah siapkan tiga skema untuk bantu Pemda bayar gaji PPPK. Skema meliputi efisiensi anggaran, pembayaran DBH, dan tambahan DAU.</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612825/pemerintah-siapkan-tiga-skema-pastikan-pppk-di-daerah-tak-dirumahkan</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kemendagri-1786368956557_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung Periksa 7 Saksi Terkait TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:34:25 +0700</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Kejagung memeriksa saksi terkait perkara tindak pidana pencucian uang (TPPU) mantan Jampidsus Febrie Adriansyah. Tujuh saksi diperiksa.</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612821/tim-9-kejagung-periksa-7-saksi-terkait-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/febrie-adriansyah-dibawa-ke-kejagung-untuk-diperiksa-tim-9-1786087110132_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>PDIP Yakin Soekarno Cup 2026 Lahirkan Bibit Unggul untuk Sepakbola RI</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:29:11 +0700</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Faiq Azmi</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Turnamen Soekarno Cup 2026 resmi dimulai, digagas PDI Perjuangan. Event ini bertujuan melahirkan bakat muda sepakbola dan menjaga persaudaraan antar atlet.</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612815/pdip-yakin-soekarno-cup-2026-lahirkan-bibit-unggul-untuk-sepakbola-ri</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/deni-wicaksono-1786368523789_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Kabel Sinyal KA di Cikarang Dirusak, 1 Terduga Pelaku Ditangkap-2 Diburu</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:28:59 +0700</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Perusakan kabel sistem persinyalan kereta api di Bekasi kini tengah ditangani KAI dan polisi. Satu terduga pelaku ditangkap, dua lainnya diburu.</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612814/kabel-sinyal-ka-di-cikarang-dirusak-1-terduga-pelaku-ditangkap-2-diburu</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/20/ilustrasi-kereta-api_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Sebelum Tewas, Sutrimo Sempat Kirim Foto Ayam Goreng ke WA Keluarga</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:19:52 +0700</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Anang Firmansyah</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Keluarga Sutrimo mengungkap komunikasi terakhirnya sebelum meninggal. Ia aktif mengirim pesan dan foto, termasuk foto makanan, hingga dini hari.</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612804/sebelum-tewas-sutrimo-sempat-kirim-foto-ayam-goreng-ke-wa-keluarga</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/sutrimo-1786212205527_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Golkar Respons Usulan PKS: Kebijakan di Kabinet Hak Prerogatif Presiden</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:15:38 +0700</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Golkar mengatakan kabinet memang harus diisi orang-orang yang berintegritas. Namun, menurutnya, sosok profesional tak perlu dipertentangkan dengan parpol.</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612801/golkar-respons-usulan-pks-kebijakan-di-kabinet-hak-prerogatif-presiden</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/03/ahmad-doli-kurnia-1764756988898_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Terungkap Brankas Ekstasi di Kelab Malam 'Sarang' Narkoba di Batam</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:14:39 +0700</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Bareskrim Polri menggerebek kelab malam di Batam, menemukan brankas berisi ekstasi.</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612799/terungkap-brankas-ekstasi-di-kelab-malam-sarang-narkoba-di-batam</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kelab-malam-di-batam-kepri-digerebek-atas-dugaan-peredaran-narkoba-1786334168655_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Bigmo Minta Maaf ke Pihak Keluarga Anak yang Diajak Promosi Vape</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:12:44 +0700</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo minta maaf setelah mengajak anak di bawah umur promosi vape. Dia mengaku kapok dan berkomitmen untuk membuat konten yang lebih positif.</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612790/bigmo-minta-maaf-ke-pihak-keluarga-anak-yang-diajak-promosi-vape</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/youtuber-bigmo-dicecar-40-pertanyaan-soal-konten-promosi-vape-ajak-anak-1786361146873_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Pemerintah Kaji Opsi Guru PPPK Jadi ASN Pusat</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:53:03 +0700</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Mendagri Tito mengkaji opsi penarikan guru PPPK menjadi ASN pusat untuk mengatasi pengelolaan tenaga pendidik. Opsi tersebut masih dibahas lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612773/pemerintah-kaji-opsi-guru-pppk-jadi-asn-pusat</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/mendagri-tito-karnavian-1786366068298_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>SDN di Parung Panjang Bogor Kemalingan, Komputer hingga Proyektor Raib</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:48:52 +0700</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Sekolah dasar negeri di Bogor menjadi sasaran pencurian, kehilangan barang elektronik seperti laptop dan CCTV. Ini adalah kejadian keempat di sekolah tersebut.</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612771/sdn-di-parung-panjang-bogor-kemalingan-komputer-hingga-proyektor-raib</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/28/ilustrasi-pencuri-ilustrasi-maling-ilustrasi-kriminal-freepik_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Gerindra Apresiasi BNN Bongkar Penyelundupan 1,3 Ton Ketamin: Bukan Perkara Kecil</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:39:14 +0700</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Anggota DPR Bimantoro Wiyono apresiasi BNN dan Polri yang gagalkan penyelundupan 1,3 ton ketamin. Ia dorong pengusutan tuntas hingga ke akar jaringan narkoba.</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612761/gerindra-apresiasi-bnn-bongkar-penyelundupan-1-3-ton-ketamin-bukan-perkara-kecil</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/anggota-komisi-iii-dpr-ri-fraksi-partai-gerindra-bimantoro-wiyono-dokistimewa-1786365676625_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Warga Tertemper KRL di Stasiun Jurangmangu Ternyata Siswi SMA</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:38:28 +0700</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>KRL greenline rute Tanah Abang-Parung Panjang sempat terhambat sore tadi akibat ada warga tewas tertempet di Stasiun Jurangmangu. Korban merupakan siswi SMA.</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612759/warga-tertemper-krl-di-stasiun-jurangmangu-ternyata-siswi-sma</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/14/ilustrasi-krl-jabodetabek-harisdetikcom-1760430701278_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Kepala Bappisus: Kita Masih Punya PR Tangkap Koruptor Besar Riza Chalid</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:28:08 +0700</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Kepala Bappisus Aris Marsudiyanto menyebut perburuan koruptor Riza Chalid masih menjadi PR pemerintah. Upaya penangkapan terus dilakukan secara sinergis.</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612748/kepala-bappisus-kita-masih-punya-pr-tangkap-koruptor-besar-riza-chalid</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kepala-bappisus-aris-marsudiyanto-1786364867494_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Bigmo Ngaku Kapok dan Minta Maaf Bikin Konten Promosi Vape Ajak Anak</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:10:30 +0700</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo dicecar 40 pertanyaan oleh Polda Metro Jaya terkait konten promosi vape untuk anak. Dia mengaku kapok dan minta maaf.</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612722/bigmo-ngaku-kapok-dan-minta-maaf-bikin-konten-promosi-vape-ajak-anak</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/youtuber-bigmo-tengah-meminta-maaf-soal-konten-promosi-vape-ajak-anak-in-frame-saat-siaran-langsung-1786363802068_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Erick Thohir Temui Pramono, Bahas Venue FIFA ASEAN Cup di Jakarta</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:09:56 +0700</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Menteri Erick Thohir dan Gubernur Pramono Anung bahas persiapan FIFA ASEAN Cup 2026. DKI Jakarta siap dukung venue dan promosi untuk kesuksesan acara.</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612720/erick-thohir-temui-pramono-bahas-venue-fifa-asean-cup-di-jakarta</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/menteri-pemuda-dan-olahraga-menpora-erick-thohir-menemui-gubernur-dki-jakarta-pramono-anung-di-balai-kota-jakarta-1786363731959_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Kemensos-Komnas HAM Sepakat Tangani Pengungsi Konflik Puncak</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:52:52 +0700</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Fara Difa Alfeni</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Kemensos dan Komnas HAM sepakat sinergi menangani pengungsi korban konflik di Puncak, Papua. Fokus pada kebutuhan dasar dan bantuan kedaruratan.</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612706/kemensos-komnas-ham-sepakat-tangani-pengungsi-konflik-puncak</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kemensos-1786362471870_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Soekarno Cup Dibuka, 400 Talenta Muda dari 16 Provinsi Unjuk Kemampuan</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:49:03 +0700</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Faiq Azmi</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Turnamen Soekarno Cup 2026 resmi dibuka di Surabaya, melibatkan 400 talenta muda dari 16 provinsi. Acara meriah dengan atraksi budaya.</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612623/soekarno-cup-dibuka-400-talenta-muda-dari-16-provinsi-unjuk-kemampuan</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kemeriahan-pembukaan-soekarno-cup-2026-di-surabaya-1786350146196.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Mendes Dorong TAPM Pusat Lebih Produktif Berkarya untuk Kemajuan Desa</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:36:33 +0700</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Inkana Izatifiqa R. Putri</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Menteri Yandri Susanto dorong TAPM Pusat lebih produktif untuk kemajuan desa. Ia tekankan pentingnya kontribusi dalam program pembangunan.</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612667/mendes-dorong-tapm-pusat-lebih-produktif-berkarya-untuk-kemajuan-desa</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/mendes-yandri-susanto-1786361779532_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Warga Tertemper KRL Green Line di Stasiun Jurangmangu</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:35:09 +0700</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Kereta Commuter Line Tanah Abang-Parung Panjang sempat terhambat akibat insiden warga tertemper di Stasiun Jurangmangu. Perjalanan kini normal kembali.</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612661/warga-tertemper-krl-green-line-di-stasiun-jurangmangu</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/28/ilustrasi-kereta-1777353614394_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Kepala Bappisus Diskusi dengan Jamintel Kejagung Bahas Optimalisasi APBN</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:34:42 +0700</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Kepala Bappisus Aris Marsudiyanto berdiskusi dengan Kejagung untuk optimalisasi APBN. Kerja sama penegakan hukum dan pemberantasan korupsi diperkuat.</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612664/kepala-bappisus-diskusi-dengan-jamintel-kejagung-bahas-optimalisasi-apbn</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kepala-badan-pengendalian-pembangunan-dan-investigasi-khusus-bappisus-aris-marsudiyanto-berdiskusi-dengan-jaksa-agung-muda-bid-1786361501206_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Bigmo Dicecar 40 Pertanyaan soal Konten Vape Ajak Anak, Klaim Tak Defensif</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:29:55 +0700</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo klarifikasi di Polda Metro Jaya terkait ajakan anak promosi vape. Ia menjawab 40 pertanyaan dan mengakui kesalahan dalam siaran langsungnya.</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612647/bigmo-dicecar-40-pertanyaan-soal-konten-vape-ajak-anak-klaim-tak-defensif</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/youtuber-bigmo-dicecar-40-pertanyaan-soal-konten-promosi-vape-ajak-anak-1786361146873_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Investasi Swasta Rp 74,54 Triliun Mengalir ke IKN</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:59:51 +0700</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Investasi swasta yang sudah masuk ke Ibu Kota Nusantara (IKN) di Kalimantan Timur mencapai Rp 74,54 triliun.</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8612867/investasi-swasta-rp-74-54-triliun-mengalir-ke-ikn</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/pembangunan-kawasan-yudikatif-di-ikn-1785673641805_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Bos LPS soal Destry Calon Tunggal Gubernur BI: Mudah-mudahan Lancar</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:17:19 +0700</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Komisioner LPS Anggito Abimanyu menyambut baik pengajuan Destry Damayanti sebagai calon tunggal Gubernur Bank Indonesia, ke DPR.</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8612802/bos-lps-soal-destry-calon-tunggal-gubernur-bi-mudah-mudahan-lancar</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/22/lps-pertahankan-tingkat-bunga-penjaminan-awal-2026-1769087170820_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Pemerintah Bakal Bebaskan Pajak ETF Emas</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:30:23 +0700</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto menyampaikan pemerintah akan memberikan insentif pajak untuk produk ETF emas tersebut.</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8612721/pemerintah-bakal-bebaskan-pajak-etf-emas</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/ilustrasi-emas-batangan-1784354557947_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Rupiah Menguat Tajam Usai Prabowo Usulkan Destry Damayanti Jadi Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:19:20 +0700</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah kembali menguat di hadapan dolar Amerika Serikat (AS) pada penutupan perdagangan Senin (10/9/2026).</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8612737/rupiah-menguat-tajam-usai-prabowo-usulkan-destry-damayanti-jadi-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/rupiah-masih-tertekan-dolar-as-betah-di-level-rp18000-1783662450904_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>RANS Lunasi Utang Pakai Duit IPO</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:00:43 +0700</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>Diketahui, RANS mengantongi dana segar dari IPO sebesar Rp 429,25 miliar pada 10 Juli 2026.</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8612648/rans-lunasi-utang-pakai-duit-ipo</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/pt-rans-entertainment-indonesia-tbk-rans-1786361330350_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Sepekan Jelang HUT RI, Pernak-Pernik Merah Putih Mulai Diburu Warga</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:00:18 +0700</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Rifkianto Nugroho</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Sepekan jelang HUT ke-81 RI, Pasar Jatinegara mulai ramai diburu warga. Pedagang sibuk melayani pembeli yang mencari pernak-pernik merah putih.</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8612163/sepekan-jelang-hut-ri-pernak-pernik-merah-putih-mulai-diburu-warga</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/sepekan-jelang-hut-ri-pernak-pernik-merah-putih-mulai-diburu-warga-1786347047405_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Pemerintah Siapkan 3 Skema Bayar Gaji PPPK, Tak Ada yang Dirumahkan</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:03:18 +0700</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>Pemerintah siapkan tiga skema untuk bantu Pemda bayar gaji PPPK. Efisiensi anggaran, pembayaran DBH, dan tambahan DAU jadi solusi untuk masalah fiskal daerah.</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810202417-25-1390778/pemerintah-siapkan-3-skema-bayar-gaji-pppk-tak-ada-yang-dirumahkan</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/kemendagri-1786368327993_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Pria di Grobogan Beri Mahar Nikah Ekskavator hingga GWM Tank</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:40:07 +0700</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>Pernikahan 'sultan' di Grobogan hebohkan media sosial dengan mahar miliaran, termasuk ekskavator dan kendaraan mewah.</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810203640-20-1390782/pria-di-grobogan-beri-mahar-nikah-ekskavator-hingga-gwm-tank</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/pasangan-asal-grobogan-rico-putra-roberto-syah-23-dan-laella-nur-fadhilah-20-berfoto-dengan-ekskavator-mahar-pernikahan-1786367446235_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>KPK Tahan 4 Tersangka Kasus Dana Iklan Bank Pembangunan Daerah</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:37:51 +0700</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>KPK menahan empat tersangka dugaan korupsi pengadaan iklan sebuah bank pembangunan daerah(BPD). Kerugian negara diperkirakan mencapai Rp223,6 miliar.</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810201935-12-1390777/kpk-tahan-4-tersangka-kasus-dana-iklan-bank-pembangunan-daerah</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/05/ilustrasi-gedung-kpk-8_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Jenazah Siswi SMA Tertemper KRL di Jurangmangu Dibawa ke RSU Tangsel</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:14:53 +0700</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Seorang pelajar SMA perempuan berinisial A (16) meninggal dunia setelah terjatuh dari peron dan tertemper kereta rel listrik (KRL) di Stasiun Jurangmangu.</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810200707-20-1390775/jenazah-siswi-sma-tertemper-krl-di-jurangmangu-dibawa-ke-rsu-tangsel</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/pelajar-16-tahun-tewas-tertemper-krl-di-stasiun-jurangmangu-tangsel-1786367207081_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Polisi Selidiki Siswi SMA Tertabrak KRL di Stasiun Jurangmangu</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:38:59 +0700</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>Seorang siswi SMA kelas 10 meninggal setelah tertabrak KRL di Stasiun Jurangmangu, Tangerang Selatan. Polisi masih menyelidiki insiden tersebut.</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810192116-20-1390751/polisi-selidiki-siswi-sma-tertabrak-krl-di-stasiun-jurangmangu</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2017/03/10/17a0dad8-2e82-477c-8765-0459ae2a4826_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Kejagung Periksa 7 Saksi soal TPPU Emas 74 Kg dan Uang Miliaran Febrie</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:32:00 +0700</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung memeriksa tujuh saksi dalam kasus TPPU emas 74 kg dan Rp543 miliar eks Jampidsus Febrie Adriansyah.</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810185256-12-1390743/kejagung-periksa-7-saksi-soal-tppu-emas-74-kg-dan-uang-miliaran-febrie</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/kejagung-periksa-febrie-adriansyah-1786091328007_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Warga Tertemper KRL di Jurangmangu, Perjalanan Commuter Line Terganggu</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:12:18 +0700</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Perjalanan kereta commuter Line Rute Tanah Abang-Parung Panjang mengalami gangguan di Stasiun Jurangmangu.</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810190833-20-1390746/warga-tertemper-krl-di-jurangmangu-perjalanan-commuter-line-terganggu</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/03/29/pengadaan-rangkaian-krl-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Prabowo Guyur Rp18,9 Triliun ke 546 Daerah Buat Gaji PPPK</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:05:19 +0700</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto alokasikan Rp18,9 triliun untuk gaji PPPK di 546 daerah. Mendagri Tito Karnavian menjelaskan opsi penanganan untuk pegawai.</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810184910-32-1390742/prabowo-guyur-rp189-triliun-ke-546-daerah-buat-gaji-pppk</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/pemerintah-pusat-cairkan-rp189-t-untuk-546-pemda-bayar-gaji-pppk-1786362353560_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Mendikdasmen Buka Suara Soal Temuan 995 Senpi di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:03:05 +0700</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>Mendikdasmen Abdul Mu'ti menanggapi temuan 995 senjata api di sekolah swasta Jakarta. Ia menekankan keamanan sekolah dan menyerahkan proses hukum kepada polisi.</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810185559-20-1390745/mendikdasmen-buka-suara-soal-temuan-995-senpi-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/20/abdul-muti-1779281792623_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Mendagri Soal Inflasi Juli 2,88 Persen: Masih dalam Rentang Ideal</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:28:42 +0700</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian menyatakan inflasi Juli 2026 masih dalam rentang ideal 2,88%. Beberapa daerah mencatat inflasi di atas 3,5%. Pemda diminta waspada.</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810175342-25-1390721/mendagri-soal-inflasi-juli-288-persen-masih-dalam-rentang-ideal</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/bnr-kemendagri-agustus-12306-333-1786359030460_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Wamenhaj Dahnil Sidak Kantor Kemenhaj Jaktim: Paling Banyak Kasusnya</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:23:41 +0700</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Haji dan Umrah, Dahnil Anzar Simanjuntak melakukan sidak ke kantor wilayah Kemenhaj Jakarta Timur usai temuan sejumlah kasus.</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810181956-20-1390727/wamenhaj-dahnil-sidak-kantor-kemenhaj-jaktim-paling-banyak-kasusnya</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/12/wamenhaj-jemaah-haji-asal-jawa-timur-catat-angka-kematian-tertinggi-capai-65-orang-1781248489629_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Khariq Anhar Dituntut 6 Bulan Penjara Kasus Timpa Teks Demo Agustus</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:18:40 +0700</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Mahasiswa Universitas Riau, Khariq Anhar, dituntut 6 bulan penjara atas dugaan manipulasi informasi elektronik terkait demonstrasi Agustus 2025.</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810174824-12-1390720/khariq-anhar-dituntut-6-bulan-penjara-kasus-timpa-teks-demo-agustus</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/sidang-tuntutan-khariq-anhar-1786359122646_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Kemenhut Padamkan Kebakaran 30 Hektare di Gunung Rinjani</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:57:57 +0700</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Taman Nasional Gunung Rinjani berhasil dipadamkan oleh tim gabungan. Menteri Kehutanan menekankan pentingnya deteksi dini.</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810171856-20-1390709/kemenhut-padamkan-kebakaran-30-hektare-di-gunung-rinjani</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/pemadaman-kebakaran-kawasan-hutan-di-boyolali-1785974493274_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>6 Provinsi Rawan Karhutla: Riau Hingga Kalsel</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:56:55 +0700</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>Pemerintah menyatakan ada enam provinsi paling rawan terjadi kebakaran hutan dan lahan (karhutla).</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810175049-24-1390719/6-provinsi-rawan-karhutla-riau-hingga-kalsel</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/thumbnail-video-1786359208888_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Pemkot Surabaya Pecat Duta Wisata Jatim yang Diduga Paksa Aborsi Pacar</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:53:37 +0700</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Surabaya memecat Tio Ferdian Rahmana, anggota Raka Raki Jatim, karena diduga memaksa pacarnya untuk aborsi.</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810173426-12-1390714/pemkot-surabaya-pecat-duta-wisata-jatim-yang-diduga-paksa-aborsi-pacar</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/runner-up-raka-jawa-timur-2026-yang-viral-meminta-pacarnya-aborsi-ke-singapura-1786331840746_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Bima Arya Dukung Penguatan Sistem Penanganan Kekerasan Anak di Daerah</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:52:24 +0700</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>Wamendagri Bima menegaskan dukungan Kemendagri untuk penguatan sistem penanganan kekerasan terhadap perempuan dan anak, mendorong integrasi dan keberlanjutan.</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810172819-25-1390713/bima-arya-dukung-penguatan-sistem-penanganan-kekerasan-anak-di-daerah</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/bnr-kemendagri-agustus-12306-233-1786357271183_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Kejagung Buka Suara soal Sosok Febrio yang Disebut Antar Sutrimo ke RS</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:30:31 +0700</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung mengonfirmasi Febrie Adianto sebagai pegawai, bukan jaksa. Ia terkait kasus kematian janggal Sutrimo.</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810170730-12-1390705/kejagung-buka-suara-soal-sosok-febrio-yang-disebut-antar-sutrimo-ke-rs</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/06/03/ilustrasi-gedung-kejaksaan-agung-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>KSOP Labuan Bajo Buka Suara soal Viral Rombongan Jessica Milla</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:29:10 +0700</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>KSOP Labuan Bajo telah menindak tegas kapal pembawa rombongan Jessica Mila ke Pulau Padar saat rute tersebut ditutup.</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810150328-20-1390641/ksop-labuan-bajo-buka-suara-soal-viral-rombongan-jessica-milla</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/ksop-labuan-bajo-tindak-tegas-2-kapal-bawa-artis-ke-pulau-padar-1786348967023_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>FOTO: Karhutla di Ogan Ilir Sumsel Semakin Meluas</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:22:45 +0700</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>Karhutla di Sumatra Selatan kembali menunjukkan peningkatan. Sejumlah titik kebakaran dilaporkan muncul di beberapa wilayah Kabupaten Ogan Ilir, Sumsel.</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810135521-22-1390583/foto-karhutla-di-ogan-ilir-sumsel-semakin-meluas</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/kebakaran-lahan-di-ogan-ilir-sumsel-makin-parah-1786344898188_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>BNPB Sebut Karhutla di Kawasan Bromo Tinggal 2 Titik Api</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:14:16 +0700</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>BNPB laporkan kebakaran hutan di Gunung Bromo tinggal dua titik api. Tiga helikopter dikerahkan untuk pemadaman, area terbakar mencapai 550 hektare.</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810165351-20-1390700/bnpb-sebut-karhutla-di-kawasan-bromo-tinggal-2-titik-api</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/upaya-pemadaman-kebakaran-hutan-di-kawasan-tnbts-1786344598944_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Alang-alang Terbakar, Perjalanan KRL Kampung Bandan Sempat Terganggu</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:06:18 +0700</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Kebakaran alang-alang dekat Stasiun Kampung Bandan, Jakarta Utara sempat mengganggu perjalanan KRL.</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810165235-20-1390701/alang-alang-terbakar-perjalanan-krl-kampung-bandan-sempat-terganggu</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/11/17/jalita-hadirkan-jejak-sejarah-transformasi-krl-jabodetabek-1763365500692_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Pemerintah Umumkan 6 Provinsi Rawan Karhutla: Riau hingga Kalsel</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:40:46 +0700</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>Enam provinsi paling rawan kebakaran hutan dan lahan adalah Riau, Jambi, Sumatera Selatan, Kalimantan Barat, Kalimantan Tengah, dan Kalimantan Selatan.</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810163737-20-1390695/pemerintah-umumkan-6-provinsi-rawan-karhutla-riau-hingga-kalsel</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/pemadaman-kebakaran-kawasan-hutan-di-boyolali-1785974493169_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Mendagri dan Menteri ATR/BPN Sepakat Perkuat Layanan Pertanahan</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:35:58 +0700</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>Surat Edaran Bersama itu bertujuan mendorong sinergi dan integrasi antara pemda dan Kementerian ATR/BPN, yang memastikan standar waktu dan mekanisme pelayanan.</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810162457-25-1390687/mendagri-dan-menteri-atr-bpn-sepakat-perkuat-layanan-pertanahan</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/kemendagri-1786354028579_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>FOTO: Pilah Sampah Jakarta Tembus 23 Persen</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:34:36 +0700</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung menyatakan pemilahan sampah Jakarta mencapai 23,14 persen hingga awal Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810143448-22-1390615/foto-pilah-sampah-jakarta-tembus-23-persen</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/pilah-sampah-jakarta-tembus-23-persen-rdf-jadi-kunci-1786347063805_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Praperadilan Kasus Korupsi Haji Ketum Kesthuri Ditolak, KPK Buka Suara</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:18:36 +0700</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>KPK merespons putusan hakim yang menolak Praperadilan Ketum Asosiasi Kesatuan Tour Travel Haji Umrah (Kesthuri) terkait dugaan korupsi kuota haji.</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810152950-12-1390663/praperadilan-kasus-korupsi-haji-ketum-kesthuri-ditolak-kpk-buka-suara</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/05/ilustrasi-gedung-kpk-8_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Karhutla di Indonesia Capai 107 Ribu Hektare hingga Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:03:57 +0700</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>Lebih dari 107 ribu hektare hutan dan lahan terbakar di RI hingga Agustus 2026. Upaya penanganan karhutla dilakukan melalui operasi udara dan darat.</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810155105-20-1390678/karhutla-di-indonesia-capai-107-ribu-hektare-hingga-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/kawasan-bromo-tutup-total-akibat-kebakaran-tiket-pengunjung-di-refund-1786242231293_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum Yaqut Sebut Perhitungan Kerugian Negara Kasus Haji Berubah</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:48:53 +0700</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>Tim hukum Yaqut Cholil Qoumas menyoroti perhitungan kerugian keuangan negara dalam kasus dugaan korupsi kuota haji tambahan periode 2023-2024.</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810153655-12-1390672/kuasa-hukum-yaqut-sebut-perhitungan-kerugian-negara-kasus-haji-berubah</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/31/yaqut-bantah-ada-pemberian-uang-dari-dua-tersangka-baru-kpk-kasus-haji-1774942971643_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Bareskrim Investigasi Bareng Polisi Malaysia Kasus Pilot Bawa Narkoba</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:33:25 +0700</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>Bareskrim Polri dan PDRM Malaysia akan investigasi kasus penyelundupan narkoba oleh pilot Malaysia Airlines. Penangkapan melibatkan 70.114 butir ekstasi.</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810151452-12-1390645/bareskrim-investigasi-bareng-polisi-malaysia-kasus-pilot-bawa-narkoba</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/31/pilot-maskapai-asing-ditangkap-di-bandara-soetta-usai-kedapatan-bawa-sabu-dan-ekstasi-25-kg-1785461146712_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Direskrimum Polda Sumbar Damai dengan Korban Pemukulan</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:10:17 +0700</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>Direskrimum Polda Sumbar Kombes Teddy Fanani lepas dari ancaman pidana setelah kesepakatan damai dengan korban yang dia aniaya di jalan raya.</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810145457-12-1390636/direskrimum-polda-sumbar-damai-dengan-korban-pemukulan</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/direskrimum-polda-sumbar-lepas-dari-ancaman-sanksi-pidana-dan-internal-1786348530754_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Disbudpar Usut Finalis Duta Wisata Jatim Diduga Minta Pacar Aborsi</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:58:00 +0700</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>Dugaan kasus aborsi melibatkan runner-up Raka Raki Jatim viral di media sosial. Disbudpar Jatim siapkan sanksi tegas setelah klarifikasi.</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810144140-20-1390633/disbudpar-usut-finalis-duta-wisata-jatim-diduga-minta-pacar-aborsi</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2014/11/27/7569bc98-96e0-4f82-9c43-509d15cd0796_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>PKS Ingin Kepala Daerah Tetap Didampingi Wakil, Gerindra Tak Buru-buru</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:50:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>Anggota Fraksi PKS dan Gerindra melontarkan pendapat masing-masing terkait kemunculan wacana pilkada digelar tanpa calon wakil kepala daerah yang muncul di DPR.</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810142930-32-1390608/pks-ingin-kepala-daerah-tetap-didampingi-wakil-gerindra-tak-buru-buru</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/11/27/antusias-warga-jakarta-gunakan-hak-suara-di-pilkada-2024-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Peserta War Ticket HUT ke-81 RI Capai 336 Ribu, Istana Tambah Kuota</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:39:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>Pemerintah memutuskan untuk menambah 3.400 kuota peserta peringatan hari ulang tahun (HUT) ke-81 Kemerdekaan RI 17 Agustus di Istana Kepresidenan, Jakarta.</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810143246-20-1390610/peserta-war-ticket-hut-ke-81-ri-capai-336-ribu-istana-tambah-kuota</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/17/upacara-penurunan-bendera-di-istana-merdeka-1755428000061_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Bigmo Penuhi Panggilan Pemeriksaan soal Promosi Vape Libatkan Anak</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:24:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>Youtuber Bigmo memenuhi panggilan Polda Metro Jaya terkait dugaan promosi liquid vape kepada anak-anak. Ia minta maaf atas aksinya yang kontroversial.</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810141606-12-1390595/bigmo-penuhi-panggilan-pemeriksaan-soal-promosi-vape-libatkan-anak</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/bigmo-memenuhi-panggilan-polda-metro-jaya-1786345392788_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Polisi Dalami Dugaan Pembunuhan Berencana di Kasus Kematian Sutrimo</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:17:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Penyidik Polda Metro Jaya tingkatkan kasus kematian misterius Sutrimo ke tahap penyidikan untuk mendalami dugaan pembunuhan berencana.</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810140145-12-1390582/polisi-dalami-dugaan-pembunuhan-berencana-di-kasus-kematian-sutrimo</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/27/olah-tkp-kasus-kematian-sutrimo-1785144097593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>FOTO: Kebakaran Bromo Meluas, Api Dekati Permukiman Warga</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:15:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>Kebakaran karhutla di Gunung Bromo, Jawa Timur, terus meluas hingga mencapai 550 hektare. Api bahkan dikabarkan sudah mendekat ke permukiman warga.</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810135022-22-1390569/foto-kebakaran-bromo-meluas-api-dekati-permukiman-warga</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/kebakaran-hutan-di-kawasan-tnbts-1786344598733_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Karhutla Sungai Tendang Meluas, 10 Ha Lahan Dekat Bandara Membara</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:02:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Desa Sungai Tendang, Kobar, telah meluas hingga 10 hektare. Tim gabungan berupaya memadamkan api di lahan gambut yang sulit dijinakkan.</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810132658-20-1390558/karhutla-sungai-tendang-meluas-10-ha-lahan-dekat-bandara-membara</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/06/24/kabut-asap-dampak-karhutla-di-kalsel-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Kematian Janggal, Makam Sutrimo Dibongkar Rabu Lusa</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:42:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menjadwalkan proses ekshumasi terhadap jasad Sutrimo di Banyumas, Jawa Tengah, Rabu (12/8) lusa.</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810133511-12-1390561/kematian-janggal-makam-sutrimo-dibongkar-rabu-lusa</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/08/24/8a7149c5-8060-403e-9fba-e91b1608a9fb_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>BPBD Sumsel Rekomendasikan Sekolah Libur Jika Asap Karhutla Memburuk</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:23:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>BPBD Sumsel siapkan langkah antisipasi kabut asap karhutla, termasuk rekomendasi libur sekolah jika kualitas udara memburuk.</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810131256-20-1390544/bpbd-sumsel-rekomendasikan-sekolah-libur-jika-asap-karhutla-memburuk</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/kabut-asap-di-palembang-1785973669671_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Panglima TNI dan Kapolri Kumpul di DPR Bahas Keamanan Jelang Agustusan</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:21:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Panglima TNI Jenderal Agus Subiyanto hingga Kapolri Jenderal Listyo Sigit Prabowo rapat koordinasi membahas pengamanan jelang hari Kemerdekaan 17 Agustus.</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810131457-32-1390546/panglima-tni-dan-kapolri-kumpul-di-dpr-bahas-keamanan-jelang-agustusan</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/12/20/antisipasi-bencana-saat-nataru-kapolri-siapkan-satgas-khusus_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Daftar 8 Korban Meninggal Dunia Drag Race Maut Kotamobagu Sulut</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:07:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>Kecelakaan di Turnamen Tidar Drag Race 2026 di Kotamobagu Sulut mengakibatkan 8 orang tewas dan 9 luka-luka.</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810124926-12-1390539/daftar-8-korban-meninggal-dunia-drag-race-maut-kotamobagu-sulut</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2016/11/30/af11432e-ec0a-4722-b7bd-a5833529f31d_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Youtuber Bigmo Diperiksa di Polda Metro Jaya Senin Siang Ini</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:59:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya memanggil YouTuber Bigmo untuk pemeriksaan terkait promosi rokok elektrik yang melibatkan anak.</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810124008-12-1390537/youtuber-bigmo-diperiksa-di-polda-metro-jaya-senin-siang-ini</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/10/16/ilustrasi-youtube-1760582870394_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Kronologi Kapal Penyelundup 1,3 Ton Narkotika Ditangkap di Laut Kepri</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:47:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>TNI AL bersama BNN dan instansi terkait menggagalkan penyelundupan 1,3 ton ketamine dari kapal MV King Sun yang berbendera Tanzania.</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810121301-12-1390529/kronologi-kapal-penyelundup-13-ton-narkotika-ditangkap-di-laut-kepri</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/kasus-penyeludupan-13-ton-ketamin-1786267600728_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>KELANA Tiba di Yogyakarta, Gen Z Belajar Langsung Transisi Energi</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:44:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Program KELANA ajak 13 pelajar SMA belajar pengelolaan lingkungan dan ekonomi sirkular di Yogyakarta. Peserta eksplorasi terkait solusi krisis ekologi.</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810124106-25-1390538/kelana-tiba-di-yogyakarta-gen-z-belajar-langsung-transisi-energi</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/kementerian-lingkungan-hidup-1786336817756_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>KPK Jadwal Ulang Pemeriksaan Rudy Tanoe 11 Agustus</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:36:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>KPK menjadwalkan ulang pemeriksaan Komisaris Utama PT Dosni Roha Logistik (DNRL) Bambang Rudijanto Tanoesoedibjo pada Selasa, 11 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810122828-12-1390532/kpk-jadwal-ulang-pemeriksaan-rudy-tanoe-11-agustus</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/11/26/50124780-d8f8-4a4c-90a7-33dcb9fa6ee9_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum: Rudy Tanoe Tak Mangkir, Ada Jadwal Pemeriksaan Kesehatan</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:31:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>Komisaris Utama PT DNRL, Rudy Tanoe, tidak hadir pemeriksaan KPK. Kuasa hukum membantah kliennya mangkir.</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810111758-12-1390500/kuasa-hukum-rudy-tanoe-tak-mangkir-ada-jadwal-pemeriksaan-kesehatan</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/01/23/5df5d027-864d-4639-bc94-f6c26355a252_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>2 Pekerja Proyek Tertimpa Beton Drainase Jatinegara Lolos dari Maut</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:21:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Dua pekerja proyek tertimpa beton drainase yang roboh di Jalan DI Panjaitan, depan Best Western Premier The Hive, Cipinang Cempedak, Jatinegara, Jakarta Timur.</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810121200-20-1390523/2-pekerja-proyek-tertimpa-beton-drainase-jatinegara-lolos-dari-maut</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/02/ilustrasi-garis-polisi-1780387910588_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Mobil Drag Race Kotamobagu Sulut Tabrak Penonton, 8 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:16:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>Kecelakaan tragis terjadi di Turnamen Tidar Drag Race 2026, Kotamobagu, Sulawesi Utara usai mobil pembalap menabrak penonton.</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810120550-12-1390521/mobil-drag-race-kotamobagu-sulut-tabrak-penonton-8-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/09/28/fb0c2676-9f0a-4c3f-ac4b-0489f57e34a1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Jangan Tunggu Sakit, Pemerintah Perkuat Deteksi dan Layanan Kesehatan</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:02:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>Pemerintah luncurkan Program Cek Kesehatan Gratis untuk deteksi dini penyakit untuk meningkatkan usia harapan hidup dan pencegahan penyakit tidak menular.</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260809124228-25-1390278/jangan-tunggu-sakit-pemerintah-perkuat-deteksi-dan-layanan-kesehatan</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/fmb9-1786252448851_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Bareskrim Gerebek Kelab Malam di Batam, Ekstasi Disimpan di Brankas</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:41:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>Bareskrim Polri menggerebek HH Club di Batam, menangkap 32 orang terkait peredaran narkoba. Brankas berisi ekstasi ditemukan dalam operasi ini.</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810113216-12-1390504/bareskrim-gerebek-kelab-malam-di-batam-ekstasi-disimpan-di-brankas</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/bareskrim-grebek-kelab-malam-di-batam-ekstasi-disimpan-di-dalam-brangkas-1786336703868_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Kebakaran Bromo Meluas Hingga 550 Hektare, Api Dekati Permukiman Warga</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:27:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan di Gunung Bromo, Jawa Timur, terus meluas hingga mencapai 550 hektare. Api bahkan dikabarkan sudah mendekat ke permukiman warga.</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810111552-20-1390498/kebakaran-bromo-meluas-hingga-550-hektare-api-dekati-permukiman-warga</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/kawasan-bromo-tutup-total-akibat-kebakaran-tiket-pengunjung-di-refund-1786242231293_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>LPSK Bakal Temui Keluarga Sutrimo, Bahas Kebutuhan Perlindungan</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:23:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>LPSK akan melindungi keluarga dari Sutrimo yang disebut sebagai Kepala Rumah Tangga mantan Jampidsus. Keluarga melaporkan kematian Sutrimo ke Polresta Banyumas</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810110330-12-1390495/lpsk-bakal-temui-keluarga-sutrimo-bahas-kebutuhan-perlindungan</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/keluarga-sutrimo-didampingi-kuasa-hukum-membuat-laporan-ke-polresta-banyumas-1786243465746_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>DPR Panggil Polda Sumut soal Kematian Mantan Istri Polisi di Medan</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:05:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>Komisi III DPR mencium kejanggalan di balik kasus kematian mantan istri polisi di Medan yang disebut tewas dengan cara menembak kepala sendiri.</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810105826-12-1390493/dpr-panggil-polda-sumut-soal-kematian-mantan-istri-polisi-di-medan</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/13/komisi-iii-gelar-audiensi-kasus-dugaan-pembakaran-3-santri-di-lombok-tengah-1783932565976_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Massa Ormas Sweeping Miras di Solo, Aniaya Pemuda Nongkrong</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:57:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>Polresta Solo menangkap sejumlah anggota ormas yang diduga melakukan intimidasi dan kekerasan terhadap warga yang sedang nongkrong dengan dalih sweeping miras.</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810082505-12-1390430/massa-ormas-sweeping-miras-di-solo-aniaya-pemuda-nongkrong</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Hakim Tolak Praperadilan Ketum Kesthuri Tersangka Kasus Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:37:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>Hakim menolak Praperadilan yang diajukan oleh Ketua Umum Asosiasi Kesatuan Tour Travel Haji Umrah Republik Indonesia (Kesthuri), Asrul Azis Taba.</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810103221-12-1390475/hakim-tolak-praperadilan-ketum-kesthuri-tersangka-kasus-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/09/kpk-tahan-tersangka-baru-kasus-korupsi-kuota-haji-1780966016107_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Pramono Ingin STY Bawa Persija Juara untuk Kado 500 Tahun Jakarta</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:17:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>Pramono Anung berharap Shin Tae-yong mampu membawa Macan Kemayoran meraih gelar juara sebagai kado bagi Jakarta yang akan memasuki usia 500 tahun pada 2027.</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810095214-20-1390454/pramono-ingin-sty-bawa-persija-juara-untuk-kado-500-tahun-jakarta</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/07/27/pramono-anung-resmikan-jersei-baru-persija-1753582912259_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>JPO 'Love-Hate' Rasuna Said Dibongkar, Target Rampung Oktober</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:04:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>Pembongkaran jembatan penyeberangan yang viral dengan sebutan JPO "Love-Hate Relationship" di Jalan HR Rasuna Said ditergetkan rampung paling lambat Oktober.</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810092516-20-1390444/jpo-love-hate-rasuna-said-dibongkar-target-rampung-oktober</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/jpo-kembar-rasuna-said-akan-terhubung-warga-tak-perlu-memutar-1785932474844_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Asal Mula Wacana Pilkada Tanpa Wakil Kepala Daerah Mencuat di DPR</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:04:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>Wacana pilkada tanpa wakil mencuat di DPR, disebut terpicu oleh ketidakharmonisan antara kepala daerah dan wakil kepala daerah.</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810091110-32-1390441/asal-mula-wacana-pilkada-tanpa-wakil-kepala-daerah-mencuat-di-dpr</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/11/27/antusias-warga-jakarta-gunakan-hak-suara-di-pilkada-2024-13_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Apa Itu Desil untuk Penerima Bansos dan Cara Mengeceknya</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:58:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>Anda bisa mengecek status desil via ponsel di laman resmi cek bansos Kemensos. Apakah status desil Anda sebagai penerima bansos?</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810084530-20-1390433/apa-itu-desil-untuk-penerima-bansos-dan-cara-mengeceknya</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/03/22/ilustrasi-hp-terkunci-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Diduga Getok Pemotor Tarif Rp5.000, Jukir di Tambora Ditangkap Polisi</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:32:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>Polisi menangkap juru parkir viral di Tambora, Jakarta yang diduga memaksa pengendara motor membayar Rp5.000. Pelaku disebut positif narkoba.</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810091326-12-1390443/diduga-getok-pemotor-tarif-rp5000-jukir-di-tambora-ditangkap-polisi</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Kecelakaan Drag Race Kotamobagu Sulut Dilaporkan Telan Korban Jiwa</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:08:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>Kejuaraan drag race di Kotamobagu berujung tragedi, dilaporkan menewaskan tujuh orang setelah mobil menabrak penonton.</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810083043-20-1390440/kecelakaan-drag-race-kotamobagu-sulut-dilaporkan-telan-korban-jiwa</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/11/30/83230fce-26cf-4a7e-9813-6cbe68d31b20_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Modus Kapal King Sun Selundupkan 1,3 Ton Narkoba di Laut Kepri</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:32:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>Koarmada menggagalkan penyelundupan 1,3 ton narkoba jenis ketamine dari kapal MV King Sun yang berbendera Tanzania setelah lihat ada anomali pelayaran.</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810071530-12-1390414/modus-kapal-king-sun-selundupkan-13-ton-narkoba-di-laut-kepri</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/koarmada-i-tangkap-kapal-asing-bawa-13-ton-narkotika-diperairan-bintan-kepri-1786252733827_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Alasan Fatwa MUI Pria Haram Berbusana Perempuan saat Acara 17 Agustus</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:19:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Komisi Fatwa MUI mengungkap alasan fatwa haram bagi pria mengenakan busana perempuan, terutama saat karnaval 17 Agustus.</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810074342-20-1390417/alasan-fatwa-mui-pria-haram-berbusana-perempuan-saat-acara-17-agustus</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/08/17/f3df46a0-21cf-441b-83c2-fd473a7ba74f_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Babak Baru Kasus Sutrimo: Ekshumasi Jenazah hingga Sosok Febrio Adiono</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:13:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Kematian Sutrimo yang disebut-sebut sebagai Kepala Rumah Tangga (Karumga) Febrie Adriansyah, kini memasuki babak baru.</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810073756-12-1390424/babak-baru-kasus-sutrimo-ekshumasi-jenazah-hingga-sosok-febrio-adiono</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/keluarga-sutrimo-didampingi-kuasa-hukum-membuat-laporan-ke-polresta-banyumas-1786243465746_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Kasus Tragedi KM Nurul Salsa Karam di Selayar Naik ke Penyidikan</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:31:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>Polisi tingkatkan status penyidikan tenggelamnya KM Nurul Salsa di Selayar, yang menewaskan 4 penumpang. Penyidik kumpulkan bukti dan periksa saksi.</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810070610-12-1390411/kasus-tragedi-km-nurul-salsa-karam-di-selayar-naik-ke-penyidikan</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/21/jenazah-diduga-korban-km-nurul-salsa-ditemukan-mengapung-1784640488303_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Update Temuan Ratusan Senjata di Sekolah Jaksel, Siswa PJJ Sementara</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:17:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Kasus ratusan senjata di Yayasan Sekolah Harapan Ibu di Jakarta masih diselidiki. Pihak yayasan bantah sengketa dan terapkan pembelajaran jarak jauh.</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810063521-12-1390404/update-temuan-ratusan-senjata-di-sekolah-jaksel-siswa-pjj-sementara</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/sterilisasi-sekolah-swasta-usai-temuan-senjata-api-1786268268243_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>FOTO: Kabut Asap Jembatan Ampera, Karhutla Bromo Meluas</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:51:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>CNN Indonesia memilih sejumlah foto dari peristiwa-peristiwa paling menonjol yang terjadi selama sepekan lalu. Berikut foto-foto tersebut.</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260809164801-22-1390344/foto-kabut-asap-jembatan-ampera-karhutla-bromo-meluas</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/09/kebakaran-di-taman-nasional-bromo-tengger-semeru-1786242695192_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Kebakaran Mal di Makassar, Pengunjung-Karyawan Alami Sesak Napas</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:40:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda mal di Makassar, Sulawesi Selatan, akibat dugaan korsleting listrik. 30 armada Damkar dikerahkan, tidak ada korban jiwa.</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810061435-20-1390399/kebakaran-mal-di-makassar-pengunjung-karyawan-alami-sesak-napas</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/kebakaran-mal-nipah-di-makassar-1786317619106_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Fatwa MUI: Pria Haram Berbusana Wanita saat Acara 17 Agustus</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:13:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>MUI merilis fatwa larangan bagi pria berbusana wanita saat karnaval 17 Agustus. Tindakan ini dianggap haram dan berpotensi mendukung LGBT.</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260809210029-12-1390383/fatwa-mui-pria-haram-berbusana-wanita-saat-acara-17-agustus</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/11/30/9a75a055-6779-4cf8-b6ea-ca9401539206_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen Mulai Gelar MPLS Sekolah Nasional Terintegrasi, 1.360 Siswa Jadi Angkatan Pertama</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:07:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Dasar dan Menengah menggelar Masa Pengenalan Lingkungan Sekolah (MPLS) Sekolah Nasional Terintegrasi (SNT).</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866546/kemendikdasmen-mulai-gelar-mpls-sekolah-nasional-terintegrasi-1360-siswa-jadi-angkatan-pertama</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/3KL6PcMRvjmZ3bSBSVfAjBMNM9Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Dirjen-Gogot-Suharwoto.jpg</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Negara Tetangga Indonesia Incar QW-19, Sistem Rudal yang Digunakan Iran Jatuhkan Pesawat F-15</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:07:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Keunggulan komparatif QW-19 dibanding sistem Barat seperti Stinger terletak pada optimalisasinya yang menyasar ancaman drone murah dan rudal jelajah.</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866545/negara-tetangga-indonesia-incar-qw-19-sistem-rudal-yang-digunakan-iran-jatuhkan-pesawat-f-15</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/nIYPL9lmk9gGenJP7P9vu49F_GQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Seorang-tentara-menembakkan-manpads-QW-12.jpg</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Main di Film Operasi Pesta Copet, Zulfa Maharani Belajar Arti Bertahan Hidup di Tengah Keterbatasan</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:04:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Aktris Zulfa Maharani mengaku belajar arti bertahan hidup di tengah keterbatasan lewat film Operasi Pesta Copet.</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866544/main-di-film-operasi-pesta-copet-zulfa-maharani-belajar-arti-bertahan-hidup-di-tengah-keterbatasan</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5Nc86OtURgN_lcoII6Oxk0hDSQU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Zulfa-dan-Kawai.jpg</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Tegaskan Wewenang BPK, Misbakhun Ingatkan Pemda Jaga Akuntabilitas Kuangan Negara</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:01:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Menurut Misbakhun, anggaran pemerintah tidak boleh berhenti sebagai angka dalam dokumen perencanaan.</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866543/tegaskan-wewenang-bpk-misbakhun-ingatkan-pemda-jaga-akuntabilitas-kuangan-negara</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/CgRQS_ZDnEaNBhEodDPRoefEswk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/anggarannegara22222.jpg</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Menteri Maman Bantah Ojol Berstatus UMKM Bakal Kena Pajak: 100 Persen Hoaks</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:56:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>Menteri UMKM Maman Abdurrahman membantah kabar yang menyebut pengemudi Ojol yang berstatus pelaku UMKM akan dikenai pajak.</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866542/menteri-maman-bantah-ojol-berstatus-umkm-bakal-kena-pajak-100-persen-hoaks</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Ad4HMS9tALxvIZVUtHyk8xu5SJY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Maman-Abdurrahman-di-Kompleks-Parlemen.jpg</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Kabar Baik untuk Guru PPPK Daerah, Pemerintah Kaji Opsi Jadi ASN Pusat</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:56:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Pemerintah mengkaji pengalihan guru PPPK daerah menjadi ASN pusat untuk mengatasi tekanan fiskal dan ketimpangan guru.</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866541/kabar-baik-untuk-guru-pppk-daerah-pemerintah-kaji-opsi-jadi-asn-pusat</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fji0ci_e85h-MwtHgicN1t7qc3U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mendagri-Tito-Karnavian-Pembayaran-PPPK.jpg</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Misbakhun Dorong Mitra SPPG Ikuti Pembenahan Tata Kelola Program MBG</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:52:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>Legislator dari Daerah Pemilihan (Dapil) II Jatim itu pun mendorong para mitra SPPG tetap mengikuti proses perbaikan tersebut.</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866540/misbakhun-dorong-mitra-sppg-ikuti-pembenahan-tata-kelola-program-mbg</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/bsbsTW3FCnSnEitsiu9VtECj1K0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/misbakhun-dooooorong-sppg.jpg</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Dituntut 6 Bulan Penjara, Khariq Anhar:  Meme 'Timpa Teks' Adalah Bentuk Kritik untuk Negara</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:47:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>Khariq Anhar dituntut 6 bulan penjara terkait kasus “timpa teks”. Ia menilai perbuatannya merupakan kritik terhadap pemerintah.</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866539/dituntut-6-bulan-penjara-khariq-anhar-meme-timpa-teks-adalah-bentuk-kritik-untuk-negara</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/YuD1ms1BTmB1MW2vDORJNJwC0rw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Khariq-Anhar12222.jpg</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Gempa M 7,4 Guncang Kolombia, BMKG Pastikan Tak Berpotensi Tsunami di Indonesia</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:45:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>Gempa berkekuatan magnitudo (M) 7,4 tercatat terjadi pada pukul 19.34.27 WIB, Senin (10/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866538/gempa-m-74-guncang-kolombia-bmkg-pastikan-tak-berpotensi-tsunami-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/k2KckAd88NNUH8AlGfySbmoSsVo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/GEMPA-BUMI-Ilustrasi-gempa.jpg</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>KPK Tahan 4 Tersangka Korupsi Pengadaan Iklan, Negara Rugi Rp 223,6 Miliar</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>KPK menahan 4 orang tersangka dalam kasus dugaan tindak pidana korupsi pengadaan barang dan jasa berupa penempatan iklan pada sebuah bank daerah</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866537/kpk-tahan-4-tersangka-korupsi-pengadaan-iklan-negara-rugi-rp-2236-miliar</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8w9BVVYwTHy1BefhbeIo5RVypn4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KPK-menahan-empat-tersangka-kasus-dugaan-korupsi-pengadaan-iklan.jpg</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Kunci Gitar Lagu Canggih - Perunggu: Tersajikan Riuh Nada dan Hening</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:42:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>Berikut ini merupakan chord kunci gitar lagu Canggih yang dipopulerkan oleh grup band Perunggu, dimainkan dari kunci A.</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866536/kunci-gitar-lagu-canggih-perunggu-tersajikan-riuh-nada-dan-hening</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GphyHvOUni2z8m3vRko7OvuuWYQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Potret-seseorang-sedang-bermain-gitar-dengan-kunci-chord-dasar-mudah-dimainkan.jpg</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Pastikan PPPK di Daerah Tak Dirumahkan, Pemerintah Siapkan Tiga Skema Pembayaran Gaji</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:42:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>Pemerintah menyiapkan tiga skema untuk membantu pemerintah daerah memenuhi kewajiban pembayaran gaji PPPK.</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kilas-kementerian/7866535/pastikan-pppk-di-daerah-tak-dirumahkan-pemerintah-siapkan-tiga-skema-pembayaran-gaji</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fji0ci_e85h-MwtHgicN1t7qc3U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mendagri-Tito-Karnavian-Pembayaran-PPPK.jpg</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Pemerintah Targetkan Perpres Ojol Selesai Sebelum 17 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:35:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>Pemerintah menargetkan peraturan presiden (perpres) terkait ojek online (ojol), rampung minggu ini atau sebelum 17 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866534/pemerintah-targetkan-perpres-ojol-selesai-sebelum-17-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/PT414fYLRnAWHtDnkUO1w8CXPnM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SURPRES-Mensesneg-Prasetyo-Hadi-4.jpg</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Tertunduk Usai Dituntut 6 Bulan, Khariq Dapat Dukungan dan Desakan Pembebasan dari Amnesty</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:35:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Usman Hamid menilai tuntutan tersebut merupakan bentuk kriminalisasi terhadap kebebasan berekspresi.</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866533/tertunduk-usai-dituntut-6-bulan-khariq-dapat-dukungan-dan-desakan-pembebasan-dari-amnesty</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vaPH1NzCY8A7jHYj-ZNhGO_Q3pE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Khariq-Anhar-tertunduk-dan-menggeleng-gelengkan-kepala.jpg</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Pesan Keluarga Bani Bishri Syansuri kepada Gus Salam yang Maju Ketua Umum PBNU: Jangan Kecewakan NU</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:34:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>Gus Salam menjadi salah satu nama yang telah menyatakan diri maju dalam bursa calon Ketua Umum PBNU periode 2026-2031.</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866532/pesan-keluarga-bani-bishri-syansuri-kepada-gus-salam-yang-maju-ketua-umum-pbnu-jangan-kecewakan-nu</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ncFC6DNznHOHzvl7Bti64bAG79A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pesaannnnn-gus-salam.jpg</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Hanura Targetkan Konsolidasi Nasional Rampung September 2026</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:34:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>Partai Hanura menargetkan konsolidasi struktur organisasi di seluruh Indonesia rampung pada September 2026.</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866531/hanura-targetkan-konsolidasi-nasional-rampung-september-2026</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/bgldBJEDQ_opPB0bZQNaBW-ETlA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KONSOLIDASI-HANURA-AS.jpg</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>PKS: Estafet Kepemimpinan Masa Depan Butuh Anak Muda yang Tangguh</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:33:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>Henda Yusamtha menyatakan, generasi muda harus segera disiapkan secara matang guna melanjutkan estafet kepemimpinan di masa depan.</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866530/pks-estafet-kepemimpinan-masa-depan-butuh-anak-muda-yang-tangguh</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/dkbK3FCFKQ2aLHp9WwvFcI6xzP8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pks-anak-muda-sjkd.jpg</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Pendaftaran Musda Demokrat Aceh, Nurdiansyah Alasta Serahkan Berkas Pencalonan</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:32:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>Nurdiansyah Alasta resmi mendaftarkan diri sebagai bakal calon Ketua DPD Partai Demokrat Aceh periode 2026–2031 pada Senin (10/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866529/pendaftaran-musda-demokrat-aceh-nurdiansyah-alasta-serahkan-berkas-pencalonan</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/YZRfoVxdP_B4Oa_L1vc5U_lgGQw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/demokrat-asd.jpg</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Mata Juling pada Anak Tak Selalu Harus Lewat Meja Operasi</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:28:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>Mendapati posisi mata anak yang tidak sejajar atau juling sering kali membuat orang tua cemas dan langsung terbayang prosedur operasi.</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7866528/mata-juling-pada-anak-tak-selalu-harus-lewat-meja-operasi</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oYC7Eu25ziOyR3hKvcJU_h4-zIA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bakti-sosial-operasi-mata-juling-jec_20231015_172841.jpg</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Mengintip Isi Garasi Destry Damayanti, Calon Tunggal Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:28:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Inilah isi garasi Destry Damayanti, Deputi Gubernur Senior BI yang kini menjadi calon tunggal Gubernur BI. Ada 3 sepeda dan 2 mobil listrik.</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866527/mengintip-isi-garasi-destry-damayanti-calon-tunggal-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/gMctDY3Den6hm7aAheqS9w41TQE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Destry-Damayanti-di-Istana-32102.jpg</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Penertiban Tambang Ilegal Jadi Katalis Produksi dan Kinerja TINS</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Penertiban tambang timah ilegal dinilai menjadi katalis bagi PT Timah Tbk (TINS) untuk meningkatkan produksi dan memperkuat kinerja perseroan. Langkah pemerintah mengamankan cadangan strategis nasional berpotensi...</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjjqmy522/penertiban-tambang-ilegal-jadi-katalis-produksi-dan-kinerja-tins</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/004391400-1737903103-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Proyek 3 Kapal Pelni Rp4,5 Triliun Uji Kemampuan Galangan Nasional</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Rencana PT Pelayaran Nasional Indonesia (Pelni) membangun tiga kapal penumpang baru senilai Rp4,5 triliun menjadi momentum bagi industri galangan kapal nasional untuk membuktikan kapasitasnya. Institusi Galangan Kapal...</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjk0px416/proyek-3-kapal-pelni-rp45-triliun-uji-kemampuan-galangan-nasional</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/005653400-1773331202-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Pemerintah Siapkan Rp 19 Triliun Bantu Daerah Bayar Gaji PPPK</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:58:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>Keputusan tersebut diambil Presiden Prabowo setelah pemerintah mengevaluasi kemampuan keuangan daerah.</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266603/pemerintah-siapkan-rp-19-triliun-bantu-daerah-bayar-gaji-pppk</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/pgcMpcbUMKLMSy1qkNdw179fjIw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320610/original/004351100_1786358921-WhatsApp_Image_2026-08-10_at_17.37.08.jpeg</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Karhutla Gunung Bromo Capai 550 Hektare</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:38:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan melanda kawasan Gunung Bromo, Jawa Timur, dengan luas area terdampak mencapai kurang lebih 550 hektare. Data BPBD Jawa Timur mencatat luasan tersebut hingga Senin (10/8/2026) pukul 06.00 WIB. Perluasan kebakaran terjadi setelah sekitar 300 hektare area terbakar pada malam sebelumnya. Relawan dan petugas gabungan terus melakukan pemadaman untuk mengendalikan api di kawasan Taman Nasional Bromo Tengger Semeru.</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8266596/karhutla-gunung-bromo-capai-550-hektare</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/TX-2Buvpt7q930pEU8wq5WJksOw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320701/original/043009700_1786369068-bro7.jpg</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>KPK Tahan 4 Tersangka Kasus Korupsi Iklan Bank BJB</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:04:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>Penyidik KPK telah menetapkan lima tersangka dalam kasus korupsi placement iklan pada Bank BJB.</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266578/kpk-tahan-4-tersangka-kasus-korupsi-iklan-bank-bjb</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/g7eNjsZCbbFLcLYkduN_BjkZeak=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320690/original/041122400_1786367089-71945.jpg</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Ritial Usaba Sri Jadi Wujud Syukur Petani di Karangasem</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:03:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>Tradisi Usaba Sri kembali digelar masyarakat Hindu Bali di Karangasem, Bali, Senin (10/8/2026). Para perempuan mengenakan pakaian adat dan berbaris mengikuti rangkaian ritual keagamaan yang ditujukan untuk menghormati Dewi Sri sebagai simbol kesuburan dan kemakmuran. Upacara ini menjadi wujud rasa syukur atas hasil panen sekaligus permohonan agar kesuburan tanah, keberlangsungan pertanian, dan keseimbangan alam tetap terjaga. Usaba Sri juga menjadi bagian dari upaya masyarakat mempertahankan tradisi keagamaan dan budaya yang diwariskan secara turun-temurun.</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8266577/ritial-usaba-sri-jadi-wujud-syukur-petani-di-karangasem</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/uFQw1aTwe1OOpghsxe9O-1Y4ODo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320685/original/094867100_1786367000-bal1.jpg</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Pramono Data 2.000 Pemulung Bantargebang untuk Jaminan Sosial</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:46:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>Sementara itu, jumlah pekerja di kawasan Bantargebang diperkirakan mencapai 6.000 orang.</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266564/pramono-data-2000-pemulung-bantargebang-untuk-jaminan-sosial</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/5UZ88uTjICZu9NmNl_7kSsUe9Pc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320670/original/046964100_1786365935-IMG_3483.jpg</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Krisis Air Bersih di Sikka, Bertahan Hidup dengan Air Tebing Bercampur Abu Gunung Lewotobi</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:16:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>Air dari ceruk tebing diambil untuk kebutuhan memasak dan minum, sementara aliran air yang keluar dimanfaatkan oleh warga untuk mandi dan cuci.</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/10/211607578/krisis-air-bersih-di-sikka-bertahan-hidup-dengan-air-tebing-bercampur-abu</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/RHydOKYPtekrffYjHz8v-LuhR4Q=/0x75:1200x675/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79dc6dcc3cd.webp</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>Edukasi</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Dirut LPDP Sebut Kapasitas Riset Indonesia Membaik tapi Hilirisasi Masih Jadi Tantangan</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:16:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>Kapasitas riset di Indonesia sudah membaik, namun Dirut LPDP menilai masih perlu lebih giat melakukan hilirisasi agar manfaatnya dirasakan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/edu/read/2026/08/10/204544271/dirut-lpdp-sebut-kapasitas-riset-indonesia-membaik-tapi-hilirisasi-masih</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/18uG9QWg9z7E2USWAEOBhj6NSUk=/0x0:1620x1080/1200x675/filters:watermark(data/photo/2026/01/30/697c819b2dbec.png,0,-0,1)/data/photo/2026/08/10/6a79cb06f1afd.jpg</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Posco Group Perkuat Investasi Sosial di Cilegon, 545 Relawan Terlibat Sejak 2018</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:16:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>Posco Group dan Krakatau Posco memperkuat program sosial dan pemberdayaan masyarakat di Kota Cilegon, Banten.</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/10/201145526/posco-group-perkuat-investasi-sosial-di-cilegon-545-relawan-terlibat-sejak</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/mq5J12Fxd4JeDEVijPWK2yFCCfk=/2x0:1280x852/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/10/6a79cc6501ad4.jpeg</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I886"/>
+  <autoFilter ref="A1:I1067"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1067</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1067"/>
+  <dimension ref="A1:I1140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -50588,8 +50588,3439 @@
         </is>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Bupati sebut Transjakarta permudah mobilitas warga kepulauan</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:43:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>Bupati Kepulauan Seribu Muhammad Fadjar Churniawan mengatakan kehadiran PT Transjakarta yang menggantikan Dinas ...</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688273/bupati-sebut-transjakarta-permudah-mobilitas-warga-kepulauan</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/12/1000303145.jpg</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Kemenimipas usulkan pemberian amensti HUT RI ke Presiden</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:40:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>Kementerian Imigrasi dan Pemasyarakatan (Kemenimipas) mengusulkan pemberian amnesti bagi warga binaan pemasyarakatan ...</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688269/kemenimipas-usulkan-pemberian-amensti-hut-ri-ke-presiden</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000013001.jpg</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Kepuasan jamaah haji naik Qodari sebut bukti perbaikan layanan</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:37:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menilai peningkatan kepuasan jamaah haji Indonesia pada ...</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688265/kepuasan-jamaah-haji-naik-qodari-sebut-bukti-perbaikan-layanan</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/kedatangan-jamaah-haji-kloter-pertama-debarkasi-medan-2797785.jpg</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Nusron: Percepatan layanan dan integrasi data tutup celah mafia tanah</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:35:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan percepatan pelayanan ...</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688261/nusron-percepatan-layanan-dan-integrasi-data-tutup-celah-mafia-tanah</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000583340.jpg</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Dompet dhuafa bantu air bersih untuk 370 warga Boyolali dan Grobogan</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:34:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>Dompet Dhuafa Jawa Tengah melakukan distribusi air bersih kepada 370 warga di Kabupaten Boyolali dan Grobogan, Jawa ...</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688260/dompet-dhuafa-bantu-air-bersih-untuk-370-warga-boyolali-dan-grobogan</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/dhompet-dhuafa.jpg</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Bupati: Peringatan HUT RI mementum percepat pembangunan</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:31:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>Bupati Kepulauan Seribu, Muhammad Fadjar Churniawan mengatakan peringatan HUT ke-81 Republik Indonesia merupakan ...</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688256/bupati-peringatan-hut-ri-mementum-percepat-pembangunan</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_4804.jpeg</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Gempa bumi di Kolombia runtuhkan 19 bangunan di Kota Cali</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:27:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>Gempa bumi di Kolombia bagian barat pada Senin menyebabkan runtuhnya 19 bangunan di Kota Cali, di negara itu, menurut ...</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688255/gempa-bumi-di-kolombia-runtuhkan-19-bangunan-di-kota-cali</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/18/ilustrasi-gempa-3.jpg</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>LPDB tegaskan pengajuan dana bergulir koperasi gratis bisa dipantau</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:26:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>Lembaga Pengelola Dana Bergulir (LPDB) Koperasi menegaskan pengajuan pembiayaan dana bergulir bagi koperasi tidak ...</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688252/lpdb-tegaskan-pengajuan-dana-bergulir-koperasi-gratis-bisa-dipantau</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-14.23.33.jpeg</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>IPB rakit 4 varietas habanero, tingkat kepedasan tembus 1,3 juta SHU</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:25:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>ANTARA - Institut Pertanian Bogor (IPB) University merakit empat varietas cabai habanero lokal pertama di ...</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688228/ipb-rakit-4-varietas-habanero-tingkat-kepedasan-tembus-13-juta-shu</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_39_59_08.Still485.jpg</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Wali kota minta Kwarcab Medan jadikan Jamnas sarana membangun karakter</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:22:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>Wali Kota Rico Tri Putra Waas meminta kontingen Kwartir Cabang (Kwarcab) Gerakan Pramuka Kota Medan memanfaatkan ...</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688251/wali-kota-minta-kwarcab-medan-jadikan-jamnas-sarana-membangun-karakter</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000108483.jpg</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Modal asing 5,9 miliar dolar AS, Indonesia masih jadi tujuan investasi</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:22:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>Permata Institute for Economic Research (PIER) mencatat arus modal asing ke Indonesia sepanjang Januari hingga awal ...</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688248/modal-asing-59-miliar-dolar-as-indonesia-masih-jadi-tujuan-investasi</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/27/realisasi-investasi-triwulan-iii-di-sumut-2654605.jpg</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Pemkab Kulon Progo komitmen tidak ada pemecatan PPPK di tengah kontrak</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:17:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten Kulon Progo, Daerah Istimewa Yogyakarta, menegaskan komitmennya untuk tidak melakukan pemutusan ...</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688245/pemkab-kulon-progo-komitmen-tidak-ada-pemecatan-pppk-di-tengah-kontrak</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000047421.jpg</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>KPK tahan tersangka korupsi pengadaan iklan Bank BJB</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:12:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>Pemimpin Divisi Change Management Office Bank BJB sekaligus eks Pemimpin Divisi Corporate Secretary Bank BJB ...</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5688244/kpk-tahan-tersangka-korupsi-pengadaan-iklan-bank-bjb</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/KPK-tahan-tersangka-kasus-korupsi-pengadaan-iklan-Bank-BJB-100826-fzn-6.jpg</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Ahli sebut kerugian negara tak cukup buktikan seseorang korupsi</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:12:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Ahli hukum pidana Universitas Kristen Indonesia Prof. Mompang Panggabean mengatakan unsur kesalahan (mens rea) harus ...</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688243/ahli-sebut-kerugian-negara-tak-cukup-buktikan-seseorang-korupsi</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000479795.jpg</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Komisi VII soroti infrastruktur pariwisata berkelanjutan Gili Lombok</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:11:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>ANTARA -Komisi VII DPR RI menyoroti aspek infrastruktur di kawasan pariwisata Gili Meno, Lombok Utara, NTB. Dalam ...</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688213/komisi-vii-soroti-infrastruktur-pariwisata-berkelanjutan-gili-lombok</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KOMISI-VII-SOROTI-INFRASTRUKTUR-PARIWISATA-BERKELANJUTAN-GILI-LOMBOK.jpg</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Melihat ritual cuci pusaka, tradisi adat di Kerajaan Mempawah</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:10:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>ANTARA - Kerajaan Mempawah menggelar ritual cuci pusaka di selasar Istana Amantubillah, Desa Pulau Pedalaman, Kecamatan ...</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688192/melihat-ritual-cuci-pusaka-tradisi-adat-di-kerajaan-mempawah</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Sequence-13.13_35_32_25.Still483.jpg</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Perpres transportasi digital ditargetkan rampung pekan ini</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:10:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>Menteri Usaha Mikro, Kecil, dan Menengah (UMKM) Maman Abdurrahman mengatakan Peraturan Presiden (Perpres) tentang ...</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688240/perpres-transportasi-digital-ditargetkan-rampung-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/15/raker-komisi-vii-dpr-dengan-menteri-umkm-2821908.jpg</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Polisi dalami kasus pria diduga tabrakkan diri ke kereta api di Jakut</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:09:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Polsek Tanjung Priok mendalami kasus yang membuat pria berinisial A (36) nekat menabrakkan diri ke kereta api yang ...</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688236/polisi-dalami-kasus-pria-diduga-tabrakkan-diri-ke-kereta-api-di-jakut</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_4803.jpeg</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>PIER: Konsumsi domestik perkuat ekonomi RI di tengah tekanan global</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:08:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>Permata Institute for Economic Research (PIER) menilai ekonomi Indonesia perlu semakin mengandalkan kekuatan domestik, ...</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688233/pier-konsumsi-domestik-perkuat-ekonomi-ri-di-tengah-tekanan-global</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000456822.jpg</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Kemensos berdayakan penerima bansos di Madura jadi petani ekspor cabai</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:07:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial (Kemensos) melalui Direktorat Jenderal Pemberdayaan Sosial memberdayakan penerima bantuan sosial ...</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688232/kemensos-berdayakan-penerima-bansos-di-madura-jadi-petani-ekspor-cabai</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/203452.jpg</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Empat korban hilang dalam kecelakaan kapal di perairan Bintan</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:05:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>Kepala Kantor Pencarian dan Pertolongan (SAR) Tanjungpinang Fazzli menyebutkan empat korban dinyatakan hilang dalam ...</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688229/empat-korban-hilang-dalam-kecelakaan-kapal-di-perairan-bintan</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/inbound887734786127890032.jpg</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>BPKP: Lingkungan pengendalian fondasi utama penyelenggaraan SPIP</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:00:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>Deputi Bidang Pengawasan Instansi Pemerintah Bidang Perekonomian, Infrastruktur, dan Pembangunan Kewilayahan (PIPK) ...</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688224/bpkp-lingkungan-pengendalian-fondasi-utama-penyelenggaraan-spip</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/BPKP-PPKD.jpg</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Jukir di Tambora diringkus polisi usai paksa pengendara bayar Rp5 ribu</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:58:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>Polisi meringkus seorang juru parkir berinisial MS di kawasan parkir Pasar Mitra, Jalan KH M Mansyur, Kelurahan ...</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688221/jukir-di-tambora-diringkus-polisi-usai-paksa-pengendara-bayar-rp5-ribu</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/25/Ilustrassi-penangkapan-pelaku.jpg</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Mantan pemain Indiana Pacers ditunjuk sebagai GM tim universitas</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:53:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Mantan pemain Indiana Pacers, Monta Ellis, memulai babak baru kariernya sebagai general manager (GM) tim bola basket ...</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688212/mantan-pemain-indiana-pacers-ditunjuk-sebagai-gm-tim-universitas</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000478622.jpg</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Kereta Y404 jadi sarana widyawisata dan ruang lelas bergerak di China</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:52:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Kereta khusus Y404 untuk widyawisata (study tour) yang mengangkut 598 guru dan murid pada Minggu (9/8) berangkat dari ...</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688208/kereta-y404-jadi-sarana-widyawisata-dan-ruang-lelas-bergerak-di-china</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CjkinzN000016_20260810_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Menhub menegaskan cabut izin operator KMP Mutiara bila terbukti lalai</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:49:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi menegaskan pemerintah akan mencabut izin operator KMP Mutiara Sentosa ...</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688205/menhub-menegaskan-cabut-izin-operator-kmp-mutiara-bila-terbukti-lalai</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/C8926C3A-5632-417E-9635-309C4AAA82A6.jpeg</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Morgan jaga peluang ke Kejuaraan Dunia Karting setelah juarai MiniRok</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:49:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>Atlet gokart muda Morgan Holindo Sonmoahi menjaga peluang meraih tiket Kejuaraan Dunia Karting di Italia setelah ...</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688204/morgan-jaga-peluang-ke-kejuaraan-dunia-karting-setelah-juarai-minirok</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001101085.jpg</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Survei IPO tempatkan Bahlil dan Golkar sama-sama di posisi ketiga</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:45:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>Survei Indonesia Political Opinion (IPO) menempatkan Menteri Energi dan Sumber Daya Mineral sekaligus Ketua Umum Partai ...</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688201/survei-ipo-tempatkan-bahlil-dan-golkar-sama-sama-di-posisi-ketiga</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_7687.jpg</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Pebasket lokal Indonesia makin berkualitas</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:44:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Pelatih kepala tim nasional bola basket putra Indonesia David Singleton menilai kualitas pemain lokal semakin bagus ...</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688200/pebasket-lokal-indonesia-makin-berkualitas</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/1000476680.jpg</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Ichsan Pratama gabung Deltras FC siap arungi musim baru</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:38:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>Gelandang senior Ichsan Pratama resmi bergabung dengan Deltras FC setelah musim lalu membela PSS Sleman, dengan target ...</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688196/ichsan-pratama-gabung-deltras-fc-siap-arungi-musim-baru</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG-20260810-WA0072.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Komisi IX ajak semua pihak ambil peran dalam program 'Genting'</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:38:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>Ketua Komisi IX DPR-RI, Felly E. Runtuwene mengajak semua pihak ikut mengambil peran dalam program 'Gerakan ...</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688193/komisi-ix-ajak-semua-pihak-ambil-peran-dalam-program-genting</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001993888.jpg</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>BTN bermitra dengan Pemkot Padang memperluas layanan KPR hingga UMKM</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:32:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>PT Bank Tabungan Negara (Persero) Tbk (BTN) bermitra dengan Pemerintah Kota (Pemkot) Padang, Sumatera Barat (Sumbar), ...</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688189/btn-bermitra-dengan-pemkot-padang-memperluas-layanan-kpr-hingga-umkm</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-18.34.39.jpeg</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Puslabfor ambil 30 item dari olah TKP di sekolah temuan senjata di Jaksel</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:31:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>Tim Pusat Laboratorium Forensik (Puslabfor) Bareskrim Polri mengambil sebanyak 30 item dari olah tempat kejadian ...</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688185/puslabfor-ambil-30-item-dari-olah-tkp-di-sekolah-temuan-senjata-di-jaksel</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001021779.jpg</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>DPRD Sulteng minta empat persoalan tambang emas CPM dievaluasi</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:22:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>Komisi III DPRD Sulawesi Tengah menyoroti empat persoalan terkait operasional tambang emas PT Citra Palu Minerals (CPM) ...</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688181/dprd-sulteng-minta-empat-persoalan-tambang-emas-cpm-dievaluasi</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/13/IMG_20260213_061140.jpg</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Polisi segera ekshumasi makam Sutrimo, penjaga kediaman eks Jampidsus</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:21:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>ANTARA - Menjelang proses pembongkaran makam untuk keperluan penyelidikan kasus atau ekshumasi terhadap makam Sutrimo, ...</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688132/polisi-segera-ekshumasi-makam-sutrimo-penjaga-kediaman-eks-jampidsus</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_POLISI-SEGERA-EKSHUMASI-MAKAM-SUTRIMO-PENJAGA-KEDIAMAN-EKS-JAMPIDSUS.jpg</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Misbakhun ingatkan pemda tertib kelola dan pertanggungjawabkan anggaran</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:18:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XI DPR RI Mukhamad Misbakhun mengingatkan pemerintah daerah, termasuk pengelola BUMD dan BLUD, agar tertib ...</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688179/misbakhun-ingatkan-pemda-tertib-kelola-dan-pertanggungjawabkan-anggaran</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001229509.jpg</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>BNPB desak kepala daerah di Kalbar-Kalteng cabut izin pembukaan lahan</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:16:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>ANTARA - BNPB mendesak kepala daerah di Kalimantan Barat dan Tengah segera mencabut izin pembukaan lahan untuk ...</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688117/bnpb-desak-kepala-daerah-di-kalbar-kalteng-cabut-izin-pembukaan-lahan</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BNPB-DESAK-KEPALA-DAERAH-DI-KALBAR-KALTENG-CABUT-IZIN-PEMBUKAAN-LAHAN.jpg</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Kemensos-Komnas HAM sinergi tangani pengungsi konflik Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:14:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial (Kemensos) bersinergi dengan Komisi Nasional Hak Asasi Manusia (Komnas HAM) untuk menangani para ...</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688173/kemensos-komnas-ham-sinergi-tangani-pengungsi-konflik-papua-tengah</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/203343.jpg</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Kemenhub sebut ETLE Hub tersebar di 51 titik pantau demi tekan ODOL</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:14:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan (Kemenhub) menyebut sistem Electronic Traffic Law Enforcement Hub (ETLE Hub) telah tersebar di ...</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688171/kemenhub-sebut-etle-hub-tersebar-di-51-titik-pantau-demi-tekan-odol</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/DFECB780-5C05-4D9B-9E7E-BC4E12249CE6.jpeg</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Bos Aprilia bertekad juara di kandang Marc Marquez</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:12:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>Bos Aprilia Racing Massimo Rivola membidik kemenangan di MotoGP Aragon yang menjadi kandang pembalap Ducati Lenovo Marc ...</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688167/bos-aprilia-bertekad-juara-di-kandang-marc-marquez</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/01/XxjpbeE000208_20260601_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Iran Tuntut AS Penuhi 5 Syarat Agar Selat Hormuz Dibuka Lagi</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:14:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>Iran menegaskan, Amerika Serikat harus memenuhi sejumlah syarat, memberikan kompensasi, mengakhiri sanksi dan ancaman militer sebelum Selat Hormuz dibuka.</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8612918/iran-tuntut-as-penuhi-5-syarat-agar-selat-hormuz-dibuka-lagi</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/18/perang-as-iran-berakhir-selat-hormuz-segera-dibuka-1781798442899_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>LRT Jakarta Velodrome-Manggarai Rp 4,1 Triliun Bakal Diresmikan Bulan Ini</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:41:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>Penyelesaian konstruksi Light Rail Transit (LRT) Jakarta Fase 1B rute Velodrome-Manggarai terus dipercepat.</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8612901/lrt-jakarta-velodrome-manggarai-rp-4-1-triliun-bakal-diresmikan-bulan-ini</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/progres-pembangunan-lrt-jakarta-fase-1-b-1781249050504_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Gak Mewah Tapi Hangat! Momo Eks Geisha Beri Kejutan di Ultah Suami</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:02:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>Momo eks Geisha merayakan ulang tahun ke-37 suaminya Nicola Reza Samudra. Dia mempersiapkan kejutan meriah lengkap dengan kehangatan keluarga.</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612215/gak-mewah-tapi-hangat-momo-eks-geisha-beri-kejutan-di-ultah-suami</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/momo-eks-geisha-1786348658920_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Bigmo Serahkan Rekaman Live Utuh ke Polisi: Spontan, Tak Ada Skenario</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:47:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>Bigmo menyerahkan rekaman siaran langsung ke Polda Metro Jaya untuk membuktikan interaksi spontan dengan anak-anak, terkait dugaan eksploitasi vape.</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612904/bigmo-serahkan-rekaman-live-utuh-ke-polisi-spontan-tak-ada-skenario</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/youtuber-bigmo-dicecar-40-pertanyaan-soal-konten-promosi-vape-ajak-anak-1786361146873_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Jonathan Frizzy Batasi Main Padel karena Berat Badan Ikut Turun</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:01:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Jonathan Frizzy keranjingan padel setelah 6 bulan berlatih. Ia mengurangi frekuensi latihan untuk menjaga berat badan karena menganggap sudah terlalu kurus.</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612520/jonathan-frizzy-batasi-main-padel-karena-berat-badan-ikut-turun</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/jonathan-frizzy-1786357077078_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Raffi Ahmad Ungkap Dampak Kolaborasi RANS &amp;amp; Mayora di Dunia Entertainment</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:32:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>PT RANS Entertainment menjalin kemitraan strategis dengan Mayora dan LINK Group. Kolaborasi ini bertujuan memberikan dampak sosial bagi UMKM di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612819/raffi-ahmad-ungkap-dampak-kolaborasi-rans-mayora-di-dunia-entertainment</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/rans-1786368608984_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Setahun Nikah, Faishal Tanjung-Nadin Amizah Kunjungi Tempat Sakral Ini</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:02:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Pasangan musisi Faishal Tanjung dan Nadin Amizah sudah setahun menikah. Begini cara mereka merayakannya.</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612075/setahun-nikah-faishal-tanjung-nadin-amizah-kunjungi-tempat-sakral-ini</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/nadin-amizah-1786345279328_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Effort Leony Saat Pacar dari Selandia Baru Ultah</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:39:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Artis Leony melakukan upaya besar untuk memberi kejutan ulang tahun ke pacarnya, Charles Seaman. Seperti apa?</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612730/effort-leony-saat-pacar-dari-selandia-baru-ultah</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/leony-1786363964103_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Kronologi Polisi Jadi Korban Begal Saat Nyambi Ngojek di Palembang, Pelakunya Sepasang Kekasih</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:41:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Aiptu Januardo Eko Satria, seorang anggota Polri menjadi korban begal saat nyambi jadi tukang ojek di Palembang, Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866572/kronologi-polisi-jadi-korban-begal-saat-nyambi-ngojek-di-palembang-pelakunya-sepasang-kekasih</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XfV5WTRcxonxe_AAIRL1RRXJanY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pelaku-begal-polisi-di-palembang.jpg</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>7 Langkah Memilih Camilan yang Aman dan Sehat untuk Anak Menurut BPOM RI</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:38:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>BPOM membagikan tips memilih camilan anak, mulai dari memperhatikan gizi, keamanan bahan, label kemasan, hingga izin edar produk</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866571/7-langkah-memilih-camilan-yang-aman-dan-sehat-untuk-anak-menurut-bpom-ri</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RJHIYu077TDo8eNWqk2tkJivOvU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/festival-camilan.jpg</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Kunci Gitar Lagu Luka Dipelupuk Mata - Dongker: Sayang, Tampar Mukaku Lihat Sekitar</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:30:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Kunci gitar lagu Luka di Pelupuk Mata - Dongker feat Binar chord dasar mudah dimainkan: sayang, tampar mukaku lihat sekitar semua yang tak pernah.</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866570/kunci-gitar-lagu-luka-dipelupuk-mata-dongker-sayang-tampar-mukakulihat-sekitar</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/E33dbHm7VtGLAEgLsyP9Ie4szxc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Dongker-1-27042026.jpg</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Kunci Gitar Lagu Moonlight - Nadin Amizah: And We'll Dance Huu, And We'll Dance Huu</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:29:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Kunci gitar lagu Moonlight - Nadin Amizah chord dasar yang mudah dimainkan: and we'll dance hu..u..u..uu.. and we'll dance hu..u..u..uu..</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866569/kunci-gitar-lagu-moonlight-nadin-amizah-and-well-dance-huu-and-well-dance-huu</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4WAU_R_lDbvx8WfDEi6lDCUI8QA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Nadin-Amizah-1-23012026.jpg</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Topan No. 15 Bergerak ke Honshu, Jepang Waspadai Hujan Lebat dan Angin Kencang</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:19:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Topan No. 15 bergerak dengan jalur tak biasa dan diperkirakan menghantam Honshu. JMA waspadai hujan lebat, angin kencang, dan gelombang tinggi</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866568/topan-no-15-bergerak-ke-honshu-jepang-waspadai-hujan-lebat-dan-angin-kencang</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zf37Zz_CtYsJh6z7y3PV1F2kY9Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/anginjepang212222.jpg</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Bulan Imunisasi Anak Sekolah Dimulai, Siswa SD Darunnajah Jaksel Terima Imunisasi Rubella hingga HPV</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:19:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Sekolah Dasar Islam (SDI) Darunnajah Ulujami melaksanakan program Bulan Imunisasi Anak Sekolah (BIAS) pada bulan Agustus 2026 ini.</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866567/bulan-imunisasi-anak-sekolah-dimulai-siswa-sd-darunnajah-jaksel-terima-imunisasi-rubella-hingga-hpv</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0NSb0BTHJjMBDMjTtkou8_0d6IM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/imnsasibias2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban Bahasa Indonesia Kawan Seiring Kelas 3 Halaman 21 Kurikulum Merdeka: Aktivitas 5</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:06:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Soal ini terdapat pada buku Bahasa Indonesia Kawan Seiring Kelas 3 Halaman 21 Kurikulum Merdeka, tepatnya pada Aktivitas 5.</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7866566/kunci-jawaban-bahasa-indonesia-kawan-seiring-kelas-3-halaman-21-kurikulum-merdeka-aktivitas-5</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fLjsurmR-3RdbbUMtGvfTJlnZfs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/siswa-SD-belajar-di-sekolah-2.jpg</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Pelajar SMA Meninggal Tertemper KRL di Stasiun Jurangmangu, Polisi Selidiki Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:04:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Pelajar SMA tewas tertemper KRL di Stasiun Jurangmangu. Polisi masih menyelidiki kronologi dan penyebab korban berada di jalur kereta.</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7866565/pelajar-sma-meninggal-tertemper-krl-di-stasiun-jurangmangu-polisi-selidiki-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vnN8t7-_sNFl5avv0zV2pk7I0Tk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tertemperKRL1.jpg</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu I Think God Can Explain - Splender: There's A Lot of Things I Understand</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:03:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>Simak terjemahan lirik lagu "I Think God Can Explain" yang dipopulerkan oleh grup musik rock alternatif asal Amerika Serikat (AS), Splender.</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7866564/terjemahan-lirik-lagu-i-think-god-can-explain-splender-theres-a-lot-of-things-i-understand</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/U-BX1ieF2y0vnLJFGFlYSjiTfIc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/headphones-desk-black-laid.jpg</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Dorong Hilirisasi Mineral, Pakar Unand: Indonesia Harus Kuasai Rantai Teknologi hingga Manufaktur</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:54:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Dekan Fakultas Teknik Unand ini menjelaskan bahwa material merupakan fondasi utama bagi hampir seluruh industri berbasis teknologi modern</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7866563/dorong-hilirisasi-mineral-pakar-unand-indonesia-harus-kuasai-rantai-teknologi-hingga-manufaktur</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/D7PvT6d8l9VJtjzMAKtL6oXp7c8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pertambangan-hilirisasi-898.jpg</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Hadapi Perubahan Teknologi, Perusahaan IT Perkuat Pengembangan AI</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:48:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>Perkembangan artificial intelligence (AI), cloud, data, hingga teknologi quantum perlu terus dipahami karena berpotensi mengubah proses bisnis</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/techno/7866562/hadapi-perubahan-teknologi-perusahaan-it-perkuat-pengembangan-ai</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/IrGaDFDwqU1c7vZPabKq0pBNfR4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/lari2222222.jpg</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Mengenal Taktik Hellscape: Cara Taiwan Mengubah Keunggulan China Jadi Beban di Medan Perang</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:42:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>hellscape adalah strategi yang dirancang untuk mengubah Selat Taiwan menjadi medan perang yang penuh hambatan bagi pasukan penyerang China.</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7866561/mengenal-taktik-hellscape-cara-taiwan-mengubah-keunggulan-china-jadi-beban-di-medan-perang</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/z4Tm0IS7mQdIa40zymiZZ-LAvAg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Tentara-Taiwan-dalam-latihan-tembak.jpg</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Personel Manchester United Makin Lengkap, 9 Pemain Boyongan ke Irlandia</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:41:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>9 pemain Manchester United akan bergabung dengan pemusatan latihan klub yang kini berada di Irlandia untuk persiapan melawan Leeds United.</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866560/personel-manchester-united-makin-lengkap-9-pemain-boyongan-ke-irlandia</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/rUPG4n-YQc8DyP71l6MuTLUdAoA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-klub-Manchester-United.jpg</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Konsumen Makin Selektif Memilih Skincare, Tak Sekadar Ikuti Tren</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:41:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>Hasil survei menunjukkan 75 persen responden menilai rutinitas kecantikan yang konsisten berkontribusi terhadap kesejahteraan dan kepercayaan diri.</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7866559/konsumen-makin-selektif-memilih-skincare-tak-sekadar-ikuti-tren</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/a3B5NvDnzgBQn-90xCwln5CAeuY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/MEMLIH-SKINCARE-teknologi-AI.jpg</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Dede Yusuf Dorong Tugas Wakil Kepala Daerah Diperjelas Agar Tak Hanya Jadi 'Ban Serep'</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:39:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi II DPR RI Dede Yusuf, menanggapi wacana wakil kepala daerah tidak lagi dipilih secara langsung melalui Pilkada.</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866558/dede-yusuf-dorong-tugas-wakil-kepala-daerah-diperjelas-agar-tak-hanya-jadi-ban-serep</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-T52nXX_9IXg4te5nAc2zjS-18k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wakil-Ketua-Umum-Partai-Demokrat-Dede-Yusuf-3219.jpg</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Morgan Holindo Menangi MiniRok Round 5, Tiket Kejuaraan Dunia Italia Makin Panas</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:37:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>Presisi dalam melewati setiap tikungan menjadi salah satu kunci Morgan mempertahankan keunggulannya.</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7866557/morgan-holindo-menangi-minirok-round-5-tiket-kejuaraan-dunia-italia-makin-panas</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/duPs0oHISYocgK343koqJuRgcBw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PACU-GOKART-Morgan-Holindo-Sonmoahi-memacu-gokartnya.jpg</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Perwira Menengah TNI AL Didakwa Edarkan Sabu, Pelaku Libatkan Istri</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:34:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>Mayor Laut Faisal mengaku sudah sudah mengonsumsi sabu bersama Kapten Laut I Made Surya sejak tahun 2024</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7866556/perwira-menengah-tni-al-didakwa-edarkan-sabu-pelaku-libatkan-istri</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/NNQ5R-oY_sv9elawTryf6vOvk-U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Suasana-Mayor-Laut-Faisal-Mulia.jpg</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Rutin Olahraga Senam Bantu Jaga Kelenturan Otot dan Keseimbangan Tubuh hingga Usia Lanjut</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:33:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>Senam salah satu olahraga yang dianjurkan, karena kelenturan otot dan mobilitas sendi cenderung mengalami penurunan seiring bertambahnya usia.</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866555/rutin-olahraga-senam-bantu-jaga-kelenturan-otot-dan-keseimbangan-tubuh-hingga-usia-lanjut</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/qni-z7ElwzZkJZT7rK3b72XOaaI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Senam-1-10082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Metode 3R dan Pentingnya Pendekatan Menyeluruh dalam Pengelolaan Diabetes</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:31:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>Banyak penderita DMT2 kesulitan konsisten ubah gaya hidup. Metode 3R hadir sebagai solusi menyeluruh cegah komplikasi.</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/tribunners/7866554/metode-3r-dan-pentingnya-pendekatan-menyeluruh-dalam-pengelolaan-diabetes</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/WHGJgJjnf79jZ8IvUeiyxZf9Mq8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-diabetes.jpg</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Singapura vs Thailand di 4 Besar Piala AFF 2026: Kisah Heroik The Lions Lanjut atau Berakhir?</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:30:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>Dongeng indah yang sejauh ini diciptakan Timnas Singapura di Piala AFF 2026 akan berlanjut pada babak semifinal.</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7866553/singapura-vs-thailand-di-4-besar-piala-aff-2026-kisah-heroik-the-lions-lanjut-atau-berakhir</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iboht6amQhsYVg3hY7SU_axQqZo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Aksi-kiper-Timnas-Indonesia-Cahya-Supriadi-dan-Beckham-Putra-berusaha-meredam-pemain-Singapura.jpg</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Jelang HUT ke-42, KBI Raih Tiga Penghargaan dalam Dua Ajang</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Ichsan Emrald Alamsyah</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Kliring Berjangka Indonesia (PT KBI) meraih tiga penghargaan dari dua ajang berbeda dalam satu hari. Capaian tersebut diraih menjelang peringatan HUT ke-42 PT KBI yang jatuh...</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjk0lg349/jelang-hut-ke42-kbi-raih-tiga-penghargaan-dalam-dua-ajang</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pt-kliring-berjangka-indonesia-pt-kbi-meraih-tiga-penghargaan_260810194049-761.jpg</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Polisi Dalami Penyebab Siswi SMA Tertemper KRL di Jurangmangu</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:36:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Petugas melakukan identifikasi dan pemeriksaan di lokasi kejadian.</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266627/polisi-dalami-penyebab-siswi-sma-tertemper-krl-di-jurangmangu</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/cXOlyfDT2PZaYxlfJ_SLh9dJWwY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/3583727/original/039256500_1632655961-2021026-FOTO---KRL-Herman-8.jpg</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Berkas Lengkap, KPK Limpahkan Ajudan Gubernur Riau Abdul Wahid ke JPU</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:21:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>Pelimpahan tahap dua tersebut dilakukan terkait kasus pemerasan di lingkungan Pemprov Riau tahun anggaran 2025.</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266623/berkas-lengkap-kpk-limpahkan-ajudan-gubernur-riau-abdul-wahid-ke-jpu</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ShIfkKlF2x04R1g_FIea0Cswkb4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5554637/original/039376600_1776082734-IMG_0315.jpg</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>KPK Bongkar Skema Korupsi Iklan Bank BJB, Negara Rugi Rp 223,6 Miliar</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:41:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>Dari anggaran tersebut, sekitar Rp 410 miliar disetujui untuk penempatan iklan di media televisi, cetak, dan daring melalui pengadaan jasa agensi.</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266619/kpk-bongkar-skema-korupsi-iklan-bank-bjb-negara-rugi-rp-2236-miliar</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/cYgvVSSkr1LAnPTCETtvLPa8NRw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4065432/original/001612500_1656325087-WhatsApp_Image_2022-06-27_at_5.08.03_PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Siswi SMA Tertemper KRL di Jurangmangu</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:55:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>Polisi masih melakukan identifikasi dan penyelidikan untuk mengetahui penyebab kejadian.</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266613/siswi-sma-tertemper-krl-di-jurangmangu</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/U_qlSYUdcatyMU2uoGrWoeWdKM0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9309837/original/095095900_1785290323-faisal-hanafi-zmr4ypKgTyg-unsplash.jpg</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1067"/>
+  <autoFilter ref="A1:I1140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1140"/>
+  <dimension ref="A1:I1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -54019,8 +54019,2170 @@
         </is>
       </c>
     </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>IDM ajak masyarakat maknai kemerdekaan dengan mencintai warisan budaya</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:34:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>InJourney Destination Management (IDM) mengajak masyarakat memaknai kemerdekaan tidak hanya sebagai perayaan seremonial ...</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688344/idm-ajak-masyarakat-maknai-kemerdekaan-dengan-mencintai-warisan-budaya</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000481689.jpg</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>PIER: Sektor jasa penopang pertumbuhan ekonomi kuartal II 2026</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:34:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Permata Institute for Economic Research (PIER) mencatat sektor jasa menjadi salah satu penopang penting pertumbuhan ...</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688340/pier-sektor-jasa-penopang-pertumbuhan-ekonomi-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000456874.jpg</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Kelompok IRT Jember ubah tutup botol jadi gantungan bernilai ekonomi</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:33:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>ANTARA - Sekelompok ibu-ibu rumah tangga di di Desa Suci, Kecamatan Panti, Jember, Jawa Timur mengubah limbah tutup ...</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688320/kelompok-irt-jember-ubah-tutup-botol-jadi-gantungan-bernilai-ekonomi</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KELOMPOK-IRT-JEMBER-UBAH-TUTUP-BOTOL-JADI-GANTUNGAN-BERNILAI-EKONOMI.jpg</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Dua kelurahan di Makassar jadi percontohan Sadar HAM</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:23:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Kementerian Hak Asasi Manusia memilih Kelurahan Mattoanging, Kecamatan Mariso, dan Kelurahan Kaluku Bodoa, Kecamatan ...</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688339/dua-kelurahan-di-makassar-jadi-percontohan-sadar-ham</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/ImgResizer_IMG-20260810-WA0029.jpg</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Antisipasi kebakaran, Pemkot Jakbar bangun pos Damkar-hidran mandiri</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:21:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Jakarta Barat (Jakbar) membangun Pos Pemadam Kebakaran (Damkar) dan hidran mandiri di lokasi ...</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688337/antisipasi-kebakaran-pemkot-jakbar-bangun-pos-damkar-hidran-mandiri</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_213619.jpg</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Pemprov Sumut: Pembangunan di Kepulauan Nias berjalan sesuai rencana</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:20:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Sumatera Utara (Sumut) memastikan berbagai program prioritas pembangunan ...</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688336/pemprov-sumut-pembangunan-di-kepulauan-nias-berjalan-sesuai-rencana</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001039869.jpg</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>OJK: Indeks literasi dan inklusi keuangan 2026 melampaui target RPJMN</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:18:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) menyampaikan, pencapaian indeks literasi dan inklusi keuangan pada 2026 telah melampaui ...</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688332/ojk-indeks-literasi-dan-inklusi-keuangan-2026-melampaui-target-rpjmn</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/9ee27bf0-fbd4-4cf3-8968-5054d21b681d.jpeg</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Ekonomi RI diproyeksikan tumbuh di kisaran 5 persen hingga akhir tahun</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:17:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Chief Economist Permata Bank, Josua Pardede mengatakan perekonomian Indonesia diproyeksikan tetap tumbuh solid di ...</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688331/ekonomi-ri-diproyeksikan-tumbuh-di-kisaran-5-persen-hingga-akhir-tahun</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000456822.jpg</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Dewa United Esports umumkan jadwal laga tim untuk MPL ID musim ke-18</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:17:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Dewa United Esports mengumumkan jadwal pertandingan tim dalam babak reguler Mobile Legends: Bang Bang Professional ...</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688328/dewa-united-esports-umumkan-jadwal-laga-tim-untuk-mpl-id-musim-ke-18</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000474548.jpg</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Polda Jateng siap bantu ekshumasi jenazah Sutrimo</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:16:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Polda Jawa Tengah siap membantu pelaksanaan ekshumasi jenazah kepala rumah tangga mantan Jaksa Agung Muda Bidang Pidana ...</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688324/polda-jateng-siap-bantu-ekshumasi-jenazah-sutrimo</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_172957.jpg</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Empat dari lima tersangka kasus Bank BJB resmi ditahan KPK</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:13:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>ANTARA - Komisi Pemberantasan Korupsi (KPK) resmi menahan empat dari lima tersangka kasus dugaan korupsi pengadaan ...</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688296/empat-dari-lima-tersangka-kasus-bank-bjb-resmi-ditahan-kpk</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/EMPAT-DARI-LIMA-TERSANGKA-KASUS-BANK-BJB-RESMI-DITAHAN-KPK.jpg</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Menhut dorong gerakan pemulihan hutan dan ekosistem dalam HKAN 2026</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:12:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan (Menhut) Raja Juli Antoni mendorong gerakan pemulihan hutan dan ekosistem yang mengalami kerusakan ...</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688323/menhut-dorong-gerakan-pemulihan-hutan-dan-ekosistem-dalam-hkan-2026</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/9827e61f-9b6b-4379-8eb9-3a7b1f977a1b.jpeg</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>BPS menilai cakupan survei pengaruhi penurunan indeks keuangan syariah</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:09:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pusat Statistik (BPS) Amalia Adininggar Widyasanti menilai perubahan cakupan data survei menjadi ...</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688319/bps-menilai-cakupan-survei-pengaruhi-penurunan-indeks-keuangan-syariah</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/c52f08ca-ef66-4b88-9ffb-343422a35fd4.jpeg</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Enam bandara ditutup akibat gempa magnitudo 7,4 guncang Kolombia</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:09:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Enam bandara di Kolombia bagian barat mengalami kerusakan dan harus ditutup menyusul gempa bumi dahsyat yang ...</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688315/enam-bandara-ditutup-akibat-gempa-magnitudo-74-guncang-kolombia</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/18/ilustrasi-gempa-2_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Motor wartawan hilang usai liputan di Kantor Kemenko Polkam</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:09:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Sepeda motor milik pewarta iNews Media Group, Danandaya Arya Putra hilang saat bertugas meliput di Kantor Kemenko ...</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688311/motor-wartawan-hilang-usai-liputan-di-kantor-kemenko-polkam</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/02/25/IMG_20230225_132120.jpg</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Puan minta dampak ekonomi penutupan wisata Bromo mulai dihitung</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:07:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Ketua DPR RI Puan Maharani meminta pemerintah mulai menghitung dampak ekonomi kebakaran di kawasan Taman Nasional Bromo ...</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688307/puan-minta-dampak-ekonomi-penutupan-wisata-bromo-mulai-dihitung</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/titik-api-baru-kebakaran-hutan-kawasan-tnbts-2838619.jpg</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Gempa bumi telan korban jiwa di sejumlah daerah Kolombia</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:06:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Empat orang, termasuk tiga anak, meninggal dunia akibat gempa bumi dahsyat di departemen Valle del Cauca di barat daya ...</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688303/gempa-bumi-telan-korban-jiwa-di-sejumlah-daerah-kolombia</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/Bendera-Kolombia.jpg</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Presiden Abelardo tangani langsung gempa Kolombia</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:05:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Presiden Kolombia Abelardo de la Espriella pada Senin menuju Bogota untuk memimpin langsung koordinasi bantuan bagi ...</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688300/presiden-abelardo-tangani-langsung-gempa-kolombia</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/08/thumbs_b_c_6e143678c2cb56b3ec9b82b9a1ee2450.jpg</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Kasus temuan senjata di sekolah, polisi identifikasi pelaku lewat DNA</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:04:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Kepolisian mengidentifikasi pelaku yang masuk atau pernah berkontak dengan ruangan yang diduga menjadi tempat ...</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688297/kasus-temuan-senjata-di-sekolah-polisi-identifikasi-pelaku-lewat-dna</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1001021852.jpg</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Tukang parkir yang viral karena paksa bayar Rp5 ribu ternyata positif narkoba</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:02:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Juru parkir (jukir) liar berinisial MS yang ditangkap usai memaksa pengendara membayar Rp5.000 di minimarket wilayah ...</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688293/tukang-parkir-yang-viral-karena-paksa-bayar-rp5-ribu-ternyata-positif-narkoba</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2015/09/20150919juru_parkir-fanny_octavianus.jpg</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Menteri ATR sebut Verifikasi BPHTB kini dipercepat jadi tiga hari</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:01:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan Surat Edaran ...</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688291/menteri-atr-sebut-verifikasi-bphtb-kini-dipercepat-jadi-tiga-hari</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_223530.jpg</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Kreator Indonesia temukan pesona budaya dalam kunjungannya ke China</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:58:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Dalam perjalanan keduanya ke China, seorang pemudi Indonesia bernama Najwa Nur Awalia (24) memperoleh sudut pandang ...</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688288/kreator-indonesia-temukan-pesona-budaya-dalam-kunjungannya-ke-china</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/CjkinzN000007_20260810_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Pemkab Sigi targetkan SRMP 22 tampung 2.160 siswa pada tahun 2027</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:57:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kabupaten Sigi menargetkan Sekolah Rakyat setingkat SMP di wilayah tersebut dapat menampung hingga ...</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5688267/pemkab-sigi-targetkan-srmp-22-tampung-2160-siswa-pada-tahun-2027</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKAB-SIGI-TARGETKAN-SRMP-22-TAMPUNG-2.160-SISWA-PADA-TAHUN-2027.jpg</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Bupati tekankan pentingnya edukasi perdamaian Aceh bagi generasi muda</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:54:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Bupati Aceh Besar, Muharram Idris menekankan pentingnya edukasi sejarah perdamaian Aceh yang sudah berumur 21 tahun ...</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688284/bupati-tekankan-pentingnya-edukasi-perdamaian-aceh-bagi-generasi-muda</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1002104834.jpg</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Wanita di Jakbar diduga jadi korban pelecehan oleh sopir taksi online</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:54:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Seorang perempuan berinisial SN diduga menjadi korban pelecehan oleh sopir taksi online di wilayah Jakarta Barat ...</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688283/wanita-di-jakbar-diduga-jadi-korban-pelecehan-oleh-sopir-taksi-online</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/1000267701.jpg</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>KKP sebut produk olahan lele marinasi Indonesia tembus pasar Taiwan</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:50:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>Produk olahan lele marinasi produksi usaha mikro kecil dan menengah (UMKM) asal Bandung, Jawa Barat, menembus pasar ...</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688279/kkp-sebut-produk-olahan-lele-marinasi-indonesia-tembus-pasar-taiwan</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/WhatsApp-Image-2026-08-10-at-22.27.38.jpeg</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Komisi XI minta mitra SPPG dukung pembenahan tata kelola MBG</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:48:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XI DPR RI Mukhamad Misbakhun meminta mitra Satuan Pelayanan Pemenuhan Gizi (SPPG) untuk mendukung ...</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688277/komisi-xi-minta-mitra-sppg-dukung-pembenahan-tata-kelola-mbg</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/dapur-mbg-wajib-memiliki-sertifikat-laik-higiene-sanitasi-2835365.jpg</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Kemenimipas usulkan amnesti warga binaan usia produktif</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:40:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Kementerian Imigrasi dan Pemasyarakatan (Kemenimipas) mengusulkan pemberian amnesti bagi warga binaan pemasyarakatan ...</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688269/kemenimipas-usulkan-amnesti-warga-binaan-usia-produktif</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000013001.jpg</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>2 Tahun Hilang, Wanita di Sulsel Ternyata Dibunuh Sopir Travel-Dibuang ke Jurang</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:25:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Agung Pramono</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Kasus hilangnya Paramita Titania Angelica terungkap. Mita dibunuh sopir travel, Alber, yang membuang jasadnya ke jurang.</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612969/2-tahun-hilang-wanita-di-sulsel-ternyata-dibunuh-sopir-travel-dibuang-ke-jurang</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/24/gadis-asal-wajo-paramitha-titania-anggelica-alias-mita-26-sudah-4-bulan-hilang_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Area Pondok Cabe Udik Tangsel Mati Listrik Sejak Sore, PLN Ungkap Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:51:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Kelurahan Pondok Cabe Udik mengalami mati listrik sejak sore. PLN sedang perbaikan jaringan dan berupaya mengembalikan pasokan listrik secepatnya.</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612951/area-pondok-cabe-udik-tangsel-mati-listrik-sejak-sore-pln-ungkap-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/08/05/13d53a89-ea1b-48d3-8905-0df8d290609a_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Periksa Istri Bos BlueRay, KPK Dalami Bukti Transfer ke Pejabat Bea Cukai</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:22:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>KPK memeriksa Vina Purnamasari, istri bos PT BlueRay Cargo, terkait kasus korupsi di Ditjen Bea Cukai. Penyidikan melibatkan tersangka baru Gatot Heroe.</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612922/periksa-istri-bos-blueray-kpk-dalami-bukti-transfer-ke-pejabat-bea-cukai</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/plt-direktur-penyidikan-kpk-achmad-taufik-husein-di-gedung-kpk-kuningan-jakarta-kamis-3072026-1785396044650_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Gunung Picung Cianjur Kebakaran, Warga Duga karena Pembakaran Sampah</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:08:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Ikbal Slamet</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Kebakaran lahan di Gunung Picung, Cianjur, diduga akibat pembakaran sampah. Petugas kesulitan memadamkan api karena akses yang sulit.</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612914/gunung-picung-cianjur-kebakaran-warga-duga-karena-pembakaran-sampah</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kebakaran-lahan-di-gunung-picung-cianjur-1786372838563_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Kelakuan Sopir Taksi Cabuli Penumpang Berujung Mohon Ampunan</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:07:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Sopir taksi online ARA (54) ditangkap setelah mencabuli penumpang wanita di Jakarta Barat. Dia meminta ampun saat diserahkan ke polisi. Kasus ditangani PPA-PPO.</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612913/kelakuan-sopir-taksi-cabuli-penumpang-berujung-mohon-ampunan</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/17/ilustrasi-rawan-pelecehan-seksual-taksi-online_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Kebakaran Dekat Stasiun Kampung Bandan yang Ganggu Arus KRL Dipicu Bara Rokok</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:33:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Kebakaran di dekat Stasiun Kampung Bandan, Jakarta Utara, diduga akibat puntung rokok. Proses pemadaman selesai dalam 3 jam, arus KRL kini normal.</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612898/kebakaran-dekat-stasiun-kampung-bandan-yang-ganggu-arus-krl-dipicu-bara-rokok</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kebakaran-alang-alang-terjadi-di-dekat-stasiun-kampung-bandan-jakarta-utara-jakut-perjalanan-kereta-rel-listrik-krl-sempat-ter-1786354296171_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Kenneth DPRD DKI Bantu Siswa SMK Al-Irsyad Agar Kembali Belajar Tanpa Beban Biaya</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:28:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Mega Putra Ratya</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Anggota DPRD DKI Jakarta, Hardiyanto Kenneth, bantu lunasi tunggakan administrasi dan seragam siswa SMK Al-Irsyad. Ia dorong masyarakat peduli pendidikan.</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612893/kenneth-dprd-dki-bantu-siswa-smk-al-irsyad-agar-kembali-belajar-tanpa-beban-biaya</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/kenneth-dprd-dki-bantu-siswa-smk-al-irsyad-agar-kembali-belajar-tanpa-beban-biaya-1786372089822.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>K3 MPR RI Beri Rekomendasi Evaluasi Implementasi Konstitusi-Tata Kelola SDA</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:20:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>K3 MPR RI menyusun rekomendasi strategis untuk evaluasi implementasi konstitusi di bidang otonomi daerah, demokrasi ekonomi, dan pengelolaan sumber daya alam.</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612886/k3-mpr-ri-beri-rekomendasi-evaluasi-implementasi-konstitusi-tata-kelola-sda</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/mpr-ri-1786371584505_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Lestari Moerdijat Dorong Reformasi Budaya Sekolah dan Kesejahteraan Guru</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:18:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Akfa Nasrulhak</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Lestari Moerdijat menekankan pentingnya kesejahteraan guru dan tata kelola pendidikan untuk menciptakan sekolah yang aman dan nyaman bagi siswa.</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612883/lestari-moerdijat-dorong-reformasi-budaya-sekolah-dan-kesejahteraan-guru</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/28/wakil-ketua-mpr-ri-lestari-moerdijat-1761654592023_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>ASN Bandung Barat Terancam Kena PHK gegara Live TikTok Bahas Fee Proyek</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:12:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Whisnu Pradana</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Indah Yusuvia, ASN di Bandung Barat, mendapat kecaman setelah live TikTok saat jam kerja. Ia terancam PHK setelah pemeriksaan oleh Inspektorat KBB.</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612879/asn-bandung-barat-terancam-kena-phk-gegara-live-tiktok-bahas-fee-proyek</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/asn-kbb-yang-melakukan-live-tiktok-saat-jam-kerja-minta-maaf-1786272528570_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Intel Cari Modal Rp 266 Triliun demi Genjot Bisnis AI</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:43:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Intel mengumumkan penawaran saham senilai US$ 15 miliar atau Rp 266,76 triliun (kurs Rp 17.784).</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8612936/intel-cari-modal-rp-266-triliun-demi-genjot-bisnis-ai</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/09/04/intel-core-ultra-lunar-lake_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Menko Polkam Pastikan Asap Kebakaran Hutan di Indonesia Belum Ganggu Negara Tetangga</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:26:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>TribunNews.com menyajikan berita dan video terkini dari regional, nasional dan internasional dengan sudut pandang dan nilai-nilai lokal</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>https://asset-2.tribunnews.com/tribunnews/foto/bank/images/logo-tribunnews1_20160901_101844.jpg</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Poslabfor Cek DNA hingga Barang Terkait Senjata di Yayasan Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:34:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Dalam pemeriksaan tersebut, petugas menemukan 30 item.</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266639/poslabfor-cek-dna-hingga-barang-terkait-senjata-di-yayasan-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ETTDU2qEXOzAfRQOJ_Mo1H87TaE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317518/original/012310700_1786017988-Bungker.webp</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Kebakaran Dekat Stasiun Kampung Bandan Diduga Akibat Rokok, KRL Terganggu</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:25:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Kebakaran tersebut sempat mengganggu perjalanan Commuter Line relasi Tanjung Priok-Jakarta Kota.</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266638/kebakaran-dekat-stasiun-kampung-bandan-diduga-akibat-rokok-krl-terganggu</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/YWJtbokY5rHQCWY7GjDLRGPOUjo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320737/original/079815200_1786378545-IMG_4802.jpeg</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Bigmo Usai Dicecar 40 Pertanyaan: Sangat Kapok</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:07:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Bigmo juga meminta maaf atas kegaduhan yang ditimbulkan akibat livestreamingnya.</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8266634/bigmo-usai-dicecar-40-pertanyaan-sangat-kapok</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/yMyvLcWzAHymwzftNQDkQrdSxmo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320662/original/029781800_1786364749-71851.jpg</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Ruangan Bekas Simpan 995 Airsoft Gun di Sekolah Swasta Jaksel Akan Dipakai Kegiatan Belajar</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:45:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Ruangan bekas penyimpanan ratusan senjata api dan airsoft gun di sekolah swasta Kebayoran Lama sterilized. Akan dibersihkan dan dipakai KBM.</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/10/23431041/ruangan-bekas-simpan-995-airsoft-gun-di-sekolah-swasta-jaksel-akan</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/sMNCYEQLxPOgZz8Tu7fMxsETD_E=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/10/6a79cb0478fef.jpeg</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Transjakarta Akan Layani Rute Kepulauan Seribu, Apakah Pakai Bus? Ini Penjelasannya</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:45:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Transjakarta akan kelola transportasi ke Kepulauan Seribu mulai 2027. Modanya bukan bus, melainkan kapal atau angkutan perairan.</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/10/22151481/transjakarta-akan-layani-rute-kepulauan-seribu-apakah-pakai-bus-ini</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/WIiKfpR36LdiI1OwHvC6_fBUfb8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/02/06/6985ab6f6b80e.jpeg</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>Hype</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Bigmo Mengaku Tak Ada Niat Eksploitasi Anak untuk Promosikan Vape</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:45:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Kreator Bigmo diperiksa polisi atas dugaan eksploitasi anak untuk promosi vape. Ia mengakui salah dan berjanji lebih bijak. Kanal YouTube-nya dicabut monetisasinya.</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/hype/read/2026/08/10/214122666/bigmo-mengaku-tak-ada-niat-eksploitasi-anak-untuk-promosikan-vape</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/OI31En78bK8vEsBJTiUbTaGfeEg=/0x0:4000x2667/1200x675/filters:watermark(data/photo/2026/01/30/697c8191ee571.png,0,-0,1)/data/photo/2026/04/13/69dcc68baa116.jpg</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1140"/>
+  <autoFilter ref="A1:I1186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1186"/>
+  <dimension ref="A1:I1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -56181,8 +56181,478 @@
         </is>
       </c>
     </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Legislator DKI minta Pemda perkuat perlindungan siswa kurang mampu</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:58:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Anggota DPRD DKI Jakarta Hardiyanto Kenneth meminta agar pemerintah daerah (Pemda) memperkuat kebijakan ...</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688359/legislator-dki-minta-pemda-perkuat-perlindungan-siswa-kurang-mampu</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/IMG_20260810_233505.jpg</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>KBRI Tunis soroti pentingnya nilai historis, revolusioner, jelang HUT</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:57:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Kedutaan Besar Republik Indonesia di Tunis, Tunisia, menyoroti pentingnya nilai historis dan revolusioner saat memulai ...</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688355/kbri-tunis-soroti-pentingnya-nilai-historis-revolusioner-jelang-hut</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000683003.jpg</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>DPRD Sulteng desak hak 1.900 pekerja GNI terdampak PHK dipenuhi</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:56:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>DPRD Sulawesi Tengah meminta PT Gunbuster Nickel Industry (GNI) untuk memastikan pemenuhan hak sekitar 1.900 pekerja ...</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688351/dprd-sulteng-desak-hak-1900-pekerja-gni-terdampak-phk-dipenuhi</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/02/08/IMG_20230208_155148.jpg</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>MK dengarkan keterangan Polri dan KPK terkait uji materiil KUHP</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:48:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Sembilan hakim Mahkamah Konstitusi (MK) melanjutkan sidang uji materiil Undang-Undang Nomor 1 Tahun 2023 tentang KUHP ...</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5688345/mk-dengarkan-keterangan-polri-dan-kpk-terkait-uji-materiil-kuhp</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1000013002.jpg</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>KPK Temukan Kasus Pemerasan Lain Dilakukan Eks Staf KPK yang Peras Bupati</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:46:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>KPK menemukan berkas terkait dugaan pemerasan oleh mantan stafnya, Setya Budi Dias, dan ayahnya. Penyidikan berlanjut untuk mengungkap kasus lebih dalam.</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8612977/kpk-temukan-kasus-pemerasan-lain-dilakukan-eks-staf-kpk-yang-peras-bupati</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>2 Pria Ditangkap Buntut Unggahan Pidato Prabowo Soal Nuklir Iran, Gun Romli: Pemerintah Represif</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:44:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Gun Romli menegaskan, penangkapan AYP dan AF terkait unggahan pidato Prabowo soal nuklir Iran justru mencederai kebebasan berpendapat.</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866577/2-pria-ditangkap-buntut-unggahan-pidato-prabowo-soal-nuklir-iran-gun-romli-pemerintah-represif</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0iL7xMX-_zskwBZCe2XRTCl1Bzs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/prabowo-kadin-dks.jpg</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>10 Provinsi dengan PHK Terbanyak dan Terendah Januari-Juli 2026</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:14:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Sejak Januari-Juli 2026, sekitar 43.805 pekerja terkena PHK, terbanyak di Jabar, terendah di Gorontalo.</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866576/10-provinsi-dengan-phk-terbanyak-dan-terendah-januari-juli-2026</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/C4q8OaWhwWglosa5Ry9IFpBZvdM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PHK-di-Jatim565.jpg</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Pengacara Khariq Anhar: Tuntutan “Timpa Teks” Bisa Batasi Hak Sipil di Medsos</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:05:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Tuntutan enam bulan penjara terhadap Khariq dinilai berpotensi membatasi hak sipil dalam bermedia sosial dan menyampaikan kritik.</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866575/pengacara-khariq-anhar-tuntutan-timpa-teks-bisa-batasi-hak-sipil-di-medsos</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8fRftMALcqsKVRKz4f9OCapaRjA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Terdakwa-Khariq-Anhar-kuasa-hukum-usai-sidang-tuntutan-kasus-timpa-teks.jpg</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Dokter Ungkap Syarat Donor hingga Tantangan Transplantasi Ginjal di Indonesia</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:02:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Transplantasi ginjal bukan sekadar mengganti organ yang mengalami kerusakan. Prosedur ini membutuhkan rangkaian  panjang.</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7866574/dokter-ungkap-syarat-donor-hingga-tantangantransplantasi-ginjal-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7hnsWcKbwnmteHzQ26LP4-GB7CA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/psien-gagal-ginjal.jpg</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>KPK Panggil Ulang Rudy Tanoesoedibjo Selasa Besok Terkait Kasus Korupsi Bansos</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:51:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>KPK menjadwalkan ulang pemeriksaan terhadap Komisaris Utama PT DNR Logistik, Bambang Rudijanto Tanoesoedibjo alias Rudy Tanoe pada Selasa besok.</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7866573/kpk-panggil-ulang-rudy-tanoesoedibjo-selasa-besok-terkait-kasus-korupsi-bansos</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/NiicxNmUufN85Wh9ihQ-pd6jyww=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Juru-Bicara-KPK-Budi-Prasetyo-302901.jpg</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1186"/>
+  <autoFilter ref="A1:I1196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1319</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1196"/>
+  <dimension ref="A1:I1319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -56651,8 +56651,5789 @@
         </is>
       </c>
     </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Jerman Hadapi Ancaman Perang Besar, Pemerintah sedang Bersiap</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>tps</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Jerman menghadapi ancaman serangan hibrida, termasuk drone berisi bahan peledak. Menteri Dalam Negeri Dobrindt ungkap rencana serangan</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810141315-4-757954/jerman-hadapi-ancaman-perang-besar-pemerintah-sedang-bersiap</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/petugas-kepolisian-bekerja-di-dekat-pesawat-kargo-antonov-di-bandara-leipzighalle-schkeuditz-jerman-rabu-582026-setelah-sebuah-1785978083174_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Potret Amukan Topan Dolphin, Jantung Ekonomi China "Tenggelam"</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Topan Dolphin membanjiri Shanghai, China, mengganggu metro, feri, dan 943 penerbangan. Di Wenzhou, angin kencang membuat sebuah truk terguling.</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810165130-7-758026/potret-amukan-topan-dolphin-jantung-ekonomi-china-tenggelam</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/tampilan-dari-drone-memperlihatkan-sebuah-desa-yang-terendam-banjir-akibat-hujan-deras-yang-dibawa-oleh-topan-dolphin-di-kota--1786355485832_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Dapat Skor Memuaskan dari Prabowo, Ini Reaksi Bahlil</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:40:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>ven</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia merespons penilaian Presiden Prabowo tentang kinerjanya.</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810164642-4-758024/dapat-skor-memuaskan-dari-prabowo-ini-reaksi-bahlil</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/peluncuran-sepuluh-buku-karya-nyata-untuk-negeri-bahlil-lahadalia-1786099773487_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Kim Jong Un Makin Keras, Korsel Satukan Kekuatan Militer dengan AS</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Korea Selatan dan AS akan menggelar latihan militer Ulchi Freedom Shield pada Agustus 2026 untuk menghadapi ancaman dari Korea Utara.</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810202716-4-758094/kim-jong-un-makin-keras-korsel-satukan-kekuatan-militer-dengan-as</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/08/27/tentara-as-dan-korea-selatan-mengambil-bagian-dalam-latihan-penyeberangan-sungai-gabungan-as-korea-selatan-yang-merupakan-bagi-1756277261849_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Freeport Perkirakan Produksi Katoda Tembaga di 2026 Capai 400.000 Ton</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:20:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia memperkirakan produksi katoda tembaga tahun ini mencapai 400 ribu ton dari smelter Manyar dan PT Smelting.</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810143312-4-757970/freeport-perkirakan-produksi-katoda-tembaga-di-2026-capai-400000-ton</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/09/23/smelter-tembaga-pt-freeport-indonesia-di-kek-jiipe-gresik-jawa-timur-doc-pt-freeport-indonesia-6_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Pemulung Didorong Jadi Pekerja Pemilah Sampah, Begini Nasibnya</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Pemerintah akan mengubah istilah pemulung menjadi pekerja pemilah sampah dan memiliki cara kerja berstandar khusus.</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810190623-7-758079/pemulung-didorong-jadi-pekerja-pemilah-sampah-begini-nasibnya</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/seorang-warga-memilah-sampah-di-kawasan-kuburan-cina-menteng-atas-jakarta-senin-1082026-1786363568404_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Presiden Tertua Bikin Heboh, "Pelesir" ke Eropa dan Tak Pulang-Pulang</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Presiden Kamerun Paul Biya, 93 tahun, kembali jadi sorotan setelah menghabiskan waktu di Jenewa. Kritik muncul terkait kepemimpinannya dan kondisi kesehatan.</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810180324-4-758055/presiden-tertua-bikin-heboh-pelesir-ke-eropa-dan-tak-pulang-pulang</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/05/presiden-kamerun-paul-biya-reuterscharles-platiau-1775375685197_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>"Kiamat Api" Buat Negara Darurat, 18.000 Orang Dievakuasi</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Pemerintah Kanada berikan bantuan darurat untuk British Columbia akibat kebakaran hutan yang membuat 18.000 warga dievakuasi</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810141439-4-757955/kiamat-api-buat-negara-darurat-18000-orang-dievakuasi</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/05/29/asap-mengepul-dari-kebakaran-hutan-edith-lake-swf076-yang-memaksa-evakuasi-kota-terdekat-swan-hills-alberta-kanada-dalam-foto--1748521069570_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Kepala BGN Warning Keras Soal MBG-Minta Guru Turun Tangan Lakukan Ini</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono minta guru makan bersama siswa untuk edukasi gizi. Pengawasan ketat pada makanan MBG juga diterapkan demi keamanan pangan.</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810153723-4-757994/kepala-bgn-warning-keras-soal-mbg-minta-guru-turun-tangan-lakukan-ini</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/sudaryono-saat-dilantik-sebagai-kepala-badan-gizi-nasional-bgn-oleh-presiden-prabowo-subianto-di-istana-merdeka-jakarta-rabu-2-1784713821615_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Raksasa Migas Untung Besar di Tengah Perang, Trump Uring-uringan</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Lima raksasa minyak dunia meraup keuntungan US$48 miliar di kuartal II-2026. Presiden AS Donald Trump justru meradang.</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810175903-4-758054/raksasa-migas-untung-besar-di-tengah-perang-trump-uring-uringan</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/30/usa-trump-1785371156663_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>RI Bangun Pipa Gas Dumai-Sei Mangkei, Begini Progresnya</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM membeberkan progres pembangunan proyek pipa transmisi gas bumi ruas Dumai - Sei Mangkei (Dusem) Segmen 1.</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810163202-4-758020/ri-bangun-pipa-gas-dumai-sei-mangkei-begini-progresnya</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/18/wakil-menteri-energi-dan-sumber-daya-mineral-esdm-yuliot-tanjung-didampingi-direktur-jenderal-minyak-dan-gas-bumi-laode-sulaem-1773835118552_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Bersaing Ketat dengan Vietnam, RI Punya Potensi di Industri Ini</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Prospek permintaan lahan industri di Indonesia tetap besar, terutama di Jabodetabek.</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810173612-4-758043/bersaing-ketat-dengan-vietnam-ri-punya-potensi-di-industri-ini</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/09/ilustrasi-lahan-industri-dok-ist-1770623185379_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Video: Rencana Damai Trump Ditolak, Israel Tetap Bertahan di Gaza</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:40:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Rencana Damai Trump Ditolak, Israel Tetap Bertahan di Gaza</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810181435-8-758057/video-rencana-damai-trump-ditolak-israel-tetap-bertahan-di-gaza</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/rencana-damai-trump-ditolak-israel-tetap-bertahan-di-gaza-1786364865179_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Indeks Keyakinan Konsumen RI Turun, Begini Kata Menko Airlangga</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:35:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Airlangga Hartanto buka suara soal data Indeks Keyakinan Konsumen (IKK) yang melandai pada Juli 2026.</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810183207-4-758070/indeks-keyakinan-konsumen-ri-turun-begini-kata-menko-airlangga</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/menko-pereknomian-airlangga-hartarto-saat-acara-peringatan-hut-ke-49-pasar-modal-indonesia-dan-peluncuran-produk-etf-emas-seni-1786330817178_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Mendagri: Inflasi Juli 2,88% Masih dalam Rentang Ideal</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:32:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian apresiasi inflasi Juli 2026 yang tercatat 2,88%. Ia minta daerah waspada terhadap inflasi di atas 3,5%</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810192750-4-758081/mendagri-inflasi-juli-288-masih-dalam-rentang-ideal</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/dok-kementerian-dalam-negeri-1786365111260_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Video: Iran Tunda Dialog Dengan As, Tunggu Kesepakatan Dipatuhi</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:30:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Iran Tunda Dialog Dengan As, Tunggu Kesepakatan Dipatuhi</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810181800-8-758059/video-iran-tunda-dialog-dengan-as-tunggu-kesepakatan-dipatuhi</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/iran-tunda-dialog-dengan-as-tunggu-kesepakatan-dipatuhi-1786364583737_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Video: Sampah Jadi Energi Pekerja Informal Dapat Perlindungan</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:20:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Sampah Jadi Energi Pekerja Informal Dapat Perlindungan</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810175820-8-758053/video-sampah-jadi-energi-pekerja-informal-dapat-perlindungan</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/sampah-jadi-energi-pekerja-informal-dapat-perlindungan-1786363502263_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Gelar Kerajaan Menantu Sultan Brunei Mendadak Dicabut, Ini Sosoknya</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Sultan Brunei Hassanal Bolkiah mencabut gelar kerajaan menantunya, Pengiran Raabi'atul Adawiyyah, karena dinilai berperilaku tidak pantas dan mencoreng monarki.</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810174135-7-758044/gelar-kerajaan-menantu-sultan-brunei-mendadak-dicabut-ini-sosoknya</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/dayangku-raabiatul-adawiyyah-pengiran-haji-bolkiah-dari-brunei-meninggalkan-pesta-pernikahan-kerajaan-setelah-menikah-dengan-p-1786358489186_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Lampung Financial Festival Siap Digelar! Pendaftaran Mulai 18 Agustus</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:16:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Lampung Financial Festival 2026 akan digelar pada 5-6 September. Acara ini bertujuan meningkatkan literasi keuangan dengan berbagai kegiatan menarik.</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810190737-4-758080/lampung-financial-festival-siap-digelar-pendaftaran-mulai-18-agustus</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/lampung-financial-festival-1785750638550_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Cek Rekening! Gaji PNS dan PPPK 546 Daerah Sudah Ditransfer 18,9 T</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:15:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Pemerintah telah mencairkan dana senilai Rp18,9 triliun untuk 546 pemerintah daerah.</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810181241-4-758056/cek-rekening-gaji-pns-pppk-546-daerah-sudah-ditransfer-189-t</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/01/menteri-dalam-negeri-mendagri-tito-karnavian-dalam-pembangunan-rumah-hunian-danantara-aceh-tamiang-kamis-112026-1767252548883_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>BEI Catat Jumlah Investor Tembus 30,2 Juta di Tengah Tekanan Global</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:10:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>BEI Catat Jumlah Investor Tembus 30,2 Juta di Tengah Tekanan Global</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810175349-8-758052/bei-catat-jumlah-investor-tembus-302-juta-di-tengah-tekanan-global</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/bei-catat-jumlah-investor-tembus-302-juta-di-tengah-tekanan-global-1786363460308_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Imbas Longsor, Tambang GBC Freeport Baru Bisa 100% Akhir 2027</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:10:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia targetkan tambang GBC beroperasi penuh pada akhir 2027.</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810151057-4-757993/imbas-longsor-tambang-gbc-freeport-baru-bisa-100-akhir-2027</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/09/17/situasi-terkini-penyelamatan-7-karyawan-di-tambang-bawah-tanah-grasberg-block-cave-freeport-indonesia-dok-ptfi-1758079241842_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Pemerintah Kaji Insentif Dampak El Nino Terhadap Produksi Pangan RI</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:05:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Chandra Dwi Pranata</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Kebutuhan untuk mitigasi dampak El Nino sedang dihitung oleh Kementerian Pertanian.</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810134911-4-757948/pemerintah-kaji-insentif-dampak-el-nino-terhadap-produksi-pangan-ri</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/29/menteri-koordinator-bidang-perekonomian-airlangga-hartarto-memberi-sambutan-dalam-acara-festival-kemudahan-dan-pelindungan-usa-1782714647064_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Penampakan "TPA" Senilai Rp1,28 T Sulap 2.500 Ton Sampah Jadi Energi</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>RDF Rorotan seluas 7,87 hektare mampu mengolah 2.500 ton sampah per hari dari 16 kecamatan, membantu mengurangi beban TPST Bantargebang.</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810143900-7-757975/penampakan-tpa-senilai-rp128-t-sulap-2500-ton-sampah-jadi-energi</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/sejumlah-pekerja-beraktivitas-di-kawasan-rdf-rorotan-jakarta-senin-1082026-1786347532004_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Desain Pengembangan LTJ, Bahlil: Ke Depannya Diolah di Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:45:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>ven</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM siapkan desain pengelolaan Logam Tanah Jarang di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810160250-4-758004/desain-pengembangan-ltj-bahlil-ke-depannya-diolah-di-dalam-negeri</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/08/23/logam-tanah-jarang-6_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Freeport Bakal Mulai Produksikan Tambang Bawah Tanah Baru di 2029</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:30:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia telah berinvestasi US$ 1,4 miliar untuk mengembangkan proyek tambang Kucing Liar di Grasberg, Papua Tengah.</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810132137-4-757938/freeport-bakal-mulai-produksikan-tambang-bawah-tanah-baru-di-2029</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/presiden-direktur-pt-freeport-indonesia-ptfi-tony-wenas-1786101675207_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Bidik Pasar Properti Australia, Pengusaha RI Ini Beberkan Alasannya</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:25:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Ferry Sandi</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Pengusaha Indonesia Chandra Leonardi membangun properti di Sydney, memanfaatkan permintaan global. Proyek Roselands menghadapi tantangan perizinan ketat.</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810164721-4-758025/bidik-pasar-properti-australia-pengusaha-ri-ini-beberkan-alasannya</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/ceo-cvig-chandra-leonardi-saat-ditemui-di-kawasan-gunawarman-jakarta-selatan-senin-1082026-1786346889727_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Kepala BGN Minta Maaf-Ngaku Bakal Pecat-pecatin Orang, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono menegaskan komitmen untuk memecat pegawai yang tidak berintegritas dalam program MBG demi keamanan pangan penerima manfaat.</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810164213-4-758023/kepala-bgn-minta-maaf-ngaku-bakal-pecat-pecatin-orang-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/kepala-badan-gizi-nasional-bgn-sudaryono-saat-ditemui-di-kantor-pusat-bgn-jakarta-rabu-2272026-1784722137132_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Video: Puluhan Ribu Lulusan Koperasi Desa Siap Diterjunkan</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Puluhan Ribu Lulusan Koperasi Desa Siap Diterjunkan</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810174426-8-758045/video-puluhan-ribu-lulusan-koperasi-desa-siap-diterjunkan</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/puluhan-ribu-lulusan-koperasi-desa-siap-diterjunkan-1786359066062_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Pengusaha Properti Asal RI Pilih Investasi di Australia, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Ferry Sandi</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Capital Value International Group mengembangkan proyek perumahan di Sydney, Australia, untuk memenuhi permintaan global di tengah kekurangan pasokan hunian.</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810142537-4-757964/pengusaha-properti-asal-ri-pilih-investasi-di-australia-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/ceo-cvig-chandra-leonardi-saat-ditemui-di-kawasan-gunawarman-jakarta-selatan-senin-1082026-1786346889727_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Anwar Ibrahim Dirawat di Rumah Sakit - Kontrakan Wajib Bayar Pajak</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>Anwar Ibrahim Dirawat di Rumah Sakit - Kontrakan Wajib Bayar Pajak</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810142208-8-757999/anwar-ibrahim-dirawat-di-rumah-sakit--kontrakan-wajib-bayar-pajak</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/anwar-ibrahim-dirawat-di-rumah-sakit-kontrakan-wajib-bayar-pajak-1786357084521_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Neraca Transaksi Berjalan Jepang Defisit, Pertama dalam 17 Bulan</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Jepang mencatat defisit transaksi berjalan pertama dalam 17 bulan, dipicu oleh lonjakan biaya impor minyak dan pembayaran dividen ke investor asing.</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810140930-4-757953/neraca-transaksi-berjalan-jepang-defisit-pertama-dalam-17-bulan</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/05/28/bendera-jepang-dok-freepik-1748397768360_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Perkuat Layanan Pertanahan, Mendagri dan Menteri ATR Teken SEB</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:15:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian dan Menteri ATR/BPN Nusron Wahid tandatangani SEB untuk integrasi data BPHTB. Tujuannya, tingkatkan layanan dan pendapatan daerah.</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810171134-4-758041/perkuat-layanan-pertanahan-mendagri-dan-menteri-atr-teken-seb</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/dok-kementerian-dalam-negeri-1786356941732_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Kinerja LPS 2025: Jaga Kepercayaan dan Dukung Stabilitas Keuangan</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:06:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Edward Ricardo</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Lembaga Penjamin Simpanan (LPS) berhasil menjamin simpanan nasabah dan menjaga stabilitas sistem keuangan dengan menangani bank bermasalah.</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810170241-16-758038/kinerja-lps-2025-jaga-kepercayaan-dukung-stabilitas-keuangan</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/infografis-kinerja-lps-2025-jaga-kepercayaan-dukung-stabilitas-keuangan-1786356041157_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Smelter ke-2 Freeport di Gresik Akan Beroperasi Lagi di September 2026</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:05:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia menargetkan smelter Manyar di Gresik berproduksi kembali pada September 2026, setelah terhenti akibat longsor.</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810134333-4-757943/smelter-ke-2-freeport-di-gresik-akan-beroperasi-lagi-di-september-2026</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/09/23/smelter-tembaga-pt-freeport-indonesia-di-kek-jiipe-gresik-jawa-timur-doc-pt-freeport-indonesia-7_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Airlangga Sebut Program Magang Nasional Bisa Jadi Game Changer Ekonomi</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>chd</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>Program Magang Nasional 2026 resmi diluncurkan untuk 150.000 lulusan baru. Diharapkan meningkatkan daya saing dan kesiapan generasi muda di pasar kerja.</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810162036-4-758019/airlangga-sebut-program-magang-nasional-bisa-jadi-game-changer-ekonomi</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/aimenteri-koordinator-bidang-perekonomian-airlangga-hartarto-pada-konferensi-pers-di-jakarta-rabu-582026-1785971442706_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Tangis Petani Padi, Sawah Kering Retak-Retak Paksa Panen Lebih Cepat</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:53:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>Di tengah kemarau, petani memilih memanen lebih awal. Bukan karena hasilnya sudah maksimal, tapi tak ingin seluruh tanamannya mati sebelum sempat dipanen.</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810153752-7-758006/tangis-petani-padi-sawah-kering-retak-retak-paksa-panen-lebih-cepat</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/seorang-petani-memanen-padi-di-desa-kali-putih-bogor-jawa-barat-senin-1082026-lahan-pertanian-seluas-puluhan-hektar-yang-dikel-1786351382797_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Mojtaba Khamenei akan Segera Muncul di Depan Publik Iran</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>tps</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Pemerintah Iran akan merilis video pemimpin baru, Mojtaba Khamenei, untuk menepis rumor kesehatan.</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810141536-4-757956/mojtaba-khamenei-akan-segera-muncul-di-depan-publik-iran</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/13/pemimpin-tertinggi-iran-yang-baru-mojtaba-khamenei-putra-kedua-dari-mendiang-pemimpin-tertinggi-iran-ayatollah-ali-khamenei-me-1773402251806_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>MagangHub 2026 Transmedia, 280 Peserta Siap Berkontribusi!</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:42:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Elga Nurmutia</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>Transmedia resmi meluncurkan program MagangHub 2026 dengan 280 peserta. Acara ini bertujuan memberikan pengalaman kerja dan peluang karir di industri media.</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810160825-4-758021/maganghub-2026-transmedia-280-peserta-siap-berkontribusi</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/onboarding-program-maganghub-2026-1786354639483_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>PM Malaysia Anwar Ibrahim Jalani Operasi Hernia, Ini Kondisi Barunya</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Perdana Menteri Malaysia Anwar Ibrahim menjalani operasi laparoskopi untuk hernia. Prosedur berjalan lancar, kini dalam pemulihan dan fisioterapi.</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810153033-4-757991/pm-malaysia-anwar-ibrahim-jalani-operasi-hernia-ini-kondisi-barunya</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/24/perdana-menteri-malaysia-anwar-ibrahim-menelfon-presiden-prabowo-subianto-bersilaturahmi-melalui-sambungan-telepon-dengan-para-1774326678850_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Bos Freeport Buka-bukaan Progres Pengembangan Tambang Bawah Tanah Baru</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:20:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia mengembangkan proyek tambang bawah tanah Kucing Liar di Grasberg, Papua Tengah, dengan investasi US$ 1,4 miliar.</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810123425-4-757916/bos-freeport-buka-bukaan-progres-pengembangan-tambang-bawah-tanah-baru</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/presiden-direktur-pt-freeport-indonesia-ptfi-tony-wenas-1786101675056_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Video: Turki Perketat Ruang Digital hingga PM Kosovo Dilempar Telur</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:00:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Turki Perketat Ruang Digital hingga PM Kosovo Dilempar Telur</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810124911-8-757921/video-turki-perketat-ruang-digital-hingga-pm-kosovo-dilempar-telur</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/turki-perketat-ruang-digital-hingga-pm-kosovo-dilempar-telur-1786346518373_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Prabowo Siapkan Calon Deputi Gubernur Senior-Deputi BI, Ini Bocorannya</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:00:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengusulkan Deputi Gubernur Senior dan Deputi BI.</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810155002-4-757998/prabowo-siapkan-calon-deputi-gubernur-senior-deputi-bi-ini-bocorannya</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/mensesneg-prasetyo-hadi-usai-menyerahkan-supres-calon-gubernur-bi-komisoner-ojk-dan-calon-dubes-cnbc-indonesiaemir-yanwardhana-1786341467218_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Ini Dia Daftar Mobil Favorit GIIAS 2026, Ada All New Mazda CX-5</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Ferry Sandi</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>GIIAS 2026 di Tangerang menampilkan mobil baru dan penghargaan untuk kendaraan favorit. Mazda, Kia, dan Toyota meraih penghargaan di berbagai kategori.</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810123914-4-757917/ini-dia-daftar-mobil-favorit-giias-2026-ada-all-new-mazda-cx-5</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/all-new-mazda-cx-5-ditampilkan-dalam-acara-giias-2026-di-ice-bsd-kabupaten-tangerang-banten-rabu-2972026-1785298153031_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Kabar Baik! Bos DJP Bakal Bebaskan Pajak ETF Emas</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:35:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>DJP Kemenkeu akan berikan insentif pajak untuk ETF berbasis emas, membebaskan PPh 22 dan PPN. Peluncuran ini dukung pendalaman pasar keuangan Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810143402-4-757971/kabar-baik-bos-djp-bakal-bebaskan-pajak-etf-emas</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/11/18/direktur-jenderal-pajak-bimo-wijayanto-dalam-program-cnbc-indonesia-squawk-box-di-jakarta-selasa-18112025-1763433909729_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Arab Saudi, Turki, dan Pakistan Bentuk "NATO Islam"</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:15:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Arab Saudi, Turki, dan Pakistan Bentuk Perjanjian Pertahanan Bersama Mekah</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810092433-8-757835/arab-saudi-turki-dan-pakistan-bentuk-nato-islam</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/arab-saudi-turki-dan-pakistan-bentuk-nato-islam-1786345043372_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Penjualan LCGC Nyungsep, Mobil Jenis Ini Lagi Naik Daun</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:15:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Peta pasar mobil Indonesia berubah, dengan penjualan SUV meningkat 15,9% di 2026. LCGC mengalami penurunan. SUV boxy semakin diminati konsumen.</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810125324-4-757925/penjualan-lcgc-nyungsep-mobil-jenis-ini-lagi-naik-daun</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/05/pt-chery-sales-indonesia-csi-resmi-memperkenalkan-suv-elektrifikasi-terbarunya-chery-c5-csh-dalam-acara-iims-2026-di-jiexpo-ke-1770289170060_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>BPS Kasih Penjelasan Harga Terkini Beras, Minyak Goreng-Bawang Putih</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Martyasari Rizky</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>BPS melaporkan harga pangan Agustus 2026, beras dan minyak goreng masih tinggi, sementara bawang putih menunjukkan penurunan. Perhatikan perkembangan ini!</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810125112-4-757923/bps-kasih-penjelasan-harga-terkini-beras-minyak-goreng-bawang-putih</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/16/pekerja-mengupas-bawang-putih-di-pasar-induk-kramat-jati-jakarta-kamis-1672026-badan-pusat-statistik-bps-mencatat-indonesia-ma-1784193464706_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Video: Keyakinan Konsumen Melemah di Juli 2026</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:04:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>Keyakinan Konsumen Melemah di Juli 2026</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810092530-8-757836/video-keyakinan-konsumen-melemah-di-juli-2026</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/keyakinan-konsumen-melemah-di-juli-2026-1786344967242_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Buat "NATO versi Islam", 3 Pemimpin Ini Kompak Salat Jamaah di Mekkah</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>MBS, Erdogan dan PM Pakistan melakukan salat bersama. Ketiganya bertemu, menyepakati fakta keamanan yang disebut pengamat "NATO Islam"</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810101246-7-757855/buat-nato-versi-islam-3-pemimpin-ini-kompak-salat-jamaah-di-mekkah</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/mulia-putra-mahkota-mohammed-bin-salman-bersama-para-pemimpin-turki-dan-pakistan-menghadiri-shalat-jumat-di-masjid-al-haram-di-1786319777403_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Menhut Bilang Modifikasi Cuaca Tak Bisa Dilakukan di Bromo, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan Raja Juli Antoni menyatakan operasi modifikasi cuaca untuk mengatasi kebakaran di Gunung Bromo belum dapat dilakukan dalam 10 hari ke depan.</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810134441-4-757944/menhut-bilang-modifikasi-cuaca-tak-bisa-dilakukan-di-bromo-ada-apa</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/tim-gabungan-melakukan-pemadaman-darat-menggunakan-gepyok-dan-sprayer-di-kecamatan-sukapura-kabupaten-probolinggo-jawa-timur-r-1785987909449_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Video: Kebakaran Gunung Bromo Meluas, Kawasan Wisata Ditutup Total</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:45:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Kebakaran Gunung Bromo Meluas, Kawasan Wisata Ditutup Total</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810124816-8-757920/video-kebakaran-gunung-bromo-meluas-kawasan-wisata-ditutup-total</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/kebakaran-gunung-bromo-meluas-kawasan-wisata-ditutup-total-1786344894843_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Bos Freeport Blak-blakan Alasan Sudah Ajukan Perpanjangan IUPK</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:40:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>ven</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia mengajukan perpanjangan IUPK ke Kementerian ESDM. IUPK Freeport akan berakhir pada 2041.</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810120359-4-757899/bos-freeport-blak-blakan-alasan-sudah-ajukan-perpanjangan-iupk</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/tony-wenas-presiden-direktur-pt-freeport-indonesia-1785306971048_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Video: RI Butuh Rp 8.705 T Untuk Pembangunan 2027</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>RI Butuh Rp 8.705 T Untuk Pembangunan 2027</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810124732-8-757919/video-ri-butuh-rp-8705-t-untuk-pembangunan-2027</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/ri-butuh-rp-8705-t-untuk-pembangunan-2027-1786344805179_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Muncul Semburan Lumpur di Blora, Badan Geologi RI Warning Ini</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:30:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Badan Geologi ESDM peringatkan masyarakat tentang semburan lumpur di Oro-oro Kesongo, Blora.</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810115533-4-757896/muncul-semburan-lumpur-di-blora-badan-geologi-ri-warning-ini</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/oro-oro-kesongo-blora-1786106075716_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Militer Israel Tiba-Tiba Tutup Akses Desa Kristen Palestina, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:25:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Militer Israel menutup akses ke desa Taybeh di Tepi Barat untuk non-penduduk, sebagai langkah mencegah serangan pemukim Israel terhadap warga Palestina.</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810142208-4-757963/militer-israel-tiba-tiba-tutup-akses-desa-kristen-palestina-ada-apa</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/11/23/tentara-israel-mengambil-bagian-dalam-penggerebekan-di-kamp-pengungsi-balata-di-nablus-di-tengah-konflik-yang-sedang-berlangsu_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Pemerintah Siapkan Anggaran Tambahan Rp 20 T Untuk Belanja Pegawai</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:00:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Pemerintah Siapkan Anggaran Tambahan Rp 20 Triliun Untuk Belanja Pegawai</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810100420-8-757850/pemerintah-siapkan-anggaran-tambahan-rp-20-t-untuk-belanja-pegawai</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/pemerintah-siapkan-anggaran-tambahan-rp-20-triliun-untuk-belanja-pegawai-1786343743749_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Eks Presiden AS Derita Kanker Prostat, Kondisinya Memburuk</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:00:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Kesehatan mantan Presiden AS Joe Biden memburuk akibat kanker prostat yang menyebar. Putranya, Hunter, mengungkapkan rasa sakit yang dialami Biden.</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810134844-4-757946/eks-presiden-as-derita-kanker-prostat-kondisinya-memburuk</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/12/05/presiden-amerika-serikat-as-joe-biden-tampaknya-sedang-mengistirahatkan-matanya-saat-pertemuan-di-angola-reuters-2_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Purbaya Bakal Terbitkan Surat Utang Syariah Besok, Cari Dana Rp 10 T</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:55:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Pemerintah berencana melelang delapan seri surat berharga syariah negara (SBSN) alias sukuk negara pada esok hari</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810120636-4-757901/purbaya-bakal-terbitkan-surat-utang-syariah-besok-cari-dana-rp-10-t</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/01/10/suasana-gedung-kementerian-keuangan-kemenkeu-di-jakarta-rabu-1012024-9_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Video: 17 Agustus, Naik Transportasi Umum di Jakarta Hanya Rp 1</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:50:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>17 Agustus, Naik Transportasi Umum di Jakarta Hanya Rp 1</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810100421-8-757851/video-17-agustus-naik-transportasi-umum-di-jakarta-hanya-rp-1</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/17-agustus-naik-transportasi-umum-di-jakarta-hanya-rp-1-1786343774390_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Mensesneg Klaim Belum Ada Rencana Presiden Prabowo Reshuffle Kabinet</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:47:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo menegaskan tidak ada rencana reshuffle kabinet dalam waktu dekat, fokus pada pengisian jabatan kosong.</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810134121-4-757942/mensesneg-klaim-belum-ada-rencana-presiden-prabowo-reshuffle-kabinet</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/mensesneg-prasetyo-hadi-usai-menyerahkan-supres-calon-gubernur-bi-komisoner-ojk-dan-calon-dubes-cnbc-indonesiaemir-yanwardhana-1786341467218_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Kebakaran Taman Nasional Gunung Bromo Meluas, Ini Arahan Mensesneg</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:31:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Emir Yanwardhana</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>El Nino memicu kebakaran hutan di Taman Nasional Bromo Tengger Semeru. Pemerintah berkoordinasi untuk pemadaman dan imbau masyarakat waspada terhadap kebakaran.</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810132748-4-757940/kebakaran-taman-nasional-gunung-bromo-meluas-ini-arahan-mensesneg</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/mensesneg-prasetyo-hadi-usai-menyerahkan-supres-calon-gubernur-bi-komisoner-ojk-dan-calon-dubes-cnbc-indonesiaemir-yanwardhana-1786341467218_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Penembakan Guncang Kantor Pemda, Pelaku Diduga Mantan Anggota Dewan</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:27:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>luc</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Seorang pria bersenjata ditangkap setelah menembaki pejabat di Bangkok, hanya beberapa hari setelah penembakan massal di sekolah.</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810132404-4-757939/penembakan-guncang-kantor-pemda-pelaku-diduga-mantan-anggota-dewan</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/04/25/ilustrasiistockphotougurhan_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Kata-Kata Kepala BPS Sorot Harga Daging Sapi Ngamuk-Ada yang Rp200.000</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Harga daging sapi di Indonesia mencapai Rp143.737/kg pada Agustus 2026, melampaui HAP. BPS mencatat kenaikan harga di 56 kabupaten/kota.</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810121355-4-757910/kata-kata-kepala-bps-sorot-harga-daging-sapi-ngamuk-ada-yang-rp200000</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/03/13/warga-membeli-daging-sapi-di-pasar-senen-jakarta-rabu-1332024-memasuki-bulan-ramadan-harga-daging-sapi-di-pasar-senen-tembus-m-11_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Haji Isam Merapat ke Kantor Seskab Teddy, Bahas Investasi di Indonesia</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:12:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Tim Redaksi</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya bertemu pengusaha Haji Isam untuk membahas investasi di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810131024-4-757933/haji-isam-merapat-ke-kantor-seskab-teddy-bahas-investasi-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/sekretaris-kabinet-teddy-indra-wijaya-menerima-kedatangan-pengusaha-nasional-andi-syamsuddin-arsyad-yang-dikenal-dengan-sapaan-1786342139806_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>2 Pesawat Nyaris Tabrakan Keras di Bandara</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:09:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Dua pesawat, Jetstar dan Qatar Airways, nyaris bertabrakan di Bandara Sydney. Insiden ini sedang diselidiki setelah seorang awak mengalami cedera.</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810124712-4-757924/2-pesawat-nyaris-tabrakan-keras-di-bandara</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/01/18/qantas-3_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Demutualisasi BEI, Danantara Bakal Ikut Beli Saham?</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Demutualisasi Bursa Efek Indonesia (BEI) hampir rampung.</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810113128-4-757881/demutualisasi-bei-danantara-bakal-ikut-beli-saham</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/30/danantara-indonesia-cnbc-indonesiamuhammad-sabki-1751266532184_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Harga Daging Ayam Belum Terkendali-Ada yang Rp100.000, BPS-KSP Warning</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Harga daging ayam ras mengalami kenaikan di 188 kabupaten/kota, dengan tekanan harga tertinggi mencapai Rp100.000/kg.</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810113636-4-757885/harga-daging-ayam-belum-terkendali-ada-yang-rp100000-bps-ksp-warning</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/02/pantauan-harga-komoditas-pangan-di-pasar-rumput-jakarta-selatan-senin-222026-1770003849508_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Terbongkar! Ini Biang Kerok Rusak Rem Bus, Bikin Kecelakaan-Bawa Maut</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Ferry Sandi</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Rentetan kecelakaan bus di Indonesia soroti keselamatan transportasi. Proses pembangunan bodi dan digitalisasi pemeriksaan jadi kunci kelayakan kendaraan.</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810103841-4-757871/terbongkar-ini-biang-kerok-rusak-rem-bus-bikin-kecelakaan-bawa-maut</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/body-maker-department-head-hmsi-heri-komala-tengah-saat-memberikan-keterangan-di-momen-giias-2026-cnbc-indonesiaferry-sandi-1786335668411_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Survei BI: Sarjana RI Mulai Pede Banyak Lapangan Kerja 6 Bulan Lagi</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:25:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Indeks Ekspektasi Konsumen (IEK) terhadap kondisi ekonomi enam bulan ke depan merosot pada Juli 2026</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810113824-4-757887/survei-bi-sarjana-ri-mulai-pede-banyak-lapangan-kerja-6-bulan-lagi</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/11/06/b6d4e9d8-0d54-4462-8690-f0ca7fae5848_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Video: RI Deindustrialisasi? Ini Faktanya</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:20:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Di tengah kabar deindustrialisasi Indonesia, industri pengolahan Indonesia tetap alami pertumbuhan.</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810092211-8-757832/video-ri-deindustrialisasi-ini-faktanya</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/ri-deindustrialisasi-ini-faktanya-1786334508425_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Potret Tanah Longsor di Nagano Jepang, 390 Orang Terisolasi</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:11:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Longsor melanda Prefektur Nagano, Jepang, dan sempat membuat sekitar 390 orang terisolasi.</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810120436-7-757903/potret-tanah-longsor-di-nagano-jepang-390-orang-terisolasi</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/lokasi-tanah-longsor-menghalangi-jalan-menuju-jalur-pendakian-di-kota-azumino-prefektur-nagano-pada-hari-minggu-982026-tangkap-1786337563835_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>ETF Buka Jalan Investasi Asuransi di Aset Emas</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:05:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Robertus Andrianto</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Menteri Airlangga Hartarto meluncurkan ETF Emas, memungkinkan asuransi berinvestasi di emas. Ini memperkaya pilihan investasi dan meningkatkan likuiditas.</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810112214-4-757880/etf-buka-jalan-investasi-asuransi-di-aset-emas</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/menko-pereknomian-airlangga-hartarto-saat-acara-peringatan-hut-ke-49-pasar-modal-indonesia-dan-peluncuran-produk-etf-emas-seni-1786330817178_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Mobil Listrik China Murah Makin Marak, LCGC Masih Punya Masa Depan?</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:00:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Pasar mobil murah di Indonesia menghadapi tantangan baru dengan munculnya merek China. Namun, LCGC tetap diminati, terutama oleh pembeli pertama.</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810101740-4-757862/mobil-listrik-china-murah-makin-marak-lcgc-masih-punya-masa-depan</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/01/pengunjung-melihat-wuling-aira-ev-dalam-ajang-pameran-gaikindo-indonesia-international-auto-show-giias-2026-yang-berlangsung-d-1785582477926_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Video: Iran Ungkap Nasib Blokade Hormuz - Petani Sawit RI Menangis</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:00:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Iran Ungkap Nasib Blokade Selat Hormuz-Petani Kelapa Sawit RI Menangis</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810100418-8-757849/video-iran-ungkap-nasib-blokade-hormuz--petani-sawit-ri-menangis</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/iran-ungkap-nasib-blokade-selat-hormuz-petani-kelapa-sawit-ri-menangis-1786337599140_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>RI Bersiap Punya Pabrik Baterai Terbesar, Ini Profilnya</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:55:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Firda Dwi Muliawati</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Indonesia segera miliki pabrik baterai kendaraan listrik besar di Karawang.</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810101201-4-757852/ri-bersiap-punya-pabrik-baterai-terbesar-ini-profilnya</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/29/presiden-prabowo-meresmikan-site-esdm-1751194370108_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Bambang Patijaya Dukung Bahlil: Daerah Jangan Jadi Penonton Hilirisasi</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:54:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XII DPR RI, Bambang Patijaya, mendukung hilirisasi sumber daya alam untuk kedaulatan ekonomi Indonesia. Fokus pada manfaat bagi rakyat dan daerah.</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810115250-4-757893/bambang-patijaya-dukung-bahlil-daerah-jangan-jadi-penonton-hilirisasi</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/03/ketua-komisi-xii-dpr-ri-bambang-patijaya-menyampaikan-pemaparan-dalam-acara-esg-sutainability-forum-2026-di-jakarta-selasa-322-1770095889400_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Update Terbaru Pengusutan Korupsi MBG, Kejagung Panggil 16 Orang Saksi</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:52:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung memanggil 16 saksi dalam kasus dugaan korupsi program Makan Bergizi Gratis (MBG) di Badan Gizi Nasional. Tujuh tersangka telah ditetapkan.</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810114728-4-757891/update-terbaru-pengusutan-korupsi-mbg-kejagung-panggil-16-orang-saksi</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/09/aksi-unjuk-rasa-ikatan-mahasiswa-nusantara-di-kawasan-kebon-sirih-tepatnya-di-depan-gedung-badan-gizi-nasional-jakarta-kamis-9-1775735851939_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Sudaryono Bakal Wajibkan SPPG Tempel Label Batas Waktu Konsumsi MBG</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional memperketat pengawasan Program Makan Bergizi Gratis di sekolah.</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810105027-4-757875/sudaryono-bakal-wajibkan-sppg-tempel-label-batas-waktu-konsumsi-mbg</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/05/makan-bergizi-gratis-mbg-cnbc-indonesiafiasal-rahman-1775372467831_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>PM Malaysia Anwar Ibrahim Dirawat di Rumah Sakit, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Perdana Menteri Malaysia Anwar Ibrahim dirawat di rumah sakit untuk pemeriksaan medis. Masyarakat diminta mendoakan kesehatan dan kelancaran prosedur medisnya.</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810104942-4-757873/pm-malaysia-anwar-ibrahim-dirawat-di-rumah-sakit-ada-apa</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/24/perdana-menteri-malaysia-anwar-ibrahim-menelfon-presiden-prabowo-subianto-bersilaturahmi-melalui-sambungan-telepon-dengan-para-1774326678850_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Video: Cara Rumah Sakit Incar Pasien Yang Suka Berobat ke Luar Negeri</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:27:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Incar Pasien Yang Suka Berobat ke Luar Negeri, JWCC Andalkan Layanan Kesehatan Ini</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807154702-8-757469/video-cara-rumah-sakit-incar-pasien-yang-suka-berobat-ke-luar-negeri</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/cara-rs-manfaatkan-teknologi-ai-demi-beri-layanan-kesehatan-terbaik-bagi-pasien-kelas-atas-1786335461655_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Kondisi Keuangan Terkini Warga RI: Tabungan Turun, Cicilan Naik</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:25:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Data hasil Survei Konsumen BI terbaru menunjukkan, proporsi pendapatan konsumen yang digunakan untuk menabung dan konsumsi turun</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810104956-4-757874/kondisi-keuangan-terkini-warga-ri-tabungan-turun-cicilan-naik</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/02/02/infografis-simulasi-perhitungan-ter-pajak-untuk-pekerja-gaji-rp10-juta_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Penuhi Kebutuhan Industri, Pertamina Genjot Produksi Gas Pangkah</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:24:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Pertamina optimalkan Wilayah Kerja Pangkah di Gresik untuk meningkatkan produksi migas. Fokus pada kontinuitas pasokan energi bagi industri Jawa Timur.</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810111904-4-757879/penuhi-kebutuhan-industri-pertamina-genjot-produksi-gas-pangkah</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/pertamina-1786335816158_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Tarif Listrik Terbaru PLN per kWh, Berlaku Hingga September 2026</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:20:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Firda Dwi Muliawati</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM mempertahankan tarif listrik PLN untuk kuartal III-2026 guna menjaga stabilitas ekonomi dan daya beli masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810101545-4-757861/tarif-listrik-terbaru-pln-per-kwh-berlaku-hingga-september-2026</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/13/pln-umumkan-tarif-listrik-juli-september-2026-tidak-naik-dok-instagram-plnid-1783931159944_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Tebang Pohon Untuk Videotron, Pemilik Padel Kena Sanksi Rp 100 Juta</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:09:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Pemilik lapangan padel Sixnine di Bandung, Jawa Barat, dijatuhkan sanksi sebesar 100 juta rupiah, wajib menanam seribu pohon.</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810092830-8-757838/tebang-pohon-untuk-videotron-pemilik-padel-kena-sanksi-rp-100-juta</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/tebang-pohon-untuk-videotron-pemilik-padel-kena-sanksi-rp-100-juta-1786333802033_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>DJP Buka Suara Soal Pajak Rumah Kontrakan: Bukan Pungutan Baru!</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:08:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Robertus Andrianto</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>DJP menegaskan penghasilan dari penyewaan properti bukan objek pajak baru.</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810105829-4-757876/djp-buka-suara-soal-pajak-rumah-kontrakan-bukan-pungutan-baru</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/direktur-penyuluhan-pelayanan-dan-hubungan-masyarakat-djp-inge-diana-rismawanti-dalam-media-briefing-di-djp-selasa-3062026-1782800874019_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Potret Ngeri Kebakaran Gunung Bromo, Meluas 520 H-Wisata Ditutup</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Taman Nasional Gunung Bromo kini ditutup untuk wisatawan. Potret terkini api dirilis Reuters sebagaimana dikutip Senin (10/8/2026).</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810083350-7-757804/potret-ngeri-kebakaran-gunung-bromo-meluas-520-h-wisata-ditutup</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/seseorang-mengamati-kobaran-api-saat-kebakaran-hutan-di-lereng-bukit-di-taman-nasional-bromo-tengger-semeru-di-probolinggo-pro-1786331440467_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Badan Geologi RI Buka-bukaan Penyebab Semburan Lumpur di Blora</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:58:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Badan Geologi ESDM menjelaskan fenomena semburan lumpur di Oro-oro Kesongo, Blora. Mereka masih mengumpulkan data untuk memetakan risiko dan dampak lingkungan.</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810103106-4-757868/badan-geologi-ri-buka-bukaan-penyebab-semburan-lumpur-di-blora</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/oro-oro-kesongo-blora-1786106075716_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Video: H1-2026, Capaian Dekarbonisasi Pertamina Tembus 118%</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:58:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>PT Pertamina Persero melaporkan, dekarbonisasi Pertamina Group berhasil mengurangi emisi karbon sebesar 118%</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810092655-8-757837/video-h1-2026-capaian-dekarbonisasi-pertamina-tembus-118</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/h1-2026-capaian-dekarbonisasi-pertamina-tembus-118-1786333744353_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>ETF Emas Resmi Tersedia di BEI, Wamenkeu Beri Pesan Penting</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:40:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Robertus Andrianto</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Keuangan Juda Agung memberikan tiga pesan penting dalam peluncuran ETF (Exchange Trade Fund) Emas</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810100119-4-757846/etf-emas-resmi-tersedia-di-bei-wamenkeu-beri-pesan-penting</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/wakil-menteri-keuangan-juda-agung-saat-acara-peringatan-hut-ke-49-pasar-modal-indonesia-dan-peluncuran-produk-etf-emas-senin-1-1786329754851_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Video: Trump: AS Siapkan Rp53,8 T untuk Proyek Mineral Kritis-Baterai</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:37:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Trump mengaku pemerintahnya akan menginvestasikan 3 miliar Dolar AS untuk proyek mineral kritis dan baterai listrik.</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810092328-8-757834/video-trump-as-siapkan-rp538-t-untuk-proyek-mineral-kritis-baterai</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/trump-as-siapkan-rp538-t-untuk-proyek-mineral-kritis-baterai-1786332696949_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Heboh Semburan Lumpur di Blora Mirip Lapindo, Badan Geologi Buka Suara</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:31:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Badan Geologi ESDM menanggapi semburan lumpur di Oro-oro Kesongo, Blora.</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810101912-4-757864/heboh-semburan-lumpur-di-blora-mirip-lapindo-badan-geologi-buka-suara</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/oro-oro-kesongo-blora-1786106075716_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Khawatir Susah Cari Kerja-Penghasilan Turun, IKK Juli 2026 Merosot</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:30:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Indeks Keyakinan Konsumen (IKK) pada Juli 2026 mengalami penurunan, berdasarkan Survei Konsumen Bank Indonesia (BI) terbaru.</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810101932-4-757865/khawatir-susah-cari-kerja-penghasilan-turun-ikk-juli-2026-merosot</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/17/para-pencari-kerja-atau-jobseeker-mencari-informasi-lowongan-pekerja-dalam-acara-mega-career-expo-2026-di-gedung-smesco-jakart-1776405321248_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Video: Kesepakatan Jalur Pelayaran Selat Hormuz Masuk Tahap Akhir</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:30:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Iran menyebut kesepakatan dengan Oman untuk menetapkan jalur pelayaran baru di Selat Hormuz sudah memasuki tahap akhir</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810084600-8-757815/video-kesepakatan-jalur-pelayaran-selat-hormuz-masuk-tahap-akhir</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/kesepakatan-jalur-pelayaran-selat-hormuz-masuk-tahap-akhir-1786329610130_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Polemik Kandungan LTJ Tuntas, 400.000 Ton Nikel Cs Resmi Diekspor Lagi</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Pemerintah akhirnya mengizinkan ekspor nikel cs pasca polemik kandungan LTJ di dalam mineral</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810085451-4-757821/polemik-kandungan-ltj-tuntas-400000-ton-nikel-cs-resmi-diekspor-lagi</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/07/24/hidup-manusia-dikepung-nikel-dari-panci-hp-hingga-mesin-perang-1753342586197_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Video: Naik Transportasi Umum Jakarta Cuma Rp1 pada 17 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:19:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Jakarta menerapkan tarif khusus pada semua transportasi umum di Jakarta, yaitu hanya 1 Rupiah pada 17 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810084941-8-757818/video-naik-transportasi-umum-jakarta-cuma-rp1-pada-17-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/naik-transportasi-umum-jakarta-cuma-rp1-pada-17-agustus-2026-1786329800080_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>RI Butuh Rp8.705 T untuk Pembangunan di 2027, Lampaui Kemampuan APBN</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:15:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Keuangan Juda Agung mengungkapkan besarnya kebutuhan dana investasi bagi Indonesia</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810092211-4-757833/ri-butuh-rp8705-t-untuk-pembangunan-di-2027-lampaui-kemampuan-apbn</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/10/wakil-menteri-keuangan-juda-agung-saat-menyampaikan-paparan-dalam-acara-economic-outlook-2026-bertema-consolidating-growth-acc-1770698499636_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Video: Kabar Rencana Reshuffle Kabinet Berembus</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:09:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Berembus kabar adanya perombakan atau reshuffle kabinet oleh Presiden Prabowo Subianto setelah 17 Agustus mendatang.</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810092109-8-757830/video-kabar-rencana-reshuffle-kabinet-berembus</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/kabar-rencana-reshuffle-kabinet-berembus-1786329853426_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Harga Resmi LPG 3 Kg, 5,5-12 Kg di Agen-Pangkalan per 10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Firda Dwi Muliawati</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Harga resmi LPG 3 Kg, 5,5 kg dan 12 kg di Agen dan Pangkalan resmi per 10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810082824-4-757802/harga-resmi-lpg-3-kg-55-12-kg-di-agen-pangkalan-per-10-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/14/gas-1771056487189_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Video: Houthi Serang Kilang Minyak Saudi di Dekat Pesisir Laut Merah</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:59:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Milisi Hutsi menggempur fasilitas minyak Arab Saudi di dekat pesisir Laut Merah</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260810084832-8-757817/video-houthi-serang-kilang-minyak-saudi-di-dekat-pesisir-laut-merah</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/houthi-serang-kilang-minyak-saudi-di-dekat-pesisir-laut-merah-1786329692397_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Amerika Siapkan 'Tombol Pembunuh', Ancaman Besar Sudah Tak Terkendali</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>AS percepat pembahasan RUU AI Kill Switch Act untuk mencegah peretasan oleh model AI. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810130602-37-757930/amerika-siapkan-tombol-pembunuh-ancaman-besar-sudah-tak-terkendali</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/30/usa-trump-1785371156663_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Suka Gonta-Ganti Kelamin, Rahasia Kesukaan Warga RI Kini Diungkap</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Penelitian terbaru mengungkap rahasia bunga alpukat yang berganti kelamin setiap hari.</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810125728-37-757927/suka-gonta-ganti-kelamin-rahasia-kesukaan-warga-ri-kini-diungkap</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/05/03/86660222-390d-48eb-b595-db45f05381de_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Pakai Baju ini Biar Wajah Tak Bisa Dilacak dan Dikenali Kamera</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Pendiri SecKC, Bill Swearington, temukan cara menghindari deteksi kamera pengawas dengan pola khusus.</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810135414-37-757949/pakai-baju-ini-biar-wajah-tak-bisa-dilacak-dan-dikenali-kamera</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/iklan-pakaian-menggunakan-ai-1786346374306_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Review Samsung Galaxy Z Fold8: Desain Baru Harga Rp 28 Juta, Worth It?</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Kartini Bohang</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Z Fold8 hadir dengan desain baru ala paspor dengan harga mulai Rp 28,5 juta. Cek kelebihan-kelemahannya sebelum beli!</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810040608-37-757767/review-samsung-galaxy-z-fold8-desain-baru-harga-rp-28-juta-worth-it</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/samsung-galaxy-z-fold8-1786349050508_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Debu dari Luar Bumi Mengandung Racun yang Bisa Masuk ke Makanan</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Penelitian NASA mengungkap debu Mars mengandung racun berbahaya bagi astronaut.</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810143010-37-757972/debu-dari-luar-bumi-mengandung-racun-yang-bisa-masuk-ke-makanan</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/01/22/helikopter-mars-1_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Karyawan Biasa Dipenjara Gara-Gara Kasih Tahu Soal Ini ke China</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Mantan karyawan SK Hynix dijatuhi hukuman 18 bulan penjara karena membocorkan informasi teknologi chip ke perusahaan China. Simak!</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810152914-37-757990/karyawan-biasa-dipenjara-gara-gara-kasih-tahu-soal-ini-ke-china</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/23/ilusrasi-sk-hynix-1782192495688_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Rakyat Ngamuk, Ramai-Ramai Tolak Proyek Data Center Raksasa</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Lebih dari 500 yurisdiksi di AS menolak pembangunan data center karena kekhawatiran penggunaan sumber daya. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810143851-37-757974/rakyat-ngamuk-ramai-ramai-tolak-proyek-data-center-raksasa</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/22/gedung-data-center-meta-di-mansfield-as-1779441817711_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Gen Z Kompak Tinggalkan Smartphone, Kompak Pindah ke Penggantinya</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Generasi Z mulai beralih dari smartphone ke ponsel jadul untuk mengurangi kecanduan media sosial. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810142754-37-757966/gen-z-kompak-tinggalkan-smartphone-kompak-pindah-ke-penggantinya</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/dumphone-2-1786348000702_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Amerika Terpecah, Trump Ngamuk Sebut Pihak yang Mau Bisnis Bangkrut</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Pemerintah AS terpecah belah. Trump blak-blakan bilang ada pihak yang mau perusahaan bangkrut. Simak!</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810131524-37-757935/amerika-terpecah-trump-ngamuk-sebut-pihak-yang-mau-bisnis-bangkrut</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/presiden-donald-trump-berbicara-di-upacara-pemakaman-senator-lindsey-graham-r-sc-di-katedral-nasional-washington-selasa-28-jul-1785285528470_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Gudang Raksasa Ecommerce Meledak, Pedagang Kecil Terancam Bangkrut</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Perang Rusia-Ukraina menghantam ekonomi Rusia, melumpuhkan Wildberries dan memicu kebangkrutan massal.</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810123047-37-757915/gudang-raksasa-ecommerce-meledak-pedagang-kecil-terancam-bangkrut</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/10/05/ilustrasi-ecommerce_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Yacht Mewahnya Tolak Tolong Kapal Terdampar, Zuckerberg Ngaku Tak Tahu</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Mark Zuckerberg mendapat kecaman setelah kapal pesiarnya menolak menolong kapal kecil terdampar di Alaska.</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810115312-37-757897/yacht-mewahnya-tolak-tolong-kapal-terdampar-zuckerberg-ngaku-tak-tahu</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/10/launchpad-kapal-pesiar-kepunyaan-zuck-dok-superyachtfancom-1786338877251_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>DPR-Pemerintah Gelar Rapat Finalisasi Perpres Ojol</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:18:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Pemerintah dan DPR menggelar rapat koordinasi untuk membahas Perpres Ojol dan isu gaji pegawai PPPK. Rapat dihadiri sejumlah menteri dan wakil ketua DPR.</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810140603-37-757959/dpr-pemerintah-gelar-rapat-finalisasi-perpres-ojol</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/03/27/infografis-bhr-ojek-online-1743044510791_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Profesi Tercela Ini Terancam Punah, Penggantinya Jauh Lebih Jahat</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Penelitian menunjukkan AI kini lebih efektif menipu manusia dibanding penipu tradisional.</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810114105-37-757888/profesi-tercela-ini-terancam-punah-penggantinya-jauh-lebih-jahat</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/03/di-dalam-kasino-osmach-sebuah-kompleks-penipuan-di-perbatasan-chong-chom-osmach-antara-thailand-dan-kamboja-di-oddar-meanchey--1770125429821_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Petaka Besar Sudah Makan Banyak Korban, Semua Diminta Siaga</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Dunia keamanan siber terguncang oleh peretasan AI canggih, termasuk insiden Hugging Face. Semua pihak diminta siaga penuh!</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810121959-37-757912/petaka-besar-sudah-makan-banyak-korban-semua-diminta-siaga</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/11/04/peta-baru-sumber-kejahatan-siber-dunia-ini-daftar-negaranya-1762251132866_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Dampak Krisis Menggila, iPhone Baru Terpaksa Pakai Chip Buatan China</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Apple uji coba chip memori dari CXMT untuk atasi kelangkaan komponen. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810120109-37-757902/dampak-krisis-menggila-iphone-baru-terpaksa-pakai-chip-buatan-china</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/21/iphone-17-cnbc-indonesiafaisal-rahman-1761031479553_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>China Balas Dendam Makin Kejam, Amerika Sekarang Kena Batunya</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 12:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Ketegangan dagang AS-China meningkat. China melarang transaksi dan kontrol ketat pada teknologi drone dan lembaga sertifikasi AS.</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810115435-37-757895/china-balas-dendam-makin-kejam-amerika-sekarang-kena-batunya</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/15/presiden-china-xi-jinping-memperlihatkan-suasana-kompleks-bersejarah-zhongnanhai-kepada-presiden-amerika-serikat-donald-trump--1778835074284_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Heboh Transaksi Kripto Kena Pajak, Negara Lagi Butuh Uang</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 11:50:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Nigeria menetapkan bea meterai dan pajak pemotongan pada transaksi kripto, langkah yang dinilai dapat menghambat adopsi aset digital.</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810114904-37-757890/heboh-transaksi-kripto-kena-pajak-negara-lagi-butuh-uang</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/02/28/818081b6-2f31-496c-8952-e85ff09a5a7a_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Harga iPhone 17 Naik Bulan Ini, Padahal iPhone 18 Rilis September</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 10:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Apple dikabarkan akan menaikkan harga iPhone 17 mulai 10 Agustus 2026. Kenaikan ini menyusul harga MacBook dan iPad yang juga meningkat sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810101211-37-757853/harga-iphone-17-naik-bulan-ini-padahal-iphone-18-rilis-september</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/27/iphone-17-pro-1761560407517_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Jepang Larang Profesi Ini Diganti AI, Terancam Tak Bisa Kerja</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 09:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Jepang melindungi selebritas dari penggunaan suara AI dengan pedoman baru.</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810084107-37-757813/jepang-larang-profesi-ini-diganti-ai-terancam-tak-bisa-kerja</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/para-wanita-yang-mengenakan-yukata-atau-kimono-kasual-musim-panas-menggunakan-kipas-portabel-saat-mereka-berjalan-di-sepanjang-1784710315450_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Orang Terkaya di Dunia Bilang 10 Tahun Lagi, Uang Tak Ada Gunanya</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Elon Musk memprediksi bahwa pada 2036, uang akan kehilangan nilai pentingnya karena kemajuan AI dan robotika.</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810080753-37-757787/orang-terkaya-di-dunia-bilang-10-tahun-lagi-uang-tak-ada-gunanya</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/07/usa-trumpmusk-regulators-1749261772164_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Shopee Cs Refund Dana Pedagang Online Usai Pajak Ditunda</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:55:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Tim Redaksi</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>E-commerce Shopee, Tokopedia, dan Blibli mulai memproses pengembalian PPh Pasal 22 yang terlanjur dipungut. Refund otomatis tanpa pengajuan dari penjual.</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810071748-37-757782/shopee-cs-refund-dana-pedagang-online-usai-pajak-ditunda</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/01/seorang-karyawan-melakukan-siaran-langsung-atau-live-streaming-di-e-commerce-di-salah-satu-toko-di-kawasan-jakarta-rabu-172026-1782897251971_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>3 Fitur Baru yang Muncul di Chat Grup WhatsApp, Ini Fungsi @Semua</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>WhatsApp meluncurkan tiga fitur baru untuk chat grup: polling yang lebih cerdas, mention @all, dan pembuatan grup baru dari grup yang ada.</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810070725-37-757775/3-fitur-baru-yang-muncul-di-chat-grup-whatsapp-ini-fungsi--semua</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/08/12/logo-whatsapp-cnbc-indonesianovina-1754986053842_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Telkomsel Punya Jurus Baru Genjot Adopsi AI Indonesia</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:11:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Telkomsel memperluas pemanfaatan AI di Indonesia melalui AI Cinefest 2026, mengumpulkan 1.111 film pendek dan mendukung pengembangan talenta digital kreatif.</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260810070453-37-757774/telkomsel-punya-jurus-baru-genjot-adopsi-ai-indonesia</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/15/dok-telkomsel-1781517179470_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1196"/>
+  <autoFilter ref="A1:I1319"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1337</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1319"/>
+  <dimension ref="A1:I1337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -62432,8 +62432,854 @@
         </is>
       </c>
     </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>FOTO: Taiwan Gelar Latihan Perang Akbar Siap-siap Hadapi China</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>REUTERS</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Taiwan kembali menggelar latihan militer besar-besaran demi menghadapi ancaman China yang masih berupaya menjegal keinginan Taipei untuk merdeka.</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810141039-115-1390585/foto-taiwan-gelar-latihan-perang-akbar-siap-siap-hadapi-china</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/china-mengancam-taiwan-gelar-latihan-perang-akbar-1786345630376_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Calon Senat Muslim AS Ejek Trump usai Disebut Tukang Bual</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Calon senator Muslim Amerika Serikat dari Partai Demokrat Abdul El Sayed mengejek balik Presiden Donald Trump usai disebut tukang bual.</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810203049-134-1390779/calon-senat-muslim-as-ejek-trump-usai-disebut-tukang-bual</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/politikus-demokrat-abdul-el-sayed-1785992947567_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>FOTO: TKP Penembakan Pejabat Daerah Thailand Gegara Utang</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Seorang mantan anggota parlemen Thailand menembak mati seorang pejabat pemerintah daerah pada Senin (10/8) siang bolong akibat masalah utang.</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810183129-108-1390732/foto-tkp-penembakan-pejabat-daerah-thailand-gegara-utang</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/eks-anggota-parlemen-diduga-tembak-mati-pejabat-thai-1786361386492_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>2 Penembakan dalam Sepekan, Bagaimana Aturan Senjata di Thailand?</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Penembakan kembali terjadi di Bangkok, Thailand, saat eks anggota parlemen Chalong Riewran menembak mati seorang pejabat pemerintah daerah di siang bolong.</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810191131-106-1390747/2-penembakan-dalam-sepekan-bagaimana-aturan-senjata-di-thailand</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/07/28/penembakan-massal-di-chatuchak-bangkok-thailand-1753694963803_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Gempa M 7,4 Guncang Kolombia</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:01:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Gempa berkekuatan magnitude 7,4 mengguncang Kolombia pada Senin (10/8).</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810194244-134-1390765/gempa-m-74-guncang-kolombia</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/11/16/1a6c82e7-a220-416f-89ca-d0bf27b2dd6b_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Malaysia Ungkap Penyebab PM Anwar Ibrahim Masuk RS</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Perdana Menteri Malaysia Anwar Ibrahim menjalani operasi di rumah sakit pada Senin (10/8).</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810192837-106-1390755/malaysia-ungkap-penyebab-pm-anwar-ibrahim-masuk-rs</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/11/05/anwar-ibrahim-1762331055170_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Terbongkar Istri Netanyahu Digugat Gegara Sering Kasar dan Hina Staf ART</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Istri PM Israel Benjamin Netanyahu, Sara Netanyahu, telah menghadapi tuduhan kekerasan terhadap staf rumah tangga, jelang pemilu pada Oktober mendatang.</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810184252-120-1390744/terbongkar-istri-netanyahu-digugat-gegara-sering-kasar-hina-staf-art</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/sara-netanyahu-istri-dari-pm-israel-benjamin-netanyahu-1786359982783_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Kata-kata Menohok Iran soal Pakta Baru Saudi, Pakistan, Turki Bak NATO</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Iran buka suara usai Turki, Arab Saudi, dan Pakistan menandatangani perjanjian serupa NATO, Pakta Pertahanan Makkah, pada pekan lalu.</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810181327-120-1390731/kata-kata-menohok-iran-soal-pakta-baru-saudi-pakistan-turki-bak-nato</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/06/iran-israel-conflict-1775454871064_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Ratusan Warga di Ceuta Demo Tuntut Solusi Krisis Migrasi</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>REUTERS/RadioTelevision Ceuta</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Ratusan warga Ceuta menggelar aksi demonstrasi menuntut solusi atas krisis migrasi pada Minggu (9/8).</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810074934-139-1390420/ratusan-warga-di-ceuta-demo-tuntut-solusi-krisis-migrasi</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/ratusan-warga-di-ceuta-demo-tuntut-solusi-krisis-migrasi-1786325135454_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Israel Larang Turis dan Peziarah Kunjungi Desa Kristen Palestina</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Militer Israel semakin keji dengan menutup Desa Taybeh yang mayoritas penduduknya beragama Kristen di Tepi Barat, Palestina.</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810164254-120-1390696/israel-larang-turis-peziarah-kunjungi-desa-kristen-palestina</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/desa-taybeh-yerusalem-palestina-1786355805645_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Eks Anggota DPR Thailand Tembak Mati Pejabat Gegara Utang</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:21:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Seorang mantan anggota parlemen Thailand menembak mati seorang pejabat pemerintah daerah pada Senin (10/8) siang bolong akibat masalah utang.</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810170010-106-1390707/eks-anggota-dpr-thailand-tembak-mati-pejabat-gegara-utang</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/04/ilustrasi-penembakan-1756966587846_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Houthi Klaim Serang Kilang Minyak Aramco Saudi, Picu Kebakaran</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Kelompok milisi Yaman Houthi mengeklaim telah melancarkan serangan ke pusat kilang minyak Aramco di Kota Jizan, pada Minggu (9/10).</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810145606-120-1390637/houthi-klaim-serang-kilang-minyak-aramco-saudi-picu-kebakaran</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/iran-crisissaudi-1786349731672_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Pilot Bawa Ekstasi ke RI, Malaysia Akui Screening Bandara Banyak Celah</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri Malaysia mengakui pemeriksaan barang di Bandara Internasional Kuala Lumpur (KLIA) tidak fokus mendeteksi barang selundupan seperti narkoba.</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810152025-106-1390685/pilot-bawa-ekstasi-ke-ri-malaysia-akui-screening-bandara-banyak-celah</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/21/bandara-internasional-kuala-lumpur-1755751783753_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Senator AS: Trump Sudah Kalah di Perang Iran</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Senator Amerika Serikat asal Partai Demokrat, Chris Murphy, menyebut bahwa Presiden Donald Trump sudah 'kalah' dalam perang melawan Iran.</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810144221-134-1390634/senator-as-trump-sudah-kalah-di-perang-iran</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/23/trump-kesulitan-lindungi-50-ribu-tentara-as-dari-serangan-iran-1784792922025_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>China Mulai Lirik Aliansi Baru Bak NATO antara Turki, Saudi, Pakistan</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>China disebut mulai melirik Pakta Pertahanan Makkah, aliansi pertahanan bak NATO, yang baru disepakati Turki, Arab Saudi, dan Pakistan.</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810141606-113-1390594/china-mulai-lirik-aliansi-baru-bak-nato-antara-turki-saudi-pakistan</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/14/menteri-luar-negeri-china-wang-yi-1778750923688_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Mojtaba Khamenei Muncul dalam Video Terbaru yang Dirilis Media Iran</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:20:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Kantor berita semi-resmi Iran, Mehr, pada Sabtu (8/8) merilis video Pemimpin Tertinggi Iran Mojtaba Khamenei sedang berdiskusi dengan sejumlah orang.</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810143516-124-1390612/mojtaba-khamenei-muncul-dalam-video-terbaru-yang-dirilis-media-iran</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/thumbnail-video-1786347574732_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Mojtaba Khamenei Muncul ke Publik Lewat Video Bertemu Presiden Iran</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Pertemuan Mojtaba Khamenei dan Presiden Masoud Pezeshkian pada Minggu (9/8) menjadi pertama kalinya sang Pemimpin Tertinggi Iran muncul ke publik.</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810131527-120-1390557/mojtaba-khamenei-muncul-ke-publik-lewat-video-bertemu-presiden-iran</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/11/mojtaba-khamenei-1773222923893_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Menteri Malaysia: Scanner Bandara Kami Canggih, Bisa Deteksi Narkoba</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Mendagri Malaysia, Saifuddin Nasution Ismail, memastikan mesin scanner yang berada di Bandara KLIA sepenuhnya mampu mendeteksi barang terlarang seperti narkoba.</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810121542-106-1390525/menteri-malaysia-scanner-bandara-kami-canggih-bisa-deteksi-narkoba</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/21/bandara-internasional-kuala-lumpur-1755751783753_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1319"/>
+  <autoFilter ref="A1:I1337"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1341</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1337"/>
+  <dimension ref="A1:I1341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -63278,8 +63278,196 @@
         </is>
       </c>
     </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Penertiban Tambang Ilegal Jadi Katalis Produksi dan Kinerja TINS</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:18:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Penertiban tambang ilegal dapat meningkatkan produksi PT Timah Tbk (TINS). Kinerja keuangan TINS membaik dengan laba bersih melonjak 805% pada semester I 2026.</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810211236-17-758105/penertiban-tambang-ilegal-jadi-katalis-produksi-dan-kinerja-tins</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/08/25/timah-balok-siap-jual-cnbc-indonesiafirda-dwi-muliawati-1756098257383_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Literasi dan Inklusi Keuangan Syariah Nasional Turun, Ini Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:05:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Zefanya Aprilia</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Survei Nasional Literasi dan Inklusi Keuangan (SNLIK) 2026 mencatat adanya penurunan tingkat literasi dan inklusi keuangan syariah.</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810204935-17-758096/literasi-dan-inklusi-keuangan-syariah-nasional-turun-ini-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/09/kepala-bps-amalia-a-widyasanti-dalam-rapat-konsultasi-dengan-pimpinan-komisi-dpr-ri-di-komplek-parlemen-jakarta-senin-922026-1770606395422_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Destry Damayanti Jadi Calon Tunggal Gubernur BI, Ini Kata Bos LPS</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:45:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>Lembaga Penjamin Simpanan (LPS) buka suara mengenai pencalonan tunggal Destry Damayanti sebagai Gubernur Bank Indonesia (BI).</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810203918-17-758095/destry-damayanti-jadi-calon-tunggal-gubernur-bi-ini-kata-bos-lps</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/ketua-dewan-komisioner-lps-anggito-abimanyu-saat-konferensi-pers-hasil-rapat-berskla-kssk-iii-tahun-2016-di-jakarta-senin-3820-1785749402657_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>OJK Buka Suara Soal Wakaf Saham di Istiqlal</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:50:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>OJK membahas integrasi Masjid Istiqlal dalam ekosistem BEI melalui wakaf saham.</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260810153342-17-757997/ojk-buka-suara-soal-wakaf-saham-di-istiqlal</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/03/26/ilustrasi-ojk-cnbc-indonesiafaisal-rahman_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1337"/>
+  <autoFilter ref="A1:I1341"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1342</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1341"/>
+  <dimension ref="A1:I1342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -63466,8 +63466,55 @@
         </is>
       </c>
     </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>BSMR: Bank Tak Cukup Hanya Canggih, Ketahanan Hadapi Risiko Jadi Kunci</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Budi Raharjo</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Dunia perbankan kini menghadapi tantangan yang tidak lagi hanya datang dari naik-turunnya ekonomi. Kemajuan kecerdasan buatan (AI), ancaman kejahatan siber, hingga hadirnya layanan bullion banking atau bank...</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjkx32415/bsmr-bank-tak-cukup-hanya-canggih-ketahanan-hadapi-risiko-jadi-kunci</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/the-jakarta-risk-management-convention-jrmc-2026-di-jakarta_260811072251-521.jpeg</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1341"/>
+  <autoFilter ref="A1:I1342"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-10.xlsx
+++ b/data/berita_2026-08-10.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1342</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1346</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1342"/>
+  <dimension ref="A1:I1346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -63513,8 +63513,196 @@
         </is>
       </c>
     </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Olah TKP Sekolah Jaksel, Polisi Kembali Temukan Senjata hingga Amunisi</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:45:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Selatan melakukan olah TKP di sekolah swasta Pondok Pinang, menemukan ratusan senjata dan narkoba. Penyelidikan berlanjut.</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810222520-12-1390810/olah-tkp-sekolah-jaksel-polisi-kembali-temukan-senjata-hingga-amunisi</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/ratusan-senjata-di-yayasan-sekolah-jaksel-1786100090384_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>KPK Sebut Dedi Congor Sudah Jadi Tersangka di Kortas Tipidkor Polri</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:15:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>KPK menetapkan Ahmad Dedi, mantan Kepala KPPBC Marunda, sebagai tersangka dalam kasus dugaan korupsi. Ia diduga menerima Rp30 miliar dari Blueray Cargo.</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810222135-12-1390809/kpk-sebut-dedi-congor-sudah-jadi-tersangka-di-kortas-tipidkor-polri</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/12/pengungkapan-suap-audit-laporan-keuangan-di-kabupaten-muara-enim-1781244746815_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Karhutla Kepung RI, Menko Polkam hingga Istana Keluarkan Imbauan</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:30:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Menko Polkam hingga Istana mengeluarkan sejumlah imbauan terkait kebakaran hutan dan lahan (Karhutla) yang terus meluas.</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810184104-20-1390740/karhutla-kepung-ri-menko-polkam-hingga-istana-keluarkan-imbauan</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/pemadaman-kebakaran-kawasan-hutan-di-boyolali-1785974493169_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum Bigmo: Konten Promosi Vape Libatkan Anak Terjadi Spontan</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 22:15:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Youtuber Bigmo diperiksa terkait dugaan promosi liquid vape kepada anak-anak. Ia meminta maaf dan berkomitmen untuk membuat konten yang lebih positif.</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260810201549-12-1390776/kuasa-hukum-bigmo-konten-promosi-vape-libatkan-anak-terjadi-spontan</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/bigmo-memenuhi-panggilan-polda-metro-jaya-1786345392788_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1342"/>
+  <autoFilter ref="A1:I1346"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>